--- a/dashboards/Adani Group.xlsx
+++ b/dashboards/Adani Group.xlsx
@@ -486,7 +486,7 @@
         <v>44564</v>
       </c>
       <c r="B2" t="n">
-        <v>2152.12109375</v>
+        <v>2152.121337890625</v>
       </c>
       <c r="C2" t="n">
         <v>1731.099975585938</v>
@@ -498,16 +498,16 @@
         <v>1346.900024414062</v>
       </c>
       <c r="F2" t="n">
-        <v>717.017822265625</v>
+        <v>717.0178833007812</v>
       </c>
       <c r="G2" t="n">
         <v>20.26000022888184</v>
       </c>
       <c r="H2" t="n">
-        <v>372.3961181640625</v>
+        <v>372.3961486816406</v>
       </c>
       <c r="I2" t="n">
-        <v>1741.248413085938</v>
+        <v>1741.248657226562</v>
       </c>
       <c r="J2" t="n">
         <v>114.9499969482422</v>
@@ -518,7 +518,7 @@
         <v>44565</v>
       </c>
       <c r="B3" t="n">
-        <v>2126.262939453125</v>
+        <v>2126.26318359375</v>
       </c>
       <c r="C3" t="n">
         <v>1754.949951171875</v>
@@ -536,10 +536,10 @@
         <v>20.11000061035156</v>
       </c>
       <c r="H3" t="n">
-        <v>375.7159423828125</v>
+        <v>375.7160034179688</v>
       </c>
       <c r="I3" t="n">
-        <v>1751.383544921875</v>
+        <v>1751.383666992188</v>
       </c>
       <c r="J3" t="n">
         <v>114.25</v>
@@ -562,16 +562,16 @@
         <v>1399.650024414062</v>
       </c>
       <c r="F4" t="n">
-        <v>734.8313598632812</v>
+        <v>734.8314208984375</v>
       </c>
       <c r="G4" t="n">
         <v>19.96999931335449</v>
       </c>
       <c r="H4" t="n">
-        <v>378.8432922363281</v>
+        <v>378.8433227539062</v>
       </c>
       <c r="I4" t="n">
-        <v>1769.107666015625</v>
+        <v>1769.107543945312</v>
       </c>
       <c r="J4" t="n">
         <v>125.6500015258789</v>
@@ -582,7 +582,7 @@
         <v>44567</v>
       </c>
       <c r="B5" t="n">
-        <v>2129.13134765625</v>
+        <v>2129.131103515625</v>
       </c>
       <c r="C5" t="n">
         <v>1760.050048828125</v>
@@ -600,10 +600,10 @@
         <v>19.96999931335449</v>
       </c>
       <c r="H5" t="n">
-        <v>372.4442443847656</v>
+        <v>372.4442749023438</v>
       </c>
       <c r="I5" t="n">
-        <v>1795.868408203125</v>
+        <v>1795.86865234375</v>
       </c>
       <c r="J5" t="n">
         <v>119.9499969482422</v>
@@ -614,7 +614,7 @@
         <v>44568</v>
       </c>
       <c r="B6" t="n">
-        <v>2183.905517578125</v>
+        <v>2183.90576171875</v>
       </c>
       <c r="C6" t="n">
         <v>1776</v>
@@ -632,10 +632,10 @@
         <v>20.04000091552734</v>
       </c>
       <c r="H6" t="n">
-        <v>382.2593688964844</v>
+        <v>382.2593383789062</v>
       </c>
       <c r="I6" t="n">
-        <v>1785.184204101562</v>
+        <v>1785.18408203125</v>
       </c>
       <c r="J6" t="n">
         <v>120.0500030517578</v>
@@ -646,28 +646,28 @@
         <v>44571</v>
       </c>
       <c r="B7" t="n">
-        <v>2217.888427734375</v>
+        <v>2217.888671875</v>
       </c>
       <c r="C7" t="n">
         <v>1819.699951171875</v>
       </c>
       <c r="D7" t="n">
-        <v>1748.696411132812</v>
+        <v>1748.6962890625</v>
       </c>
       <c r="E7" t="n">
         <v>1438.900024414062</v>
       </c>
       <c r="F7" t="n">
-        <v>719.2080078125</v>
+        <v>719.2080688476562</v>
       </c>
       <c r="G7" t="n">
         <v>21.73999977111816</v>
       </c>
       <c r="H7" t="n">
-        <v>384.2801208496094</v>
+        <v>384.2800903320312</v>
       </c>
       <c r="I7" t="n">
-        <v>1760.77001953125</v>
+        <v>1760.769897460938</v>
       </c>
       <c r="J7" t="n">
         <v>120.0500030517578</v>
@@ -690,7 +690,7 @@
         <v>1567.949951171875</v>
       </c>
       <c r="F8" t="n">
-        <v>744.7601928710938</v>
+        <v>744.76025390625</v>
       </c>
       <c r="G8" t="n">
         <v>21.70999908447266</v>
@@ -699,7 +699,7 @@
         <v>382.6442565917969</v>
       </c>
       <c r="I8" t="n">
-        <v>1777.345458984375</v>
+        <v>1777.345581054688</v>
       </c>
       <c r="J8" t="n">
         <v>119.6999969482422</v>
@@ -731,7 +731,7 @@
         <v>382.8848266601562</v>
       </c>
       <c r="I9" t="n">
-        <v>1794.070922851562</v>
+        <v>1794.071044921875</v>
       </c>
       <c r="J9" t="n">
         <v>120</v>
@@ -742,7 +742,7 @@
         <v>44574</v>
       </c>
       <c r="B10" t="n">
-        <v>2212.15283203125</v>
+        <v>2212.153076171875</v>
       </c>
       <c r="C10" t="n">
         <v>2019.699951171875</v>
@@ -754,16 +754,16 @@
         <v>1661.800048828125</v>
       </c>
       <c r="F10" t="n">
-        <v>751.6715087890625</v>
+        <v>751.6715698242188</v>
       </c>
       <c r="G10" t="n">
         <v>23.29000091552734</v>
       </c>
       <c r="H10" t="n">
-        <v>381.44140625</v>
+        <v>381.4414367675781</v>
       </c>
       <c r="I10" t="n">
-        <v>1818.585205078125</v>
+        <v>1818.585083007812</v>
       </c>
       <c r="J10" t="n">
         <v>119.9499969482422</v>
@@ -780,13 +780,13 @@
         <v>2020.599975585938</v>
       </c>
       <c r="D11" t="n">
-        <v>1866.084350585938</v>
+        <v>1866.084228515625</v>
       </c>
       <c r="E11" t="n">
         <v>1697.949951171875</v>
       </c>
       <c r="F11" t="n">
-        <v>759.3615112304688</v>
+        <v>759.3614501953125</v>
       </c>
       <c r="G11" t="n">
         <v>23.43000030517578</v>
@@ -795,7 +795,7 @@
         <v>387.5037231445312</v>
       </c>
       <c r="I11" t="n">
-        <v>1803.207885742188</v>
+        <v>1803.207641601562</v>
       </c>
       <c r="J11" t="n">
         <v>118.9000015258789</v>
@@ -812,7 +812,7 @@
         <v>2002.699951171875</v>
       </c>
       <c r="D12" t="n">
-        <v>1873.617431640625</v>
+        <v>1873.617553710938</v>
       </c>
       <c r="E12" t="n">
         <v>1835.300048828125</v>
@@ -827,7 +827,7 @@
         <v>392.4112243652344</v>
       </c>
       <c r="I12" t="n">
-        <v>1796.168090820312</v>
+        <v>1796.168212890625</v>
       </c>
       <c r="J12" t="n">
         <v>117.4000015258789</v>
@@ -850,13 +850,13 @@
         <v>1900.099975585938</v>
       </c>
       <c r="F13" t="n">
-        <v>742.6674194335938</v>
+        <v>742.6673583984375</v>
       </c>
       <c r="G13" t="n">
         <v>21.95000076293945</v>
       </c>
       <c r="H13" t="n">
-        <v>366.2857360839844</v>
+        <v>366.2857055664062</v>
       </c>
       <c r="I13" t="n">
         <v>1812.793579101562</v>
@@ -876,13 +876,13 @@
         <v>2043.25</v>
       </c>
       <c r="D14" t="n">
-        <v>1845.18115234375</v>
+        <v>1845.181030273438</v>
       </c>
       <c r="E14" t="n">
         <v>1938.449951171875</v>
       </c>
       <c r="F14" t="n">
-        <v>724.4158325195312</v>
+        <v>724.4158935546875</v>
       </c>
       <c r="G14" t="n">
         <v>22.78000068664551</v>
@@ -891,7 +891,7 @@
         <v>360.7046203613281</v>
       </c>
       <c r="I14" t="n">
-        <v>1792.273681640625</v>
+        <v>1792.273803710938</v>
       </c>
       <c r="J14" t="n">
         <v>117.3000030517578</v>
@@ -908,13 +908,13 @@
         <v>2039.75</v>
       </c>
       <c r="D15" t="n">
-        <v>1861.694091796875</v>
+        <v>1861.693969726562</v>
       </c>
       <c r="E15" t="n">
         <v>1966.699951171875</v>
       </c>
       <c r="F15" t="n">
-        <v>718.380615234375</v>
+        <v>718.3806762695312</v>
       </c>
       <c r="G15" t="n">
         <v>22.75</v>
@@ -923,7 +923,7 @@
         <v>360.9452209472656</v>
       </c>
       <c r="I15" t="n">
-        <v>1801.060668945312</v>
+        <v>1801.060913085938</v>
       </c>
       <c r="J15" t="n">
         <v>119.8000030517578</v>
@@ -940,22 +940,22 @@
         <v>2066.800048828125</v>
       </c>
       <c r="D16" t="n">
-        <v>1824.277587890625</v>
+        <v>1824.277465820312</v>
       </c>
       <c r="E16" t="n">
         <v>1934.550048828125</v>
       </c>
       <c r="F16" t="n">
-        <v>704.655517578125</v>
+        <v>704.6555786132812</v>
       </c>
       <c r="G16" t="n">
         <v>21.98999977111816</v>
       </c>
       <c r="H16" t="n">
-        <v>354.7386169433594</v>
+        <v>354.7385864257812</v>
       </c>
       <c r="I16" t="n">
-        <v>1824.626342773438</v>
+        <v>1824.62646484375</v>
       </c>
       <c r="J16" t="n">
         <v>114.4000015258789</v>
@@ -978,7 +978,7 @@
         <v>1837.849975585938</v>
       </c>
       <c r="F17" t="n">
-        <v>683.7757568359375</v>
+        <v>683.7758178710938</v>
       </c>
       <c r="G17" t="n">
         <v>20.55999946594238</v>
@@ -987,7 +987,7 @@
         <v>339.5348205566406</v>
       </c>
       <c r="I17" t="n">
-        <v>1778.5439453125</v>
+        <v>1778.543823242188</v>
       </c>
       <c r="J17" t="n">
         <v>106.6999969482422</v>
@@ -998,7 +998,7 @@
         <v>44586</v>
       </c>
       <c r="B18" t="n">
-        <v>2083.86767578125</v>
+        <v>2083.867919921875</v>
       </c>
       <c r="C18" t="n">
         <v>1992.449951171875</v>
@@ -1010,16 +1010,16 @@
         <v>1929</v>
       </c>
       <c r="F18" t="n">
-        <v>692.1956787109375</v>
+        <v>692.19580078125</v>
       </c>
       <c r="G18" t="n">
         <v>21.43000030517578</v>
       </c>
       <c r="H18" t="n">
-        <v>338.2357482910156</v>
+        <v>338.2357788085938</v>
       </c>
       <c r="I18" t="n">
-        <v>1822.529541015625</v>
+        <v>1822.529174804688</v>
       </c>
       <c r="J18" t="n">
         <v>108.8000030517578</v>
@@ -1030,7 +1030,7 @@
         <v>44588</v>
       </c>
       <c r="B19" t="n">
-        <v>2072.15771484375</v>
+        <v>2072.157958984375</v>
       </c>
       <c r="C19" t="n">
         <v>2009.300048828125</v>
@@ -1042,7 +1042,7 @@
         <v>1910.25</v>
       </c>
       <c r="F19" t="n">
-        <v>690.2490234375</v>
+        <v>690.2489624023438</v>
       </c>
       <c r="G19" t="n">
         <v>21.1299991607666</v>
@@ -1051,7 +1051,7 @@
         <v>338.380126953125</v>
       </c>
       <c r="I19" t="n">
-        <v>1828.071411132812</v>
+        <v>1828.071166992188</v>
       </c>
       <c r="J19" t="n">
         <v>117.5999984741211</v>
@@ -1062,7 +1062,7 @@
         <v>44589</v>
       </c>
       <c r="B20" t="n">
-        <v>2118.281005859375</v>
+        <v>2118.28125</v>
       </c>
       <c r="C20" t="n">
         <v>1986.800048828125</v>
@@ -1083,7 +1083,7 @@
         <v>347.0885925292969</v>
       </c>
       <c r="I20" t="n">
-        <v>1828.220947265625</v>
+        <v>1828.221069335938</v>
       </c>
       <c r="J20" t="n">
         <v>112.8499984741211</v>
@@ -1106,16 +1106,16 @@
         <v>1877.849975585938</v>
       </c>
       <c r="F21" t="n">
-        <v>697.2575073242188</v>
+        <v>697.257568359375</v>
       </c>
       <c r="G21" t="n">
         <v>21.25</v>
       </c>
       <c r="H21" t="n">
-        <v>351.3706359863281</v>
+        <v>351.3706970214844</v>
       </c>
       <c r="I21" t="n">
-        <v>1818.585205078125</v>
+        <v>1818.585083007812</v>
       </c>
       <c r="J21" t="n">
         <v>111</v>
@@ -1126,7 +1126,7 @@
         <v>44593</v>
       </c>
       <c r="B22" t="n">
-        <v>2229.74169921875</v>
+        <v>2229.741943359375</v>
       </c>
       <c r="C22" t="n">
         <v>1986.900024414062</v>
@@ -1144,10 +1144,10 @@
         <v>21.60000038146973</v>
       </c>
       <c r="H22" t="n">
-        <v>366.0451965332031</v>
+        <v>366.045166015625</v>
       </c>
       <c r="I22" t="n">
-        <v>1861.921752929688</v>
+        <v>1861.921630859375</v>
       </c>
       <c r="J22" t="n">
         <v>110.9000015258789</v>
@@ -1164,22 +1164,22 @@
         <v>2016</v>
       </c>
       <c r="D23" t="n">
-        <v>1775.38671875</v>
+        <v>1775.386840820312</v>
       </c>
       <c r="E23" t="n">
         <v>1916.300048828125</v>
       </c>
       <c r="F23" t="n">
-        <v>725.3893432617188</v>
+        <v>725.3892822265625</v>
       </c>
       <c r="G23" t="n">
         <v>21.67000007629395</v>
       </c>
       <c r="H23" t="n">
-        <v>365.6602478027344</v>
+        <v>365.6602783203125</v>
       </c>
       <c r="I23" t="n">
-        <v>1874.353393554688</v>
+        <v>1874.353515625</v>
       </c>
       <c r="J23" t="n">
         <v>112.0500030517578</v>
@@ -1190,13 +1190,13 @@
         <v>44595</v>
       </c>
       <c r="B24" t="n">
-        <v>2192.5087890625</v>
+        <v>2192.508544921875</v>
       </c>
       <c r="C24" t="n">
         <v>2006.199951171875</v>
       </c>
       <c r="D24" t="n">
-        <v>1747.947998046875</v>
+        <v>1747.947875976562</v>
       </c>
       <c r="E24" t="n">
         <v>1912.550048828125</v>
@@ -1211,7 +1211,7 @@
         <v>367.4885864257812</v>
       </c>
       <c r="I24" t="n">
-        <v>1848.940673828125</v>
+        <v>1848.940795898438</v>
       </c>
       <c r="J24" t="n">
         <v>115.1500015258789</v>
@@ -1222,28 +1222,28 @@
         <v>44596</v>
       </c>
       <c r="B25" t="n">
-        <v>2174.489501953125</v>
+        <v>2174.48974609375</v>
       </c>
       <c r="C25" t="n">
         <v>2033.099975585938</v>
       </c>
       <c r="D25" t="n">
-        <v>1753.385986328125</v>
+        <v>1753.385864257812</v>
       </c>
       <c r="E25" t="n">
         <v>1950.349975585938</v>
       </c>
       <c r="F25" t="n">
-        <v>707.6244506835938</v>
+        <v>707.62451171875</v>
       </c>
       <c r="G25" t="n">
         <v>21.70999908447266</v>
       </c>
       <c r="H25" t="n">
-        <v>366.0451965332031</v>
+        <v>366.045166015625</v>
       </c>
       <c r="I25" t="n">
-        <v>1848.3916015625</v>
+        <v>1848.391479492188</v>
       </c>
       <c r="J25" t="n">
         <v>112.9499969482422</v>
@@ -1272,7 +1272,7 @@
         <v>22.34000015258789</v>
       </c>
       <c r="H26" t="n">
-        <v>368.2102966308594</v>
+        <v>368.2102661132812</v>
       </c>
       <c r="I26" t="n">
         <v>1817.48681640625</v>
@@ -1286,7 +1286,7 @@
         <v>44600</v>
       </c>
       <c r="B27" t="n">
-        <v>2203.16748046875</v>
+        <v>2203.167236328125</v>
       </c>
       <c r="C27" t="n">
         <v>1968.300048828125</v>
@@ -1304,10 +1304,10 @@
         <v>21.6299991607666</v>
       </c>
       <c r="H27" t="n">
-        <v>362.0998840332031</v>
+        <v>362.0999145507812</v>
       </c>
       <c r="I27" t="n">
-        <v>1806.403076171875</v>
+        <v>1806.402954101562</v>
       </c>
       <c r="J27" t="n">
         <v>115.5999984741211</v>
@@ -1324,22 +1324,22 @@
         <v>1955.199951171875</v>
       </c>
       <c r="D28" t="n">
-        <v>1779.17822265625</v>
+        <v>1779.178344726562</v>
       </c>
       <c r="E28" t="n">
         <v>1919.800048828125</v>
       </c>
       <c r="F28" t="n">
-        <v>713.95166015625</v>
+        <v>713.9517211914062</v>
       </c>
       <c r="G28" t="n">
         <v>21.52000045776367</v>
       </c>
       <c r="H28" t="n">
-        <v>368.3545837402344</v>
+        <v>368.3546142578125</v>
       </c>
       <c r="I28" t="n">
-        <v>1762.41748046875</v>
+        <v>1762.417358398438</v>
       </c>
       <c r="J28" t="n">
         <v>117.4000015258789</v>
@@ -1382,25 +1382,25 @@
         <v>44603</v>
       </c>
       <c r="B30" t="n">
-        <v>2150.208984375</v>
+        <v>2150.209228515625</v>
       </c>
       <c r="C30" t="n">
         <v>2016.050048828125</v>
       </c>
       <c r="D30" t="n">
-        <v>1760.370239257812</v>
+        <v>1760.370361328125</v>
       </c>
       <c r="E30" t="n">
         <v>1907.599975585938</v>
       </c>
       <c r="F30" t="n">
-        <v>704.4608154296875</v>
+        <v>704.4608764648438</v>
       </c>
       <c r="G30" t="n">
         <v>25</v>
       </c>
       <c r="H30" t="n">
-        <v>354.0169372558594</v>
+        <v>354.0169067382812</v>
       </c>
       <c r="I30" t="n">
         <v>1787.680541992188</v>
@@ -1435,7 +1435,7 @@
         <v>341.6999206542969</v>
       </c>
       <c r="I31" t="n">
-        <v>1709.794677734375</v>
+        <v>1709.794799804688</v>
       </c>
       <c r="J31" t="n">
         <v>174.3000030517578</v>
@@ -1464,10 +1464,10 @@
         <v>23.59000015258789</v>
       </c>
       <c r="H32" t="n">
-        <v>349.8310546875</v>
+        <v>349.8310241699219</v>
       </c>
       <c r="I32" t="n">
-        <v>1735.157348632812</v>
+        <v>1735.1572265625</v>
       </c>
       <c r="J32" t="n">
         <v>156.8999938964844</v>
@@ -1499,7 +1499,7 @@
         <v>347.0885925292969</v>
       </c>
       <c r="I33" t="n">
-        <v>1683.882446289062</v>
+        <v>1683.882568359375</v>
       </c>
       <c r="J33" t="n">
         <v>165.8500061035156</v>
@@ -1516,13 +1516,13 @@
         <v>2020.849975585938</v>
       </c>
       <c r="D34" t="n">
-        <v>1727.094482421875</v>
+        <v>1727.094604492188</v>
       </c>
       <c r="E34" t="n">
         <v>2047.599975585938</v>
       </c>
       <c r="F34" t="n">
-        <v>714.6817016601562</v>
+        <v>714.6817626953125</v>
       </c>
       <c r="G34" t="n">
         <v>26.39999961853027</v>
@@ -1531,7 +1531,7 @@
         <v>346.2225646972656</v>
       </c>
       <c r="I34" t="n">
-        <v>1724.323364257812</v>
+        <v>1724.3232421875</v>
       </c>
       <c r="J34" t="n">
         <v>163.6000061035156</v>
@@ -1542,7 +1542,7 @@
         <v>44610</v>
       </c>
       <c r="B35" t="n">
-        <v>2085.0146484375</v>
+        <v>2085.014892578125</v>
       </c>
       <c r="C35" t="n">
         <v>1958.099975585938</v>
@@ -1554,16 +1554,16 @@
         <v>2041.849975585938</v>
       </c>
       <c r="F35" t="n">
-        <v>708.1597900390625</v>
+        <v>708.1598510742188</v>
       </c>
       <c r="G35" t="n">
         <v>26.31999969482422</v>
       </c>
       <c r="H35" t="n">
-        <v>325.5820007324219</v>
+        <v>325.5819702148438</v>
       </c>
       <c r="I35" t="n">
-        <v>1662.763427734375</v>
+        <v>1662.763549804688</v>
       </c>
       <c r="J35" t="n">
         <v>164.6499938964844</v>
@@ -1586,7 +1586,7 @@
         <v>1955.900024414062</v>
       </c>
       <c r="F36" t="n">
-        <v>692.1956787109375</v>
+        <v>692.19580078125</v>
       </c>
       <c r="G36" t="n">
         <v>24.03000068664551</v>
@@ -1624,7 +1624,7 @@
         <v>24.11000061035156</v>
       </c>
       <c r="H37" t="n">
-        <v>324.6197509765625</v>
+        <v>324.6197814941406</v>
       </c>
       <c r="I37" t="n">
         <v>1585.177124023438</v>
@@ -1656,7 +1656,7 @@
         <v>25.11000061035156</v>
       </c>
       <c r="H38" t="n">
-        <v>318.4612731933594</v>
+        <v>318.4612426757812</v>
       </c>
       <c r="I38" t="n">
         <v>1639.397827148438</v>
@@ -1670,19 +1670,19 @@
         <v>44616</v>
       </c>
       <c r="B39" t="n">
-        <v>1925.232177734375</v>
+        <v>1925.232299804688</v>
       </c>
       <c r="C39" t="n">
         <v>1957.300048828125</v>
       </c>
       <c r="D39" t="n">
-        <v>1540.510864257812</v>
+        <v>1540.510986328125</v>
       </c>
       <c r="E39" t="n">
         <v>1849.75</v>
       </c>
       <c r="F39" t="n">
-        <v>637.4411010742188</v>
+        <v>637.441162109375</v>
       </c>
       <c r="G39" t="n">
         <v>22.22999954223633</v>
@@ -1691,7 +1691,7 @@
         <v>295.3669128417969</v>
       </c>
       <c r="I39" t="n">
-        <v>1562.760131835938</v>
+        <v>1562.760009765625</v>
       </c>
       <c r="J39" t="n">
         <v>135.5</v>
@@ -1702,7 +1702,7 @@
         <v>44617</v>
       </c>
       <c r="B40" t="n">
-        <v>1968.774780273438</v>
+        <v>1968.774658203125</v>
       </c>
       <c r="C40" t="n">
         <v>2032.849975585938</v>
@@ -1714,16 +1714,16 @@
         <v>1923.5</v>
       </c>
       <c r="F40" t="n">
-        <v>676.6697387695312</v>
+        <v>676.6698608398438</v>
       </c>
       <c r="G40" t="n">
         <v>24.80999946594238</v>
       </c>
       <c r="H40" t="n">
-        <v>297.0508728027344</v>
+        <v>297.0509033203125</v>
       </c>
       <c r="I40" t="n">
-        <v>1570.898071289062</v>
+        <v>1570.898193359375</v>
       </c>
       <c r="J40" t="n">
         <v>143.9499969482422</v>
@@ -1734,7 +1734,7 @@
         <v>44620</v>
       </c>
       <c r="B41" t="n">
-        <v>1997.069946289062</v>
+        <v>1997.06982421875</v>
       </c>
       <c r="C41" t="n">
         <v>2134.39990234375</v>
@@ -1746,7 +1746,7 @@
         <v>1843.400024414062</v>
       </c>
       <c r="F41" t="n">
-        <v>688.6915283203125</v>
+        <v>688.6914672851562</v>
       </c>
       <c r="G41" t="n">
         <v>24.75</v>
@@ -1755,7 +1755,7 @@
         <v>302.3914489746094</v>
       </c>
       <c r="I41" t="n">
-        <v>1586.17578125</v>
+        <v>1586.175659179688</v>
       </c>
       <c r="J41" t="n">
         <v>149.25</v>
@@ -1778,16 +1778,16 @@
         <v>1882.550048828125</v>
       </c>
       <c r="F42" t="n">
-        <v>691.4170532226562</v>
+        <v>691.4169921875</v>
       </c>
       <c r="G42" t="n">
         <v>24.6200008392334</v>
       </c>
       <c r="H42" t="n">
-        <v>292.6725463867188</v>
+        <v>292.6725769042969</v>
       </c>
       <c r="I42" t="n">
-        <v>1665.45947265625</v>
+        <v>1665.459716796875</v>
       </c>
       <c r="J42" t="n">
         <v>153.5</v>
@@ -1816,7 +1816,7 @@
         <v>24.54000091552734</v>
       </c>
       <c r="H43" t="n">
-        <v>279.2489929199219</v>
+        <v>279.2490234375</v>
       </c>
       <c r="I43" t="n">
         <v>1748.687622070312</v>
@@ -1836,7 +1836,7 @@
         <v>2323.199951171875</v>
       </c>
       <c r="D44" t="n">
-        <v>1611.40283203125</v>
+        <v>1611.402709960938</v>
       </c>
       <c r="E44" t="n">
         <v>1894.300048828125</v>
@@ -1848,10 +1848,10 @@
         <v>23.95000076293945</v>
       </c>
       <c r="H44" t="n">
-        <v>281.5584106445312</v>
+        <v>281.5584411621094</v>
       </c>
       <c r="I44" t="n">
-        <v>1802.558715820312</v>
+        <v>1802.55859375</v>
       </c>
       <c r="J44" t="n">
         <v>167.6999969482422</v>
@@ -1862,7 +1862,7 @@
         <v>44627</v>
       </c>
       <c r="B45" t="n">
-        <v>1864.196411132812</v>
+        <v>1864.1962890625</v>
       </c>
       <c r="C45" t="n">
         <v>2207.35009765625</v>
@@ -1880,10 +1880,10 @@
         <v>23.29000091552734</v>
       </c>
       <c r="H45" t="n">
-        <v>270.5886535644531</v>
+        <v>270.588623046875</v>
       </c>
       <c r="I45" t="n">
-        <v>1712.440551757812</v>
+        <v>1712.440673828125</v>
       </c>
       <c r="J45" t="n">
         <v>159.0500030517578</v>
@@ -1900,7 +1900,7 @@
         <v>2217</v>
       </c>
       <c r="D46" t="n">
-        <v>1598.032836914062</v>
+        <v>1598.03271484375</v>
       </c>
       <c r="E46" t="n">
         <v>1783.949951171875</v>
@@ -1912,10 +1912,10 @@
         <v>23.73999977111816</v>
       </c>
       <c r="H46" t="n">
-        <v>272.2244567871094</v>
+        <v>272.2244873046875</v>
       </c>
       <c r="I46" t="n">
-        <v>1627.265625</v>
+        <v>1627.265502929688</v>
       </c>
       <c r="J46" t="n">
         <v>172.3500061035156</v>
@@ -1926,7 +1926,7 @@
         <v>44629</v>
       </c>
       <c r="B47" t="n">
-        <v>1912.661743164062</v>
+        <v>1912.66162109375</v>
       </c>
       <c r="C47" t="n">
         <v>2164.64990234375</v>
@@ -1944,7 +1944,7 @@
         <v>24.26000022888184</v>
       </c>
       <c r="H47" t="n">
-        <v>280.644287109375</v>
+        <v>280.6442565917969</v>
       </c>
       <c r="I47" t="n">
         <v>1612.986450195312</v>
@@ -1958,7 +1958,7 @@
         <v>44630</v>
       </c>
       <c r="B48" t="n">
-        <v>1957.351196289062</v>
+        <v>1957.351318359375</v>
       </c>
       <c r="C48" t="n">
         <v>2272.75</v>
@@ -1970,13 +1970,13 @@
         <v>1881.849975585938</v>
       </c>
       <c r="F48" t="n">
-        <v>710.9827270507812</v>
+        <v>710.9827880859375</v>
       </c>
       <c r="G48" t="n">
         <v>24.5</v>
       </c>
       <c r="H48" t="n">
-        <v>282.1358032226562</v>
+        <v>282.1357727050781</v>
       </c>
       <c r="I48" t="n">
         <v>1693.568481445312</v>
@@ -1990,28 +1990,28 @@
         <v>44631</v>
       </c>
       <c r="B49" t="n">
-        <v>1951.90234375</v>
+        <v>1951.902465820312</v>
       </c>
       <c r="C49" t="n">
         <v>2307.25</v>
       </c>
       <c r="D49" t="n">
-        <v>1730.237548828125</v>
+        <v>1730.237426757812</v>
       </c>
       <c r="E49" t="n">
         <v>1860.050048828125</v>
       </c>
       <c r="F49" t="n">
-        <v>710.0579833984375</v>
+        <v>710.0579223632812</v>
       </c>
       <c r="G49" t="n">
         <v>24.36000061035156</v>
       </c>
       <c r="H49" t="n">
-        <v>282.3763427734375</v>
+        <v>282.3763732910156</v>
       </c>
       <c r="I49" t="n">
-        <v>1659.41845703125</v>
+        <v>1659.418334960938</v>
       </c>
       <c r="J49" t="n">
         <v>169</v>
@@ -2022,7 +2022,7 @@
         <v>44634</v>
       </c>
       <c r="B50" t="n">
-        <v>1967.3408203125</v>
+        <v>1967.340698242188</v>
       </c>
       <c r="C50" t="n">
         <v>2268.300048828125</v>
@@ -2040,10 +2040,10 @@
         <v>24.43000030517578</v>
       </c>
       <c r="H50" t="n">
-        <v>280.2112731933594</v>
+        <v>280.2112426757812</v>
       </c>
       <c r="I50" t="n">
-        <v>1647.935302734375</v>
+        <v>1647.935180664062</v>
       </c>
       <c r="J50" t="n">
         <v>162.8999938964844</v>
@@ -2054,7 +2054,7 @@
         <v>44635</v>
       </c>
       <c r="B51" t="n">
-        <v>1969.539306640625</v>
+        <v>1969.539184570312</v>
       </c>
       <c r="C51" t="n">
         <v>2217.550048828125</v>
@@ -2066,7 +2066,7 @@
         <v>1798.75</v>
       </c>
       <c r="F51" t="n">
-        <v>702.1246948242188</v>
+        <v>702.1246337890625</v>
       </c>
       <c r="G51" t="n">
         <v>24.45999908447266</v>
@@ -2075,7 +2075,7 @@
         <v>283.964111328125</v>
       </c>
       <c r="I51" t="n">
-        <v>1622.023315429688</v>
+        <v>1622.023193359375</v>
       </c>
       <c r="J51" t="n">
         <v>179.1499938964844</v>
@@ -2086,19 +2086,19 @@
         <v>44636</v>
       </c>
       <c r="B52" t="n">
-        <v>2035.306640625</v>
+        <v>2035.306762695312</v>
       </c>
       <c r="C52" t="n">
         <v>2305.39990234375</v>
       </c>
       <c r="D52" t="n">
-        <v>1754.084228515625</v>
+        <v>1754.084350585938</v>
       </c>
       <c r="E52" t="n">
         <v>1833.650024414062</v>
       </c>
       <c r="F52" t="n">
-        <v>704.5581665039062</v>
+        <v>704.5582275390625</v>
       </c>
       <c r="G52" t="n">
         <v>24.57999992370605</v>
@@ -2118,7 +2118,7 @@
         <v>44637</v>
       </c>
       <c r="B53" t="n">
-        <v>2029.093139648438</v>
+        <v>2029.093017578125</v>
       </c>
       <c r="C53" t="n">
         <v>2389.800048828125</v>
@@ -2130,13 +2130,13 @@
         <v>1901.199951171875</v>
       </c>
       <c r="F53" t="n">
-        <v>720.4248046875</v>
+        <v>720.4248657226562</v>
       </c>
       <c r="G53" t="n">
         <v>25.02000045776367</v>
       </c>
       <c r="H53" t="n">
-        <v>294.6452331542969</v>
+        <v>294.6452026367188</v>
       </c>
       <c r="I53" t="n">
         <v>1764.214965820312</v>
@@ -2156,13 +2156,13 @@
         <v>2289.050048828125</v>
       </c>
       <c r="D54" t="n">
-        <v>1798.934204101562</v>
+        <v>1798.93408203125</v>
       </c>
       <c r="E54" t="n">
         <v>1876.050048828125</v>
       </c>
       <c r="F54" t="n">
-        <v>715.6065063476562</v>
+        <v>715.6064453125</v>
       </c>
       <c r="G54" t="n">
         <v>24.90999984741211</v>
@@ -2171,7 +2171,7 @@
         <v>289.0159606933594</v>
       </c>
       <c r="I54" t="n">
-        <v>1811.495483398438</v>
+        <v>1811.49560546875</v>
       </c>
       <c r="J54" t="n">
         <v>227.25</v>
@@ -2200,10 +2200,10 @@
         <v>24.75</v>
       </c>
       <c r="H55" t="n">
-        <v>289.5451965332031</v>
+        <v>289.5452270507812</v>
       </c>
       <c r="I55" t="n">
-        <v>1881.193481445312</v>
+        <v>1881.193359375</v>
       </c>
       <c r="J55" t="n">
         <v>238.6000061035156</v>
@@ -2235,7 +2235,7 @@
         <v>286.6103210449219</v>
       </c>
       <c r="I56" t="n">
-        <v>1895.222778320312</v>
+        <v>1895.222900390625</v>
       </c>
       <c r="J56" t="n">
         <v>250.5</v>
@@ -2252,13 +2252,13 @@
         <v>2414.39990234375</v>
       </c>
       <c r="D57" t="n">
-        <v>1828.717895507812</v>
+        <v>1828.7177734375</v>
       </c>
       <c r="E57" t="n">
         <v>1911.400024414062</v>
       </c>
       <c r="F57" t="n">
-        <v>713.95166015625</v>
+        <v>713.9517211914062</v>
       </c>
       <c r="G57" t="n">
         <v>26.43000030517578</v>
@@ -2267,7 +2267,7 @@
         <v>285.8404846191406</v>
       </c>
       <c r="I57" t="n">
-        <v>1976.853149414062</v>
+        <v>1976.853271484375</v>
       </c>
       <c r="J57" t="n">
         <v>263</v>
@@ -2278,25 +2278,25 @@
         <v>44645</v>
       </c>
       <c r="B58" t="n">
-        <v>1973.2197265625</v>
+        <v>1973.219604492188</v>
       </c>
       <c r="C58" t="n">
         <v>2448.75</v>
       </c>
       <c r="D58" t="n">
-        <v>1862.841552734375</v>
+        <v>1862.841430664062</v>
       </c>
       <c r="E58" t="n">
         <v>1921.25</v>
       </c>
       <c r="F58" t="n">
-        <v>723.4910888671875</v>
+        <v>723.4911499023438</v>
       </c>
       <c r="G58" t="n">
         <v>28.63999938964844</v>
       </c>
       <c r="H58" t="n">
-        <v>286.5621948242188</v>
+        <v>286.5621337890625</v>
       </c>
       <c r="I58" t="n">
         <v>2051.59375</v>
@@ -2316,7 +2316,7 @@
         <v>2439</v>
       </c>
       <c r="D59" t="n">
-        <v>1905.446533203125</v>
+        <v>1905.446411132812</v>
       </c>
       <c r="E59" t="n">
         <v>1930.849975585938</v>
@@ -2328,7 +2328,7 @@
         <v>30.45000076293945</v>
       </c>
       <c r="H59" t="n">
-        <v>280.7886047363281</v>
+        <v>280.78857421875</v>
       </c>
       <c r="I59" t="n">
         <v>2138.06689453125</v>
@@ -2342,7 +2342,7 @@
         <v>44649</v>
       </c>
       <c r="B60" t="n">
-        <v>2034.7333984375</v>
+        <v>2034.733276367188</v>
       </c>
       <c r="C60" t="n">
         <v>2461.550048828125</v>
@@ -2354,7 +2354,7 @@
         <v>1923.300048828125</v>
       </c>
       <c r="F60" t="n">
-        <v>741.6939086914062</v>
+        <v>741.6939697265625</v>
       </c>
       <c r="G60" t="n">
         <v>34.70999908447266</v>
@@ -2363,7 +2363,7 @@
         <v>291.0367431640625</v>
       </c>
       <c r="I60" t="n">
-        <v>2177.609375</v>
+        <v>2177.609130859375</v>
       </c>
       <c r="J60" t="n">
         <v>227.5500030517578</v>
@@ -2380,13 +2380,13 @@
         <v>2377.39990234375</v>
       </c>
       <c r="D61" t="n">
-        <v>1990.805908203125</v>
+        <v>1990.805786132812</v>
       </c>
       <c r="E61" t="n">
         <v>1857.150024414062</v>
       </c>
       <c r="F61" t="n">
-        <v>746.9991455078125</v>
+        <v>746.9990844726562</v>
       </c>
       <c r="G61" t="n">
         <v>34.29999923706055</v>
@@ -2418,7 +2418,7 @@
         <v>1914.699951171875</v>
       </c>
       <c r="F62" t="n">
-        <v>753.6182861328125</v>
+        <v>753.6183471679688</v>
       </c>
       <c r="G62" t="n">
         <v>37.02000045776367</v>
@@ -2427,7 +2427,7 @@
         <v>294.0831909179688</v>
       </c>
       <c r="I62" t="n">
-        <v>2146.654296875</v>
+        <v>2146.654541015625</v>
       </c>
       <c r="J62" t="n">
         <v>227</v>
@@ -2444,22 +2444,22 @@
         <v>2421.449951171875</v>
       </c>
       <c r="D63" t="n">
-        <v>2039.09814453125</v>
+        <v>2039.098022460938</v>
       </c>
       <c r="E63" t="n">
         <v>1945.099975585938</v>
       </c>
       <c r="F63" t="n">
-        <v>764.861328125</v>
+        <v>764.8612670898438</v>
       </c>
       <c r="G63" t="n">
         <v>40.68999862670898</v>
       </c>
       <c r="H63" t="n">
-        <v>299.684814453125</v>
+        <v>299.6847839355469</v>
       </c>
       <c r="I63" t="n">
-        <v>2246.20849609375</v>
+        <v>2246.208740234375</v>
       </c>
       <c r="J63" t="n">
         <v>223.25</v>
@@ -2488,7 +2488,7 @@
         <v>42.38999938964844</v>
       </c>
       <c r="H64" t="n">
-        <v>306.2691040039062</v>
+        <v>306.2691345214844</v>
       </c>
       <c r="I64" t="n">
         <v>2366.332763671875</v>
@@ -2514,13 +2514,13 @@
         <v>2189.800048828125</v>
       </c>
       <c r="F65" t="n">
-        <v>825.5050048828125</v>
+        <v>825.5050659179688</v>
       </c>
       <c r="G65" t="n">
         <v>46.61999893188477</v>
       </c>
       <c r="H65" t="n">
-        <v>311.3302001953125</v>
+        <v>311.3301696777344</v>
       </c>
       <c r="I65" t="n">
         <v>2464.538818359375</v>
@@ -2540,7 +2540,7 @@
         <v>2484.050048828125</v>
       </c>
       <c r="D66" t="n">
-        <v>2155.18896484375</v>
+        <v>2155.188720703125</v>
       </c>
       <c r="E66" t="n">
         <v>2197.39990234375</v>
@@ -2552,10 +2552,10 @@
         <v>48.95000076293945</v>
       </c>
       <c r="H66" t="n">
-        <v>315.162841796875</v>
+        <v>315.1628723144531</v>
       </c>
       <c r="I66" t="n">
-        <v>2533.238037109375</v>
+        <v>2533.23779296875</v>
       </c>
       <c r="J66" t="n">
         <v>213.6999969482422</v>
@@ -2578,7 +2578,7 @@
         <v>2166</v>
       </c>
       <c r="F67" t="n">
-        <v>795.6698608398438</v>
+        <v>795.669921875</v>
       </c>
       <c r="G67" t="n">
         <v>46.5099983215332</v>
@@ -2610,7 +2610,7 @@
         <v>2321.85009765625</v>
       </c>
       <c r="F68" t="n">
-        <v>816.9876708984375</v>
+        <v>816.9876098632812</v>
       </c>
       <c r="G68" t="n">
         <v>44.18999862670898</v>
@@ -2619,7 +2619,7 @@
         <v>331.525390625</v>
       </c>
       <c r="I68" t="n">
-        <v>2423.548828125</v>
+        <v>2423.548583984375</v>
       </c>
       <c r="J68" t="n">
         <v>210</v>
@@ -2683,7 +2683,7 @@
         <v>353.4403686523438</v>
       </c>
       <c r="I70" t="n">
-        <v>2498.38916015625</v>
+        <v>2498.388916015625</v>
       </c>
       <c r="J70" t="n">
         <v>206.8500061035156</v>
@@ -2706,7 +2706,7 @@
         <v>2864.300048828125</v>
       </c>
       <c r="F71" t="n">
-        <v>818.1557006835938</v>
+        <v>818.15576171875</v>
       </c>
       <c r="G71" t="n">
         <v>44.65000152587891</v>
@@ -2747,7 +2747,7 @@
         <v>357.1256103515625</v>
       </c>
       <c r="I72" t="n">
-        <v>2491.349609375</v>
+        <v>2491.34912109375</v>
       </c>
       <c r="J72" t="n">
         <v>210.1000061035156</v>
@@ -2802,13 +2802,13 @@
         <v>2810.85009765625</v>
       </c>
       <c r="F74" t="n">
-        <v>805.6474609375</v>
+        <v>805.6473999023438</v>
       </c>
       <c r="G74" t="n">
         <v>47.0099983215332</v>
       </c>
       <c r="H74" t="n">
-        <v>364.8892211914062</v>
+        <v>364.8891906738281</v>
       </c>
       <c r="I74" t="n">
         <v>2474.7734375</v>
@@ -2828,7 +2828,7 @@
         <v>2699.60009765625</v>
       </c>
       <c r="D75" t="n">
-        <v>2281.257568359375</v>
+        <v>2281.2578125</v>
       </c>
       <c r="E75" t="n">
         <v>2811.5</v>
@@ -2843,7 +2843,7 @@
         <v>370.8347778320312</v>
       </c>
       <c r="I75" t="n">
-        <v>2439.775146484375</v>
+        <v>2439.77490234375</v>
       </c>
       <c r="J75" t="n">
         <v>214.3500061035156</v>
@@ -2898,16 +2898,16 @@
         <v>2824</v>
       </c>
       <c r="F77" t="n">
-        <v>836.6992797851562</v>
+        <v>836.6993408203125</v>
       </c>
       <c r="G77" t="n">
         <v>54.40999984741211</v>
       </c>
       <c r="H77" t="n">
-        <v>369.8519897460938</v>
+        <v>369.8520202636719</v>
       </c>
       <c r="I77" t="n">
-        <v>2416.458984375</v>
+        <v>2416.459228515625</v>
       </c>
       <c r="J77" t="n">
         <v>201.8500061035156</v>
@@ -2930,7 +2930,7 @@
         <v>2952.449951171875</v>
       </c>
       <c r="F78" t="n">
-        <v>885.321533203125</v>
+        <v>885.3214111328125</v>
       </c>
       <c r="G78" t="n">
         <v>57.13000106811523</v>
@@ -2968,7 +2968,7 @@
         <v>59.84000015258789</v>
       </c>
       <c r="H79" t="n">
-        <v>377.9104309082031</v>
+        <v>377.9104614257812</v>
       </c>
       <c r="I79" t="n">
         <v>2499.337890625</v>
@@ -2994,16 +2994,16 @@
         <v>2912.199951171875</v>
       </c>
       <c r="F80" t="n">
-        <v>863.516845703125</v>
+        <v>863.5169067382812</v>
       </c>
       <c r="G80" t="n">
         <v>56.84999847412109</v>
       </c>
       <c r="H80" t="n">
-        <v>376.7311401367188</v>
+        <v>376.7311706542969</v>
       </c>
       <c r="I80" t="n">
-        <v>2558.850830078125</v>
+        <v>2558.8505859375</v>
       </c>
       <c r="J80" t="n">
         <v>199.8999938964844</v>
@@ -3026,7 +3026,7 @@
         <v>2882.800048828125</v>
       </c>
       <c r="F81" t="n">
-        <v>833.633056640625</v>
+        <v>833.6331176757812</v>
       </c>
       <c r="G81" t="n">
         <v>56.06999969482422</v>
@@ -3035,7 +3035,7 @@
         <v>365.773681640625</v>
       </c>
       <c r="I81" t="n">
-        <v>2447.364013671875</v>
+        <v>2447.363525390625</v>
       </c>
       <c r="J81" t="n">
         <v>189.9499969482422</v>
@@ -3064,10 +3064,10 @@
         <v>56.06999969482422</v>
       </c>
       <c r="H82" t="n">
-        <v>371.6209106445312</v>
+        <v>371.6209411621094</v>
       </c>
       <c r="I82" t="n">
-        <v>2484.55908203125</v>
+        <v>2484.559326171875</v>
       </c>
       <c r="J82" t="n">
         <v>186.3999938964844</v>
@@ -3099,7 +3099,7 @@
         <v>361.7444763183594</v>
       </c>
       <c r="I83" t="n">
-        <v>2443.4697265625</v>
+        <v>2443.469482421875</v>
       </c>
       <c r="J83" t="n">
         <v>180.25</v>
@@ -3122,7 +3122,7 @@
         <v>2845.89990234375</v>
       </c>
       <c r="F84" t="n">
-        <v>789.7807006835938</v>
+        <v>789.7806396484375</v>
       </c>
       <c r="G84" t="n">
         <v>55.63000106811523</v>
@@ -3131,7 +3131,7 @@
         <v>360.0246887207031</v>
       </c>
       <c r="I84" t="n">
-        <v>2446.914306640625</v>
+        <v>2446.914794921875</v>
       </c>
       <c r="J84" t="n">
         <v>180.3500061035156</v>
@@ -3160,10 +3160,10 @@
         <v>58.40999984741211</v>
       </c>
       <c r="H85" t="n">
-        <v>359.091064453125</v>
+        <v>359.0910339355469</v>
       </c>
       <c r="I85" t="n">
-        <v>2434.08349609375</v>
+        <v>2434.083251953125</v>
       </c>
       <c r="J85" t="n">
         <v>174.3500061035156</v>
@@ -3195,7 +3195,7 @@
         <v>360.4177551269531</v>
       </c>
       <c r="I86" t="n">
-        <v>2371.774658203125</v>
+        <v>2371.7744140625</v>
       </c>
       <c r="J86" t="n">
         <v>170.6999969482422</v>
@@ -3212,7 +3212,7 @@
         <v>2482.550048828125</v>
       </c>
       <c r="D87" t="n">
-        <v>2104.80126953125</v>
+        <v>2104.801513671875</v>
       </c>
       <c r="E87" t="n">
         <v>2486.699951171875</v>
@@ -3224,7 +3224,7 @@
         <v>53.5099983215332</v>
       </c>
       <c r="H87" t="n">
-        <v>352.0154418945312</v>
+        <v>352.0154113769531</v>
       </c>
       <c r="I87" t="n">
         <v>2357.19580078125</v>
@@ -3250,7 +3250,7 @@
         <v>2648.050048828125</v>
       </c>
       <c r="F88" t="n">
-        <v>739.698486328125</v>
+        <v>739.6985473632812</v>
       </c>
       <c r="G88" t="n">
         <v>51.06000137329102</v>
@@ -3259,7 +3259,7 @@
         <v>352.8507385253906</v>
       </c>
       <c r="I88" t="n">
-        <v>2351.604248046875</v>
+        <v>2351.60400390625</v>
       </c>
       <c r="J88" t="n">
         <v>157.9499969482422</v>
@@ -3291,7 +3291,7 @@
         <v>367.100341796875</v>
       </c>
       <c r="I89" t="n">
-        <v>2290.743408203125</v>
+        <v>2290.74365234375</v>
       </c>
       <c r="J89" t="n">
         <v>150.3500061035156</v>
@@ -3314,7 +3314,7 @@
         <v>2171.550048828125</v>
       </c>
       <c r="F90" t="n">
-        <v>687.134033203125</v>
+        <v>687.1340942382812</v>
       </c>
       <c r="G90" t="n">
         <v>50.93000030517578</v>
@@ -3378,7 +3378,7 @@
         <v>2285.800048828125</v>
       </c>
       <c r="F92" t="n">
-        <v>724.951171875</v>
+        <v>724.9512329101562</v>
       </c>
       <c r="G92" t="n">
         <v>56.13999938964844</v>
@@ -3410,7 +3410,7 @@
         <v>2396.10009765625</v>
       </c>
       <c r="F93" t="n">
-        <v>739.6011352539062</v>
+        <v>739.6011962890625</v>
       </c>
       <c r="G93" t="n">
         <v>58.93999862670898</v>
@@ -3442,13 +3442,13 @@
         <v>2317.5</v>
       </c>
       <c r="F94" t="n">
-        <v>713.3189086914062</v>
+        <v>713.3189697265625</v>
       </c>
       <c r="G94" t="n">
         <v>59.47999954223633</v>
       </c>
       <c r="H94" t="n">
-        <v>357.7152709960938</v>
+        <v>357.7152404785156</v>
       </c>
       <c r="I94" t="n">
         <v>2375.019775390625</v>
@@ -3474,7 +3474,7 @@
         <v>2273.64990234375</v>
       </c>
       <c r="F95" t="n">
-        <v>747.1451416015625</v>
+        <v>747.1450805664062</v>
       </c>
       <c r="G95" t="n">
         <v>62.45000076293945</v>
@@ -3500,7 +3500,7 @@
         <v>2199.199951171875</v>
       </c>
       <c r="D96" t="n">
-        <v>2165.81494140625</v>
+        <v>2165.815185546875</v>
       </c>
       <c r="E96" t="n">
         <v>2248.35009765625</v>
@@ -3515,7 +3515,7 @@
         <v>357.1747741699219</v>
       </c>
       <c r="I96" t="n">
-        <v>2328.188232421875</v>
+        <v>2328.1884765625</v>
       </c>
       <c r="J96" t="n">
         <v>160.6000061035156</v>
@@ -3564,13 +3564,13 @@
         <v>2087.949951171875</v>
       </c>
       <c r="D98" t="n">
-        <v>2069.5302734375</v>
+        <v>2069.530029296875</v>
       </c>
       <c r="E98" t="n">
         <v>2187.35009765625</v>
       </c>
       <c r="F98" t="n">
-        <v>689.0808715820312</v>
+        <v>689.080810546875</v>
       </c>
       <c r="G98" t="n">
         <v>59.86999893188477</v>
@@ -3579,7 +3579,7 @@
         <v>355.4549560546875</v>
       </c>
       <c r="I98" t="n">
-        <v>2213.706298828125</v>
+        <v>2213.7060546875</v>
       </c>
       <c r="J98" t="n">
         <v>155.3500061035156</v>
@@ -3596,7 +3596,7 @@
         <v>2148.10009765625</v>
       </c>
       <c r="D99" t="n">
-        <v>2041.842041015625</v>
+        <v>2041.841918945312</v>
       </c>
       <c r="E99" t="n">
         <v>2164</v>
@@ -3608,10 +3608,10 @@
         <v>62.86000061035156</v>
       </c>
       <c r="H99" t="n">
-        <v>359.091064453125</v>
+        <v>359.0910339355469</v>
       </c>
       <c r="I99" t="n">
-        <v>2387.85107421875</v>
+        <v>2387.851318359375</v>
       </c>
       <c r="J99" t="n">
         <v>155.3000030517578</v>
@@ -3628,7 +3628,7 @@
         <v>2186.25</v>
       </c>
       <c r="D100" t="n">
-        <v>2075.516845703125</v>
+        <v>2075.5166015625</v>
       </c>
       <c r="E100" t="n">
         <v>2166.449951171875</v>
@@ -3698,7 +3698,7 @@
         <v>1888.949951171875</v>
       </c>
       <c r="F102" t="n">
-        <v>720.1815185546875</v>
+        <v>720.1814575195312</v>
       </c>
       <c r="G102" t="n">
         <v>64.65000152587891</v>
@@ -3707,7 +3707,7 @@
         <v>363.0220336914062</v>
       </c>
       <c r="I102" t="n">
-        <v>2394.39111328125</v>
+        <v>2394.3916015625</v>
       </c>
       <c r="J102" t="n">
         <v>170.5</v>
@@ -3739,7 +3739,7 @@
         <v>365.233154296875</v>
       </c>
       <c r="I103" t="n">
-        <v>2322.49658203125</v>
+        <v>2322.496337890625</v>
       </c>
       <c r="J103" t="n">
         <v>179</v>
@@ -3768,10 +3768,10 @@
         <v>59.06999969482422</v>
       </c>
       <c r="H104" t="n">
-        <v>367.0512390136719</v>
+        <v>367.0512084960938</v>
       </c>
       <c r="I104" t="n">
-        <v>2442.271728515625</v>
+        <v>2442.271484375</v>
       </c>
       <c r="J104" t="n">
         <v>173.0500030517578</v>
@@ -3794,7 +3794,7 @@
         <v>1855.900024414062</v>
       </c>
       <c r="F105" t="n">
-        <v>720.230224609375</v>
+        <v>720.2301635742188</v>
       </c>
       <c r="G105" t="n">
         <v>56.81999969482422</v>
@@ -3826,7 +3826,7 @@
         <v>1802.349975585938</v>
       </c>
       <c r="F106" t="n">
-        <v>721.5442504882812</v>
+        <v>721.5443115234375</v>
       </c>
       <c r="G106" t="n">
         <v>59.65999984741211</v>
@@ -3835,7 +3835,7 @@
         <v>358.5997009277344</v>
       </c>
       <c r="I106" t="n">
-        <v>2476.47119140625</v>
+        <v>2476.471435546875</v>
       </c>
       <c r="J106" t="n">
         <v>178.5</v>
@@ -3858,7 +3858,7 @@
         <v>1829.25</v>
       </c>
       <c r="F107" t="n">
-        <v>715.0223999023438</v>
+        <v>715.0223388671875</v>
       </c>
       <c r="G107" t="n">
         <v>58.27999877929688</v>
@@ -3890,16 +3890,16 @@
         <v>1801.900024414062</v>
       </c>
       <c r="F108" t="n">
-        <v>709.2305297851562</v>
+        <v>709.2305908203125</v>
       </c>
       <c r="G108" t="n">
         <v>56.90000152587891</v>
       </c>
       <c r="H108" t="n">
-        <v>356.7816467285156</v>
+        <v>356.7816162109375</v>
       </c>
       <c r="I108" t="n">
-        <v>2443.76904296875</v>
+        <v>2443.769287109375</v>
       </c>
       <c r="J108" t="n">
         <v>210.6999969482422</v>
@@ -3922,16 +3922,16 @@
         <v>1812.650024414062</v>
       </c>
       <c r="F109" t="n">
-        <v>715.9470825195312</v>
+        <v>715.9471435546875</v>
       </c>
       <c r="G109" t="n">
         <v>57.54999923706055</v>
       </c>
       <c r="H109" t="n">
-        <v>358.9927978515625</v>
+        <v>358.9927673339844</v>
       </c>
       <c r="I109" t="n">
-        <v>2494.39453125</v>
+        <v>2494.39501953125</v>
       </c>
       <c r="J109" t="n">
         <v>204.0500030517578</v>
@@ -3986,16 +3986,16 @@
         <v>1798.699951171875</v>
       </c>
       <c r="F111" t="n">
-        <v>676.7672119140625</v>
+        <v>676.7671508789062</v>
       </c>
       <c r="G111" t="n">
         <v>53.2400016784668</v>
       </c>
       <c r="H111" t="n">
-        <v>356.437744140625</v>
+        <v>356.4377136230469</v>
       </c>
       <c r="I111" t="n">
-        <v>2334.129638671875</v>
+        <v>2334.1298828125</v>
       </c>
       <c r="J111" t="n">
         <v>180</v>
@@ -4024,10 +4024,10 @@
         <v>53.33000183105469</v>
       </c>
       <c r="H112" t="n">
-        <v>353.3420715332031</v>
+        <v>353.342041015625</v>
       </c>
       <c r="I112" t="n">
-        <v>2371.2255859375</v>
+        <v>2371.225341796875</v>
       </c>
       <c r="J112" t="n">
         <v>192.4499969482422</v>
@@ -4050,16 +4050,16 @@
         <v>1757.849975585938</v>
       </c>
       <c r="F113" t="n">
-        <v>685.0411376953125</v>
+        <v>685.0411987304688</v>
       </c>
       <c r="G113" t="n">
         <v>54.40999984741211</v>
       </c>
       <c r="H113" t="n">
-        <v>355.7006530761719</v>
+        <v>355.70068359375</v>
       </c>
       <c r="I113" t="n">
-        <v>2348.359130859375</v>
+        <v>2348.358642578125</v>
       </c>
       <c r="J113" t="n">
         <v>192.1999969482422</v>
@@ -4082,13 +4082,13 @@
         <v>1711.099975585938</v>
       </c>
       <c r="F114" t="n">
-        <v>663.5773315429688</v>
+        <v>663.577392578125</v>
       </c>
       <c r="G114" t="n">
         <v>51.86000061035156</v>
       </c>
       <c r="H114" t="n">
-        <v>353.1946411132812</v>
+        <v>353.1946716308594</v>
       </c>
       <c r="I114" t="n">
         <v>2373.022705078125</v>
@@ -4114,13 +4114,13 @@
         <v>1711.25</v>
       </c>
       <c r="F115" t="n">
-        <v>651.1663208007812</v>
+        <v>651.1663818359375</v>
       </c>
       <c r="G115" t="n">
         <v>52.2599983215332</v>
       </c>
       <c r="H115" t="n">
-        <v>351.1800537109375</v>
+        <v>351.1800842285156</v>
       </c>
       <c r="I115" t="n">
         <v>2145.905517578125</v>
@@ -4187,7 +4187,7 @@
         <v>352.7032775878906</v>
       </c>
       <c r="I117" t="n">
-        <v>2379.413330078125</v>
+        <v>2379.41357421875</v>
       </c>
       <c r="J117" t="n">
         <v>170.75</v>
@@ -4210,7 +4210,7 @@
         <v>1736.099975585938</v>
       </c>
       <c r="F118" t="n">
-        <v>650.5336303710938</v>
+        <v>650.5335693359375</v>
       </c>
       <c r="G118" t="n">
         <v>49.45999908447266</v>
@@ -4219,7 +4219,7 @@
         <v>351.7697143554688</v>
       </c>
       <c r="I118" t="n">
-        <v>2267.4775390625</v>
+        <v>2267.477294921875</v>
       </c>
       <c r="J118" t="n">
         <v>172.3500061035156</v>
@@ -4242,16 +4242,16 @@
         <v>1796.75</v>
       </c>
       <c r="F119" t="n">
-        <v>657.3475952148438</v>
+        <v>657.3474731445312</v>
       </c>
       <c r="G119" t="n">
         <v>50.52000045776367</v>
       </c>
       <c r="H119" t="n">
-        <v>352.7524719238281</v>
+        <v>352.75244140625</v>
       </c>
       <c r="I119" t="n">
-        <v>2261.336181640625</v>
+        <v>2261.33642578125</v>
       </c>
       <c r="J119" t="n">
         <v>173</v>
@@ -4274,7 +4274,7 @@
         <v>1857.599975585938</v>
       </c>
       <c r="F120" t="n">
-        <v>668.1525268554688</v>
+        <v>668.1524658203125</v>
       </c>
       <c r="G120" t="n">
         <v>52.88999938964844</v>
@@ -4338,7 +4338,7 @@
         <v>1909.849975585938</v>
       </c>
       <c r="F122" t="n">
-        <v>660.0244140625</v>
+        <v>660.0244750976562</v>
       </c>
       <c r="G122" t="n">
         <v>54.04999923706055</v>
@@ -4347,7 +4347,7 @@
         <v>360.1229553222656</v>
       </c>
       <c r="I122" t="n">
-        <v>2390.896484375</v>
+        <v>2390.896240234375</v>
       </c>
       <c r="J122" t="n">
         <v>178.3500061035156</v>
@@ -4379,7 +4379,7 @@
         <v>359.1893615722656</v>
       </c>
       <c r="I123" t="n">
-        <v>2344.2646484375</v>
+        <v>2344.264892578125</v>
       </c>
       <c r="J123" t="n">
         <v>176.8999938964844</v>
@@ -4411,7 +4411,7 @@
         <v>356.7325134277344</v>
       </c>
       <c r="I124" t="n">
-        <v>2389.398681640625</v>
+        <v>2389.3984375</v>
       </c>
       <c r="J124" t="n">
         <v>176</v>
@@ -4434,7 +4434,7 @@
         <v>1963.650024414062</v>
       </c>
       <c r="F125" t="n">
-        <v>659.8784790039062</v>
+        <v>659.87841796875</v>
       </c>
       <c r="G125" t="n">
         <v>52.65000152587891</v>
@@ -4443,7 +4443,7 @@
         <v>361.2039489746094</v>
       </c>
       <c r="I125" t="n">
-        <v>2385.504150390625</v>
+        <v>2385.50439453125</v>
       </c>
       <c r="J125" t="n">
         <v>168.0500030517578</v>
@@ -4472,10 +4472,10 @@
         <v>52.34000015258789</v>
       </c>
       <c r="H126" t="n">
-        <v>362.1867065429688</v>
+        <v>362.1866760253906</v>
       </c>
       <c r="I126" t="n">
-        <v>2393.29296875</v>
+        <v>2393.293212890625</v>
       </c>
       <c r="J126" t="n">
         <v>168.8000030517578</v>
@@ -4498,13 +4498,13 @@
         <v>1876.400024414062</v>
       </c>
       <c r="F127" t="n">
-        <v>660.705810546875</v>
+        <v>660.7058715820312</v>
       </c>
       <c r="G127" t="n">
         <v>52.54999923706055</v>
       </c>
       <c r="H127" t="n">
-        <v>360.3194885253906</v>
+        <v>360.3194580078125</v>
       </c>
       <c r="I127" t="n">
         <v>2406.923095703125</v>
@@ -4530,16 +4530,16 @@
         <v>1903.699951171875</v>
       </c>
       <c r="F128" t="n">
-        <v>675.8910522460938</v>
+        <v>675.89111328125</v>
       </c>
       <c r="G128" t="n">
         <v>52.54000091552734</v>
       </c>
       <c r="H128" t="n">
-        <v>361.891845703125</v>
+        <v>361.8918762207031</v>
       </c>
       <c r="I128" t="n">
-        <v>2471.728271484375</v>
+        <v>2471.72802734375</v>
       </c>
       <c r="J128" t="n">
         <v>164.8500061035156</v>
@@ -4556,22 +4556,22 @@
         <v>2466.10009765625</v>
       </c>
       <c r="D129" t="n">
-        <v>2269.234375</v>
+        <v>2269.234619140625</v>
       </c>
       <c r="E129" t="n">
         <v>1909.699951171875</v>
       </c>
       <c r="F129" t="n">
-        <v>684.8951416015625</v>
+        <v>684.8950805664062</v>
       </c>
       <c r="G129" t="n">
         <v>55.11999893188477</v>
       </c>
       <c r="H129" t="n">
-        <v>360.6143188476562</v>
+        <v>360.6143493652344</v>
       </c>
       <c r="I129" t="n">
-        <v>2482.113037109375</v>
+        <v>2482.11279296875</v>
       </c>
       <c r="J129" t="n">
         <v>167.4499969482422</v>
@@ -4600,10 +4600,10 @@
         <v>54.31000137329102</v>
       </c>
       <c r="H130" t="n">
-        <v>362.0884094238281</v>
+        <v>362.0884399414062</v>
       </c>
       <c r="I130" t="n">
-        <v>2537.082275390625</v>
+        <v>2537.08251953125</v>
       </c>
       <c r="J130" t="n">
         <v>190.5</v>
@@ -4626,7 +4626,7 @@
         <v>2207.35009765625</v>
       </c>
       <c r="F131" t="n">
-        <v>709.8146362304688</v>
+        <v>709.814697265625</v>
       </c>
       <c r="G131" t="n">
         <v>57.02000045776367</v>
@@ -4635,7 +4635,7 @@
         <v>362.8255004882812</v>
       </c>
       <c r="I131" t="n">
-        <v>2712.67529296875</v>
+        <v>2712.675048828125</v>
       </c>
       <c r="J131" t="n">
         <v>191.0500030517578</v>
@@ -4652,7 +4652,7 @@
         <v>2749.800048828125</v>
       </c>
       <c r="D132" t="n">
-        <v>2360.380615234375</v>
+        <v>2360.380859375</v>
       </c>
       <c r="E132" t="n">
         <v>2294.75</v>
@@ -4667,7 +4667,7 @@
         <v>364.4961242675781</v>
       </c>
       <c r="I132" t="n">
-        <v>2793.45654296875</v>
+        <v>2793.456787109375</v>
       </c>
       <c r="J132" t="n">
         <v>196.8500061035156</v>
@@ -4696,10 +4696,10 @@
         <v>57.33000183105469</v>
       </c>
       <c r="H133" t="n">
-        <v>364.7909545898438</v>
+        <v>364.7909240722656</v>
       </c>
       <c r="I133" t="n">
-        <v>2668.190185546875</v>
+        <v>2668.1904296875</v>
       </c>
       <c r="J133" t="n">
         <v>201.6000061035156</v>
@@ -4728,10 +4728,10 @@
         <v>56.7400016784668</v>
       </c>
       <c r="H134" t="n">
-        <v>363.5133972167969</v>
+        <v>363.5133666992188</v>
       </c>
       <c r="I134" t="n">
-        <v>2761.062744140625</v>
+        <v>2761.063232421875</v>
       </c>
       <c r="J134" t="n">
         <v>193.8500061035156</v>
@@ -4754,16 +4754,16 @@
         <v>2072.64990234375</v>
       </c>
       <c r="F135" t="n">
-        <v>716.398193359375</v>
+        <v>716.3982543945312</v>
       </c>
       <c r="G135" t="n">
         <v>57.34999847412109</v>
       </c>
       <c r="H135" t="n">
-        <v>362.7763366699219</v>
+        <v>362.7763671875</v>
       </c>
       <c r="I135" t="n">
-        <v>2803.854248046875</v>
+        <v>2803.85400390625</v>
       </c>
       <c r="J135" t="n">
         <v>187.6999969482422</v>
@@ -4792,7 +4792,7 @@
         <v>57.97000122070312</v>
       </c>
       <c r="H136" t="n">
-        <v>364.2996215820312</v>
+        <v>364.2995910644531</v>
       </c>
       <c r="I136" t="n">
         <v>2828.919677734375</v>
@@ -4812,7 +4812,7 @@
         <v>3029.75</v>
       </c>
       <c r="D137" t="n">
-        <v>2446.84814453125</v>
+        <v>2446.847900390625</v>
       </c>
       <c r="E137" t="n">
         <v>2109</v>
@@ -4850,7 +4850,7 @@
         <v>2084.300048828125</v>
       </c>
       <c r="F138" t="n">
-        <v>728.7972412109375</v>
+        <v>728.7971801757812</v>
       </c>
       <c r="G138" t="n">
         <v>57.97999954223633</v>
@@ -4940,7 +4940,7 @@
         <v>2969.75</v>
       </c>
       <c r="D141" t="n">
-        <v>2545.9677734375</v>
+        <v>2545.968017578125</v>
       </c>
       <c r="E141" t="n">
         <v>2137.60009765625</v>
@@ -4972,7 +4972,7 @@
         <v>2993.75</v>
       </c>
       <c r="D142" t="n">
-        <v>2555.05126953125</v>
+        <v>2555.051025390625</v>
       </c>
       <c r="E142" t="n">
         <v>2103.64990234375</v>
@@ -4984,7 +4984,7 @@
         <v>59.54000091552734</v>
       </c>
       <c r="H142" t="n">
-        <v>363.5625610351562</v>
+        <v>363.5625305175781</v>
       </c>
       <c r="I142" t="n">
         <v>2894.230224609375</v>
@@ -5010,7 +5010,7 @@
         <v>2099.199951171875</v>
       </c>
       <c r="F143" t="n">
-        <v>745.5579833984375</v>
+        <v>745.5579223632812</v>
       </c>
       <c r="G143" t="n">
         <v>62.4900016784668</v>
@@ -5019,7 +5019,7 @@
         <v>364.4469909667969</v>
       </c>
       <c r="I143" t="n">
-        <v>2956.04541015625</v>
+        <v>2956.045654296875</v>
       </c>
       <c r="J143" t="n">
         <v>252.5</v>
@@ -5036,13 +5036,13 @@
         <v>3012.64990234375</v>
       </c>
       <c r="D144" t="n">
-        <v>2545.76806640625</v>
+        <v>2545.767822265625</v>
       </c>
       <c r="E144" t="n">
         <v>2143.949951171875</v>
       </c>
       <c r="F144" t="n">
-        <v>749.3314819335938</v>
+        <v>749.33154296875</v>
       </c>
       <c r="G144" t="n">
         <v>64.38999938964844</v>
@@ -5074,13 +5074,13 @@
         <v>2174.699951171875</v>
       </c>
       <c r="F145" t="n">
-        <v>748.54736328125</v>
+        <v>748.5474243164062</v>
       </c>
       <c r="G145" t="n">
         <v>62.79000091552734</v>
       </c>
       <c r="H145" t="n">
-        <v>368.3287658691406</v>
+        <v>368.3287353515625</v>
       </c>
       <c r="I145" t="n">
         <v>3122.916259765625</v>
@@ -5202,7 +5202,7 @@
         <v>2190.949951171875</v>
       </c>
       <c r="F149" t="n">
-        <v>791.2333984375</v>
+        <v>791.2333374023438</v>
       </c>
       <c r="G149" t="n">
         <v>69.44999694824219</v>
@@ -5228,7 +5228,7 @@
         <v>3313.550048828125</v>
       </c>
       <c r="D150" t="n">
-        <v>2693.499267578125</v>
+        <v>2693.4990234375</v>
       </c>
       <c r="E150" t="n">
         <v>2106.199951171875</v>
@@ -5260,19 +5260,19 @@
         <v>3447.35009765625</v>
       </c>
       <c r="D151" t="n">
-        <v>2786.829345703125</v>
+        <v>2786.8291015625</v>
       </c>
       <c r="E151" t="n">
         <v>2165.199951171875</v>
       </c>
       <c r="F151" t="n">
-        <v>785.7444458007812</v>
+        <v>785.744384765625</v>
       </c>
       <c r="G151" t="n">
         <v>65.72000122070312</v>
       </c>
       <c r="H151" t="n">
-        <v>373.6355285644531</v>
+        <v>373.6355590820312</v>
       </c>
       <c r="I151" t="n">
         <v>3360.390869140625</v>
@@ -5292,13 +5292,13 @@
         <v>3436.14990234375</v>
       </c>
       <c r="D152" t="n">
-        <v>2822.065185546875</v>
+        <v>2822.0654296875</v>
       </c>
       <c r="E152" t="n">
         <v>2164.949951171875</v>
       </c>
       <c r="F152" t="n">
-        <v>774.8646850585938</v>
+        <v>774.8646240234375</v>
       </c>
       <c r="G152" t="n">
         <v>67.94999694824219</v>
@@ -5307,7 +5307,7 @@
         <v>373.4881286621094</v>
       </c>
       <c r="I152" t="n">
-        <v>3346.809326171875</v>
+        <v>3346.8095703125</v>
       </c>
       <c r="J152" t="n">
         <v>294.5</v>
@@ -5324,7 +5324,7 @@
         <v>3493.949951171875</v>
       </c>
       <c r="D153" t="n">
-        <v>2828.9033203125</v>
+        <v>2828.903076171875</v>
       </c>
       <c r="E153" t="n">
         <v>2164.89990234375</v>
@@ -5336,7 +5336,7 @@
         <v>68.48000335693359</v>
       </c>
       <c r="H153" t="n">
-        <v>373.6355285644531</v>
+        <v>373.6355590820312</v>
       </c>
       <c r="I153" t="n">
         <v>3347.708251953125</v>
@@ -5356,7 +5356,7 @@
         <v>3535.60009765625</v>
       </c>
       <c r="D154" t="n">
-        <v>2859.34765625</v>
+        <v>2859.347412109375</v>
       </c>
       <c r="E154" t="n">
         <v>2176</v>
@@ -5371,7 +5371,7 @@
         <v>378.1560974121094</v>
       </c>
       <c r="I154" t="n">
-        <v>3420.708251953125</v>
+        <v>3420.7080078125</v>
       </c>
       <c r="J154" t="n">
         <v>311.1000061035156</v>
@@ -5400,7 +5400,7 @@
         <v>72.47000122070312</v>
       </c>
       <c r="H155" t="n">
-        <v>389.2610473632812</v>
+        <v>389.2610168457031</v>
       </c>
       <c r="I155" t="n">
         <v>3484.919921875</v>
@@ -5426,7 +5426,7 @@
         <v>2227.050048828125</v>
       </c>
       <c r="F156" t="n">
-        <v>808.3861083984375</v>
+        <v>808.3861694335938</v>
       </c>
       <c r="G156" t="n">
         <v>76.08999633789062</v>
@@ -5435,7 +5435,7 @@
         <v>391.4230041503906</v>
       </c>
       <c r="I156" t="n">
-        <v>3467.0947265625</v>
+        <v>3467.094482421875</v>
       </c>
       <c r="J156" t="n">
         <v>331.3500061035156</v>
@@ -5452,7 +5452,7 @@
         <v>3599.550048828125</v>
       </c>
       <c r="D157" t="n">
-        <v>3147.92236328125</v>
+        <v>3147.922607421875</v>
       </c>
       <c r="E157" t="n">
         <v>2296.35009765625</v>
@@ -5464,7 +5464,7 @@
         <v>79.88999938964844</v>
       </c>
       <c r="H157" t="n">
-        <v>402.5279541015625</v>
+        <v>402.5279235839844</v>
       </c>
       <c r="I157" t="n">
         <v>3458.556396484375</v>
@@ -5563,7 +5563,7 @@
         <v>398.4495849609375</v>
       </c>
       <c r="I160" t="n">
-        <v>3426.25048828125</v>
+        <v>3426.250732421875</v>
       </c>
       <c r="J160" t="n">
         <v>369.75</v>
@@ -5580,7 +5580,7 @@
         <v>3700.39990234375</v>
       </c>
       <c r="D161" t="n">
-        <v>3128.95703125</v>
+        <v>3128.956787109375</v>
       </c>
       <c r="E161" t="n">
         <v>2358.85009765625</v>
@@ -5612,7 +5612,7 @@
         <v>3715.800048828125</v>
       </c>
       <c r="D162" t="n">
-        <v>3060.78125</v>
+        <v>3060.781005859375</v>
       </c>
       <c r="E162" t="n">
         <v>2368.300048828125</v>
@@ -5644,7 +5644,7 @@
         <v>3751.199951171875</v>
       </c>
       <c r="D163" t="n">
-        <v>3133.84814453125</v>
+        <v>3133.847900390625</v>
       </c>
       <c r="E163" t="n">
         <v>2392.75</v>
@@ -5659,7 +5659,7 @@
         <v>395.8944702148438</v>
       </c>
       <c r="I163" t="n">
-        <v>3454.911376953125</v>
+        <v>3454.9111328125</v>
       </c>
       <c r="J163" t="n">
         <v>427.7000122070312</v>
@@ -5691,7 +5691,7 @@
         <v>396.484130859375</v>
       </c>
       <c r="I164" t="n">
-        <v>3532.5546875</v>
+        <v>3532.554931640625</v>
       </c>
       <c r="J164" t="n">
         <v>449.0499877929688</v>
@@ -5787,7 +5787,7 @@
         <v>408.4243469238281</v>
       </c>
       <c r="I167" t="n">
-        <v>3617.8876953125</v>
+        <v>3617.887939453125</v>
       </c>
       <c r="J167" t="n">
         <v>519.7999877929688</v>
@@ -5816,10 +5816,10 @@
         <v>77.97000122070312</v>
       </c>
       <c r="H168" t="n">
-        <v>410.7337646484375</v>
+        <v>410.7337951660156</v>
       </c>
       <c r="I168" t="n">
-        <v>3525.76416015625</v>
+        <v>3525.763916015625</v>
       </c>
       <c r="J168" t="n">
         <v>545.75</v>
@@ -5842,13 +5842,13 @@
         <v>2374.89990234375</v>
       </c>
       <c r="F169" t="n">
-        <v>833.4781494140625</v>
+        <v>833.4782104492188</v>
       </c>
       <c r="G169" t="n">
         <v>81.55000305175781</v>
       </c>
       <c r="H169" t="n">
-        <v>428.9634704589844</v>
+        <v>428.9634399414062</v>
       </c>
       <c r="I169" t="n">
         <v>3677.8056640625</v>
@@ -5883,7 +5883,7 @@
         <v>441.1493835449219</v>
       </c>
       <c r="I170" t="n">
-        <v>3656.2353515625</v>
+        <v>3656.235107421875</v>
       </c>
       <c r="J170" t="n">
         <v>492.6000061035156</v>
@@ -5915,7 +5915,7 @@
         <v>453.9249267578125</v>
       </c>
       <c r="I171" t="n">
-        <v>3624.927734375</v>
+        <v>3624.927978515625</v>
       </c>
       <c r="J171" t="n">
         <v>468</v>
@@ -5932,13 +5932,13 @@
         <v>3931.10009765625</v>
       </c>
       <c r="D172" t="n">
-        <v>3444.931884765625</v>
+        <v>3444.93212890625</v>
       </c>
       <c r="E172" t="n">
         <v>2315.89990234375</v>
       </c>
       <c r="F172" t="n">
-        <v>888.8571166992188</v>
+        <v>888.857177734375</v>
       </c>
       <c r="G172" t="n">
         <v>79.40000152587891</v>
@@ -5964,19 +5964,19 @@
         <v>4006</v>
       </c>
       <c r="D173" t="n">
-        <v>3457.50927734375</v>
+        <v>3457.509033203125</v>
       </c>
       <c r="E173" t="n">
         <v>2355.949951171875</v>
       </c>
       <c r="F173" t="n">
-        <v>919.879150390625</v>
+        <v>919.8792114257812</v>
       </c>
       <c r="G173" t="n">
         <v>79.51999664306641</v>
       </c>
       <c r="H173" t="n">
-        <v>467.4375305175781</v>
+        <v>467.4375</v>
       </c>
       <c r="I173" t="n">
         <v>3630.420654296875</v>
@@ -6011,7 +6011,7 @@
         <v>478.1001892089844</v>
       </c>
       <c r="I174" t="n">
-        <v>3599.8125</v>
+        <v>3599.812255859375</v>
       </c>
       <c r="J174" t="n">
         <v>443.5</v>
@@ -6034,7 +6034,7 @@
         <v>2293.60009765625</v>
       </c>
       <c r="F175" t="n">
-        <v>929.043701171875</v>
+        <v>929.0436401367188</v>
       </c>
       <c r="G175" t="n">
         <v>76.91000366210938</v>
@@ -6066,7 +6066,7 @@
         <v>2343.89990234375</v>
       </c>
       <c r="F176" t="n">
-        <v>949.3330078125</v>
+        <v>949.3329467773438</v>
       </c>
       <c r="G176" t="n">
         <v>79.83999633789062</v>
@@ -6092,7 +6092,7 @@
         <v>4094.75</v>
       </c>
       <c r="D177" t="n">
-        <v>3695.47607421875</v>
+        <v>3695.476318359375</v>
       </c>
       <c r="E177" t="n">
         <v>2316.60009765625</v>
@@ -6124,7 +6124,7 @@
         <v>4029.39990234375</v>
       </c>
       <c r="D178" t="n">
-        <v>3771.787109375</v>
+        <v>3771.787353515625</v>
       </c>
       <c r="E178" t="n">
         <v>2346.35009765625</v>
@@ -6156,7 +6156,7 @@
         <v>4021.550048828125</v>
       </c>
       <c r="D179" t="n">
-        <v>3827.585693359375</v>
+        <v>3827.58544921875</v>
       </c>
       <c r="E179" t="n">
         <v>2399.949951171875</v>
@@ -6168,10 +6168,10 @@
         <v>79.65000152587891</v>
       </c>
       <c r="H179" t="n">
-        <v>564.433349609375</v>
+        <v>564.4332885742188</v>
       </c>
       <c r="I179" t="n">
-        <v>3669.916259765625</v>
+        <v>3669.91650390625</v>
       </c>
       <c r="J179" t="n">
         <v>438.5</v>
@@ -6232,10 +6232,10 @@
         <v>79.25</v>
       </c>
       <c r="H181" t="n">
-        <v>524.8292236328125</v>
+        <v>524.8291625976562</v>
       </c>
       <c r="I181" t="n">
-        <v>3624.927734375</v>
+        <v>3624.927978515625</v>
       </c>
       <c r="J181" t="n">
         <v>408.4500122070312</v>
@@ -6264,7 +6264,7 @@
         <v>77.12000274658203</v>
       </c>
       <c r="H182" t="n">
-        <v>530.0376586914062</v>
+        <v>530.0377197265625</v>
       </c>
       <c r="I182" t="n">
         <v>3540.39404296875</v>
@@ -6284,13 +6284,13 @@
         <v>3713</v>
       </c>
       <c r="D183" t="n">
-        <v>3579.6865234375</v>
+        <v>3579.686767578125</v>
       </c>
       <c r="E183" t="n">
         <v>2210.35009765625</v>
       </c>
       <c r="F183" t="n">
-        <v>846.269287109375</v>
+        <v>846.2692260742188</v>
       </c>
       <c r="G183" t="n">
         <v>73.30000305175781</v>
@@ -6299,7 +6299,7 @@
         <v>502.3737182617188</v>
       </c>
       <c r="I183" t="n">
-        <v>3366.4326171875</v>
+        <v>3366.432861328125</v>
       </c>
       <c r="J183" t="n">
         <v>368.6499938964844</v>
@@ -6360,10 +6360,10 @@
         <v>73.55000305175781</v>
       </c>
       <c r="H185" t="n">
-        <v>491.4162292480469</v>
+        <v>491.416259765625</v>
       </c>
       <c r="I185" t="n">
-        <v>3443.3271484375</v>
+        <v>3443.327392578125</v>
       </c>
       <c r="J185" t="n">
         <v>367.75</v>
@@ -6380,13 +6380,13 @@
         <v>3406.39990234375</v>
       </c>
       <c r="D186" t="n">
-        <v>3464.396728515625</v>
+        <v>3464.396484375</v>
       </c>
       <c r="E186" t="n">
         <v>2004.050048828125</v>
       </c>
       <c r="F186" t="n">
-        <v>800.2018432617188</v>
+        <v>800.2017822265625</v>
       </c>
       <c r="G186" t="n">
         <v>73.88999938964844</v>
@@ -6424,10 +6424,10 @@
         <v>74.69999694824219</v>
       </c>
       <c r="H187" t="n">
-        <v>506.6976928710938</v>
+        <v>506.6977233886719</v>
       </c>
       <c r="I187" t="n">
-        <v>3335.275390625</v>
+        <v>3335.275146484375</v>
       </c>
       <c r="J187" t="n">
         <v>373.0499877929688</v>
@@ -6482,7 +6482,7 @@
         <v>2134.199951171875</v>
       </c>
       <c r="F189" t="n">
-        <v>806.7197875976562</v>
+        <v>806.7198486328125</v>
       </c>
       <c r="G189" t="n">
         <v>70.5</v>
@@ -6508,7 +6508,7 @@
         <v>3358.75</v>
       </c>
       <c r="D190" t="n">
-        <v>3279.033935546875</v>
+        <v>3279.03369140625</v>
       </c>
       <c r="E190" t="n">
         <v>2201.699951171875</v>
@@ -6523,7 +6523,7 @@
         <v>498.1479797363281</v>
       </c>
       <c r="I190" t="n">
-        <v>3303.468994140625</v>
+        <v>3303.46923828125</v>
       </c>
       <c r="J190" t="n">
         <v>352.75</v>
@@ -6555,7 +6555,7 @@
         <v>512.7906494140625</v>
       </c>
       <c r="I191" t="n">
-        <v>3183.23388671875</v>
+        <v>3183.234130859375</v>
       </c>
       <c r="J191" t="n">
         <v>349.8500061035156</v>
@@ -6578,7 +6578,7 @@
         <v>2155.89990234375</v>
       </c>
       <c r="F192" t="n">
-        <v>792.06640625</v>
+        <v>792.0664672851562</v>
       </c>
       <c r="G192" t="n">
         <v>73.06999969482422</v>
@@ -6616,7 +6616,7 @@
         <v>71.37000274658203</v>
       </c>
       <c r="H193" t="n">
-        <v>491.5636901855469</v>
+        <v>491.5636596679688</v>
       </c>
       <c r="I193" t="n">
         <v>3169.253173828125</v>
@@ -6651,7 +6651,7 @@
         <v>496.7230224609375</v>
       </c>
       <c r="I194" t="n">
-        <v>3198.463134765625</v>
+        <v>3198.462890625</v>
       </c>
       <c r="J194" t="n">
         <v>341</v>
@@ -6674,7 +6674,7 @@
         <v>2083.35009765625</v>
       </c>
       <c r="F195" t="n">
-        <v>769.1798095703125</v>
+        <v>769.1797485351562</v>
       </c>
       <c r="G195" t="n">
         <v>69.37000274658203</v>
@@ -6776,10 +6776,10 @@
         <v>69.12000274658203</v>
       </c>
       <c r="H198" t="n">
-        <v>499.08154296875</v>
+        <v>499.0815734863281</v>
       </c>
       <c r="I198" t="n">
-        <v>3148.53173828125</v>
+        <v>3148.531494140625</v>
       </c>
       <c r="J198" t="n">
         <v>326.2999877929688</v>
@@ -6802,13 +6802,13 @@
         <v>2119.800048828125</v>
       </c>
       <c r="F199" t="n">
-        <v>789.0769653320312</v>
+        <v>789.076904296875</v>
       </c>
       <c r="G199" t="n">
         <v>66.72000122070312</v>
       </c>
       <c r="H199" t="n">
-        <v>501.8823852539062</v>
+        <v>501.8823547363281</v>
       </c>
       <c r="I199" t="n">
         <v>3162.512451171875</v>
@@ -6866,7 +6866,7 @@
         <v>2105.300048828125</v>
       </c>
       <c r="F201" t="n">
-        <v>785.7444458007812</v>
+        <v>785.744384765625</v>
       </c>
       <c r="G201" t="n">
         <v>66.44000244140625</v>
@@ -6930,13 +6930,13 @@
         <v>2079.89990234375</v>
       </c>
       <c r="F203" t="n">
-        <v>784.4702758789062</v>
+        <v>784.47021484375</v>
       </c>
       <c r="G203" t="n">
         <v>66.47000122070312</v>
       </c>
       <c r="H203" t="n">
-        <v>504.2408752441406</v>
+        <v>504.2409057617188</v>
       </c>
       <c r="I203" t="n">
         <v>3378.31640625</v>
@@ -6968,7 +6968,7 @@
         <v>67.48000335693359</v>
       </c>
       <c r="H204" t="n">
-        <v>518.4905395507812</v>
+        <v>518.4906005859375</v>
       </c>
       <c r="I204" t="n">
         <v>3502.9453125</v>
@@ -6988,7 +6988,7 @@
         <v>3277.949951171875</v>
       </c>
       <c r="D205" t="n">
-        <v>3317.264404296875</v>
+        <v>3317.26416015625</v>
       </c>
       <c r="E205" t="n">
         <v>2098.550048828125</v>
@@ -7000,10 +7000,10 @@
         <v>66.66000366210938</v>
       </c>
       <c r="H205" t="n">
-        <v>511.1200561523438</v>
+        <v>511.1201171875</v>
       </c>
       <c r="I205" t="n">
-        <v>3439.33251953125</v>
+        <v>3439.332763671875</v>
       </c>
       <c r="J205" t="n">
         <v>312.7000122070312</v>
@@ -7026,7 +7026,7 @@
         <v>2102.89990234375</v>
       </c>
       <c r="F206" t="n">
-        <v>807.2098999023438</v>
+        <v>807.2099609375</v>
       </c>
       <c r="G206" t="n">
         <v>66.98000335693359</v>
@@ -7035,7 +7035,7 @@
         <v>523.7482299804688</v>
       </c>
       <c r="I206" t="n">
-        <v>3597.915283203125</v>
+        <v>3597.9150390625</v>
       </c>
       <c r="J206" t="n">
         <v>321.75</v>
@@ -7052,7 +7052,7 @@
         <v>3342.449951171875</v>
       </c>
       <c r="D207" t="n">
-        <v>3569.2060546875</v>
+        <v>3569.205810546875</v>
       </c>
       <c r="E207" t="n">
         <v>2121.25</v>
@@ -7067,7 +7067,7 @@
         <v>534.6565551757812</v>
       </c>
       <c r="I207" t="n">
-        <v>3676.157470703125</v>
+        <v>3676.15771484375</v>
       </c>
       <c r="J207" t="n">
         <v>318</v>
@@ -7090,7 +7090,7 @@
         <v>2137.050048828125</v>
       </c>
       <c r="F208" t="n">
-        <v>816.8645629882812</v>
+        <v>816.864501953125</v>
       </c>
       <c r="G208" t="n">
         <v>68.62999725341797</v>
@@ -7131,7 +7131,7 @@
         <v>530.1851196289062</v>
       </c>
       <c r="I209" t="n">
-        <v>3655.88525390625</v>
+        <v>3655.885498046875</v>
       </c>
       <c r="J209" t="n">
         <v>318.6000061035156</v>
@@ -7160,7 +7160,7 @@
         <v>69.37000274658203</v>
       </c>
       <c r="H210" t="n">
-        <v>548.955322265625</v>
+        <v>548.9552612304688</v>
       </c>
       <c r="I210" t="n">
         <v>3754.10107421875</v>
@@ -7180,13 +7180,13 @@
         <v>3332.449951171875</v>
       </c>
       <c r="D211" t="n">
-        <v>3953.406982421875</v>
+        <v>3953.4072265625</v>
       </c>
       <c r="E211" t="n">
         <v>2165.699951171875</v>
       </c>
       <c r="F211" t="n">
-        <v>836.0756225585938</v>
+        <v>836.0755615234375</v>
       </c>
       <c r="G211" t="n">
         <v>69.72000122070312</v>
@@ -7195,7 +7195,7 @@
         <v>558.2913208007812</v>
       </c>
       <c r="I211" t="n">
-        <v>3795.1943359375</v>
+        <v>3795.194580078125</v>
       </c>
       <c r="J211" t="n">
         <v>351.2000122070312</v>
@@ -7218,7 +7218,7 @@
         <v>2215.5</v>
       </c>
       <c r="F212" t="n">
-        <v>873.1256103515625</v>
+        <v>873.1255493164062</v>
       </c>
       <c r="G212" t="n">
         <v>73.16000366210938</v>
@@ -7256,7 +7256,7 @@
         <v>74.27999877929688</v>
       </c>
       <c r="H213" t="n">
-        <v>548.5130615234375</v>
+        <v>548.5131225585938</v>
       </c>
       <c r="I213" t="n">
         <v>3702.0224609375</v>
@@ -7276,7 +7276,7 @@
         <v>3292.050048828125</v>
       </c>
       <c r="D214" t="n">
-        <v>4001.5693359375</v>
+        <v>4001.569580078125</v>
       </c>
       <c r="E214" t="n">
         <v>2196.699951171875</v>
@@ -7288,10 +7288,10 @@
         <v>72.04000091552734</v>
       </c>
       <c r="H214" t="n">
-        <v>547.9234619140625</v>
+        <v>547.9234008789062</v>
       </c>
       <c r="I214" t="n">
-        <v>3795.394287109375</v>
+        <v>3795.39404296875</v>
       </c>
       <c r="J214" t="n">
         <v>357.8500061035156</v>
@@ -7314,7 +7314,7 @@
         <v>2178.550048828125</v>
       </c>
       <c r="F215" t="n">
-        <v>877.2913208007812</v>
+        <v>877.291259765625</v>
       </c>
       <c r="G215" t="n">
         <v>71.95999908447266</v>
@@ -7323,7 +7323,7 @@
         <v>570.2806396484375</v>
       </c>
       <c r="I215" t="n">
-        <v>3864.998779296875</v>
+        <v>3864.99853515625</v>
       </c>
       <c r="J215" t="n">
         <v>364.8500061035156</v>
@@ -7346,7 +7346,7 @@
         <v>2196.949951171875</v>
       </c>
       <c r="F216" t="n">
-        <v>888.90625</v>
+        <v>888.9061889648438</v>
       </c>
       <c r="G216" t="n">
         <v>71.41000366210938</v>
@@ -7378,13 +7378,13 @@
         <v>2110.14990234375</v>
       </c>
       <c r="F217" t="n">
-        <v>869.7440185546875</v>
+        <v>869.7440795898438</v>
       </c>
       <c r="G217" t="n">
         <v>69.02999877929688</v>
       </c>
       <c r="H217" t="n">
-        <v>567.2341918945312</v>
+        <v>567.2342529296875</v>
       </c>
       <c r="I217" t="n">
         <v>3804.431640625</v>
@@ -7416,7 +7416,7 @@
         <v>67.19999694824219</v>
       </c>
       <c r="H218" t="n">
-        <v>564.2860107421875</v>
+        <v>564.2859497070312</v>
       </c>
       <c r="I218" t="n">
         <v>3748.308837890625</v>
@@ -7436,13 +7436,13 @@
         <v>3116.25</v>
       </c>
       <c r="D219" t="n">
-        <v>4012.499267578125</v>
+        <v>4012.49951171875</v>
       </c>
       <c r="E219" t="n">
         <v>2085.39990234375</v>
       </c>
       <c r="F219" t="n">
-        <v>871.2633056640625</v>
+        <v>871.2633666992188</v>
       </c>
       <c r="G219" t="n">
         <v>67.30000305175781</v>
@@ -7483,7 +7483,7 @@
         <v>554.3112182617188</v>
       </c>
       <c r="I220" t="n">
-        <v>3655.9853515625</v>
+        <v>3655.985595703125</v>
       </c>
       <c r="J220" t="n">
         <v>381.1000061035156</v>
@@ -7500,7 +7500,7 @@
         <v>2875.14990234375</v>
       </c>
       <c r="D221" t="n">
-        <v>4026.67333984375</v>
+        <v>4026.673583984375</v>
       </c>
       <c r="E221" t="n">
         <v>1986.099975585938</v>
@@ -7512,7 +7512,7 @@
         <v>65.69999694824219</v>
       </c>
       <c r="H221" t="n">
-        <v>556.0801391601562</v>
+        <v>556.0802001953125</v>
       </c>
       <c r="I221" t="n">
         <v>3666.37109375</v>
@@ -7532,7 +7532,7 @@
         <v>2856.85009765625</v>
       </c>
       <c r="D222" t="n">
-        <v>3896.210693359375</v>
+        <v>3896.2109375</v>
       </c>
       <c r="E222" t="n">
         <v>2036.5</v>
@@ -7576,10 +7576,10 @@
         <v>64.98999786376953</v>
       </c>
       <c r="H223" t="n">
-        <v>548.21826171875</v>
+        <v>548.2182006835938</v>
       </c>
       <c r="I223" t="n">
-        <v>3725.8896484375</v>
+        <v>3725.889404296875</v>
       </c>
       <c r="J223" t="n">
         <v>367.25</v>
@@ -7602,7 +7602,7 @@
         <v>2023.949951171875</v>
       </c>
       <c r="F224" t="n">
-        <v>862.1478271484375</v>
+        <v>862.1477661132812</v>
       </c>
       <c r="G224" t="n">
         <v>64.79000091552734</v>
@@ -7611,7 +7611,7 @@
         <v>554.90087890625</v>
       </c>
       <c r="I224" t="n">
-        <v>3659.730224609375</v>
+        <v>3659.73046875</v>
       </c>
       <c r="J224" t="n">
         <v>385.6000061035156</v>
@@ -7640,10 +7640,10 @@
         <v>65.65000152587891</v>
       </c>
       <c r="H225" t="n">
-        <v>558.6351928710938</v>
+        <v>558.63525390625</v>
       </c>
       <c r="I225" t="n">
-        <v>3600.211669921875</v>
+        <v>3600.2119140625</v>
       </c>
       <c r="J225" t="n">
         <v>404.8500061035156</v>
@@ -7660,7 +7660,7 @@
         <v>2782.699951171875</v>
       </c>
       <c r="D226" t="n">
-        <v>3871.356201171875</v>
+        <v>3871.35595703125</v>
       </c>
       <c r="E226" t="n">
         <v>2012.050048828125</v>
@@ -7698,7 +7698,7 @@
         <v>2116.5</v>
       </c>
       <c r="F227" t="n">
-        <v>863.5200805664062</v>
+        <v>863.52001953125</v>
       </c>
       <c r="G227" t="n">
         <v>66.55000305175781</v>
@@ -7724,13 +7724,13 @@
         <v>2834.25</v>
       </c>
       <c r="D228" t="n">
-        <v>3907.989990234375</v>
+        <v>3907.98974609375</v>
       </c>
       <c r="E228" t="n">
         <v>2113.550048828125</v>
       </c>
       <c r="F228" t="n">
-        <v>872.8805541992188</v>
+        <v>872.880615234375</v>
       </c>
       <c r="G228" t="n">
         <v>66.08000183105469</v>
@@ -7762,16 +7762,16 @@
         <v>2062.300048828125</v>
       </c>
       <c r="F229" t="n">
-        <v>870.5772705078125</v>
+        <v>870.5772094726562</v>
       </c>
       <c r="G229" t="n">
         <v>65.05999755859375</v>
       </c>
       <c r="H229" t="n">
-        <v>567.97119140625</v>
+        <v>567.9712524414062</v>
       </c>
       <c r="I229" t="n">
-        <v>3574.746826171875</v>
+        <v>3574.74658203125</v>
       </c>
       <c r="J229" t="n">
         <v>410.9500122070312</v>
@@ -7788,13 +7788,13 @@
         <v>2716.14990234375</v>
       </c>
       <c r="D230" t="n">
-        <v>3923.26171875</v>
+        <v>3923.261474609375</v>
       </c>
       <c r="E230" t="n">
         <v>2042.099975585938</v>
       </c>
       <c r="F230" t="n">
-        <v>875.428955078125</v>
+        <v>875.4290161132812</v>
       </c>
       <c r="G230" t="n">
         <v>64.61000061035156</v>
@@ -7826,16 +7826,16 @@
         <v>2063.300048828125</v>
       </c>
       <c r="F231" t="n">
-        <v>878.6635131835938</v>
+        <v>878.66357421875</v>
       </c>
       <c r="G231" t="n">
         <v>64.95999908447266</v>
       </c>
       <c r="H231" t="n">
-        <v>570.9685668945312</v>
+        <v>570.968505859375</v>
       </c>
       <c r="I231" t="n">
-        <v>3691.78662109375</v>
+        <v>3691.786376953125</v>
       </c>
       <c r="J231" t="n">
         <v>373.3500061035156</v>
@@ -7852,13 +7852,13 @@
         <v>2741.550048828125</v>
       </c>
       <c r="D232" t="n">
-        <v>3992.036865234375</v>
+        <v>3992.03662109375</v>
       </c>
       <c r="E232" t="n">
         <v>2032.699951171875</v>
       </c>
       <c r="F232" t="n">
-        <v>869.1559448242188</v>
+        <v>869.156005859375</v>
       </c>
       <c r="G232" t="n">
         <v>64.88999938964844</v>
@@ -7867,7 +7867,7 @@
         <v>571.9513549804688</v>
       </c>
       <c r="I232" t="n">
-        <v>3725.24072265625</v>
+        <v>3725.240478515625</v>
       </c>
       <c r="J232" t="n">
         <v>357.25</v>
@@ -7884,7 +7884,7 @@
         <v>2691.39990234375</v>
       </c>
       <c r="D233" t="n">
-        <v>4017.690185546875</v>
+        <v>4017.68994140625</v>
       </c>
       <c r="E233" t="n">
         <v>2052.699951171875</v>
@@ -7899,7 +7899,7 @@
         <v>577.60205078125</v>
       </c>
       <c r="I233" t="n">
-        <v>3689.839111328125</v>
+        <v>3689.8388671875</v>
       </c>
       <c r="J233" t="n">
         <v>339.3999938964844</v>
@@ -7928,10 +7928,10 @@
         <v>63.20999908447266</v>
       </c>
       <c r="H234" t="n">
-        <v>570.9685668945312</v>
+        <v>570.968505859375</v>
       </c>
       <c r="I234" t="n">
-        <v>3616.340087890625</v>
+        <v>3616.33984375</v>
       </c>
       <c r="J234" t="n">
         <v>330.8500061035156</v>
@@ -7948,7 +7948,7 @@
         <v>2687.85009765625</v>
       </c>
       <c r="D235" t="n">
-        <v>4009.405029296875</v>
+        <v>4009.40478515625</v>
       </c>
       <c r="E235" t="n">
         <v>2024.050048828125</v>
@@ -7980,7 +7980,7 @@
         <v>2652.800048828125</v>
       </c>
       <c r="D236" t="n">
-        <v>4052.825927734375</v>
+        <v>4052.826171875</v>
       </c>
       <c r="E236" t="n">
         <v>2021.400024414062</v>
@@ -7995,7 +7995,7 @@
         <v>574.4572143554688</v>
       </c>
       <c r="I236" t="n">
-        <v>3581.387939453125</v>
+        <v>3581.3876953125</v>
       </c>
       <c r="J236" t="n">
         <v>358.2999877929688</v>
@@ -8012,13 +8012,13 @@
         <v>2672.449951171875</v>
       </c>
       <c r="D237" t="n">
-        <v>4048.43408203125</v>
+        <v>4048.434326171875</v>
       </c>
       <c r="E237" t="n">
         <v>2018.150024414062</v>
       </c>
       <c r="F237" t="n">
-        <v>882.6820678710938</v>
+        <v>882.68212890625</v>
       </c>
       <c r="G237" t="n">
         <v>63.86999893188477</v>
@@ -8027,7 +8027,7 @@
         <v>572.1478881835938</v>
       </c>
       <c r="I237" t="n">
-        <v>3513.03173828125</v>
+        <v>3513.031494140625</v>
       </c>
       <c r="J237" t="n">
         <v>376.2000122070312</v>
@@ -8056,7 +8056,7 @@
         <v>63.09000015258789</v>
       </c>
       <c r="H238" t="n">
-        <v>551.510498046875</v>
+        <v>551.5104370117188</v>
       </c>
       <c r="I238" t="n">
         <v>3545.886474609375</v>
@@ -8076,7 +8076,7 @@
         <v>2643.5</v>
       </c>
       <c r="D239" t="n">
-        <v>3973.570068359375</v>
+        <v>3973.5703125</v>
       </c>
       <c r="E239" t="n">
         <v>2044.25</v>
@@ -8091,7 +8091,7 @@
         <v>546.4494018554688</v>
       </c>
       <c r="I239" t="n">
-        <v>3579.8896484375</v>
+        <v>3579.889892578125</v>
       </c>
       <c r="J239" t="n">
         <v>363.4500122070312</v>
@@ -8108,7 +8108,7 @@
         <v>2679.300048828125</v>
       </c>
       <c r="D240" t="n">
-        <v>4067.898681640625</v>
+        <v>4067.8984375</v>
       </c>
       <c r="E240" t="n">
         <v>2062.050048828125</v>
@@ -8120,7 +8120,7 @@
         <v>61.15999984741211</v>
       </c>
       <c r="H240" t="n">
-        <v>554.1146850585938</v>
+        <v>554.1146240234375</v>
       </c>
       <c r="I240" t="n">
         <v>3613.49365234375</v>
@@ -8152,10 +8152,10 @@
         <v>61.15000152587891</v>
       </c>
       <c r="H241" t="n">
-        <v>550.429443359375</v>
+        <v>550.4293823242188</v>
       </c>
       <c r="I241" t="n">
-        <v>3609.249267578125</v>
+        <v>3609.24951171875</v>
       </c>
       <c r="J241" t="n">
         <v>359.1000061035156</v>
@@ -8204,22 +8204,22 @@
         <v>2518</v>
       </c>
       <c r="D243" t="n">
-        <v>3861.524169921875</v>
+        <v>3861.52392578125</v>
       </c>
       <c r="E243" t="n">
         <v>1980.75</v>
       </c>
       <c r="F243" t="n">
-        <v>839.8983154296875</v>
+        <v>839.8982543945312</v>
       </c>
       <c r="G243" t="n">
         <v>55.20000076293945</v>
       </c>
       <c r="H243" t="n">
-        <v>523.6499633789062</v>
+        <v>523.64990234375</v>
       </c>
       <c r="I243" t="n">
-        <v>3546.685546875</v>
+        <v>3546.685302734375</v>
       </c>
       <c r="J243" t="n">
         <v>331.6499938964844</v>
@@ -8268,7 +8268,7 @@
         <v>2466.14990234375</v>
       </c>
       <c r="D245" t="n">
-        <v>3710</v>
+        <v>3709.999755859375</v>
       </c>
       <c r="E245" t="n">
         <v>1876.849975585938</v>
@@ -8306,13 +8306,13 @@
         <v>1908.699951171875</v>
       </c>
       <c r="F246" t="n">
-        <v>800.9369506835938</v>
+        <v>800.9368896484375</v>
       </c>
       <c r="G246" t="n">
         <v>57.81000137329102</v>
       </c>
       <c r="H246" t="n">
-        <v>514.2647705078125</v>
+        <v>514.2648315429688</v>
       </c>
       <c r="I246" t="n">
         <v>3348.307373046875</v>
@@ -8344,10 +8344,10 @@
         <v>60.70000076293945</v>
       </c>
       <c r="H247" t="n">
-        <v>509.4494018554688</v>
+        <v>509.4494323730469</v>
       </c>
       <c r="I247" t="n">
-        <v>3600.861083984375</v>
+        <v>3600.861328125</v>
       </c>
       <c r="J247" t="n">
         <v>331.1000061035156</v>
@@ -8370,13 +8370,13 @@
         <v>1910.25</v>
       </c>
       <c r="F248" t="n">
-        <v>803.2892456054688</v>
+        <v>803.289306640625</v>
       </c>
       <c r="G248" t="n">
         <v>60.90000152587891</v>
       </c>
       <c r="H248" t="n">
-        <v>513.7243041992188</v>
+        <v>513.724365234375</v>
       </c>
       <c r="I248" t="n">
         <v>3787.804443359375</v>
@@ -8411,7 +8411,7 @@
         <v>515.0509643554688</v>
       </c>
       <c r="I249" t="n">
-        <v>3687.791748046875</v>
+        <v>3687.79150390625</v>
       </c>
       <c r="J249" t="n">
         <v>345.7999877929688</v>
@@ -8434,16 +8434,16 @@
         <v>1888.699951171875</v>
       </c>
       <c r="F250" t="n">
-        <v>805.9847412109375</v>
+        <v>805.9846801757812</v>
       </c>
       <c r="G250" t="n">
         <v>59.63000106811523</v>
       </c>
       <c r="H250" t="n">
-        <v>517.4096069335938</v>
+        <v>517.4095458984375</v>
       </c>
       <c r="I250" t="n">
-        <v>3545.736572265625</v>
+        <v>3545.73681640625</v>
       </c>
       <c r="J250" t="n">
         <v>339.75</v>
@@ -8472,7 +8472,7 @@
         <v>58.95000076293945</v>
       </c>
       <c r="H251" t="n">
-        <v>521.78271484375</v>
+        <v>521.7827758789062</v>
       </c>
       <c r="I251" t="n">
         <v>3593.720703125</v>
@@ -8507,7 +8507,7 @@
         <v>509.8916320800781</v>
       </c>
       <c r="I252" t="n">
-        <v>3472.537353515625</v>
+        <v>3472.537109375</v>
       </c>
       <c r="J252" t="n">
         <v>333.7999877929688</v>
@@ -8536,7 +8536,7 @@
         <v>57.75</v>
       </c>
       <c r="H253" t="n">
-        <v>515.6897583007812</v>
+        <v>515.689697265625</v>
       </c>
       <c r="I253" t="n">
         <v>3628.72265625</v>
@@ -8556,7 +8556,7 @@
         <v>2523.35009765625</v>
       </c>
       <c r="D254" t="n">
-        <v>3817.3046875</v>
+        <v>3817.304443359375</v>
       </c>
       <c r="E254" t="n">
         <v>1838.25</v>
@@ -8568,10 +8568,10 @@
         <v>56.68000030517578</v>
       </c>
       <c r="H254" t="n">
-        <v>510.8252563476562</v>
+        <v>510.8251953125</v>
       </c>
       <c r="I254" t="n">
-        <v>3550.530029296875</v>
+        <v>3550.52978515625</v>
       </c>
       <c r="J254" t="n">
         <v>318.5</v>
@@ -8600,7 +8600,7 @@
         <v>57.54000091552734</v>
       </c>
       <c r="H255" t="n">
-        <v>515.6897583007812</v>
+        <v>515.689697265625</v>
       </c>
       <c r="I255" t="n">
         <v>3624.029296875</v>
@@ -8620,7 +8620,7 @@
         <v>2652</v>
       </c>
       <c r="D256" t="n">
-        <v>3640.2763671875</v>
+        <v>3640.276611328125</v>
       </c>
       <c r="E256" t="n">
         <v>1895.199951171875</v>
@@ -8684,7 +8684,7 @@
         <v>2624</v>
       </c>
       <c r="D258" t="n">
-        <v>3640.576171875</v>
+        <v>3640.575927734375</v>
       </c>
       <c r="E258" t="n">
         <v>1889.849975585938</v>
@@ -8696,7 +8696,7 @@
         <v>54.72999954223633</v>
       </c>
       <c r="H258" t="n">
-        <v>501.5875244140625</v>
+        <v>501.5875549316406</v>
       </c>
       <c r="I258" t="n">
         <v>3644.0517578125</v>
@@ -8722,7 +8722,7 @@
         <v>1915.650024414062</v>
       </c>
       <c r="F259" t="n">
-        <v>778.8833618164062</v>
+        <v>778.88330078125</v>
       </c>
       <c r="G259" t="n">
         <v>55.7400016784668</v>
@@ -8731,7 +8731,7 @@
         <v>509.6950988769531</v>
       </c>
       <c r="I259" t="n">
-        <v>3710.011474609375</v>
+        <v>3710.01123046875</v>
       </c>
       <c r="J259" t="n">
         <v>304.5499877929688</v>
@@ -8754,16 +8754,16 @@
         <v>2089.800048828125</v>
       </c>
       <c r="F260" t="n">
-        <v>771.4342041015625</v>
+        <v>771.4341430664062</v>
       </c>
       <c r="G260" t="n">
         <v>54.59000015258789</v>
       </c>
       <c r="H260" t="n">
-        <v>508.0735778808594</v>
+        <v>508.0735473632812</v>
       </c>
       <c r="I260" t="n">
-        <v>3725.589599609375</v>
+        <v>3725.58984375</v>
       </c>
       <c r="J260" t="n">
         <v>296.9500122070312</v>
@@ -8780,13 +8780,13 @@
         <v>2725.050048828125</v>
       </c>
       <c r="D261" t="n">
-        <v>3632.740478515625</v>
+        <v>3632.740234375</v>
       </c>
       <c r="E261" t="n">
         <v>2166.14990234375</v>
       </c>
       <c r="F261" t="n">
-        <v>769.1798095703125</v>
+        <v>769.1797485351562</v>
       </c>
       <c r="G261" t="n">
         <v>56.38999938964844</v>
@@ -8795,7 +8795,7 @@
         <v>508.56494140625</v>
       </c>
       <c r="I261" t="n">
-        <v>3844.7265625</v>
+        <v>3844.726318359375</v>
       </c>
       <c r="J261" t="n">
         <v>296.7999877929688</v>
@@ -8824,7 +8824,7 @@
         <v>55.7400016784668</v>
       </c>
       <c r="H262" t="n">
-        <v>511.4639892578125</v>
+        <v>511.4640502929688</v>
       </c>
       <c r="I262" t="n">
         <v>3800.237548828125</v>
@@ -8882,13 +8882,13 @@
         <v>1975.599975585938</v>
       </c>
       <c r="F264" t="n">
-        <v>759.0841674804688</v>
+        <v>759.0841064453125</v>
       </c>
       <c r="G264" t="n">
         <v>55.0099983215332</v>
       </c>
       <c r="H264" t="n">
-        <v>508.8106079101562</v>
+        <v>508.8106384277344</v>
       </c>
       <c r="I264" t="n">
         <v>3913.5322265625</v>
@@ -8946,16 +8946,16 @@
         <v>1916.800048828125</v>
       </c>
       <c r="F266" t="n">
-        <v>746.0969848632812</v>
+        <v>746.0970458984375</v>
       </c>
       <c r="G266" t="n">
         <v>54.93000030517578</v>
       </c>
       <c r="H266" t="n">
-        <v>490.3352661132812</v>
+        <v>490.3352355957031</v>
       </c>
       <c r="I266" t="n">
-        <v>3886.419189453125</v>
+        <v>3886.41943359375</v>
       </c>
       <c r="J266" t="n">
         <v>284</v>
@@ -8987,7 +8987,7 @@
         <v>452.2543029785156</v>
       </c>
       <c r="I267" t="n">
-        <v>3654.98681640625</v>
+        <v>3654.986572265625</v>
       </c>
       <c r="J267" t="n">
         <v>269.7999877929688</v>
@@ -9010,7 +9010,7 @@
         <v>1486.25</v>
       </c>
       <c r="F268" t="n">
-        <v>585.10595703125</v>
+        <v>585.1058959960938</v>
       </c>
       <c r="G268" t="n">
         <v>49.59000015258789</v>
@@ -9019,7 +9019,7 @@
         <v>373.8812255859375</v>
       </c>
       <c r="I268" t="n">
-        <v>2923.989501953125</v>
+        <v>2923.9892578125</v>
       </c>
       <c r="J268" t="n">
         <v>256.3500061035156</v>
@@ -9036,19 +9036,19 @@
         <v>1708.199951171875</v>
       </c>
       <c r="D269" t="n">
-        <v>2887.59619140625</v>
+        <v>2887.596435546875</v>
       </c>
       <c r="E269" t="n">
         <v>1189</v>
       </c>
       <c r="F269" t="n">
-        <v>585.1548461914062</v>
+        <v>585.1549072265625</v>
       </c>
       <c r="G269" t="n">
         <v>47.11000061035156</v>
       </c>
       <c r="H269" t="n">
-        <v>380.8095397949219</v>
+        <v>380.8095092773438</v>
       </c>
       <c r="I269" t="n">
         <v>2339.191650390625</v>
@@ -9068,7 +9068,7 @@
         <v>1774</v>
       </c>
       <c r="D270" t="n">
-        <v>2968.498779296875</v>
+        <v>2968.49853515625</v>
       </c>
       <c r="E270" t="n">
         <v>1223.900024414062</v>
@@ -9115,7 +9115,7 @@
         <v>328.3315124511719</v>
       </c>
       <c r="I271" t="n">
-        <v>1894.801147460938</v>
+        <v>1894.801025390625</v>
       </c>
       <c r="J271" t="n">
         <v>235.6999969482422</v>
@@ -9132,13 +9132,13 @@
         <v>1551.150024414062</v>
       </c>
       <c r="D272" t="n">
-        <v>1562.4072265625</v>
+        <v>1562.407348632812</v>
       </c>
       <c r="E272" t="n">
         <v>1039.849975585938</v>
       </c>
       <c r="F272" t="n">
-        <v>453.2745056152344</v>
+        <v>453.2745361328125</v>
       </c>
       <c r="G272" t="n">
         <v>40.40999984741211</v>
@@ -9147,7 +9147,7 @@
         <v>346.4629516601562</v>
       </c>
       <c r="I272" t="n">
-        <v>1705.360961914062</v>
+        <v>1705.36083984375</v>
       </c>
       <c r="J272" t="n">
         <v>223.9499969482422</v>
@@ -9179,7 +9179,7 @@
         <v>367.1495056152344</v>
       </c>
       <c r="I273" t="n">
-        <v>1620.127807617188</v>
+        <v>1620.127685546875</v>
       </c>
       <c r="J273" t="n">
         <v>212.75</v>
@@ -9228,13 +9228,13 @@
         <v>1252.199951171875</v>
       </c>
       <c r="D275" t="n">
-        <v>1799.675415039062</v>
+        <v>1799.675537109375</v>
       </c>
       <c r="E275" t="n">
         <v>844.6500244140625</v>
       </c>
       <c r="F275" t="n">
-        <v>542.1749877929688</v>
+        <v>542.1749267578125</v>
       </c>
       <c r="G275" t="n">
         <v>34.65000152587891</v>
@@ -9243,7 +9243,7 @@
         <v>377.4190673828125</v>
       </c>
       <c r="I275" t="n">
-        <v>1462.194458007812</v>
+        <v>1462.194580078125</v>
       </c>
       <c r="J275" t="n">
         <v>216.8999938964844</v>
@@ -9272,7 +9272,7 @@
         <v>36.38000106811523</v>
       </c>
       <c r="H276" t="n">
-        <v>378.0086975097656</v>
+        <v>378.0087280273438</v>
       </c>
       <c r="I276" t="n">
         <v>1389.0947265625</v>
@@ -9324,19 +9324,19 @@
         <v>1186.650024414062</v>
       </c>
       <c r="D278" t="n">
-        <v>1843.595458984375</v>
+        <v>1843.595581054688</v>
       </c>
       <c r="E278" t="n">
         <v>724.25</v>
       </c>
       <c r="F278" t="n">
-        <v>572.3638916015625</v>
+        <v>572.3638305664062</v>
       </c>
       <c r="G278" t="n">
         <v>32.84000015258789</v>
       </c>
       <c r="H278" t="n">
-        <v>354.5704956054688</v>
+        <v>354.5705261230469</v>
       </c>
       <c r="I278" t="n">
         <v>1253.680419921875</v>
@@ -9356,7 +9356,7 @@
         <v>1127.349975585938</v>
       </c>
       <c r="D279" t="n">
-        <v>1714.530395507812</v>
+        <v>1714.530517578125</v>
       </c>
       <c r="E279" t="n">
         <v>688.0499877929688</v>
@@ -9499,7 +9499,7 @@
         <v>347.1999816894531</v>
       </c>
       <c r="I283" t="n">
-        <v>970.1692504882812</v>
+        <v>970.1693115234375</v>
       </c>
       <c r="J283" t="n">
         <v>217.1999969482422</v>
@@ -9516,7 +9516,7 @@
         <v>874.4000244140625</v>
       </c>
       <c r="D284" t="n">
-        <v>1618.505249023438</v>
+        <v>1618.505126953125</v>
       </c>
       <c r="E284" t="n">
         <v>597.25</v>
@@ -9528,7 +9528,7 @@
         <v>32.58000183105469</v>
       </c>
       <c r="H284" t="n">
-        <v>346.3647155761719</v>
+        <v>346.3646850585938</v>
       </c>
       <c r="I284" t="n">
         <v>921.6858520507812</v>
@@ -9554,13 +9554,13 @@
         <v>567.4000244140625</v>
       </c>
       <c r="F285" t="n">
-        <v>571.6287231445312</v>
+        <v>571.6287841796875</v>
       </c>
       <c r="G285" t="n">
         <v>34.20000076293945</v>
       </c>
       <c r="H285" t="n">
-        <v>346.7577514648438</v>
+        <v>346.7577819824219</v>
       </c>
       <c r="I285" t="n">
         <v>875.5989990234375</v>
@@ -9644,7 +9644,7 @@
         <v>712.2999877929688</v>
       </c>
       <c r="D288" t="n">
-        <v>1313.2607421875</v>
+        <v>1313.260620117188</v>
       </c>
       <c r="E288" t="n">
         <v>486.5</v>
@@ -9656,7 +9656,7 @@
         <v>29.32999992370605</v>
       </c>
       <c r="H288" t="n">
-        <v>339.2890014648438</v>
+        <v>339.2889709472656</v>
       </c>
       <c r="I288" t="n">
         <v>750.7702026367188</v>
@@ -9691,7 +9691,7 @@
         <v>324.2040100097656</v>
       </c>
       <c r="I289" t="n">
-        <v>713.271728515625</v>
+        <v>713.2716674804688</v>
       </c>
       <c r="J289" t="n">
         <v>181.1000061035156</v>
@@ -9708,7 +9708,7 @@
         <v>642.9000244140625</v>
       </c>
       <c r="D290" t="n">
-        <v>1361.373046875</v>
+        <v>1361.373168945312</v>
       </c>
       <c r="E290" t="n">
         <v>485.2999877929688</v>
@@ -9740,7 +9740,7 @@
         <v>675</v>
       </c>
       <c r="D291" t="n">
-        <v>1561.459106445312</v>
+        <v>1561.458984375</v>
       </c>
       <c r="E291" t="n">
         <v>509.5499877929688</v>
@@ -9752,10 +9752,10 @@
         <v>30.71999931335449</v>
       </c>
       <c r="H291" t="n">
-        <v>347.4948120117188</v>
+        <v>347.4947814941406</v>
       </c>
       <c r="I291" t="n">
-        <v>710.6752319335938</v>
+        <v>710.67529296875</v>
       </c>
       <c r="J291" t="n">
         <v>199.6499938964844</v>
@@ -9784,7 +9784,7 @@
         <v>32.25</v>
       </c>
       <c r="H292" t="n">
-        <v>364.2996215820312</v>
+        <v>364.2995910644531</v>
       </c>
       <c r="I292" t="n">
         <v>743.080810546875</v>
@@ -9804,7 +9804,7 @@
         <v>744.1500244140625</v>
       </c>
       <c r="D293" t="n">
-        <v>1876.08642578125</v>
+        <v>1876.086547851562</v>
       </c>
       <c r="E293" t="n">
         <v>561.75</v>
@@ -9816,10 +9816,10 @@
         <v>33.86000061035156</v>
       </c>
       <c r="H293" t="n">
-        <v>385.0843811035156</v>
+        <v>385.0844116210938</v>
       </c>
       <c r="I293" t="n">
-        <v>780.2297973632812</v>
+        <v>780.2298583984375</v>
       </c>
       <c r="J293" t="n">
         <v>220</v>
@@ -9836,7 +9836,7 @@
         <v>781.3499755859375</v>
       </c>
       <c r="D294" t="n">
-        <v>1979.298706054688</v>
+        <v>1979.298583984375</v>
       </c>
       <c r="E294" t="n">
         <v>589.7999877929688</v>
@@ -9848,7 +9848,7 @@
         <v>35.54999923706055</v>
       </c>
       <c r="H294" t="n">
-        <v>378.8440551757812</v>
+        <v>378.8440246582031</v>
       </c>
       <c r="I294" t="n">
         <v>819.2263793945312</v>
@@ -9883,7 +9883,7 @@
         <v>385.330078125</v>
       </c>
       <c r="I295" t="n">
-        <v>860.1701049804688</v>
+        <v>860.170166015625</v>
       </c>
       <c r="J295" t="n">
         <v>242.1999969482422</v>
@@ -9932,7 +9932,7 @@
         <v>904.4500122070312</v>
       </c>
       <c r="D297" t="n">
-        <v>1892.756103515625</v>
+        <v>1892.756225585938</v>
       </c>
       <c r="E297" t="n">
         <v>682.7000122070312</v>
@@ -9944,7 +9944,7 @@
         <v>40.97999954223633</v>
       </c>
       <c r="H297" t="n">
-        <v>371.8175048828125</v>
+        <v>371.8174743652344</v>
       </c>
       <c r="I297" t="n">
         <v>948.29931640625</v>
@@ -9964,7 +9964,7 @@
         <v>949.6500244140625</v>
       </c>
       <c r="D298" t="n">
-        <v>1870.995849609375</v>
+        <v>1870.995727539062</v>
       </c>
       <c r="E298" t="n">
         <v>716.7999877929688</v>
@@ -10011,7 +10011,7 @@
         <v>347.2982482910156</v>
       </c>
       <c r="I299" t="n">
-        <v>945.9026489257812</v>
+        <v>945.902587890625</v>
       </c>
       <c r="J299" t="n">
         <v>211.1000061035156</v>
@@ -10028,13 +10028,13 @@
         <v>928.3499755859375</v>
       </c>
       <c r="D300" t="n">
-        <v>1835.660034179688</v>
+        <v>1835.66015625</v>
       </c>
       <c r="E300" t="n">
         <v>740.4000244140625</v>
       </c>
       <c r="F300" t="n">
-        <v>665.8709716796875</v>
+        <v>665.8710327148438</v>
       </c>
       <c r="G300" t="n">
         <v>40.36000061035156</v>
@@ -10043,7 +10043,7 @@
         <v>358.8453674316406</v>
       </c>
       <c r="I300" t="n">
-        <v>918.5900268554688</v>
+        <v>918.590087890625</v>
       </c>
       <c r="J300" t="n">
         <v>213.3000030517578</v>
@@ -10060,7 +10060,7 @@
         <v>973.7000122070312</v>
       </c>
       <c r="D301" t="n">
-        <v>1840.451416015625</v>
+        <v>1840.451293945312</v>
       </c>
       <c r="E301" t="n">
         <v>777.4000244140625</v>
@@ -10072,10 +10072,10 @@
         <v>39.7400016784668</v>
       </c>
       <c r="H301" t="n">
-        <v>372.2596740722656</v>
+        <v>372.2597045898438</v>
       </c>
       <c r="I301" t="n">
-        <v>887.1832275390625</v>
+        <v>887.1831665039062</v>
       </c>
       <c r="J301" t="n">
         <v>209.1000061035156</v>
@@ -10104,10 +10104,10 @@
         <v>39.9900016784668</v>
       </c>
       <c r="H302" t="n">
-        <v>371.915771484375</v>
+        <v>371.9157409667969</v>
       </c>
       <c r="I302" t="n">
-        <v>896.5203857421875</v>
+        <v>896.5203247070312</v>
       </c>
       <c r="J302" t="n">
         <v>206.6499938964844</v>
@@ -10136,10 +10136,10 @@
         <v>38.04000091552734</v>
       </c>
       <c r="H303" t="n">
-        <v>359.091064453125</v>
+        <v>359.0910339355469</v>
       </c>
       <c r="I303" t="n">
-        <v>851.7318725585938</v>
+        <v>851.7318115234375</v>
       </c>
       <c r="J303" t="n">
         <v>199.3500061035156</v>
@@ -10156,13 +10156,13 @@
         <v>1006.099975585938</v>
       </c>
       <c r="D304" t="n">
-        <v>1820.936767578125</v>
+        <v>1820.936889648438</v>
       </c>
       <c r="E304" t="n">
         <v>891.0499877929688</v>
       </c>
       <c r="F304" t="n">
-        <v>651.6097412109375</v>
+        <v>651.6096801757812</v>
       </c>
       <c r="G304" t="n">
         <v>39.93999862670898</v>
@@ -10235,7 +10235,7 @@
         <v>365.7245178222656</v>
       </c>
       <c r="I306" t="n">
-        <v>980.7048950195312</v>
+        <v>980.704833984375</v>
       </c>
       <c r="J306" t="n">
         <v>202.1000061035156</v>
@@ -10284,7 +10284,7 @@
         <v>1068.400024414062</v>
       </c>
       <c r="D308" t="n">
-        <v>1719.920776367188</v>
+        <v>1719.920654296875</v>
       </c>
       <c r="E308" t="n">
         <v>984.9000244140625</v>
@@ -10296,10 +10296,10 @@
         <v>36.59999847412109</v>
       </c>
       <c r="H308" t="n">
-        <v>363.6116638183594</v>
+        <v>363.6116333007812</v>
       </c>
       <c r="I308" t="n">
-        <v>956.5379638671875</v>
+        <v>956.5380249023438</v>
       </c>
       <c r="J308" t="n">
         <v>182.9499969482422</v>
@@ -10328,7 +10328,7 @@
         <v>34.77000045776367</v>
       </c>
       <c r="H309" t="n">
-        <v>352.7524719238281</v>
+        <v>352.75244140625</v>
       </c>
       <c r="I309" t="n">
         <v>908.70361328125</v>
@@ -10380,7 +10380,7 @@
         <v>993.0499877929688</v>
       </c>
       <c r="D311" t="n">
-        <v>1747.270751953125</v>
+        <v>1747.270874023438</v>
       </c>
       <c r="E311" t="n">
         <v>881.1500244140625</v>
@@ -10392,7 +10392,7 @@
         <v>38.31999969482422</v>
       </c>
       <c r="H311" t="n">
-        <v>359.2384643554688</v>
+        <v>359.2384948730469</v>
       </c>
       <c r="I311" t="n">
         <v>866.5614013671875</v>
@@ -10424,7 +10424,7 @@
         <v>38.11000061035156</v>
       </c>
       <c r="H312" t="n">
-        <v>368.3287658691406</v>
+        <v>368.3287353515625</v>
       </c>
       <c r="I312" t="n">
         <v>844.1920776367188</v>
@@ -10459,7 +10459,7 @@
         <v>373.3898620605469</v>
       </c>
       <c r="I313" t="n">
-        <v>820.82421875</v>
+        <v>820.8241577148438</v>
       </c>
       <c r="J313" t="n">
         <v>185.1499938964844</v>
@@ -10482,7 +10482,7 @@
         <v>856.3499755859375</v>
       </c>
       <c r="F314" t="n">
-        <v>628.8699951171875</v>
+        <v>628.8699340820312</v>
       </c>
       <c r="G314" t="n">
         <v>38.43999862670898</v>
@@ -10508,19 +10508,19 @@
         <v>1000.849975585938</v>
       </c>
       <c r="D315" t="n">
-        <v>1793.985961914062</v>
+        <v>1793.98583984375</v>
       </c>
       <c r="E315" t="n">
         <v>899.1500244140625</v>
       </c>
       <c r="F315" t="n">
-        <v>639.063720703125</v>
+        <v>639.0636596679688</v>
       </c>
       <c r="G315" t="n">
         <v>38.79999923706055</v>
       </c>
       <c r="H315" t="n">
-        <v>377.7138977050781</v>
+        <v>377.7138671875</v>
       </c>
       <c r="I315" t="n">
         <v>904.9088134765625</v>
@@ -10540,7 +10540,7 @@
         <v>1050.849975585938</v>
       </c>
       <c r="D316" t="n">
-        <v>1799.875244140625</v>
+        <v>1799.875122070312</v>
       </c>
       <c r="E316" t="n">
         <v>944.0999755859375</v>
@@ -10587,7 +10587,7 @@
         <v>389.2118835449219</v>
       </c>
       <c r="I317" t="n">
-        <v>937.56396484375</v>
+        <v>937.5640258789062</v>
       </c>
       <c r="J317" t="n">
         <v>187</v>
@@ -10616,7 +10616,7 @@
         <v>37.83000183105469</v>
       </c>
       <c r="H318" t="n">
-        <v>385.87060546875</v>
+        <v>385.8705749511719</v>
       </c>
       <c r="I318" t="n">
         <v>912.8978881835938</v>
@@ -10668,22 +10668,22 @@
         <v>1032.050048828125</v>
       </c>
       <c r="D320" t="n">
-        <v>1847.58837890625</v>
+        <v>1847.588256835938</v>
       </c>
       <c r="E320" t="n">
         <v>952.25</v>
       </c>
       <c r="F320" t="n">
-        <v>645.483642578125</v>
+        <v>645.4837036132812</v>
       </c>
       <c r="G320" t="n">
         <v>37.66999816894531</v>
       </c>
       <c r="H320" t="n">
-        <v>376.4363403320312</v>
+        <v>376.4363098144531</v>
       </c>
       <c r="I320" t="n">
-        <v>946.7513427734375</v>
+        <v>946.7514038085938</v>
       </c>
       <c r="J320" t="n">
         <v>187.1000061035156</v>
@@ -10706,7 +10706,7 @@
         <v>935.7999877929688</v>
       </c>
       <c r="F321" t="n">
-        <v>645.3367919921875</v>
+        <v>645.3367309570312</v>
       </c>
       <c r="G321" t="n">
         <v>37.45999908447266</v>
@@ -10732,7 +10732,7 @@
         <v>1011.099975585938</v>
       </c>
       <c r="D322" t="n">
-        <v>1839.552856445312</v>
+        <v>1839.552978515625</v>
       </c>
       <c r="E322" t="n">
         <v>933.0499877929688</v>
@@ -10770,7 +10770,7 @@
         <v>916.2000122070312</v>
       </c>
       <c r="F323" t="n">
-        <v>648.4732055664062</v>
+        <v>648.47314453125</v>
       </c>
       <c r="G323" t="n">
         <v>39.84999847412109</v>
@@ -10796,7 +10796,7 @@
         <v>965.0999755859375</v>
       </c>
       <c r="D324" t="n">
-        <v>1798.677368164062</v>
+        <v>1798.67724609375</v>
       </c>
       <c r="E324" t="n">
         <v>887.0999755859375</v>
@@ -10808,7 +10808,7 @@
         <v>40.27999877929688</v>
       </c>
       <c r="H324" t="n">
-        <v>373.7338256835938</v>
+        <v>373.7337951660156</v>
       </c>
       <c r="I324" t="n">
         <v>889.9293823242188</v>
@@ -10828,7 +10828,7 @@
         <v>1012.950012207031</v>
       </c>
       <c r="D325" t="n">
-        <v>1841.25</v>
+        <v>1841.249877929688</v>
       </c>
       <c r="E325" t="n">
         <v>931.1500244140625</v>
@@ -10904,10 +10904,10 @@
         <v>42.83000183105469</v>
       </c>
       <c r="H327" t="n">
-        <v>382.0870666503906</v>
+        <v>382.0870361328125</v>
       </c>
       <c r="I327" t="n">
-        <v>915.8438110351562</v>
+        <v>915.84375</v>
       </c>
       <c r="J327" t="n">
         <v>181.5</v>
@@ -10924,7 +10924,7 @@
         <v>1029.449951171875</v>
       </c>
       <c r="D328" t="n">
-        <v>1921.453979492188</v>
+        <v>1921.453857421875</v>
       </c>
       <c r="E328" t="n">
         <v>951</v>
@@ -10936,7 +10936,7 @@
         <v>44.97000122070312</v>
       </c>
       <c r="H328" t="n">
-        <v>389.6540832519531</v>
+        <v>389.6541137695312</v>
       </c>
       <c r="I328" t="n">
         <v>943.7056274414062</v>
@@ -10962,7 +10962,7 @@
         <v>974.6500244140625</v>
       </c>
       <c r="F329" t="n">
-        <v>667.9783935546875</v>
+        <v>667.9783325195312</v>
       </c>
       <c r="G329" t="n">
         <v>47.18999862670898</v>
@@ -10971,7 +10971,7 @@
         <v>387.5903625488281</v>
       </c>
       <c r="I329" t="n">
-        <v>957.736328125</v>
+        <v>957.7362670898438</v>
       </c>
       <c r="J329" t="n">
         <v>185.6999969482422</v>
@@ -10988,13 +10988,13 @@
         <v>993.0499877929688</v>
       </c>
       <c r="D330" t="n">
-        <v>1835.660034179688</v>
+        <v>1835.66015625</v>
       </c>
       <c r="E330" t="n">
         <v>942.0499877929688</v>
       </c>
       <c r="F330" t="n">
-        <v>656.3634643554688</v>
+        <v>656.363525390625</v>
       </c>
       <c r="G330" t="n">
         <v>46.33000183105469</v>
@@ -11020,7 +11020,7 @@
         <v>1011.549987792969</v>
       </c>
       <c r="D331" t="n">
-        <v>1907.77880859375</v>
+        <v>1907.778930664062</v>
       </c>
       <c r="E331" t="n">
         <v>945.5499877929688</v>
@@ -11052,7 +11052,7 @@
         <v>999</v>
       </c>
       <c r="D332" t="n">
-        <v>1916.8125</v>
+        <v>1916.812377929688</v>
       </c>
       <c r="E332" t="n">
         <v>940.5499877929688</v>
@@ -11064,7 +11064,7 @@
         <v>47.97000122070312</v>
       </c>
       <c r="H332" t="n">
-        <v>393.6342163085938</v>
+        <v>393.6341857910156</v>
       </c>
       <c r="I332" t="n">
         <v>917.54150390625</v>
@@ -11084,13 +11084,13 @@
         <v>949.0499877929688</v>
       </c>
       <c r="D333" t="n">
-        <v>1884.072021484375</v>
+        <v>1884.071899414062</v>
       </c>
       <c r="E333" t="n">
         <v>917.2999877929688</v>
       </c>
       <c r="F333" t="n">
-        <v>671.5069580078125</v>
+        <v>671.5068969726562</v>
       </c>
       <c r="G333" t="n">
         <v>47.7400016784668</v>
@@ -11148,7 +11148,7 @@
         <v>890.6500244140625</v>
       </c>
       <c r="D335" t="n">
-        <v>1888.713623046875</v>
+        <v>1888.713500976562</v>
       </c>
       <c r="E335" t="n">
         <v>902.3499755859375</v>
@@ -11163,7 +11163,7 @@
         <v>401.2503662109375</v>
       </c>
       <c r="I335" t="n">
-        <v>834.9547729492188</v>
+        <v>834.9547119140625</v>
       </c>
       <c r="J335" t="n">
         <v>179.3500061035156</v>
@@ -11186,7 +11186,7 @@
         <v>913.5499877929688</v>
       </c>
       <c r="F336" t="n">
-        <v>694.7366333007812</v>
+        <v>694.736572265625</v>
       </c>
       <c r="G336" t="n">
         <v>48.52999877929688</v>
@@ -11276,7 +11276,7 @@
         <v>812.0999755859375</v>
       </c>
       <c r="D339" t="n">
-        <v>1885.718994140625</v>
+        <v>1885.718872070312</v>
       </c>
       <c r="E339" t="n">
         <v>874.1500244140625</v>
@@ -11320,7 +11320,7 @@
         <v>46.86999893188477</v>
       </c>
       <c r="H340" t="n">
-        <v>399.2848815917969</v>
+        <v>399.284912109375</v>
       </c>
       <c r="I340" t="n">
         <v>700.7388305664062</v>
@@ -11346,7 +11346,7 @@
         <v>860.5499877929688</v>
       </c>
       <c r="F341" t="n">
-        <v>651.7566528320312</v>
+        <v>651.7567138671875</v>
       </c>
       <c r="G341" t="n">
         <v>45.0099983215332</v>
@@ -11355,7 +11355,7 @@
         <v>392.1600952148438</v>
       </c>
       <c r="I341" t="n">
-        <v>665.7368774414062</v>
+        <v>665.7369384765625</v>
       </c>
       <c r="J341" t="n">
         <v>171.6499938964844</v>
@@ -11378,7 +11378,7 @@
         <v>896.9500122070312</v>
       </c>
       <c r="F342" t="n">
-        <v>674.4473266601562</v>
+        <v>674.4473876953125</v>
       </c>
       <c r="G342" t="n">
         <v>47.22000122070312</v>
@@ -11387,7 +11387,7 @@
         <v>396.1892700195312</v>
       </c>
       <c r="I342" t="n">
-        <v>687.157470703125</v>
+        <v>687.1574096679688</v>
       </c>
       <c r="J342" t="n">
         <v>178.0500030517578</v>
@@ -11416,7 +11416,7 @@
         <v>49.58000183105469</v>
       </c>
       <c r="H343" t="n">
-        <v>416.5810241699219</v>
+        <v>416.5810546875</v>
       </c>
       <c r="I343" t="n">
         <v>721.5103149414062</v>
@@ -11468,7 +11468,7 @@
         <v>911.4000244140625</v>
       </c>
       <c r="D345" t="n">
-        <v>2471.10400390625</v>
+        <v>2471.104248046875</v>
       </c>
       <c r="E345" t="n">
         <v>984.25</v>
@@ -11480,7 +11480,7 @@
         <v>51.20999908447266</v>
       </c>
       <c r="H345" t="n">
-        <v>415.0086669921875</v>
+        <v>415.0086364746094</v>
       </c>
       <c r="I345" t="n">
         <v>795.4089965820312</v>
@@ -11500,7 +11500,7 @@
         <v>891.75</v>
       </c>
       <c r="D346" t="n">
-        <v>2532.841552734375</v>
+        <v>2532.841796875</v>
       </c>
       <c r="E346" t="n">
         <v>970.6500244140625</v>
@@ -11538,7 +11538,7 @@
         <v>963.3499755859375</v>
       </c>
       <c r="F347" t="n">
-        <v>712.4285888671875</v>
+        <v>712.4285278320312</v>
       </c>
       <c r="G347" t="n">
         <v>51.61000061035156</v>
@@ -11564,7 +11564,7 @@
         <v>832.2000122070312</v>
       </c>
       <c r="D348" t="n">
-        <v>2529.44775390625</v>
+        <v>2529.447998046875</v>
       </c>
       <c r="E348" t="n">
         <v>977.8499755859375</v>
@@ -11579,7 +11579,7 @@
         <v>419.6275024414062</v>
       </c>
       <c r="I348" t="n">
-        <v>728.2012329101562</v>
+        <v>728.201171875</v>
       </c>
       <c r="J348" t="n">
         <v>238.5</v>
@@ -11596,7 +11596,7 @@
         <v>804.2999877929688</v>
       </c>
       <c r="D349" t="n">
-        <v>2491.915771484375</v>
+        <v>2491.916015625</v>
       </c>
       <c r="E349" t="n">
         <v>966.8499755859375</v>
@@ -11608,7 +11608,7 @@
         <v>50.22000122070312</v>
       </c>
       <c r="H349" t="n">
-        <v>423.4601440429688</v>
+        <v>423.4601745605469</v>
       </c>
       <c r="I349" t="n">
         <v>697.0938110351562</v>
@@ -11675,7 +11675,7 @@
         <v>421.8386535644531</v>
       </c>
       <c r="I351" t="n">
-        <v>693.3989868164062</v>
+        <v>693.39892578125</v>
       </c>
       <c r="J351" t="n">
         <v>241</v>
@@ -11692,7 +11692,7 @@
         <v>794.6500244140625</v>
       </c>
       <c r="D352" t="n">
-        <v>2440.609130859375</v>
+        <v>2440.609375</v>
       </c>
       <c r="E352" t="n">
         <v>983.5499877929688</v>
@@ -11707,7 +11707,7 @@
         <v>430.4866943359375</v>
       </c>
       <c r="I352" t="n">
-        <v>673.4762573242188</v>
+        <v>673.476318359375</v>
       </c>
       <c r="J352" t="n">
         <v>242</v>
@@ -11736,7 +11736,7 @@
         <v>51.88999938964844</v>
       </c>
       <c r="H353" t="n">
-        <v>431.4694519042969</v>
+        <v>431.469482421875</v>
       </c>
       <c r="I353" t="n">
         <v>680.5665893554688</v>
@@ -11771,7 +11771,7 @@
         <v>451.222412109375</v>
       </c>
       <c r="I354" t="n">
-        <v>677.4708251953125</v>
+        <v>677.4707641601562</v>
       </c>
       <c r="J354" t="n">
         <v>236.3000030517578</v>
@@ -11788,22 +11788,22 @@
         <v>837.25</v>
       </c>
       <c r="D355" t="n">
-        <v>2435.119140625</v>
+        <v>2435.119384765625</v>
       </c>
       <c r="E355" t="n">
         <v>985.5499877929688</v>
       </c>
       <c r="F355" t="n">
-        <v>728.9932250976562</v>
+        <v>728.9931640625</v>
       </c>
       <c r="G355" t="n">
         <v>54.97000122070312</v>
       </c>
       <c r="H355" t="n">
-        <v>447.881103515625</v>
+        <v>447.8811340332031</v>
       </c>
       <c r="I355" t="n">
-        <v>679.1185302734375</v>
+        <v>679.1184692382812</v>
       </c>
       <c r="J355" t="n">
         <v>237.3999938964844</v>
@@ -11826,7 +11826,7 @@
         <v>976</v>
       </c>
       <c r="F356" t="n">
-        <v>721.7891235351562</v>
+        <v>721.7891845703125</v>
       </c>
       <c r="G356" t="n">
         <v>55.83000183105469</v>
@@ -11835,7 +11835,7 @@
         <v>443.9010314941406</v>
       </c>
       <c r="I356" t="n">
-        <v>669.9810180664062</v>
+        <v>669.9810791015625</v>
       </c>
       <c r="J356" t="n">
         <v>231.8000030517578</v>
@@ -11864,7 +11864,7 @@
         <v>55.2400016784668</v>
       </c>
       <c r="H357" t="n">
-        <v>447.8320007324219</v>
+        <v>447.83203125</v>
       </c>
       <c r="I357" t="n">
         <v>668.1834716796875</v>
@@ -11884,7 +11884,7 @@
         <v>830.4000244140625</v>
       </c>
       <c r="D358" t="n">
-        <v>2480.287353515625</v>
+        <v>2480.287109375</v>
       </c>
       <c r="E358" t="n">
         <v>961.0999755859375</v>
@@ -11899,7 +11899,7 @@
         <v>448.4215698242188</v>
       </c>
       <c r="I358" t="n">
-        <v>669.2820434570312</v>
+        <v>669.281982421875</v>
       </c>
       <c r="J358" t="n">
         <v>228.5500030517578</v>
@@ -11916,13 +11916,13 @@
         <v>823</v>
       </c>
       <c r="D359" t="n">
-        <v>2458.077392578125</v>
+        <v>2458.07763671875</v>
       </c>
       <c r="E359" t="n">
         <v>955.2999877929688</v>
       </c>
       <c r="F359" t="n">
-        <v>723.2103271484375</v>
+        <v>723.2102661132812</v>
       </c>
       <c r="G359" t="n">
         <v>53.56000137329102</v>
@@ -11954,7 +11954,7 @@
         <v>957.6500244140625</v>
       </c>
       <c r="F360" t="n">
-        <v>724.6804809570312</v>
+        <v>724.6805419921875</v>
       </c>
       <c r="G360" t="n">
         <v>53.04999923706055</v>
@@ -11992,7 +11992,7 @@
         <v>53.84999847412109</v>
       </c>
       <c r="H361" t="n">
-        <v>450.4361877441406</v>
+        <v>450.4362182617188</v>
       </c>
       <c r="I361" t="n">
         <v>668.1834716796875</v>
@@ -12012,7 +12012,7 @@
         <v>810.9000244140625</v>
       </c>
       <c r="D362" t="n">
-        <v>2505.0419921875</v>
+        <v>2505.042236328125</v>
       </c>
       <c r="E362" t="n">
         <v>975.0499877929688</v>
@@ -12027,7 +12027,7 @@
         <v>452.9421997070312</v>
       </c>
       <c r="I362" t="n">
-        <v>670.33056640625</v>
+        <v>670.3306274414062</v>
       </c>
       <c r="J362" t="n">
         <v>238.9499969482422</v>
@@ -12059,7 +12059,7 @@
         <v>445.0311889648438</v>
       </c>
       <c r="I363" t="n">
-        <v>656.6493530273438</v>
+        <v>656.6492919921875</v>
       </c>
       <c r="J363" t="n">
         <v>232.3999938964844</v>
@@ -12076,19 +12076,19 @@
         <v>811.9500122070312</v>
       </c>
       <c r="D364" t="n">
-        <v>2410.41455078125</v>
+        <v>2410.414306640625</v>
       </c>
       <c r="E364" t="n">
         <v>961.7000122070312</v>
       </c>
       <c r="F364" t="n">
-        <v>723.1612548828125</v>
+        <v>723.1613159179688</v>
       </c>
       <c r="G364" t="n">
         <v>52.34000015258789</v>
       </c>
       <c r="H364" t="n">
-        <v>441.1985473632812</v>
+        <v>441.1985168457031</v>
       </c>
       <c r="I364" t="n">
         <v>657.6978759765625</v>
@@ -12108,7 +12108,7 @@
         <v>806.7000122070312</v>
       </c>
       <c r="D365" t="n">
-        <v>2401.58056640625</v>
+        <v>2401.580322265625</v>
       </c>
       <c r="E365" t="n">
         <v>977</v>
@@ -12152,7 +12152,7 @@
         <v>51.31999969482422</v>
       </c>
       <c r="H366" t="n">
-        <v>437.1693420410156</v>
+        <v>437.1693115234375</v>
       </c>
       <c r="I366" t="n">
         <v>654.252685546875</v>
@@ -12187,7 +12187,7 @@
         <v>418.4481811523438</v>
       </c>
       <c r="I367" t="n">
-        <v>633.43115234375</v>
+        <v>633.4312133789062</v>
       </c>
       <c r="J367" t="n">
         <v>214.1999969482422</v>
@@ -12210,16 +12210,16 @@
         <v>968.4500122070312</v>
       </c>
       <c r="F368" t="n">
-        <v>710.027099609375</v>
+        <v>710.0271606445312</v>
       </c>
       <c r="G368" t="n">
         <v>50.11999893188477</v>
       </c>
       <c r="H368" t="n">
-        <v>424.5903015136719</v>
+        <v>424.59033203125</v>
       </c>
       <c r="I368" t="n">
-        <v>643.1178588867188</v>
+        <v>643.117919921875</v>
       </c>
       <c r="J368" t="n">
         <v>224.8999938964844</v>
@@ -12242,13 +12242,13 @@
         <v>959.5499877929688</v>
       </c>
       <c r="F369" t="n">
-        <v>705.9595336914062</v>
+        <v>705.95947265625</v>
       </c>
       <c r="G369" t="n">
         <v>50.61999893188477</v>
       </c>
       <c r="H369" t="n">
-        <v>426.3592834472656</v>
+        <v>426.3592529296875</v>
       </c>
       <c r="I369" t="n">
         <v>640.621337890625</v>
@@ -12268,7 +12268,7 @@
         <v>819.1500244140625</v>
       </c>
       <c r="D370" t="n">
-        <v>2397.637451171875</v>
+        <v>2397.63720703125</v>
       </c>
       <c r="E370" t="n">
         <v>956.6500244140625</v>
@@ -12280,7 +12280,7 @@
         <v>50.93000030517578</v>
       </c>
       <c r="H370" t="n">
-        <v>426.7523193359375</v>
+        <v>426.7523498535156</v>
       </c>
       <c r="I370" t="n">
         <v>653.6034545898438</v>
@@ -12306,13 +12306,13 @@
         <v>945.9000244140625</v>
       </c>
       <c r="F371" t="n">
-        <v>724.5824584960938</v>
+        <v>724.58251953125</v>
       </c>
       <c r="G371" t="n">
         <v>49.97000122070312</v>
       </c>
       <c r="H371" t="n">
-        <v>418.5465087890625</v>
+        <v>418.5464782714844</v>
       </c>
       <c r="I371" t="n">
         <v>653.703369140625</v>
@@ -12347,7 +12347,7 @@
         <v>428.32470703125</v>
       </c>
       <c r="I372" t="n">
-        <v>656.7991943359375</v>
+        <v>656.7991333007812</v>
       </c>
       <c r="J372" t="n">
         <v>225.6499938964844</v>
@@ -12364,13 +12364,13 @@
         <v>770.5999755859375</v>
       </c>
       <c r="D373" t="n">
-        <v>2383.363525390625</v>
+        <v>2383.36328125</v>
       </c>
       <c r="E373" t="n">
         <v>946</v>
       </c>
       <c r="F373" t="n">
-        <v>726.9839477539062</v>
+        <v>726.9840087890625</v>
       </c>
       <c r="G373" t="n">
         <v>49.41999816894531</v>
@@ -12408,7 +12408,7 @@
         <v>49.13000106811523</v>
       </c>
       <c r="H374" t="n">
-        <v>424.9342651367188</v>
+        <v>424.9342956542969</v>
       </c>
       <c r="I374" t="n">
         <v>649.0098266601562</v>
@@ -12428,7 +12428,7 @@
         <v>769.3499755859375</v>
       </c>
       <c r="D375" t="n">
-        <v>2398.535888671875</v>
+        <v>2398.5361328125</v>
       </c>
       <c r="E375" t="n">
         <v>962.2000122070312</v>
@@ -12443,7 +12443,7 @@
         <v>424.0497741699219</v>
       </c>
       <c r="I375" t="n">
-        <v>647.861328125</v>
+        <v>647.8613891601562</v>
       </c>
       <c r="J375" t="n">
         <v>227</v>
@@ -12498,7 +12498,7 @@
         <v>959.4500122070312</v>
       </c>
       <c r="F377" t="n">
-        <v>705.8124389648438</v>
+        <v>705.8125</v>
       </c>
       <c r="G377" t="n">
         <v>48.40999984741211</v>
@@ -12530,7 +12530,7 @@
         <v>965.1500244140625</v>
       </c>
       <c r="F378" t="n">
-        <v>715.4180297851562</v>
+        <v>715.4180908203125</v>
       </c>
       <c r="G378" t="n">
         <v>48.84000015258789</v>
@@ -12562,7 +12562,7 @@
         <v>954.5499877929688</v>
       </c>
       <c r="F379" t="n">
-        <v>709.8311157226562</v>
+        <v>709.8311767578125</v>
       </c>
       <c r="G379" t="n">
         <v>48.16999816894531</v>
@@ -12594,7 +12594,7 @@
         <v>947.0499877929688</v>
       </c>
       <c r="F380" t="n">
-        <v>702.9700317382812</v>
+        <v>702.9700927734375</v>
       </c>
       <c r="G380" t="n">
         <v>47.43999862670898</v>
@@ -12620,7 +12620,7 @@
         <v>742.2999877929688</v>
       </c>
       <c r="D381" t="n">
-        <v>2372.93359375</v>
+        <v>2372.933837890625</v>
       </c>
       <c r="E381" t="n">
         <v>965.2000122070312</v>
@@ -12690,7 +12690,7 @@
         <v>973.75</v>
       </c>
       <c r="F383" t="n">
-        <v>713.7027587890625</v>
+        <v>713.7026977539062</v>
       </c>
       <c r="G383" t="n">
         <v>49.31000137329102</v>
@@ -12699,7 +12699,7 @@
         <v>411.3974914550781</v>
       </c>
       <c r="I383" t="n">
-        <v>645.114013671875</v>
+        <v>645.1140747070312</v>
       </c>
       <c r="J383" t="n">
         <v>229.8500061035156</v>
@@ -12722,7 +12722,7 @@
         <v>979.6500244140625</v>
       </c>
       <c r="F384" t="n">
-        <v>716.8883056640625</v>
+        <v>716.8883666992188</v>
       </c>
       <c r="G384" t="n">
         <v>49.13999938964844</v>
@@ -12731,7 +12731,7 @@
         <v>414.4617309570312</v>
       </c>
       <c r="I384" t="n">
-        <v>640.5186157226562</v>
+        <v>640.5186767578125</v>
       </c>
       <c r="J384" t="n">
         <v>235.8999938964844</v>
@@ -12748,7 +12748,7 @@
         <v>780.2999877929688</v>
       </c>
       <c r="D385" t="n">
-        <v>2416.525146484375</v>
+        <v>2416.525390625</v>
       </c>
       <c r="E385" t="n">
         <v>985</v>
@@ -12812,7 +12812,7 @@
         <v>773.25</v>
       </c>
       <c r="D387" t="n">
-        <v>2414.977294921875</v>
+        <v>2414.9775390625</v>
       </c>
       <c r="E387" t="n">
         <v>989.1500244140625</v>
@@ -12908,7 +12908,7 @@
         <v>805</v>
       </c>
       <c r="D390" t="n">
-        <v>2425.163818359375</v>
+        <v>2425.16357421875</v>
       </c>
       <c r="E390" t="n">
         <v>1119.199951171875</v>
@@ -12987,7 +12987,7 @@
         <v>457.6575012207031</v>
       </c>
       <c r="I392" t="n">
-        <v>663.0464477539062</v>
+        <v>663.04638671875</v>
       </c>
       <c r="J392" t="n">
         <v>228.8500061035156</v>
@@ -13100,7 +13100,7 @@
         <v>796.6500244140625</v>
       </c>
       <c r="D396" t="n">
-        <v>2538.412841796875</v>
+        <v>2538.41259765625</v>
       </c>
       <c r="E396" t="n">
         <v>1012.549987792969</v>
@@ -13202,7 +13202,7 @@
         <v>971.2999877929688</v>
       </c>
       <c r="F399" t="n">
-        <v>780.6165161132812</v>
+        <v>780.6165771484375</v>
       </c>
       <c r="G399" t="n">
         <v>55.43000030517578</v>
@@ -13234,7 +13234,7 @@
         <v>973.9000244140625</v>
       </c>
       <c r="F400" t="n">
-        <v>792.1615600585938</v>
+        <v>792.1614990234375</v>
       </c>
       <c r="G400" t="n">
         <v>56.38000106811523</v>
@@ -13260,13 +13260,13 @@
         <v>831.7000122070312</v>
       </c>
       <c r="D401" t="n">
-        <v>2536.11572265625</v>
+        <v>2536.115966796875</v>
       </c>
       <c r="E401" t="n">
         <v>971.3499755859375</v>
       </c>
       <c r="F401" t="n">
-        <v>790.4347534179688</v>
+        <v>790.4346923828125</v>
       </c>
       <c r="G401" t="n">
         <v>57.61999893188477</v>
@@ -13292,13 +13292,13 @@
         <v>808.2999877929688</v>
       </c>
       <c r="D402" t="n">
-        <v>2452.72705078125</v>
+        <v>2452.726806640625</v>
       </c>
       <c r="E402" t="n">
         <v>951.25</v>
       </c>
       <c r="F402" t="n">
-        <v>776.718994140625</v>
+        <v>776.7189331054688</v>
       </c>
       <c r="G402" t="n">
         <v>57.22000122070312</v>
@@ -13356,13 +13356,13 @@
         <v>822.2000122070312</v>
       </c>
       <c r="D404" t="n">
-        <v>2476.3955078125</v>
+        <v>2476.395263671875</v>
       </c>
       <c r="E404" t="n">
         <v>933.5</v>
       </c>
       <c r="F404" t="n">
-        <v>798.9207763671875</v>
+        <v>798.9207153320312</v>
       </c>
       <c r="G404" t="n">
         <v>57.31000137329102</v>
@@ -13394,7 +13394,7 @@
         <v>994.75</v>
       </c>
       <c r="F405" t="n">
-        <v>824.8229370117188</v>
+        <v>824.8228759765625</v>
       </c>
       <c r="G405" t="n">
         <v>60.91999816894531</v>
@@ -13452,7 +13452,7 @@
         <v>960.1500244140625</v>
       </c>
       <c r="D407" t="n">
-        <v>2694.45458984375</v>
+        <v>2694.454345703125</v>
       </c>
       <c r="E407" t="n">
         <v>1015.099975585938</v>
@@ -13522,7 +13522,7 @@
         <v>983.6500244140625</v>
       </c>
       <c r="F409" t="n">
-        <v>811.452392578125</v>
+        <v>811.4524536132812</v>
       </c>
       <c r="G409" t="n">
         <v>65.76000213623047</v>
@@ -13548,7 +13548,7 @@
         <v>874.5499877929688</v>
       </c>
       <c r="D410" t="n">
-        <v>2492.423828125</v>
+        <v>2492.424072265625</v>
       </c>
       <c r="E410" t="n">
         <v>979.4500122070312</v>
@@ -13586,7 +13586,7 @@
         <v>980.0999755859375</v>
       </c>
       <c r="F411" t="n">
-        <v>796.7499389648438</v>
+        <v>796.7498779296875</v>
       </c>
       <c r="G411" t="n">
         <v>64.36000061035156</v>
@@ -13618,7 +13618,7 @@
         <v>974.5</v>
       </c>
       <c r="F412" t="n">
-        <v>812.6365356445312</v>
+        <v>812.6365966796875</v>
       </c>
       <c r="G412" t="n">
         <v>66.54000091552734</v>
@@ -13650,7 +13650,7 @@
         <v>970.5</v>
       </c>
       <c r="F413" t="n">
-        <v>807.8507690429688</v>
+        <v>807.850830078125</v>
       </c>
       <c r="G413" t="n">
         <v>65.68000030517578</v>
@@ -13676,13 +13676,13 @@
         <v>811.9500122070312</v>
       </c>
       <c r="D414" t="n">
-        <v>2416.02587890625</v>
+        <v>2416.026123046875</v>
       </c>
       <c r="E414" t="n">
         <v>928.6500244140625</v>
       </c>
       <c r="F414" t="n">
-        <v>781.7020874023438</v>
+        <v>781.7020263671875</v>
       </c>
       <c r="G414" t="n">
         <v>64.26000213623047</v>
@@ -13714,7 +13714,7 @@
         <v>949.0999755859375</v>
       </c>
       <c r="F415" t="n">
-        <v>788.9052734375</v>
+        <v>788.9052124023438</v>
       </c>
       <c r="G415" t="n">
         <v>66.05000305175781</v>
@@ -13740,13 +13740,13 @@
         <v>817.5999755859375</v>
       </c>
       <c r="D416" t="n">
-        <v>2467.3076171875</v>
+        <v>2467.307861328125</v>
       </c>
       <c r="E416" t="n">
         <v>959.2000122070312</v>
       </c>
       <c r="F416" t="n">
-        <v>790.4347534179688</v>
+        <v>790.4346923828125</v>
       </c>
       <c r="G416" t="n">
         <v>68.34999847412109</v>
@@ -13772,13 +13772,13 @@
         <v>813.4500122070312</v>
       </c>
       <c r="D417" t="n">
-        <v>2490.72607421875</v>
+        <v>2490.726318359375</v>
       </c>
       <c r="E417" t="n">
         <v>962.0999755859375</v>
       </c>
       <c r="F417" t="n">
-        <v>794.2830810546875</v>
+        <v>794.2830200195312</v>
       </c>
       <c r="G417" t="n">
         <v>68.48999786376953</v>
@@ -13804,7 +13804,7 @@
         <v>855.9500122070312</v>
       </c>
       <c r="D418" t="n">
-        <v>2493.173095703125</v>
+        <v>2493.1728515625</v>
       </c>
       <c r="E418" t="n">
         <v>1006.099975585938</v>
@@ -13868,13 +13868,13 @@
         <v>833</v>
       </c>
       <c r="D420" t="n">
-        <v>2515.942626953125</v>
+        <v>2515.94287109375</v>
       </c>
       <c r="E420" t="n">
         <v>1001.200012207031</v>
       </c>
       <c r="F420" t="n">
-        <v>814.0673217773438</v>
+        <v>814.0673828125</v>
       </c>
       <c r="G420" t="n">
         <v>73.83000183105469</v>
@@ -13900,7 +13900,7 @@
         <v>874.9000244140625</v>
       </c>
       <c r="D421" t="n">
-        <v>2611.465087890625</v>
+        <v>2611.46533203125</v>
       </c>
       <c r="E421" t="n">
         <v>1014.650024414062</v>
@@ -13915,7 +13915,7 @@
         <v>445.6971130371094</v>
       </c>
       <c r="I421" t="n">
-        <v>658.2510986328125</v>
+        <v>658.2511596679688</v>
       </c>
       <c r="J421" t="n">
         <v>224.4499969482422</v>
@@ -13932,7 +13932,7 @@
         <v>852.2999877929688</v>
       </c>
       <c r="D422" t="n">
-        <v>2532.32080078125</v>
+        <v>2532.321044921875</v>
       </c>
       <c r="E422" t="n">
         <v>1004.799987792969</v>
@@ -13970,7 +13970,7 @@
         <v>985.7999877929688</v>
       </c>
       <c r="F423" t="n">
-        <v>838.4400634765625</v>
+        <v>838.4400024414062</v>
       </c>
       <c r="G423" t="n">
         <v>75.41999816894531</v>
@@ -13979,7 +13979,7 @@
         <v>438.7778625488281</v>
       </c>
       <c r="I423" t="n">
-        <v>635.923095703125</v>
+        <v>635.9231567382812</v>
       </c>
       <c r="J423" t="n">
         <v>218.5</v>
@@ -13996,7 +13996,7 @@
         <v>851.75</v>
       </c>
       <c r="D424" t="n">
-        <v>2516.44189453125</v>
+        <v>2516.442138671875</v>
       </c>
       <c r="E424" t="n">
         <v>983.7999877929688</v>
@@ -14028,13 +14028,13 @@
         <v>846.0999755859375</v>
       </c>
       <c r="D425" t="n">
-        <v>2536.6650390625</v>
+        <v>2536.665283203125</v>
       </c>
       <c r="E425" t="n">
         <v>1006.450012207031</v>
       </c>
       <c r="F425" t="n">
-        <v>834.4437255859375</v>
+        <v>834.4437866210938</v>
       </c>
       <c r="G425" t="n">
         <v>75.87999725341797</v>
@@ -14066,7 +14066,7 @@
         <v>1004.950012207031</v>
       </c>
       <c r="F426" t="n">
-        <v>820.2344970703125</v>
+        <v>820.2345581054688</v>
       </c>
       <c r="G426" t="n">
         <v>75</v>
@@ -14092,13 +14092,13 @@
         <v>855.2000122070312</v>
       </c>
       <c r="D427" t="n">
-        <v>2467.008056640625</v>
+        <v>2467.0078125</v>
       </c>
       <c r="E427" t="n">
         <v>1008.950012207031</v>
       </c>
       <c r="F427" t="n">
-        <v>807.2094116210938</v>
+        <v>807.2093505859375</v>
       </c>
       <c r="G427" t="n">
         <v>73.68000030517578</v>
@@ -14124,7 +14124,7 @@
         <v>847.3499755859375</v>
       </c>
       <c r="D428" t="n">
-        <v>2475.9462890625</v>
+        <v>2475.946044921875</v>
       </c>
       <c r="E428" t="n">
         <v>1023.450012207031</v>
@@ -14156,13 +14156,13 @@
         <v>839.0999755859375</v>
       </c>
       <c r="D429" t="n">
-        <v>2461.615234375</v>
+        <v>2461.614990234375</v>
       </c>
       <c r="E429" t="n">
         <v>1018.799987792969</v>
       </c>
       <c r="F429" t="n">
-        <v>816.0901489257812</v>
+        <v>816.0902099609375</v>
       </c>
       <c r="G429" t="n">
         <v>76.77999877929688</v>
@@ -14194,7 +14194,7 @@
         <v>1013.799987792969</v>
       </c>
       <c r="F430" t="n">
-        <v>814.708740234375</v>
+        <v>814.7088012695312</v>
       </c>
       <c r="G430" t="n">
         <v>76.23000335693359</v>
@@ -14220,7 +14220,7 @@
         <v>817.8499755859375</v>
       </c>
       <c r="D431" t="n">
-        <v>2454.674560546875</v>
+        <v>2454.67431640625</v>
       </c>
       <c r="E431" t="n">
         <v>1012.299987792969</v>
@@ -14284,7 +14284,7 @@
         <v>830.5</v>
       </c>
       <c r="D433" t="n">
-        <v>2471.951416015625</v>
+        <v>2471.951171875</v>
       </c>
       <c r="E433" t="n">
         <v>1012.450012207031</v>
@@ -14380,7 +14380,7 @@
         <v>808.0999755859375</v>
       </c>
       <c r="D436" t="n">
-        <v>2461.665283203125</v>
+        <v>2461.6650390625</v>
       </c>
       <c r="E436" t="n">
         <v>971.9000244140625</v>
@@ -14412,13 +14412,13 @@
         <v>807.7000122070312</v>
       </c>
       <c r="D437" t="n">
-        <v>2463.0634765625</v>
+        <v>2463.063232421875</v>
       </c>
       <c r="E437" t="n">
         <v>959.6500244140625</v>
       </c>
       <c r="F437" t="n">
-        <v>814.2646484375</v>
+        <v>814.2647094726562</v>
       </c>
       <c r="G437" t="n">
         <v>73.16999816894531</v>
@@ -14523,7 +14523,7 @@
         <v>432.1552124023438</v>
       </c>
       <c r="I440" t="n">
-        <v>607.201416015625</v>
+        <v>607.2014770507812</v>
       </c>
       <c r="J440" t="n">
         <v>209.6000061035156</v>
@@ -14546,7 +14546,7 @@
         <v>962.4500122070312</v>
       </c>
       <c r="F441" t="n">
-        <v>804.0518188476562</v>
+        <v>804.0517578125</v>
       </c>
       <c r="G441" t="n">
         <v>69.95999908447266</v>
@@ -14572,7 +14572,7 @@
         <v>793.7000122070312</v>
       </c>
       <c r="D442" t="n">
-        <v>2503.01025390625</v>
+        <v>2503.010009765625</v>
       </c>
       <c r="E442" t="n">
         <v>948.6500244140625</v>
@@ -14604,13 +14604,13 @@
         <v>785.2000122070312</v>
       </c>
       <c r="D443" t="n">
-        <v>2451.279052734375</v>
+        <v>2451.27880859375</v>
       </c>
       <c r="E443" t="n">
         <v>948.9000244140625</v>
       </c>
       <c r="F443" t="n">
-        <v>802.9664916992188</v>
+        <v>802.9664306640625</v>
       </c>
       <c r="G443" t="n">
         <v>68.37999725341797</v>
@@ -14642,7 +14642,7 @@
         <v>938.7999877929688</v>
       </c>
       <c r="F444" t="n">
-        <v>794.9738159179688</v>
+        <v>794.9737548828125</v>
       </c>
       <c r="G444" t="n">
         <v>65.93000030517578</v>
@@ -14668,7 +14668,7 @@
         <v>774.9000244140625</v>
       </c>
       <c r="D445" t="n">
-        <v>2425.163818359375</v>
+        <v>2425.16357421875</v>
       </c>
       <c r="E445" t="n">
         <v>948.6500244140625</v>
@@ -14683,7 +14683,7 @@
         <v>437.5423278808594</v>
       </c>
       <c r="I445" t="n">
-        <v>594.9635009765625</v>
+        <v>594.9635620117188</v>
       </c>
       <c r="J445" t="n">
         <v>211.8999938964844</v>
@@ -14706,7 +14706,7 @@
         <v>939.0499877929688</v>
       </c>
       <c r="F446" t="n">
-        <v>788.01708984375</v>
+        <v>788.0171508789062</v>
       </c>
       <c r="G446" t="n">
         <v>66.79000091552734</v>
@@ -14770,7 +14770,7 @@
         <v>920.1500244140625</v>
       </c>
       <c r="F448" t="n">
-        <v>783.1328735351562</v>
+        <v>783.1328125</v>
       </c>
       <c r="G448" t="n">
         <v>67.66000366210938</v>
@@ -14811,7 +14811,7 @@
         <v>411.150390625</v>
       </c>
       <c r="I449" t="n">
-        <v>572.5855712890625</v>
+        <v>572.5856323242188</v>
       </c>
       <c r="J449" t="n">
         <v>199.5500030517578</v>
@@ -14843,7 +14843,7 @@
         <v>413.1273498535156</v>
       </c>
       <c r="I450" t="n">
-        <v>549.9080200195312</v>
+        <v>549.907958984375</v>
       </c>
       <c r="J450" t="n">
         <v>195.75</v>
@@ -14866,7 +14866,7 @@
         <v>848.1500244140625</v>
       </c>
       <c r="F451" t="n">
-        <v>760.1415405273438</v>
+        <v>760.1414794921875</v>
       </c>
       <c r="G451" t="n">
         <v>65.47000122070312</v>
@@ -14956,13 +14956,13 @@
         <v>769.7999877929688</v>
       </c>
       <c r="D454" t="n">
-        <v>2291.591796875</v>
+        <v>2291.592041015625</v>
       </c>
       <c r="E454" t="n">
         <v>911.6500244140625</v>
       </c>
       <c r="F454" t="n">
-        <v>774.3507690429688</v>
+        <v>774.3507080078125</v>
       </c>
       <c r="G454" t="n">
         <v>72.61000061035156</v>
@@ -15026,7 +15026,7 @@
         <v>892.0999755859375</v>
       </c>
       <c r="F456" t="n">
-        <v>764.0391845703125</v>
+        <v>764.0392456054688</v>
       </c>
       <c r="G456" t="n">
         <v>74.58999633789062</v>
@@ -15099,7 +15099,7 @@
         <v>416.3892517089844</v>
       </c>
       <c r="I458" t="n">
-        <v>550.4075317382812</v>
+        <v>550.407470703125</v>
       </c>
       <c r="J458" t="n">
         <v>194.1499938964844</v>
@@ -15122,7 +15122,7 @@
         <v>932.1500244140625</v>
       </c>
       <c r="F459" t="n">
-        <v>786.9811401367188</v>
+        <v>786.9810791015625</v>
       </c>
       <c r="G459" t="n">
         <v>76.76000213623047</v>
@@ -15154,7 +15154,7 @@
         <v>946.6500244140625</v>
       </c>
       <c r="F460" t="n">
-        <v>807.8507690429688</v>
+        <v>807.850830078125</v>
       </c>
       <c r="G460" t="n">
         <v>78.68000030517578</v>
@@ -15195,7 +15195,7 @@
         <v>413.4732666015625</v>
       </c>
       <c r="I461" t="n">
-        <v>534.4732055664062</v>
+        <v>534.47314453125</v>
       </c>
       <c r="J461" t="n">
         <v>192.5</v>
@@ -15282,7 +15282,7 @@
         <v>950.1500244140625</v>
       </c>
       <c r="F464" t="n">
-        <v>800.0062255859375</v>
+        <v>800.0061645507812</v>
       </c>
       <c r="G464" t="n">
         <v>78.19999694824219</v>
@@ -15387,7 +15387,7 @@
         <v>416.6363830566406</v>
       </c>
       <c r="I467" t="n">
-        <v>530.527099609375</v>
+        <v>530.5270385742188</v>
       </c>
       <c r="J467" t="n">
         <v>191.5</v>
@@ -15436,13 +15436,13 @@
         <v>726.9500122070312</v>
       </c>
       <c r="D469" t="n">
-        <v>2169.75439453125</v>
+        <v>2169.754638671875</v>
       </c>
       <c r="E469" t="n">
         <v>914.4500122070312</v>
       </c>
       <c r="F469" t="n">
-        <v>781.4059448242188</v>
+        <v>781.406005859375</v>
       </c>
       <c r="G469" t="n">
         <v>77.44000244140625</v>
@@ -15532,7 +15532,7 @@
         <v>865.0999755859375</v>
       </c>
       <c r="D472" t="n">
-        <v>2420.2705078125</v>
+        <v>2420.270263671875</v>
       </c>
       <c r="E472" t="n">
         <v>1052.800048828125</v>
@@ -15579,7 +15579,7 @@
         <v>430.6230773925781</v>
       </c>
       <c r="I473" t="n">
-        <v>731.82861328125</v>
+        <v>731.8285522460938</v>
       </c>
       <c r="J473" t="n">
         <v>219.1499938964844</v>
@@ -15602,7 +15602,7 @@
         <v>1028.800048828125</v>
       </c>
       <c r="F474" t="n">
-        <v>814.5607299804688</v>
+        <v>814.5606689453125</v>
       </c>
       <c r="G474" t="n">
         <v>86.30000305175781</v>
@@ -15643,7 +15643,7 @@
         <v>436.8998107910156</v>
       </c>
       <c r="I475" t="n">
-        <v>700.7592163085938</v>
+        <v>700.75927734375</v>
       </c>
       <c r="J475" t="n">
         <v>219.1000061035156</v>
@@ -15660,7 +15660,7 @@
         <v>903.7000122070312</v>
       </c>
       <c r="D476" t="n">
-        <v>2527.82666015625</v>
+        <v>2527.826904296875</v>
       </c>
       <c r="E476" t="n">
         <v>1123.75</v>
@@ -15692,7 +15692,7 @@
         <v>1084.400024414062</v>
       </c>
       <c r="D477" t="n">
-        <v>2955.406494140625</v>
+        <v>2955.40625</v>
       </c>
       <c r="E477" t="n">
         <v>1348.5</v>
@@ -15707,7 +15707,7 @@
         <v>503.1761169433594</v>
       </c>
       <c r="I477" t="n">
-        <v>876.9855346679688</v>
+        <v>876.9854736328125</v>
       </c>
       <c r="J477" t="n">
         <v>266.6499938964844</v>
@@ -15724,7 +15724,7 @@
         <v>1164.300048828125</v>
       </c>
       <c r="D478" t="n">
-        <v>2880.10693359375</v>
+        <v>2880.106689453125</v>
       </c>
       <c r="E478" t="n">
         <v>1563.449951171875</v>
@@ -15756,13 +15756,13 @@
         <v>1198.699951171875</v>
       </c>
       <c r="D479" t="n">
-        <v>2883.302490234375</v>
+        <v>2883.30224609375</v>
       </c>
       <c r="E479" t="n">
         <v>1624.150024414062</v>
       </c>
       <c r="F479" t="n">
-        <v>1025.872802734375</v>
+        <v>1025.872924804688</v>
       </c>
       <c r="G479" t="n">
         <v>112.4800033569336</v>
@@ -15788,7 +15788,7 @@
         <v>1131.5</v>
       </c>
       <c r="D480" t="n">
-        <v>2818.388916015625</v>
+        <v>2818.388671875</v>
       </c>
       <c r="E480" t="n">
         <v>1550.300048828125</v>
@@ -15826,7 +15826,7 @@
         <v>1530</v>
       </c>
       <c r="F481" t="n">
-        <v>1018.225524902344</v>
+        <v>1018.2255859375</v>
       </c>
       <c r="G481" t="n">
         <v>105.2300033569336</v>
@@ -15852,7 +15852,7 @@
         <v>1089.150024414062</v>
       </c>
       <c r="D482" t="n">
-        <v>2853.841796875</v>
+        <v>2853.841552734375</v>
       </c>
       <c r="E482" t="n">
         <v>1463.900024414062</v>
@@ -15931,7 +15931,7 @@
         <v>514.2468872070312</v>
       </c>
       <c r="I484" t="n">
-        <v>1050.514526367188</v>
+        <v>1050.5146484375</v>
       </c>
       <c r="J484" t="n">
         <v>269.4500122070312</v>
@@ -15954,7 +15954,7 @@
         <v>1526.650024414062</v>
       </c>
       <c r="F485" t="n">
-        <v>1064.257446289062</v>
+        <v>1064.25732421875</v>
       </c>
       <c r="G485" t="n">
         <v>107.7699966430664</v>
@@ -15963,7 +15963,7 @@
         <v>516.3720703125</v>
       </c>
       <c r="I485" t="n">
-        <v>1045.9189453125</v>
+        <v>1045.919067382812</v>
       </c>
       <c r="J485" t="n">
         <v>266.2000122070312</v>
@@ -15980,7 +15980,7 @@
         <v>1043.050048828125</v>
       </c>
       <c r="D486" t="n">
-        <v>2976.6279296875</v>
+        <v>2976.628173828125</v>
       </c>
       <c r="E486" t="n">
         <v>1524.650024414062</v>
@@ -15995,7 +15995,7 @@
         <v>519.5845947265625</v>
       </c>
       <c r="I486" t="n">
-        <v>1029.535278320312</v>
+        <v>1029.53515625</v>
       </c>
       <c r="J486" t="n">
         <v>266.2999877929688</v>
@@ -16012,13 +16012,13 @@
         <v>1076.199951171875</v>
       </c>
       <c r="D487" t="n">
-        <v>2937.330322265625</v>
+        <v>2937.33056640625</v>
       </c>
       <c r="E487" t="n">
         <v>1531.800048828125</v>
       </c>
       <c r="F487" t="n">
-        <v>1059.767578125</v>
+        <v>1059.767700195312</v>
       </c>
       <c r="G487" t="n">
         <v>107.0899963378906</v>
@@ -16050,7 +16050,7 @@
         <v>1452.150024414062</v>
       </c>
       <c r="F488" t="n">
-        <v>998.7373657226562</v>
+        <v>998.7373046875</v>
       </c>
       <c r="G488" t="n">
         <v>101.7600021362305</v>
@@ -16059,7 +16059,7 @@
         <v>484.7907409667969</v>
       </c>
       <c r="I488" t="n">
-        <v>959.75390625</v>
+        <v>959.7539672851562</v>
       </c>
       <c r="J488" t="n">
         <v>264.0499877929688</v>
@@ -16091,7 +16091,7 @@
         <v>498.0855407714844</v>
       </c>
       <c r="I489" t="n">
-        <v>984.030029296875</v>
+        <v>984.0299682617188</v>
       </c>
       <c r="J489" t="n">
         <v>264.8500061035156</v>
@@ -16123,7 +16123,7 @@
         <v>497.9866943359375</v>
       </c>
       <c r="I490" t="n">
-        <v>995.31884765625</v>
+        <v>995.3187866210938</v>
       </c>
       <c r="J490" t="n">
         <v>267.1499938964844</v>
@@ -16140,13 +16140,13 @@
         <v>1041.599975585938</v>
       </c>
       <c r="D491" t="n">
-        <v>2861.63134765625</v>
+        <v>2861.631103515625</v>
       </c>
       <c r="E491" t="n">
         <v>1600.199951171875</v>
       </c>
       <c r="F491" t="n">
-        <v>1015.117370605469</v>
+        <v>1015.117309570312</v>
       </c>
       <c r="G491" t="n">
         <v>102.3399963378906</v>
@@ -16155,7 +16155,7 @@
         <v>499.5188293457031</v>
       </c>
       <c r="I491" t="n">
-        <v>994.070068359375</v>
+        <v>994.0701293945312</v>
       </c>
       <c r="J491" t="n">
         <v>267.5499877929688</v>
@@ -16187,7 +16187,7 @@
         <v>511.0343627929688</v>
       </c>
       <c r="I492" t="n">
-        <v>998.1160888671875</v>
+        <v>998.1160278320312</v>
       </c>
       <c r="J492" t="n">
         <v>268.5</v>
@@ -16210,7 +16210,7 @@
         <v>1561</v>
       </c>
       <c r="F493" t="n">
-        <v>1003.473693847656</v>
+        <v>1003.4736328125</v>
       </c>
       <c r="G493" t="n">
         <v>104.6800003051758</v>
@@ -16236,13 +16236,13 @@
         <v>1045.75</v>
       </c>
       <c r="D494" t="n">
-        <v>2845.153564453125</v>
+        <v>2845.1533203125</v>
       </c>
       <c r="E494" t="n">
         <v>1597</v>
       </c>
       <c r="F494" t="n">
-        <v>1010.775573730469</v>
+        <v>1010.775634765625</v>
       </c>
       <c r="G494" t="n">
         <v>105.0299987792969</v>
@@ -16300,7 +16300,7 @@
         <v>1062.449951171875</v>
       </c>
       <c r="D496" t="n">
-        <v>2928.491943359375</v>
+        <v>2928.4921875</v>
       </c>
       <c r="E496" t="n">
         <v>1603.550048828125</v>
@@ -16370,7 +16370,7 @@
         <v>1692.5</v>
       </c>
       <c r="F498" t="n">
-        <v>1108.315673828125</v>
+        <v>1108.315551757812</v>
       </c>
       <c r="G498" t="n">
         <v>111.7099990844727</v>
@@ -16492,7 +16492,7 @@
         <v>1170.300048828125</v>
       </c>
       <c r="D502" t="n">
-        <v>3094.0712890625</v>
+        <v>3094.071044921875</v>
       </c>
       <c r="E502" t="n">
         <v>1723.25</v>
@@ -16562,7 +16562,7 @@
         <v>1710.699951171875</v>
       </c>
       <c r="F504" t="n">
-        <v>1191.103881835938</v>
+        <v>1191.103759765625</v>
       </c>
       <c r="G504" t="n">
         <v>108.2300033569336</v>
@@ -16594,7 +16594,7 @@
         <v>1694.800048828125</v>
       </c>
       <c r="F505" t="n">
-        <v>1187.156860351562</v>
+        <v>1187.15673828125</v>
       </c>
       <c r="G505" t="n">
         <v>108.2300033569336</v>
@@ -16620,7 +16620,7 @@
         <v>1126.349975585938</v>
       </c>
       <c r="D506" t="n">
-        <v>3052.4267578125</v>
+        <v>3052.427001953125</v>
       </c>
       <c r="E506" t="n">
         <v>1666.800048828125</v>
@@ -16667,7 +16667,7 @@
         <v>514.5433959960938</v>
       </c>
       <c r="I507" t="n">
-        <v>1003.111145019531</v>
+        <v>1003.111206054688</v>
       </c>
       <c r="J507" t="n">
         <v>266.0499877929688</v>
@@ -16684,13 +16684,13 @@
         <v>1065.5</v>
       </c>
       <c r="D508" t="n">
-        <v>2915.01025390625</v>
+        <v>2915.010009765625</v>
       </c>
       <c r="E508" t="n">
         <v>1588.25</v>
       </c>
       <c r="F508" t="n">
-        <v>1138.756958007812</v>
+        <v>1138.7568359375</v>
       </c>
       <c r="G508" t="n">
         <v>104.7099990844727</v>
@@ -16699,7 +16699,7 @@
         <v>518.1019287109375</v>
       </c>
       <c r="I508" t="n">
-        <v>982.1318359375</v>
+        <v>982.1318969726562</v>
       </c>
       <c r="J508" t="n">
         <v>268.8999938964844</v>
@@ -16731,7 +16731,7 @@
         <v>530.9024658203125</v>
       </c>
       <c r="I509" t="n">
-        <v>989.5245971679688</v>
+        <v>989.524658203125</v>
       </c>
       <c r="J509" t="n">
         <v>267.75</v>
@@ -16748,7 +16748,7 @@
         <v>1056.150024414062</v>
       </c>
       <c r="D510" t="n">
-        <v>2892.68994140625</v>
+        <v>2892.689697265625</v>
       </c>
       <c r="E510" t="n">
         <v>1680.900024414062</v>
@@ -16795,7 +16795,7 @@
         <v>521.3638305664062</v>
       </c>
       <c r="I511" t="n">
-        <v>1001.213134765625</v>
+        <v>1001.213073730469</v>
       </c>
       <c r="J511" t="n">
         <v>264.25</v>
@@ -16827,7 +16827,7 @@
         <v>553.6865234375</v>
       </c>
       <c r="I512" t="n">
-        <v>1001.962280273438</v>
+        <v>1001.962341308594</v>
       </c>
       <c r="J512" t="n">
         <v>277.7999877929688</v>
@@ -16876,7 +16876,7 @@
         <v>1072.699951171875</v>
       </c>
       <c r="D514" t="n">
-        <v>3086.980712890625</v>
+        <v>3086.98046875</v>
       </c>
       <c r="E514" t="n">
         <v>1679.449951171875</v>
@@ -16955,7 +16955,7 @@
         <v>558.5299072265625</v>
       </c>
       <c r="I516" t="n">
-        <v>1003.111145019531</v>
+        <v>1003.111206054688</v>
       </c>
       <c r="J516" t="n">
         <v>271.3999938964844</v>
@@ -17068,13 +17068,13 @@
         <v>1065.849975585938</v>
       </c>
       <c r="D520" t="n">
-        <v>3225.5458984375</v>
+        <v>3225.545654296875</v>
       </c>
       <c r="E520" t="n">
         <v>1866</v>
       </c>
       <c r="F520" t="n">
-        <v>1239.010620117188</v>
+        <v>1239.010498046875</v>
       </c>
       <c r="G520" t="n">
         <v>113.9400024414062</v>
@@ -17083,7 +17083,7 @@
         <v>561.6436157226562</v>
       </c>
       <c r="I520" t="n">
-        <v>1039.02587890625</v>
+        <v>1039.026000976562</v>
       </c>
       <c r="J520" t="n">
         <v>271.5</v>
@@ -17115,7 +17115,7 @@
         <v>556.8495483398438</v>
       </c>
       <c r="I521" t="n">
-        <v>1022.092468261719</v>
+        <v>1022.092407226562</v>
       </c>
       <c r="J521" t="n">
         <v>268.5499877929688</v>
@@ -17138,7 +17138,7 @@
         <v>1880.699951171875</v>
       </c>
       <c r="F522" t="n">
-        <v>1254.650390625</v>
+        <v>1254.650512695312</v>
       </c>
       <c r="G522" t="n">
         <v>113.9000015258789</v>
@@ -17164,13 +17164,13 @@
         <v>1069.449951171875</v>
       </c>
       <c r="D523" t="n">
-        <v>3165.526123046875</v>
+        <v>3165.52587890625</v>
       </c>
       <c r="E523" t="n">
         <v>1842.599975585938</v>
       </c>
       <c r="F523" t="n">
-        <v>1232.793823242188</v>
+        <v>1232.7939453125</v>
       </c>
       <c r="G523" t="n">
         <v>112.370002746582</v>
@@ -17179,7 +17179,7 @@
         <v>556.997802734375</v>
       </c>
       <c r="I523" t="n">
-        <v>1024.240356445312</v>
+        <v>1024.240478515625</v>
       </c>
       <c r="J523" t="n">
         <v>245.5500030517578</v>
@@ -17260,7 +17260,7 @@
         <v>1052</v>
       </c>
       <c r="D526" t="n">
-        <v>3189.5439453125</v>
+        <v>3189.543701171875</v>
       </c>
       <c r="E526" t="n">
         <v>1900.75</v>
@@ -17292,7 +17292,7 @@
         <v>1061.599975585938</v>
       </c>
       <c r="D527" t="n">
-        <v>3219.303955078125</v>
+        <v>3219.30419921875</v>
       </c>
       <c r="E527" t="n">
         <v>1904.75</v>
@@ -17339,7 +17339,7 @@
         <v>578.1015014648438</v>
       </c>
       <c r="I528" t="n">
-        <v>1010.703674316406</v>
+        <v>1010.703735351562</v>
       </c>
       <c r="J528" t="n">
         <v>267.4500122070312</v>
@@ -17394,7 +17394,7 @@
         <v>1904.949951171875</v>
       </c>
       <c r="F530" t="n">
-        <v>1273.89208984375</v>
+        <v>1273.891967773438</v>
       </c>
       <c r="G530" t="n">
         <v>108.1500015258789</v>
@@ -17420,7 +17420,7 @@
         <v>1058.900024414062</v>
       </c>
       <c r="D531" t="n">
-        <v>3258.701416015625</v>
+        <v>3258.70166015625</v>
       </c>
       <c r="E531" t="n">
         <v>1922.650024414062</v>
@@ -17435,7 +17435,7 @@
         <v>585.9102783203125</v>
       </c>
       <c r="I531" t="n">
-        <v>1017.147399902344</v>
+        <v>1017.147338867188</v>
       </c>
       <c r="J531" t="n">
         <v>263.8999938964844</v>
@@ -17467,7 +17467,7 @@
         <v>595.9926147460938</v>
       </c>
       <c r="I532" t="n">
-        <v>1028.38623046875</v>
+        <v>1028.386352539062</v>
       </c>
       <c r="J532" t="n">
         <v>269.8999938964844</v>
@@ -17490,7 +17490,7 @@
         <v>1970.449951171875</v>
       </c>
       <c r="F533" t="n">
-        <v>1320.417358398438</v>
+        <v>1320.417236328125</v>
       </c>
       <c r="G533" t="n">
         <v>114.0899963378906</v>
@@ -17522,7 +17522,7 @@
         <v>1979.5</v>
       </c>
       <c r="F534" t="n">
-        <v>1311.83251953125</v>
+        <v>1311.832397460938</v>
       </c>
       <c r="G534" t="n">
         <v>113.3399963378906</v>
@@ -17531,7 +17531,7 @@
         <v>596.3880004882812</v>
       </c>
       <c r="I534" t="n">
-        <v>1047.267822265625</v>
+        <v>1047.267700195312</v>
       </c>
       <c r="J534" t="n">
         <v>268.1000061035156</v>
@@ -17563,7 +17563,7 @@
         <v>582.4507446289062</v>
       </c>
       <c r="I535" t="n">
-        <v>1017.896606445312</v>
+        <v>1017.896667480469</v>
       </c>
       <c r="J535" t="n">
         <v>256.75</v>
@@ -17595,7 +17595,7 @@
         <v>598.9086303710938</v>
       </c>
       <c r="I536" t="n">
-        <v>1024.64013671875</v>
+        <v>1024.640014648438</v>
       </c>
       <c r="J536" t="n">
         <v>255.3500061035156</v>
@@ -17618,7 +17618,7 @@
         <v>1969.550048828125</v>
       </c>
       <c r="F537" t="n">
-        <v>1304.579833984375</v>
+        <v>1304.579956054688</v>
       </c>
       <c r="G537" t="n">
         <v>110.8300018310547</v>
@@ -17682,7 +17682,7 @@
         <v>1947.400024414062</v>
       </c>
       <c r="F539" t="n">
-        <v>1320.565185546875</v>
+        <v>1320.565307617188</v>
       </c>
       <c r="G539" t="n">
         <v>114.7699966430664</v>
@@ -17691,7 +17691,7 @@
         <v>606.0255126953125</v>
       </c>
       <c r="I539" t="n">
-        <v>1019.145446777344</v>
+        <v>1019.145385742188</v>
       </c>
       <c r="J539" t="n">
         <v>251.4499969482422</v>
@@ -17708,13 +17708,13 @@
         <v>1069.5</v>
       </c>
       <c r="D540" t="n">
-        <v>3229.64013671875</v>
+        <v>3229.640380859375</v>
       </c>
       <c r="E540" t="n">
         <v>1910.5</v>
       </c>
       <c r="F540" t="n">
-        <v>1307.244262695312</v>
+        <v>1307.244140625</v>
       </c>
       <c r="G540" t="n">
         <v>115.3399963378906</v>
@@ -17723,7 +17723,7 @@
         <v>591.3963012695312</v>
       </c>
       <c r="I540" t="n">
-        <v>1004.859497070312</v>
+        <v>1004.859436035156</v>
       </c>
       <c r="J540" t="n">
         <v>246.75</v>
@@ -17755,7 +17755,7 @@
         <v>596.1903686523438</v>
       </c>
       <c r="I541" t="n">
-        <v>1008.206176757812</v>
+        <v>1008.206237792969</v>
       </c>
       <c r="J541" t="n">
         <v>246.3000030517578</v>
@@ -17772,7 +17772,7 @@
         <v>1063.75</v>
       </c>
       <c r="D542" t="n">
-        <v>3203.07568359375</v>
+        <v>3203.075927734375</v>
       </c>
       <c r="E542" t="n">
         <v>1930.300048828125</v>
@@ -17787,7 +17787,7 @@
         <v>595.1029663085938</v>
       </c>
       <c r="I542" t="n">
-        <v>999.1650390625</v>
+        <v>999.1651000976562</v>
       </c>
       <c r="J542" t="n">
         <v>242.3999938964844</v>
@@ -17810,7 +17810,7 @@
         <v>1897.099975585938</v>
       </c>
       <c r="F543" t="n">
-        <v>1284.055541992188</v>
+        <v>1284.0556640625</v>
       </c>
       <c r="G543" t="n">
         <v>111.2200012207031</v>
@@ -17836,7 +17836,7 @@
         <v>947.9500122070312</v>
       </c>
       <c r="D544" t="n">
-        <v>2902.326904296875</v>
+        <v>2902.3271484375</v>
       </c>
       <c r="E544" t="n">
         <v>1725</v>
@@ -17883,7 +17883,7 @@
         <v>575.7291870117188</v>
       </c>
       <c r="I545" t="n">
-        <v>972.341552734375</v>
+        <v>972.3414916992188</v>
       </c>
       <c r="J545" t="n">
         <v>220.25</v>
@@ -17906,7 +17906,7 @@
         <v>1902.599975585938</v>
       </c>
       <c r="F546" t="n">
-        <v>1265.998168945312</v>
+        <v>1265.998046875</v>
       </c>
       <c r="G546" t="n">
         <v>106.0800018310547</v>
@@ -17932,7 +17932,7 @@
         <v>1008.849975585938</v>
       </c>
       <c r="D547" t="n">
-        <v>3107.60302734375</v>
+        <v>3107.603271484375</v>
       </c>
       <c r="E547" t="n">
         <v>1869.900024414062</v>
@@ -17947,7 +17947,7 @@
         <v>577.90380859375</v>
       </c>
       <c r="I547" t="n">
-        <v>946.317138671875</v>
+        <v>946.3171997070312</v>
       </c>
       <c r="J547" t="n">
         <v>214</v>
@@ -18028,7 +18028,7 @@
         <v>1008.900024414062</v>
       </c>
       <c r="D550" t="n">
-        <v>3062.41357421875</v>
+        <v>3062.413330078125</v>
       </c>
       <c r="E550" t="n">
         <v>1855.349975585938</v>
@@ -18043,7 +18043,7 @@
         <v>580.4243774414062</v>
       </c>
       <c r="I550" t="n">
-        <v>935.1282348632812</v>
+        <v>935.128173828125</v>
       </c>
       <c r="J550" t="n">
         <v>214.1499938964844</v>
@@ -18098,7 +18098,7 @@
         <v>1859</v>
       </c>
       <c r="F552" t="n">
-        <v>1286.917114257812</v>
+        <v>1286.9169921875</v>
       </c>
       <c r="G552" t="n">
         <v>104.4000015258789</v>
@@ -18107,7 +18107,7 @@
         <v>588.1837768554688</v>
       </c>
       <c r="I552" t="n">
-        <v>948.165283203125</v>
+        <v>948.1653442382812</v>
       </c>
       <c r="J552" t="n">
         <v>212.3500061035156</v>
@@ -18124,7 +18124,7 @@
         <v>1014.849975585938</v>
       </c>
       <c r="D553" t="n">
-        <v>3117.939453125</v>
+        <v>3117.939697265625</v>
       </c>
       <c r="E553" t="n">
         <v>1822.5</v>
@@ -18139,7 +18139,7 @@
         <v>594.5593872070312</v>
       </c>
       <c r="I553" t="n">
-        <v>918.8941650390625</v>
+        <v>918.8942260742188</v>
       </c>
       <c r="J553" t="n">
         <v>211.1999969482422</v>
@@ -18203,7 +18203,7 @@
         <v>614.3285522460938</v>
       </c>
       <c r="I555" t="n">
-        <v>968.59521484375</v>
+        <v>968.5951538085938</v>
       </c>
       <c r="J555" t="n">
         <v>222.6499938964844</v>
@@ -18226,7 +18226,7 @@
         <v>1892.650024414062</v>
       </c>
       <c r="F556" t="n">
-        <v>1385.54248046875</v>
+        <v>1385.542602539062</v>
       </c>
       <c r="G556" t="n">
         <v>117.6900024414062</v>
@@ -18235,7 +18235,7 @@
         <v>627.3762817382812</v>
       </c>
       <c r="I556" t="n">
-        <v>975.2886352539062</v>
+        <v>975.28857421875</v>
       </c>
       <c r="J556" t="n">
         <v>228.1499938964844</v>
@@ -18267,7 +18267,7 @@
         <v>627.6234130859375</v>
       </c>
       <c r="I557" t="n">
-        <v>974.93896484375</v>
+        <v>974.9390258789062</v>
       </c>
       <c r="J557" t="n">
         <v>229.3999938964844</v>
@@ -18284,13 +18284,13 @@
         <v>1102</v>
       </c>
       <c r="D558" t="n">
-        <v>3206.52099609375</v>
+        <v>3206.521240234375</v>
       </c>
       <c r="E558" t="n">
         <v>1890.849975585938</v>
       </c>
       <c r="F558" t="n">
-        <v>1348.73681640625</v>
+        <v>1348.736938476562</v>
       </c>
       <c r="G558" t="n">
         <v>128.3999938964844</v>
@@ -18299,7 +18299,7 @@
         <v>617.4916381835938</v>
       </c>
       <c r="I558" t="n">
-        <v>983.2307739257812</v>
+        <v>983.2308349609375</v>
       </c>
       <c r="J558" t="n">
         <v>229.3500061035156</v>
@@ -18395,7 +18395,7 @@
         <v>615.9100952148438</v>
       </c>
       <c r="I561" t="n">
-        <v>961.2025756835938</v>
+        <v>961.2025146484375</v>
       </c>
       <c r="J561" t="n">
         <v>223.6000061035156</v>
@@ -18418,7 +18418,7 @@
         <v>1907.5</v>
       </c>
       <c r="F562" t="n">
-        <v>1334.379760742188</v>
+        <v>1334.3798828125</v>
       </c>
       <c r="G562" t="n">
         <v>123.5699996948242</v>
@@ -18427,7 +18427,7 @@
         <v>618.4307250976562</v>
       </c>
       <c r="I562" t="n">
-        <v>960.3533935546875</v>
+        <v>960.3533325195312</v>
       </c>
       <c r="J562" t="n">
         <v>231.3999938964844</v>
@@ -18450,7 +18450,7 @@
         <v>1884.050048828125</v>
       </c>
       <c r="F563" t="n">
-        <v>1326.387084960938</v>
+        <v>1326.386962890625</v>
       </c>
       <c r="G563" t="n">
         <v>119.0400009155273</v>
@@ -18491,7 +18491,7 @@
         <v>599.8475952148438</v>
       </c>
       <c r="I564" t="n">
-        <v>925.3378295898438</v>
+        <v>925.337890625</v>
       </c>
       <c r="J564" t="n">
         <v>217.6000061035156</v>
@@ -18508,13 +18508,13 @@
         <v>1051.75</v>
       </c>
       <c r="D565" t="n">
-        <v>3102.26025390625</v>
+        <v>3102.260009765625</v>
       </c>
       <c r="E565" t="n">
         <v>1811.650024414062</v>
       </c>
       <c r="F565" t="n">
-        <v>1287.065185546875</v>
+        <v>1287.065063476562</v>
       </c>
       <c r="G565" t="n">
         <v>120.3199996948242</v>
@@ -18572,7 +18572,7 @@
         <v>1040.599975585938</v>
       </c>
       <c r="D567" t="n">
-        <v>3022.916015625</v>
+        <v>3022.916259765625</v>
       </c>
       <c r="E567" t="n">
         <v>1770.050048828125</v>
@@ -18587,7 +18587,7 @@
         <v>602.6153564453125</v>
       </c>
       <c r="I567" t="n">
-        <v>911.50146484375</v>
+        <v>911.5015258789062</v>
       </c>
       <c r="J567" t="n">
         <v>217.5500030517578</v>
@@ -18642,7 +18642,7 @@
         <v>1816.400024414062</v>
       </c>
       <c r="F569" t="n">
-        <v>1304.579833984375</v>
+        <v>1304.579956054688</v>
       </c>
       <c r="G569" t="n">
         <v>120.4899978637695</v>
@@ -18668,7 +18668,7 @@
         <v>1047.849975585938</v>
       </c>
       <c r="D570" t="n">
-        <v>3039.494140625</v>
+        <v>3039.493896484375</v>
       </c>
       <c r="E570" t="n">
         <v>1808.300048828125</v>
@@ -18683,7 +18683,7 @@
         <v>637.0137939453125</v>
       </c>
       <c r="I570" t="n">
-        <v>918.594482421875</v>
+        <v>918.5945434570312</v>
       </c>
       <c r="J570" t="n">
         <v>220.6499938964844</v>
@@ -18715,7 +18715,7 @@
         <v>630.9840698242188</v>
       </c>
       <c r="I571" t="n">
-        <v>917.2457885742188</v>
+        <v>917.245849609375</v>
       </c>
       <c r="J571" t="n">
         <v>234.6499938964844</v>
@@ -18747,7 +18747,7 @@
         <v>625.0533447265625</v>
       </c>
       <c r="I572" t="n">
-        <v>918.244873046875</v>
+        <v>918.2449340820312</v>
       </c>
       <c r="J572" t="n">
         <v>237.6000061035156</v>
@@ -18802,7 +18802,7 @@
         <v>1797.650024414062</v>
       </c>
       <c r="F574" t="n">
-        <v>1307.3427734375</v>
+        <v>1307.342895507812</v>
       </c>
       <c r="G574" t="n">
         <v>122.4899978637695</v>
@@ -18811,7 +18811,7 @@
         <v>612.7470703125</v>
       </c>
       <c r="I574" t="n">
-        <v>928.18505859375</v>
+        <v>928.1849975585938</v>
       </c>
       <c r="J574" t="n">
         <v>229.6000061035156</v>
@@ -18860,7 +18860,7 @@
         <v>1061.550048828125</v>
       </c>
       <c r="D576" t="n">
-        <v>2989.26123046875</v>
+        <v>2989.260986328125</v>
       </c>
       <c r="E576" t="n">
         <v>1799.800048828125</v>
@@ -18907,7 +18907,7 @@
         <v>600.440673828125</v>
       </c>
       <c r="I577" t="n">
-        <v>916.2468872070312</v>
+        <v>916.246826171875</v>
       </c>
       <c r="J577" t="n">
         <v>217.9499969482422</v>
@@ -18924,13 +18924,13 @@
         <v>1021.549987792969</v>
       </c>
       <c r="D578" t="n">
-        <v>2832.170654296875</v>
+        <v>2832.17041015625</v>
       </c>
       <c r="E578" t="n">
         <v>1726</v>
       </c>
       <c r="F578" t="n">
-        <v>1270.586547851562</v>
+        <v>1270.58642578125</v>
       </c>
       <c r="G578" t="n">
         <v>116.1100006103516</v>
@@ -18939,7 +18939,7 @@
         <v>587.0964965820312</v>
       </c>
       <c r="I578" t="n">
-        <v>902.2106323242188</v>
+        <v>902.210693359375</v>
       </c>
       <c r="J578" t="n">
         <v>215.1999969482422</v>
@@ -18956,7 +18956,7 @@
         <v>1019.5</v>
       </c>
       <c r="D579" t="n">
-        <v>2856.738037109375</v>
+        <v>2856.73779296875</v>
       </c>
       <c r="E579" t="n">
         <v>1773</v>
@@ -18971,7 +18971,7 @@
         <v>587.6895141601562</v>
       </c>
       <c r="I579" t="n">
-        <v>894.718017578125</v>
+        <v>894.7179565429688</v>
       </c>
       <c r="J579" t="n">
         <v>216.1499938964844</v>
@@ -18988,13 +18988,13 @@
         <v>980.0499877929688</v>
       </c>
       <c r="D580" t="n">
-        <v>2762.962646484375</v>
+        <v>2762.962890625</v>
       </c>
       <c r="E580" t="n">
         <v>1712.150024414062</v>
       </c>
       <c r="F580" t="n">
-        <v>1228.057739257812</v>
+        <v>1228.0576171875</v>
       </c>
       <c r="G580" t="n">
         <v>122.5599975585938</v>
@@ -19020,7 +19020,7 @@
         <v>990.5499877929688</v>
       </c>
       <c r="D581" t="n">
-        <v>2793.52197265625</v>
+        <v>2793.522216796875</v>
       </c>
       <c r="E581" t="n">
         <v>1714.75</v>
@@ -19035,7 +19035,7 @@
         <v>575.086669921875</v>
       </c>
       <c r="I581" t="n">
-        <v>866.1961059570312</v>
+        <v>866.1961669921875</v>
       </c>
       <c r="J581" t="n">
         <v>214</v>
@@ -19067,7 +19067,7 @@
         <v>581.4127807617188</v>
       </c>
       <c r="I582" t="n">
-        <v>861.001220703125</v>
+        <v>861.0012817382812</v>
       </c>
       <c r="J582" t="n">
         <v>216.1999969482422</v>
@@ -19084,7 +19084,7 @@
         <v>1022.049987792969</v>
       </c>
       <c r="D583" t="n">
-        <v>3033.502197265625</v>
+        <v>3033.501953125</v>
       </c>
       <c r="E583" t="n">
         <v>1788.800048828125</v>
@@ -19099,7 +19099,7 @@
         <v>603.1590576171875</v>
       </c>
       <c r="I583" t="n">
-        <v>908.0548706054688</v>
+        <v>908.054931640625</v>
       </c>
       <c r="J583" t="n">
         <v>219.8999938964844</v>
@@ -19154,7 +19154,7 @@
         <v>1844.400024414062</v>
       </c>
       <c r="F585" t="n">
-        <v>1327.225830078125</v>
+        <v>1327.225952148438</v>
       </c>
       <c r="G585" t="n">
         <v>128.0700073242188</v>
@@ -19195,7 +19195,7 @@
         <v>613.537841796875</v>
       </c>
       <c r="I586" t="n">
-        <v>912.7503051757812</v>
+        <v>912.750244140625</v>
       </c>
       <c r="J586" t="n">
         <v>216.3000030517578</v>
@@ -19250,7 +19250,7 @@
         <v>1866.449951171875</v>
       </c>
       <c r="F588" t="n">
-        <v>1359.9365234375</v>
+        <v>1359.936401367188</v>
       </c>
       <c r="G588" t="n">
         <v>138.2899932861328</v>
@@ -19323,7 +19323,7 @@
         <v>627.9693603515625</v>
       </c>
       <c r="I590" t="n">
-        <v>978.7852172851562</v>
+        <v>978.78515625</v>
       </c>
       <c r="J590" t="n">
         <v>242.3000030517578</v>
@@ -19372,7 +19372,7 @@
         <v>1088.099975585938</v>
       </c>
       <c r="D592" t="n">
-        <v>3239.72705078125</v>
+        <v>3239.726806640625</v>
       </c>
       <c r="E592" t="n">
         <v>1893.650024414062</v>
@@ -19387,7 +19387,7 @@
         <v>622.384521484375</v>
       </c>
       <c r="I592" t="n">
-        <v>950.7628173828125</v>
+        <v>950.7628784179688</v>
       </c>
       <c r="J592" t="n">
         <v>229.3500061035156</v>
@@ -19410,7 +19410,7 @@
         <v>1879.599975585938</v>
       </c>
       <c r="F593" t="n">
-        <v>1391.315063476562</v>
+        <v>1391.31494140625</v>
       </c>
       <c r="G593" t="n">
         <v>135.8500061035156</v>
@@ -19419,7 +19419,7 @@
         <v>622.8292846679688</v>
       </c>
       <c r="I593" t="n">
-        <v>949.813720703125</v>
+        <v>949.8137817382812</v>
       </c>
       <c r="J593" t="n">
         <v>231.1499938964844</v>
@@ -19442,7 +19442,7 @@
         <v>1874.900024414062</v>
       </c>
       <c r="F594" t="n">
-        <v>1365.166259765625</v>
+        <v>1365.166381835938</v>
       </c>
       <c r="G594" t="n">
         <v>139.6799926757812</v>
@@ -19451,7 +19451,7 @@
         <v>612.0056762695312</v>
       </c>
       <c r="I594" t="n">
-        <v>954.2593994140625</v>
+        <v>954.2593383789062</v>
       </c>
       <c r="J594" t="n">
         <v>229.9499969482422</v>
@@ -19506,7 +19506,7 @@
         <v>2038</v>
       </c>
       <c r="F596" t="n">
-        <v>1562.959838867188</v>
+        <v>1562.9599609375</v>
       </c>
       <c r="G596" t="n">
         <v>174.8999938964844</v>
@@ -19532,13 +19532,13 @@
         <v>977.5999755859375</v>
       </c>
       <c r="D597" t="n">
-        <v>2937.330322265625</v>
+        <v>2937.33056640625</v>
       </c>
       <c r="E597" t="n">
         <v>1646</v>
       </c>
       <c r="F597" t="n">
-        <v>1232.399169921875</v>
+        <v>1232.399291992188</v>
       </c>
       <c r="G597" t="n">
         <v>144.5899963378906</v>
@@ -19596,13 +19596,13 @@
         <v>1001.049987792969</v>
       </c>
       <c r="D599" t="n">
-        <v>3181.404296875</v>
+        <v>3181.404541015625</v>
       </c>
       <c r="E599" t="n">
         <v>1865.199951171875</v>
       </c>
       <c r="F599" t="n">
-        <v>1335.021118164062</v>
+        <v>1335.02099609375</v>
       </c>
       <c r="G599" t="n">
         <v>149.8699951171875</v>
@@ -19611,7 +19611,7 @@
         <v>603.0106811523438</v>
       </c>
       <c r="I599" t="n">
-        <v>968.59521484375</v>
+        <v>968.5951538085938</v>
       </c>
       <c r="J599" t="n">
         <v>228.8999938964844</v>
@@ -19634,7 +19634,7 @@
         <v>1864.25</v>
       </c>
       <c r="F600" t="n">
-        <v>1360.577758789062</v>
+        <v>1360.577880859375</v>
       </c>
       <c r="G600" t="n">
         <v>153.4100036621094</v>
@@ -19643,7 +19643,7 @@
         <v>614.130859375</v>
       </c>
       <c r="I600" t="n">
-        <v>977.1368408203125</v>
+        <v>977.1367797851562</v>
       </c>
       <c r="J600" t="n">
         <v>239.75</v>
@@ -19675,7 +19675,7 @@
         <v>632.9610595703125</v>
       </c>
       <c r="I601" t="n">
-        <v>969.8439331054688</v>
+        <v>969.843994140625</v>
       </c>
       <c r="J601" t="n">
         <v>242.9499969482422</v>
@@ -19707,7 +19707,7 @@
         <v>632.3679809570312</v>
       </c>
       <c r="I602" t="n">
-        <v>955.90771484375</v>
+        <v>955.9076538085938</v>
       </c>
       <c r="J602" t="n">
         <v>237.3899993896484</v>
@@ -19739,7 +19739,7 @@
         <v>660.9839477539062</v>
       </c>
       <c r="I603" t="n">
-        <v>950.7628173828125</v>
+        <v>950.7628784179688</v>
       </c>
       <c r="J603" t="n">
         <v>233.5500030517578</v>
@@ -20204,7 +20204,7 @@
         <v>1025.849975585938</v>
       </c>
       <c r="D618" t="n">
-        <v>3141.287353515625</v>
+        <v>3141.28759765625</v>
       </c>
       <c r="E618" t="n">
         <v>1766.800048828125</v>
@@ -20236,7 +20236,7 @@
         <v>1012.650024414062</v>
       </c>
       <c r="D619" t="n">
-        <v>3144.93408203125</v>
+        <v>3144.933837890625</v>
       </c>
       <c r="E619" t="n">
         <v>1754.300048828125</v>
@@ -20396,7 +20396,7 @@
         <v>1004.799987792969</v>
       </c>
       <c r="D624" t="n">
-        <v>3062.5615234375</v>
+        <v>3062.561767578125</v>
       </c>
       <c r="E624" t="n">
         <v>1735.25</v>
@@ -20460,7 +20460,7 @@
         <v>1022.25</v>
       </c>
       <c r="D626" t="n">
-        <v>3106.370361328125</v>
+        <v>3106.37060546875</v>
       </c>
       <c r="E626" t="n">
         <v>1759.949951171875</v>
@@ -20492,7 +20492,7 @@
         <v>1010.450012207031</v>
       </c>
       <c r="D627" t="n">
-        <v>3089.28662109375</v>
+        <v>3089.286376953125</v>
       </c>
       <c r="E627" t="n">
         <v>1747.550048828125</v>
@@ -20748,7 +20748,7 @@
         <v>1124.900024414062</v>
       </c>
       <c r="D635" t="n">
-        <v>3125.80224609375</v>
+        <v>3125.802001953125</v>
       </c>
       <c r="E635" t="n">
         <v>1832.400024414062</v>
@@ -20780,7 +20780,7 @@
         <v>1138.050048828125</v>
       </c>
       <c r="D636" t="n">
-        <v>3166.41357421875</v>
+        <v>3166.413818359375</v>
       </c>
       <c r="E636" t="n">
         <v>1847.199951171875</v>
@@ -20972,7 +20972,7 @@
         <v>1101.449951171875</v>
       </c>
       <c r="D642" t="n">
-        <v>3164.565673828125</v>
+        <v>3164.5654296875</v>
       </c>
       <c r="E642" t="n">
         <v>1778.150024414062</v>
@@ -21036,7 +21036,7 @@
         <v>1063</v>
       </c>
       <c r="D644" t="n">
-        <v>3148.780517578125</v>
+        <v>3148.7802734375</v>
       </c>
       <c r="E644" t="n">
         <v>1798.300048828125</v>
@@ -21068,7 +21068,7 @@
         <v>1071.25</v>
       </c>
       <c r="D645" t="n">
-        <v>3089.28662109375</v>
+        <v>3089.286376953125</v>
       </c>
       <c r="E645" t="n">
         <v>1825.650024414062</v>
@@ -21132,7 +21132,7 @@
         <v>1085.300048828125</v>
       </c>
       <c r="D647" t="n">
-        <v>3105.870849609375</v>
+        <v>3105.87109375</v>
       </c>
       <c r="E647" t="n">
         <v>1831</v>
@@ -21164,7 +21164,7 @@
         <v>1092.550048828125</v>
       </c>
       <c r="D648" t="n">
-        <v>3099.626953125</v>
+        <v>3099.626708984375</v>
       </c>
       <c r="E648" t="n">
         <v>1898</v>
@@ -21292,7 +21292,7 @@
         <v>1065.650024414062</v>
       </c>
       <c r="D652" t="n">
-        <v>3073.45166015625</v>
+        <v>3073.451416015625</v>
       </c>
       <c r="E652" t="n">
         <v>1900.900024414062</v>
@@ -21388,7 +21388,7 @@
         <v>1027.150024414062</v>
       </c>
       <c r="D655" t="n">
-        <v>3025.14697265625</v>
+        <v>3025.147216796875</v>
       </c>
       <c r="E655" t="n">
         <v>1861.099975585938</v>
@@ -21548,7 +21548,7 @@
         <v>1028.599975585938</v>
       </c>
       <c r="D660" t="n">
-        <v>3009.511962890625</v>
+        <v>3009.51171875</v>
       </c>
       <c r="E660" t="n">
         <v>1930.900024414062</v>
@@ -21708,7 +21708,7 @@
         <v>998.0999755859375</v>
       </c>
       <c r="D665" t="n">
-        <v>2935.08203125</v>
+        <v>2935.082275390625</v>
       </c>
       <c r="E665" t="n">
         <v>1814.449951171875</v>
@@ -21772,7 +21772,7 @@
         <v>983.2999877929688</v>
       </c>
       <c r="D667" t="n">
-        <v>2965.55322265625</v>
+        <v>2965.553466796875</v>
       </c>
       <c r="E667" t="n">
         <v>1788.199951171875</v>
@@ -21900,7 +21900,7 @@
         <v>979</v>
       </c>
       <c r="D671" t="n">
-        <v>2940.376708984375</v>
+        <v>2940.376953125</v>
       </c>
       <c r="E671" t="n">
         <v>1962.949951171875</v>
@@ -21932,7 +21932,7 @@
         <v>1007.150024414062</v>
       </c>
       <c r="D672" t="n">
-        <v>3005.66552734375</v>
+        <v>3005.665283203125</v>
       </c>
       <c r="E672" t="n">
         <v>2003.949951171875</v>
@@ -22124,7 +22124,7 @@
         <v>1009.650024414062</v>
       </c>
       <c r="D678" t="n">
-        <v>3132.895751953125</v>
+        <v>3132.8955078125</v>
       </c>
       <c r="E678" t="n">
         <v>1902.699951171875</v>
@@ -22444,7 +22444,7 @@
         <v>1004.700012207031</v>
       </c>
       <c r="D688" t="n">
-        <v>3101.77490234375</v>
+        <v>3101.774658203125</v>
       </c>
       <c r="E688" t="n">
         <v>1763</v>
@@ -22540,7 +22540,7 @@
         <v>1043.300048828125</v>
       </c>
       <c r="D691" t="n">
-        <v>2999.171630859375</v>
+        <v>2999.17138671875</v>
       </c>
       <c r="E691" t="n">
         <v>1736.050048828125</v>
@@ -22604,7 +22604,7 @@
         <v>1009.849975585938</v>
       </c>
       <c r="D693" t="n">
-        <v>2821.1396484375</v>
+        <v>2821.139404296875</v>
       </c>
       <c r="E693" t="n">
         <v>1684.449951171875</v>
@@ -22700,7 +22700,7 @@
         <v>919.3499755859375</v>
       </c>
       <c r="D696" t="n">
-        <v>2690.912109375</v>
+        <v>2690.912353515625</v>
       </c>
       <c r="E696" t="n">
         <v>1644</v>
@@ -22732,7 +22732,7 @@
         <v>940</v>
       </c>
       <c r="D697" t="n">
-        <v>2796.01318359375</v>
+        <v>2796.012939453125</v>
       </c>
       <c r="E697" t="n">
         <v>1613.150024414062</v>
@@ -22764,7 +22764,7 @@
         <v>930.5999755859375</v>
       </c>
       <c r="D698" t="n">
-        <v>2845.916015625</v>
+        <v>2845.916259765625</v>
       </c>
       <c r="E698" t="n">
         <v>1635.099975585938</v>
@@ -22796,7 +22796,7 @@
         <v>945.9000244140625</v>
       </c>
       <c r="D699" t="n">
-        <v>2966.502197265625</v>
+        <v>2966.50244140625</v>
       </c>
       <c r="E699" t="n">
         <v>1634.199951171875</v>
@@ -22860,7 +22860,7 @@
         <v>978.75</v>
       </c>
       <c r="D701" t="n">
-        <v>2946.72119140625</v>
+        <v>2946.720947265625</v>
       </c>
       <c r="E701" t="n">
         <v>1632.650024414062</v>
@@ -22892,7 +22892,7 @@
         <v>964.7999877929688</v>
       </c>
       <c r="D702" t="n">
-        <v>2894.669921875</v>
+        <v>2894.670166015625</v>
       </c>
       <c r="E702" t="n">
         <v>1611.949951171875</v>
@@ -22924,7 +22924,7 @@
         <v>1015</v>
       </c>
       <c r="D703" t="n">
-        <v>2912.802978515625</v>
+        <v>2912.80322265625</v>
       </c>
       <c r="E703" t="n">
         <v>1644.25</v>
@@ -23052,7 +23052,7 @@
         <v>901.9500122070312</v>
       </c>
       <c r="D707" t="n">
-        <v>2900.914306640625</v>
+        <v>2900.9140625</v>
       </c>
       <c r="E707" t="n">
         <v>1557.400024414062</v>
@@ -23116,7 +23116,7 @@
         <v>889.8499755859375</v>
       </c>
       <c r="D709" t="n">
-        <v>2814.046142578125</v>
+        <v>2814.0458984375</v>
       </c>
       <c r="E709" t="n">
         <v>1468.449951171875</v>
@@ -23148,7 +23148,7 @@
         <v>879.7000122070312</v>
       </c>
       <c r="D710" t="n">
-        <v>2824.136474609375</v>
+        <v>2824.13671875</v>
       </c>
       <c r="E710" t="n">
         <v>1490.300048828125</v>
@@ -23212,7 +23212,7 @@
         <v>871.5499877929688</v>
       </c>
       <c r="D712" t="n">
-        <v>2818.841552734375</v>
+        <v>2818.841796875</v>
       </c>
       <c r="E712" t="n">
         <v>1412.699951171875</v>
@@ -23276,7 +23276,7 @@
         <v>648.9500122070312</v>
       </c>
       <c r="D714" t="n">
-        <v>2225.900634765625</v>
+        <v>2225.90087890625</v>
       </c>
       <c r="E714" t="n">
         <v>1051.800048828125</v>
@@ -23308,7 +23308,7 @@
         <v>625.2000122070312</v>
       </c>
       <c r="D715" t="n">
-        <v>2255.372802734375</v>
+        <v>2255.373046875</v>
       </c>
       <c r="E715" t="n">
         <v>968.7999877929688</v>
@@ -23468,7 +23468,7 @@
         <v>807</v>
       </c>
       <c r="D720" t="n">
-        <v>2454.735107421875</v>
+        <v>2454.73486328125</v>
       </c>
       <c r="E720" t="n">
         <v>1327.949951171875</v>
@@ -23500,7 +23500,7 @@
         <v>801.8499755859375</v>
       </c>
       <c r="D721" t="n">
-        <v>2511.831298828125</v>
+        <v>2511.8310546875</v>
       </c>
       <c r="E721" t="n">
         <v>1312.800048828125</v>
@@ -23756,7 +23756,7 @@
         <v>832.4000244140625</v>
       </c>
       <c r="D729" t="n">
-        <v>2525.168701171875</v>
+        <v>2525.16845703125</v>
       </c>
       <c r="E729" t="n">
         <v>1198.400024414062</v>
@@ -23916,7 +23916,7 @@
         <v>767.5499877929688</v>
       </c>
       <c r="D734" t="n">
-        <v>2342.740478515625</v>
+        <v>2342.74072265625</v>
       </c>
       <c r="E734" t="n">
         <v>1034.349975585938</v>
@@ -23948,7 +23948,7 @@
         <v>773.2999877929688</v>
       </c>
       <c r="D735" t="n">
-        <v>2336.74609375</v>
+        <v>2336.746337890625</v>
       </c>
       <c r="E735" t="n">
         <v>1034.650024414062</v>
@@ -24044,7 +24044,7 @@
         <v>805.9500122070312</v>
       </c>
       <c r="D738" t="n">
-        <v>2407.67919921875</v>
+        <v>2407.679443359375</v>
       </c>
       <c r="E738" t="n">
         <v>1054</v>
@@ -24204,7 +24204,7 @@
         <v>821.25</v>
       </c>
       <c r="D743" t="n">
-        <v>2562.18359375</v>
+        <v>2562.183837890625</v>
       </c>
       <c r="E743" t="n">
         <v>1038.25</v>
@@ -24236,7 +24236,7 @@
         <v>768.5999755859375</v>
       </c>
       <c r="D744" t="n">
-        <v>2472.118408203125</v>
+        <v>2472.11865234375</v>
       </c>
       <c r="E744" t="n">
         <v>982.5999755859375</v>
@@ -24268,7 +24268,7 @@
         <v>781.5499877929688</v>
       </c>
       <c r="D745" t="n">
-        <v>2518.17529296875</v>
+        <v>2518.175048828125</v>
       </c>
       <c r="E745" t="n">
         <v>1005.5</v>
@@ -24556,7 +24556,7 @@
         <v>815.75</v>
       </c>
       <c r="D754" t="n">
-        <v>2440.498291015625</v>
+        <v>2440.49853515625</v>
       </c>
       <c r="E754" t="n">
         <v>1066.75</v>
@@ -24588,7 +24588,7 @@
         <v>813.3499755859375</v>
       </c>
       <c r="D755" t="n">
-        <v>2382.053466796875</v>
+        <v>2382.0537109375</v>
       </c>
       <c r="E755" t="n">
         <v>1045.699951171875</v>
@@ -24684,7 +24684,7 @@
         <v>790.4500122070312</v>
       </c>
       <c r="D758" t="n">
-        <v>2312.9189453125</v>
+        <v>2312.918701171875</v>
       </c>
       <c r="E758" t="n">
         <v>1012.099975585938</v>
@@ -24716,7 +24716,7 @@
         <v>755.6500244140625</v>
       </c>
       <c r="D759" t="n">
-        <v>2257.57080078125</v>
+        <v>2257.571044921875</v>
       </c>
       <c r="E759" t="n">
         <v>998.9500122070312</v>
@@ -24812,7 +24812,7 @@
         <v>740.25</v>
       </c>
       <c r="D762" t="n">
-        <v>2250.4775390625</v>
+        <v>2250.477783203125</v>
       </c>
       <c r="E762" t="n">
         <v>971.8499755859375</v>
@@ -24908,7 +24908,7 @@
         <v>728.1500244140625</v>
       </c>
       <c r="D765" t="n">
-        <v>2259.71923828125</v>
+        <v>2259.718994140625</v>
       </c>
       <c r="E765" t="n">
         <v>970.0999755859375</v>
@@ -25516,7 +25516,7 @@
         <v>654.0499877929688</v>
       </c>
       <c r="D784" t="n">
-        <v>2115.10546875</v>
+        <v>2115.105224609375</v>
       </c>
       <c r="E784" t="n">
         <v>804.0999755859375</v>
@@ -25996,7 +25996,7 @@
         <v>816.5499877929688</v>
       </c>
       <c r="D799" t="n">
-        <v>2318.163818359375</v>
+        <v>2318.1640625</v>
       </c>
       <c r="E799" t="n">
         <v>923.4000244140625</v>
@@ -26028,7 +26028,7 @@
         <v>803</v>
       </c>
       <c r="D800" t="n">
-        <v>2310.42138671875</v>
+        <v>2310.421142578125</v>
       </c>
       <c r="E800" t="n">
         <v>912.0999755859375</v>
@@ -26060,7 +26060,7 @@
         <v>872.8499755859375</v>
       </c>
       <c r="D801" t="n">
-        <v>2361.12353515625</v>
+        <v>2361.123291015625</v>
       </c>
       <c r="E801" t="n">
         <v>959.9000244140625</v>
@@ -26380,7 +26380,7 @@
         <v>887.4000244140625</v>
       </c>
       <c r="D811" t="n">
-        <v>2415.92138671875</v>
+        <v>2415.921630859375</v>
       </c>
       <c r="E811" t="n">
         <v>936.6500244140625</v>
@@ -26412,7 +26412,7 @@
         <v>895.1500244140625</v>
       </c>
       <c r="D812" t="n">
-        <v>2413.32421875</v>
+        <v>2413.323974609375</v>
       </c>
       <c r="E812" t="n">
         <v>945.5999755859375</v>
@@ -26444,7 +26444,7 @@
         <v>914.1500244140625</v>
       </c>
       <c r="D813" t="n">
-        <v>2415.822021484375</v>
+        <v>2415.82177734375</v>
       </c>
       <c r="E813" t="n">
         <v>947.1500244140625</v>
@@ -26508,7 +26508,7 @@
         <v>929.5999755859375</v>
       </c>
       <c r="D815" t="n">
-        <v>2443.19580078125</v>
+        <v>2443.196044921875</v>
       </c>
       <c r="E815" t="n">
         <v>943.2999877929688</v>
@@ -26540,7 +26540,7 @@
         <v>938.7999877929688</v>
       </c>
       <c r="D816" t="n">
-        <v>2451.28857421875</v>
+        <v>2451.288330078125</v>
       </c>
       <c r="E816" t="n">
         <v>952.5</v>
@@ -26636,7 +26636,7 @@
         <v>925.2999877929688</v>
       </c>
       <c r="D819" t="n">
-        <v>2367.5673828125</v>
+        <v>2367.567138671875</v>
       </c>
       <c r="E819" t="n">
         <v>941</v>
@@ -26700,7 +26700,7 @@
         <v>899.6500244140625</v>
       </c>
       <c r="D821" t="n">
-        <v>2299.1318359375</v>
+        <v>2299.131591796875</v>
       </c>
       <c r="E821" t="n">
         <v>900.7000122070312</v>
@@ -26764,7 +26764,7 @@
         <v>937.2000122070312</v>
       </c>
       <c r="D823" t="n">
-        <v>2453.1865234375</v>
+        <v>2453.186279296875</v>
       </c>
       <c r="E823" t="n">
         <v>965.7000122070312</v>
@@ -26796,7 +26796,7 @@
         <v>907.4000244140625</v>
       </c>
       <c r="D824" t="n">
-        <v>2351.7822265625</v>
+        <v>2351.781982421875</v>
       </c>
       <c r="E824" t="n">
         <v>923.25</v>
@@ -26828,7 +26828,7 @@
         <v>871.5999755859375</v>
       </c>
       <c r="D825" t="n">
-        <v>2350.8828125</v>
+        <v>2350.883056640625</v>
       </c>
       <c r="E825" t="n">
         <v>917.25</v>
@@ -26924,7 +26924,7 @@
         <v>894.2999877929688</v>
       </c>
       <c r="D828" t="n">
-        <v>2423.014892578125</v>
+        <v>2423.01513671875</v>
       </c>
       <c r="E828" t="n">
         <v>940.5499877929688</v>
@@ -26956,7 +26956,7 @@
         <v>904.2000122070312</v>
       </c>
       <c r="D829" t="n">
-        <v>2438.89990234375</v>
+        <v>2438.899658203125</v>
       </c>
       <c r="E829" t="n">
         <v>958.0499877929688</v>
@@ -27084,7 +27084,7 @@
         <v>888.9000244140625</v>
       </c>
       <c r="D833" t="n">
-        <v>2538.206298828125</v>
+        <v>2538.20654296875</v>
       </c>
       <c r="E833" t="n">
         <v>1014</v>
@@ -27148,7 +27148,7 @@
         <v>872.1500244140625</v>
       </c>
       <c r="D835" t="n">
-        <v>2498.044189453125</v>
+        <v>2498.0439453125</v>
       </c>
       <c r="E835" t="n">
         <v>996.5</v>
@@ -27212,7 +27212,7 @@
         <v>876.5499877929688</v>
       </c>
       <c r="D837" t="n">
-        <v>2537.606689453125</v>
+        <v>2537.60693359375</v>
       </c>
       <c r="E837" t="n">
         <v>986.9500122070312</v>
@@ -27276,7 +27276,7 @@
         <v>879.1500244140625</v>
       </c>
       <c r="D839" t="n">
-        <v>2537.90673828125</v>
+        <v>2537.906494140625</v>
       </c>
       <c r="E839" t="n">
         <v>1013</v>
@@ -27340,7 +27340,7 @@
         <v>880.9500122070312</v>
       </c>
       <c r="D841" t="n">
-        <v>2538.40625</v>
+        <v>2538.406005859375</v>
       </c>
       <c r="E841" t="n">
         <v>1019.049987792969</v>
@@ -27564,7 +27564,7 @@
         <v>901.4000244140625</v>
       </c>
       <c r="D848" t="n">
-        <v>2579.667236328125</v>
+        <v>2579.66748046875</v>
       </c>
       <c r="E848" t="n">
         <v>1034.300048828125</v>
@@ -27628,7 +27628,7 @@
         <v>904.5</v>
       </c>
       <c r="D850" t="n">
-        <v>2578.76806640625</v>
+        <v>2578.767822265625</v>
       </c>
       <c r="E850" t="n">
         <v>1046.800048828125</v>
@@ -27660,7 +27660,7 @@
         <v>876.9500122070312</v>
       </c>
       <c r="D851" t="n">
-        <v>2541.303466796875</v>
+        <v>2541.30322265625</v>
       </c>
       <c r="E851" t="n">
         <v>1015.799987792969</v>
@@ -38578,7 +38578,7 @@
         <v>-3.606959520527531</v>
       </c>
       <c r="D18" t="n">
-        <v>9.498968063267776</v>
+        <v>9.498979690765118</v>
       </c>
       <c r="E18" t="n">
         <v>12.61795956907161</v>
@@ -38610,7 +38610,7 @@
         <v>3.170874359410836</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6261330564401923</v>
+        <v>-0.6261436087702577</v>
       </c>
       <c r="E19" t="n">
         <v>-5.054552361040388</v>
@@ -38802,7 +38802,7 @@
         <v>-3.313030396492445</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.014327393575347</v>
+        <v>-6.01432006944953</v>
       </c>
       <c r="E25" t="n">
         <v>-15.99831345747761</v>
@@ -38834,7 +38834,7 @@
         <v>0.2233472250815938</v>
       </c>
       <c r="D26" t="n">
-        <v>3.858450973590455</v>
+        <v>3.858442880098312</v>
       </c>
       <c r="E26" t="n">
         <v>3.511678910886973</v>
@@ -38866,7 +38866,7 @@
         <v>-11.48016509015537</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.734321642174832</v>
+        <v>-4.734328987463099</v>
       </c>
       <c r="E27" t="n">
         <v>-0.4899267538455265</v>
@@ -38898,7 +38898,7 @@
         <v>14.10739225812152</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2439363004366091</v>
+        <v>-0.2439286089246928</v>
       </c>
       <c r="E28" t="n">
         <v>3.264752948883731</v>
@@ -38968,7 +38968,7 @@
         <v>6.158036863040528</v>
       </c>
       <c r="F30" t="n">
-        <v>8.491214362386735</v>
+        <v>8.491204232254468</v>
       </c>
       <c r="G30" t="n">
         <v>23.40599746783077</v>
@@ -38977,7 +38977,7 @@
         <v>2.282621168438115</v>
       </c>
       <c r="I30" t="n">
-        <v>11.86094860233686</v>
+        <v>11.86095595803696</v>
       </c>
       <c r="J30" t="n">
         <v>7.970377746731483</v>
@@ -39000,7 +39000,7 @@
         <v>-2.043429665210794</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.26318745484254</v>
+        <v>-1.263178235505569</v>
       </c>
       <c r="G31" t="n">
         <v>14.73397846832833</v>
@@ -39009,7 +39009,7 @@
         <v>1.232976914127226</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2752207373969195</v>
+        <v>0.275214143546143</v>
       </c>
       <c r="J31" t="n">
         <v>9.047733448417429</v>
@@ -39041,7 +39041,7 @@
         <v>1.064507492928168</v>
       </c>
       <c r="I32" t="n">
-        <v>-9.662184894372693</v>
+        <v>-9.662174131992574</v>
       </c>
       <c r="J32" t="n">
         <v>-17.54454747637502</v>
@@ -39073,7 +39073,7 @@
         <v>8.138513568615835</v>
       </c>
       <c r="I33" t="n">
-        <v>1.313789268309984</v>
+        <v>1.313777198310517</v>
       </c>
       <c r="J33" t="n">
         <v>-5.670485929559521</v>
@@ -39090,13 +39090,13 @@
         <v>2.113313467457556</v>
       </c>
       <c r="D34" t="n">
-        <v>10.28623492748986</v>
+        <v>10.28624439107486</v>
       </c>
       <c r="E34" t="n">
         <v>4.536628125978392</v>
       </c>
       <c r="F34" t="n">
-        <v>17.89428211519826</v>
+        <v>17.8942749962139</v>
       </c>
       <c r="G34" t="n">
         <v>7.150340115695419</v>
@@ -39122,13 +39122,13 @@
         <v>19.83612797148144</v>
       </c>
       <c r="D35" t="n">
-        <v>20.79243993442199</v>
+        <v>20.79242956930774</v>
       </c>
       <c r="E35" t="n">
         <v>55.22938610073884</v>
       </c>
       <c r="F35" t="n">
-        <v>24.08842416877926</v>
+        <v>24.08844095975935</v>
       </c>
       <c r="G35" t="n">
         <v>21.70335465261326</v>
@@ -39154,13 +39154,13 @@
         <v>13.36061811535836</v>
       </c>
       <c r="D36" t="n">
-        <v>2.784753621212066</v>
+        <v>2.784742670775175</v>
       </c>
       <c r="E36" t="n">
         <v>12.8503286652526</v>
       </c>
       <c r="F36" t="n">
-        <v>5.192732098296493</v>
+        <v>5.192732507593223</v>
       </c>
       <c r="G36" t="n">
         <v>18.85415552448646</v>
@@ -39186,13 +39186,13 @@
         <v>-4.992287837955112</v>
       </c>
       <c r="D37" t="n">
-        <v>-4.940138180910026</v>
+        <v>-4.9401280534632</v>
       </c>
       <c r="E37" t="n">
         <v>-7.648280214024627</v>
       </c>
       <c r="F37" t="n">
-        <v>-4.896078404180482</v>
+        <v>-4.896085900373349</v>
       </c>
       <c r="G37" t="n">
         <v>-3.815071313970964</v>
@@ -39218,13 +39218,13 @@
         <v>-0.20937399858032</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2211490209924283</v>
+        <v>-0.2211591036942795</v>
       </c>
       <c r="E38" t="n">
         <v>6.299466802567633</v>
       </c>
       <c r="F38" t="n">
-        <v>4.159296257236145</v>
+        <v>4.159304389975604</v>
       </c>
       <c r="G38" t="n">
         <v>17.47587201091527</v>
@@ -39250,13 +39250,13 @@
         <v>-1.066163015700394</v>
       </c>
       <c r="D39" t="n">
-        <v>-2.927132781209218</v>
+        <v>-2.927122971947371</v>
       </c>
       <c r="E39" t="n">
         <v>-15.05991192358821</v>
       </c>
       <c r="F39" t="n">
-        <v>1.844846410574297</v>
+        <v>1.844838458547282</v>
       </c>
       <c r="G39" t="n">
         <v>17.56312168975038</v>
@@ -39265,7 +39265,7 @@
         <v>-7.473006572657748</v>
       </c>
       <c r="I39" t="n">
-        <v>-4.203720527170574</v>
+        <v>-4.203711708872182</v>
       </c>
       <c r="J39" t="n">
         <v>-6.357877502164633</v>
@@ -39288,16 +39288,16 @@
         <v>15.58304478376236</v>
       </c>
       <c r="F40" t="n">
-        <v>5.92888431923726</v>
+        <v>5.928875396325339</v>
       </c>
       <c r="G40" t="n">
         <v>9.385628401317447</v>
       </c>
       <c r="H40" t="n">
-        <v>9.344479433073394</v>
+        <v>9.344487405733215</v>
       </c>
       <c r="I40" t="n">
-        <v>1.429253550515419</v>
+        <v>1.429244213687864</v>
       </c>
       <c r="J40" t="n">
         <v>0.6376483051671933</v>
@@ -39320,13 +39320,13 @@
         <v>-3.252530162210432</v>
       </c>
       <c r="F41" t="n">
-        <v>0.05413338709308047</v>
+        <v>0.05414181514649119</v>
       </c>
       <c r="G41" t="n">
         <v>0.08011399015193099</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5429713919922641</v>
+        <v>0.5429640610794095</v>
       </c>
       <c r="I41" t="n">
         <v>-1.437929259655957</v>
@@ -39346,7 +39346,7 @@
         <v>-24.55194044908406</v>
       </c>
       <c r="D42" t="n">
-        <v>29.52803240496473</v>
+        <v>29.52804063390415</v>
       </c>
       <c r="E42" t="n">
         <v>2.807572261517488</v>
@@ -39358,7 +39358,7 @@
         <v>11.02957293714546</v>
       </c>
       <c r="H42" t="n">
-        <v>6.834808549531513</v>
+        <v>6.834800182265521</v>
       </c>
       <c r="I42" t="n">
         <v>-29.71957821123238</v>
@@ -39378,7 +39378,7 @@
         <v>3.66547140892719</v>
       </c>
       <c r="D43" t="n">
-        <v>9.968874448585474</v>
+        <v>9.968859779442596</v>
       </c>
       <c r="E43" t="n">
         <v>7.927137678102603</v>
@@ -39390,7 +39390,7 @@
         <v>17.35386633308638</v>
       </c>
       <c r="H43" t="n">
-        <v>8.466693273242566</v>
+        <v>8.466692553990661</v>
       </c>
       <c r="I43" t="n">
         <v>8.902338132359366</v>
@@ -39410,7 +39410,7 @@
         <v>54.46413907015047</v>
       </c>
       <c r="D44" t="n">
-        <v>28.34621310918004</v>
+        <v>28.34621056745881</v>
       </c>
       <c r="E44" t="n">
         <v>81.56811180262491</v>
@@ -39422,7 +39422,7 @@
         <v>30.96377100161289</v>
       </c>
       <c r="H44" t="n">
-        <v>6.854717482614991</v>
+        <v>6.854726560003721</v>
       </c>
       <c r="I44" t="n">
         <v>27.8829882720756</v>
@@ -39442,7 +39442,7 @@
         <v>-63.75986333629861</v>
       </c>
       <c r="D45" t="n">
-        <v>-54.13934287695892</v>
+        <v>-54.13933499301339</v>
       </c>
       <c r="E45" t="n">
         <v>-60.34806944094112</v>
@@ -39474,7 +39474,7 @@
         <v>-31.48595153036594</v>
       </c>
       <c r="D46" t="n">
-        <v>-22.9230130346567</v>
+        <v>-22.92301937376114</v>
       </c>
       <c r="E46" t="n">
         <v>-36.64458052185531</v>
@@ -39489,7 +39489,7 @@
         <v>-23.44970934142473</v>
       </c>
       <c r="I46" t="n">
-        <v>-42.91130303183772</v>
+        <v>-42.91129925242932</v>
       </c>
       <c r="J46" t="n">
         <v>-28.25332132398638</v>
@@ -39512,7 +39512,7 @@
         <v>-8.726669084425943</v>
       </c>
       <c r="F47" t="n">
-        <v>-7.139625469848454</v>
+        <v>-7.139618906309286</v>
       </c>
       <c r="G47" t="n">
         <v>-9.977464913384882</v>
@@ -39521,7 +39521,7 @@
         <v>-8.173465264910885</v>
       </c>
       <c r="I47" t="n">
-        <v>1.654398082501785</v>
+        <v>1.65439135273775</v>
       </c>
       <c r="J47" t="n">
         <v>-22.51848593969048</v>
@@ -39544,7 +39544,7 @@
         <v>0.6467306237967874</v>
       </c>
       <c r="F48" t="n">
-        <v>6.975903128898064</v>
+        <v>6.975887478934362</v>
       </c>
       <c r="G48" t="n">
         <v>-0.6419831048444791</v>
@@ -39553,7 +39553,7 @@
         <v>7.092594636276428</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8298873160666131</v>
+        <v>0.8298941579935271</v>
       </c>
       <c r="J48" t="n">
         <v>38.71017491622961</v>
@@ -39576,16 +39576,16 @@
         <v>-6.984259690113759</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3533717178334728</v>
+        <v>0.3533793058025037</v>
       </c>
       <c r="G49" t="n">
         <v>-10.33466386438756</v>
       </c>
       <c r="H49" t="n">
-        <v>3.36503152654235</v>
+        <v>3.365025301034952</v>
       </c>
       <c r="I49" t="n">
-        <v>7.874608894856761</v>
+        <v>7.874609471274563</v>
       </c>
       <c r="J49" t="n">
         <v>-13.75150501852815</v>
@@ -39614,10 +39614,10 @@
         <v>-9.771716243293183</v>
       </c>
       <c r="H50" t="n">
-        <v>25.3738531445044</v>
+        <v>25.37386069556771</v>
       </c>
       <c r="I50" t="n">
-        <v>-10.81722885248916</v>
+        <v>-10.81723538062699</v>
       </c>
       <c r="J50" t="n">
         <v>-20.88017226023993</v>
@@ -39640,13 +39640,13 @@
         <v>12.02464734774498</v>
       </c>
       <c r="F51" t="n">
-        <v>10.27236998744312</v>
+        <v>10.27236099604043</v>
       </c>
       <c r="G51" t="n">
         <v>31.85220530081916</v>
       </c>
       <c r="H51" t="n">
-        <v>9.725183453655561</v>
+        <v>9.725192544846495</v>
       </c>
       <c r="I51" t="n">
         <v>19.75410166075582</v>
@@ -39672,16 +39672,16 @@
         <v>12.70211332333331</v>
       </c>
       <c r="F52" t="n">
-        <v>14.4246082042711</v>
+        <v>14.42461753424029</v>
       </c>
       <c r="G52" t="n">
         <v>19.44074810734559</v>
       </c>
       <c r="H52" t="n">
-        <v>3.250685599129</v>
+        <v>3.250677044378025</v>
       </c>
       <c r="I52" t="n">
-        <v>30.698835810077</v>
+        <v>30.69884916444059</v>
       </c>
       <c r="J52" t="n">
         <v>45.79545801336116</v>
@@ -39704,7 +39704,7 @@
         <v>2.151990548444327</v>
       </c>
       <c r="F53" t="n">
-        <v>-9.16402572525814</v>
+        <v>-9.164018026937349</v>
       </c>
       <c r="G53" t="n">
         <v>-18.6852305428317</v>
@@ -39713,7 +39713,7 @@
         <v>-1.732545046843736</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2085052693744482</v>
+        <v>-0.2085358159142237</v>
       </c>
       <c r="J53" t="n">
         <v>3.2258064516129</v>
@@ -39736,7 +39736,7 @@
         <v>-34.47516583955436</v>
       </c>
       <c r="F54" t="n">
-        <v>-13.60928974471389</v>
+        <v>-13.60930339146794</v>
       </c>
       <c r="G54" t="n">
         <v>15.30230404450439</v>
@@ -39745,7 +39745,7 @@
         <v>-0.7522815575130015</v>
       </c>
       <c r="I54" t="n">
-        <v>-2.164487999933762</v>
+        <v>-2.164448529144036</v>
       </c>
       <c r="J54" t="n">
         <v>-10.23953527808792</v>
@@ -39768,7 +39768,7 @@
         <v>50.56145204702873</v>
       </c>
       <c r="F55" t="n">
-        <v>10.61741361378157</v>
+        <v>10.61741275388277</v>
       </c>
       <c r="G55" t="n">
         <v>51.45866829146802</v>
@@ -39777,7 +39777,7 @@
         <v>24.37762270562873</v>
       </c>
       <c r="I55" t="n">
-        <v>14.00829734133877</v>
+        <v>14.00826162894047</v>
       </c>
       <c r="J55" t="n">
         <v>-16.3215872474704</v>
@@ -39788,7 +39788,7 @@
         <v>44651</v>
       </c>
       <c r="B56" t="n">
-        <v>2.977292721997449</v>
+        <v>2.977299016454538</v>
       </c>
       <c r="C56" t="n">
         <v>10.95155597333577</v>
@@ -39800,7 +39800,7 @@
         <v>3.867848856109002</v>
       </c>
       <c r="F56" t="n">
-        <v>9.427552850962662</v>
+        <v>9.427571411441527</v>
       </c>
       <c r="G56" t="n">
         <v>49.57575942530777</v>
@@ -39809,7 +39809,7 @@
         <v>-2.747517525648757</v>
       </c>
       <c r="I56" t="n">
-        <v>35.33520825688752</v>
+        <v>35.33523406391175</v>
       </c>
       <c r="J56" t="n">
         <v>52.09380234505863</v>
@@ -39820,7 +39820,7 @@
         <v>44620</v>
       </c>
       <c r="B57" t="n">
-        <v>-8.601111826336716</v>
+        <v>-8.60111741306685</v>
       </c>
       <c r="C57" t="n">
         <v>8.295696174558387</v>
@@ -39832,16 +39832,16 @@
         <v>-1.834542248835702</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.228524456736058</v>
+        <v>-1.228541856401</v>
       </c>
       <c r="G57" t="n">
         <v>16.47058823529413</v>
       </c>
       <c r="H57" t="n">
-        <v>-13.93946505354093</v>
+        <v>-13.93948000276193</v>
       </c>
       <c r="I57" t="n">
-        <v>-12.77968297438892</v>
+        <v>-12.7796838322096</v>
       </c>
       <c r="J57" t="n">
         <v>34.45945945945945</v>
@@ -40173,7 +40173,7 @@
         <v>-20.15054794111463</v>
       </c>
       <c r="D9" t="n">
-        <v>-19.36318556372528</v>
+        <v>-19.36317927985075</v>
       </c>
       <c r="E9" t="n">
         <v>-45.30404278767618</v>
@@ -40205,7 +40205,7 @@
         <v>1.233273086601194</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.299896279961799</v>
+        <v>-1.299903971473726</v>
       </c>
       <c r="E10" t="n">
         <v>6.367391504621644</v>
@@ -40269,13 +40269,13 @@
         <v>-1.821663765539083</v>
       </c>
       <c r="D12" t="n">
-        <v>12.22028207403472</v>
+        <v>12.22029170357897</v>
       </c>
       <c r="E12" t="n">
         <v>14.91233715805025</v>
       </c>
       <c r="F12" t="n">
-        <v>30.99527449183894</v>
+        <v>30.99526658175804</v>
       </c>
       <c r="G12" t="n">
         <v>1.64715164909115</v>
@@ -40301,13 +40301,13 @@
         <v>29.06510336315953</v>
       </c>
       <c r="D13" t="n">
-        <v>18.0227233575484</v>
+        <v>18.02271323010156</v>
       </c>
       <c r="E13" t="n">
         <v>61.77885432844141</v>
       </c>
       <c r="F13" t="n">
-        <v>24.1410543620159</v>
+        <v>24.14106185820877</v>
       </c>
       <c r="G13" t="n">
         <v>39.13101305001452</v>
@@ -40339,13 +40339,13 @@
         <v>4.360925989567699</v>
       </c>
       <c r="F14" t="n">
-        <v>12.37028767662276</v>
+        <v>12.37027821111969</v>
       </c>
       <c r="G14" t="n">
         <v>51.07063441994313</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3229691550785674</v>
+        <v>0.3229764699508975</v>
       </c>
       <c r="I14" t="n">
         <v>-6.28072516525251</v>
@@ -40365,19 +40365,19 @@
         <v>-22.73802835392045</v>
       </c>
       <c r="D15" t="n">
-        <v>36.42494342110834</v>
+        <v>36.42493388999573</v>
       </c>
       <c r="E15" t="n">
         <v>7.348351382394469</v>
       </c>
       <c r="F15" t="n">
-        <v>16.98843129458243</v>
+        <v>16.98844114909532</v>
       </c>
       <c r="G15" t="n">
         <v>30.40188313846057</v>
       </c>
       <c r="H15" t="n">
-        <v>16.50938034711897</v>
+        <v>16.5093619544856</v>
       </c>
       <c r="I15" t="n">
         <v>-24.56352566485572</v>
@@ -40397,7 +40397,7 @@
         <v>-61.64719560517645</v>
       </c>
       <c r="D16" t="n">
-        <v>-54.63216427358078</v>
+        <v>-54.63216110402858</v>
       </c>
       <c r="E16" t="n">
         <v>-54.3871000029952</v>
@@ -40409,10 +40409,10 @@
         <v>-36.03738976394022</v>
       </c>
       <c r="H16" t="n">
-        <v>-30.25186064741821</v>
+        <v>-30.25185472226123</v>
       </c>
       <c r="I16" t="n">
-        <v>-76.50188891967301</v>
+        <v>-76.50188736404179</v>
       </c>
       <c r="J16" t="n">
         <v>-44.5633303309966</v>
@@ -40441,10 +40441,10 @@
         <v>-19.79919371493109</v>
       </c>
       <c r="H17" t="n">
-        <v>1.648571051713899</v>
+        <v>1.648564929586116</v>
       </c>
       <c r="I17" t="n">
-        <v>10.56933284767878</v>
+        <v>10.56933362134915</v>
       </c>
       <c r="J17" t="n">
         <v>-7.304651090116887</v>
@@ -40473,10 +40473,10 @@
         <v>42.09624763531581</v>
       </c>
       <c r="H18" t="n">
-        <v>42.03855095864111</v>
+        <v>42.03855951339208</v>
       </c>
       <c r="I18" t="n">
-        <v>39.58639118085186</v>
+        <v>39.58639522565499</v>
       </c>
       <c r="J18" t="n">
         <v>111.9602203369141</v>
@@ -40499,7 +40499,7 @@
         <v>0.7781910896766497</v>
       </c>
       <c r="F19" t="n">
-        <v>-13.19426413035678</v>
+        <v>-13.19427116070798</v>
       </c>
       <c r="G19" t="n">
         <v>42.00431940783369</v>
@@ -40508,7 +40508,7 @@
         <v>21.30326534957958</v>
       </c>
       <c r="I19" t="n">
-        <v>11.30803339499058</v>
+        <v>11.30800936277003</v>
       </c>
       <c r="J19" t="n">
         <v>-22.46696035242291</v>

--- a/dashboards/Adani Group.xlsx
+++ b/dashboards/Adani Group.xlsx
@@ -492,13 +492,13 @@
         <v>1731.099975585938</v>
       </c>
       <c r="D2" t="n">
-        <v>1713.325317382812</v>
+        <v>1713.3251953125</v>
       </c>
       <c r="E2" t="n">
         <v>1346.900024414062</v>
       </c>
       <c r="F2" t="n">
-        <v>717.017822265625</v>
+        <v>717.0178833007812</v>
       </c>
       <c r="G2" t="n">
         <v>20.26000022888184</v>
@@ -507,7 +507,7 @@
         <v>372.3961181640625</v>
       </c>
       <c r="I2" t="n">
-        <v>1741.24853515625</v>
+        <v>1741.248657226562</v>
       </c>
       <c r="J2" t="n">
         <v>114.9499969482422</v>
@@ -524,7 +524,7 @@
         <v>1754.949951171875</v>
       </c>
       <c r="D3" t="n">
-        <v>1715.17138671875</v>
+        <v>1715.171264648438</v>
       </c>
       <c r="E3" t="n">
         <v>1366.699951171875</v>
@@ -536,10 +536,10 @@
         <v>20.11000061035156</v>
       </c>
       <c r="H3" t="n">
-        <v>375.7159729003906</v>
+        <v>375.7160034179688</v>
       </c>
       <c r="I3" t="n">
-        <v>1751.383544921875</v>
+        <v>1751.383666992188</v>
       </c>
       <c r="J3" t="n">
         <v>114.25</v>
@@ -588,7 +588,7 @@
         <v>1760.050048828125</v>
       </c>
       <c r="D5" t="n">
-        <v>1709.284301757812</v>
+        <v>1709.2841796875</v>
       </c>
       <c r="E5" t="n">
         <v>1409.800048828125</v>
@@ -632,7 +632,7 @@
         <v>20.04000091552734</v>
       </c>
       <c r="H6" t="n">
-        <v>382.2593383789062</v>
+        <v>382.2593078613281</v>
       </c>
       <c r="I6" t="n">
         <v>1785.184204101562</v>
@@ -646,13 +646,13 @@
         <v>44571</v>
       </c>
       <c r="B7" t="n">
-        <v>2217.888427734375</v>
+        <v>2217.888671875</v>
       </c>
       <c r="C7" t="n">
         <v>1819.699951171875</v>
       </c>
       <c r="D7" t="n">
-        <v>1748.696166992188</v>
+        <v>1748.696411132812</v>
       </c>
       <c r="E7" t="n">
         <v>1438.900024414062</v>
@@ -667,7 +667,7 @@
         <v>384.2800903320312</v>
       </c>
       <c r="I7" t="n">
-        <v>1760.769897460938</v>
+        <v>1760.77001953125</v>
       </c>
       <c r="J7" t="n">
         <v>120.0500030517578</v>
@@ -684,7 +684,7 @@
         <v>1867.449951171875</v>
       </c>
       <c r="D8" t="n">
-        <v>1839.79296875</v>
+        <v>1839.793090820312</v>
       </c>
       <c r="E8" t="n">
         <v>1567.949951171875</v>
@@ -716,7 +716,7 @@
         <v>1928.25</v>
       </c>
       <c r="D9" t="n">
-        <v>1826.023681640625</v>
+        <v>1826.023559570312</v>
       </c>
       <c r="E9" t="n">
         <v>1647.550048828125</v>
@@ -742,7 +742,7 @@
         <v>44574</v>
       </c>
       <c r="B10" t="n">
-        <v>2212.15283203125</v>
+        <v>2212.153076171875</v>
       </c>
       <c r="C10" t="n">
         <v>2019.699951171875</v>
@@ -754,7 +754,7 @@
         <v>1661.800048828125</v>
       </c>
       <c r="F10" t="n">
-        <v>751.6714477539062</v>
+        <v>751.6715087890625</v>
       </c>
       <c r="G10" t="n">
         <v>23.29000091552734</v>
@@ -763,7 +763,7 @@
         <v>381.44140625</v>
       </c>
       <c r="I10" t="n">
-        <v>1818.585205078125</v>
+        <v>1818.585083007812</v>
       </c>
       <c r="J10" t="n">
         <v>119.9499969482422</v>
@@ -774,7 +774,7 @@
         <v>44575</v>
       </c>
       <c r="B11" t="n">
-        <v>2254.165771484375</v>
+        <v>2254.166015625</v>
       </c>
       <c r="C11" t="n">
         <v>2020.599975585938</v>
@@ -786,13 +786,13 @@
         <v>1697.949951171875</v>
       </c>
       <c r="F11" t="n">
-        <v>759.3614501953125</v>
+        <v>759.3613891601562</v>
       </c>
       <c r="G11" t="n">
         <v>23.43000030517578</v>
       </c>
       <c r="H11" t="n">
-        <v>387.503662109375</v>
+        <v>387.5037231445312</v>
       </c>
       <c r="I11" t="n">
         <v>1803.207641601562</v>
@@ -838,19 +838,19 @@
         <v>44579</v>
       </c>
       <c r="B13" t="n">
-        <v>2153.937255859375</v>
+        <v>2153.93701171875</v>
       </c>
       <c r="C13" t="n">
         <v>2026.75</v>
       </c>
       <c r="D13" t="n">
-        <v>1836.849365234375</v>
+        <v>1836.849487304688</v>
       </c>
       <c r="E13" t="n">
         <v>1900.099975585938</v>
       </c>
       <c r="F13" t="n">
-        <v>742.6674194335938</v>
+        <v>742.66748046875</v>
       </c>
       <c r="G13" t="n">
         <v>21.95000076293945</v>
@@ -876,7 +876,7 @@
         <v>2043.25</v>
       </c>
       <c r="D14" t="n">
-        <v>1845.180908203125</v>
+        <v>1845.181030273438</v>
       </c>
       <c r="E14" t="n">
         <v>1938.449951171875</v>
@@ -888,7 +888,7 @@
         <v>22.78000068664551</v>
       </c>
       <c r="H14" t="n">
-        <v>360.7046508789062</v>
+        <v>360.7046813964844</v>
       </c>
       <c r="I14" t="n">
         <v>1792.273803710938</v>
@@ -908,22 +908,22 @@
         <v>2039.75</v>
       </c>
       <c r="D15" t="n">
-        <v>1861.693969726562</v>
+        <v>1861.694091796875</v>
       </c>
       <c r="E15" t="n">
         <v>1966.699951171875</v>
       </c>
       <c r="F15" t="n">
-        <v>718.3807373046875</v>
+        <v>718.3806762695312</v>
       </c>
       <c r="G15" t="n">
         <v>22.75</v>
       </c>
       <c r="H15" t="n">
-        <v>360.9452209472656</v>
+        <v>360.9451904296875</v>
       </c>
       <c r="I15" t="n">
-        <v>1801.060791015625</v>
+        <v>1801.060668945312</v>
       </c>
       <c r="J15" t="n">
         <v>119.8000030517578</v>
@@ -952,10 +952,10 @@
         <v>21.98999977111816</v>
       </c>
       <c r="H16" t="n">
-        <v>354.7385864257812</v>
+        <v>354.7386169433594</v>
       </c>
       <c r="I16" t="n">
-        <v>1824.626586914062</v>
+        <v>1824.62646484375</v>
       </c>
       <c r="J16" t="n">
         <v>114.4000015258789</v>
@@ -972,13 +972,13 @@
         <v>2035.900024414062</v>
       </c>
       <c r="D17" t="n">
-        <v>1711.978271484375</v>
+        <v>1711.978393554688</v>
       </c>
       <c r="E17" t="n">
         <v>1837.849975585938</v>
       </c>
       <c r="F17" t="n">
-        <v>683.7758178710938</v>
+        <v>683.7757568359375</v>
       </c>
       <c r="G17" t="n">
         <v>20.55999946594238</v>
@@ -1010,7 +1010,7 @@
         <v>1929</v>
       </c>
       <c r="F18" t="n">
-        <v>692.19580078125</v>
+        <v>692.1957397460938</v>
       </c>
       <c r="G18" t="n">
         <v>21.43000030517578</v>
@@ -1048,7 +1048,7 @@
         <v>21.1299991607666</v>
       </c>
       <c r="H19" t="n">
-        <v>338.380126953125</v>
+        <v>338.3800964355469</v>
       </c>
       <c r="I19" t="n">
         <v>1828.0712890625</v>
@@ -1068,22 +1068,22 @@
         <v>1986.800048828125</v>
       </c>
       <c r="D20" t="n">
-        <v>1689.927490234375</v>
+        <v>1689.927368164062</v>
       </c>
       <c r="E20" t="n">
         <v>1938.400024414062</v>
       </c>
       <c r="F20" t="n">
-        <v>691.2711181640625</v>
+        <v>691.2710571289062</v>
       </c>
       <c r="G20" t="n">
         <v>21.14999961853027</v>
       </c>
       <c r="H20" t="n">
-        <v>347.088623046875</v>
+        <v>347.0885925292969</v>
       </c>
       <c r="I20" t="n">
-        <v>1828.221069335938</v>
+        <v>1828.22119140625</v>
       </c>
       <c r="J20" t="n">
         <v>112.8499984741211</v>
@@ -1094,7 +1094,7 @@
         <v>44592</v>
       </c>
       <c r="B21" t="n">
-        <v>2185.00439453125</v>
+        <v>2185.004638671875</v>
       </c>
       <c r="C21" t="n">
         <v>1970.900024414062</v>
@@ -1115,7 +1115,7 @@
         <v>351.3706665039062</v>
       </c>
       <c r="I21" t="n">
-        <v>1818.585205078125</v>
+        <v>1818.585083007812</v>
       </c>
       <c r="J21" t="n">
         <v>111</v>
@@ -1126,7 +1126,7 @@
         <v>44593</v>
       </c>
       <c r="B22" t="n">
-        <v>2229.741943359375</v>
+        <v>2229.7421875</v>
       </c>
       <c r="C22" t="n">
         <v>1986.900024414062</v>
@@ -1144,10 +1144,10 @@
         <v>21.60000038146973</v>
       </c>
       <c r="H22" t="n">
-        <v>366.0451965332031</v>
+        <v>366.045166015625</v>
       </c>
       <c r="I22" t="n">
-        <v>1861.921752929688</v>
+        <v>1861.921630859375</v>
       </c>
       <c r="J22" t="n">
         <v>110.9000015258789</v>
@@ -1164,13 +1164,13 @@
         <v>2016</v>
       </c>
       <c r="D23" t="n">
-        <v>1775.386840820312</v>
+        <v>1775.38671875</v>
       </c>
       <c r="E23" t="n">
         <v>1916.300048828125</v>
       </c>
       <c r="F23" t="n">
-        <v>725.3892211914062</v>
+        <v>725.3892822265625</v>
       </c>
       <c r="G23" t="n">
         <v>21.67000007629395</v>
@@ -1179,7 +1179,7 @@
         <v>365.6602783203125</v>
       </c>
       <c r="I23" t="n">
-        <v>1874.353393554688</v>
+        <v>1874.353515625</v>
       </c>
       <c r="J23" t="n">
         <v>112.0500030517578</v>
@@ -1196,7 +1196,7 @@
         <v>2006.199951171875</v>
       </c>
       <c r="D24" t="n">
-        <v>1747.947998046875</v>
+        <v>1747.947875976562</v>
       </c>
       <c r="E24" t="n">
         <v>1912.550048828125</v>
@@ -1222,13 +1222,13 @@
         <v>44596</v>
       </c>
       <c r="B25" t="n">
-        <v>2174.489501953125</v>
+        <v>2174.48974609375</v>
       </c>
       <c r="C25" t="n">
         <v>2033.099975585938</v>
       </c>
       <c r="D25" t="n">
-        <v>1753.385864257812</v>
+        <v>1753.385986328125</v>
       </c>
       <c r="E25" t="n">
         <v>1950.349975585938</v>
@@ -1240,7 +1240,7 @@
         <v>21.70999908447266</v>
       </c>
       <c r="H25" t="n">
-        <v>366.0451965332031</v>
+        <v>366.045166015625</v>
       </c>
       <c r="I25" t="n">
         <v>1848.391479492188</v>
@@ -1254,13 +1254,13 @@
         <v>44599</v>
       </c>
       <c r="B26" t="n">
-        <v>2181.611083984375</v>
+        <v>2181.61083984375</v>
       </c>
       <c r="C26" t="n">
         <v>2028.5</v>
       </c>
       <c r="D26" t="n">
-        <v>1727.94287109375</v>
+        <v>1727.942749023438</v>
       </c>
       <c r="E26" t="n">
         <v>2024.650024414062</v>
@@ -1292,13 +1292,13 @@
         <v>1968.300048828125</v>
       </c>
       <c r="D27" t="n">
-        <v>1712.177856445312</v>
+        <v>1712.177978515625</v>
       </c>
       <c r="E27" t="n">
         <v>1928</v>
       </c>
       <c r="F27" t="n">
-        <v>698.7176513671875</v>
+        <v>698.7177124023438</v>
       </c>
       <c r="G27" t="n">
         <v>21.6299991607666</v>
@@ -1324,13 +1324,13 @@
         <v>1955.199951171875</v>
       </c>
       <c r="D28" t="n">
-        <v>1779.178466796875</v>
+        <v>1779.178344726562</v>
       </c>
       <c r="E28" t="n">
         <v>1919.800048828125</v>
       </c>
       <c r="F28" t="n">
-        <v>713.95166015625</v>
+        <v>713.9515991210938</v>
       </c>
       <c r="G28" t="n">
         <v>21.52000045776367</v>
@@ -1350,28 +1350,28 @@
         <v>44602</v>
       </c>
       <c r="B29" t="n">
-        <v>2202.020263671875</v>
+        <v>2202.0205078125</v>
       </c>
       <c r="C29" t="n">
         <v>2036.400024414062</v>
       </c>
       <c r="D29" t="n">
-        <v>1782.121704101562</v>
+        <v>1782.121826171875</v>
       </c>
       <c r="E29" t="n">
         <v>1907.949951171875</v>
       </c>
       <c r="F29" t="n">
-        <v>711.6153564453125</v>
+        <v>711.6154174804688</v>
       </c>
       <c r="G29" t="n">
         <v>24.54999923706055</v>
       </c>
       <c r="H29" t="n">
-        <v>360.7046508789062</v>
+        <v>360.7046813964844</v>
       </c>
       <c r="I29" t="n">
-        <v>1807.901000976562</v>
+        <v>1807.901123046875</v>
       </c>
       <c r="J29" t="n">
         <v>140.8500061035156</v>
@@ -1382,19 +1382,19 @@
         <v>44603</v>
       </c>
       <c r="B30" t="n">
-        <v>2150.208984375</v>
+        <v>2150.209228515625</v>
       </c>
       <c r="C30" t="n">
         <v>2016.050048828125</v>
       </c>
       <c r="D30" t="n">
-        <v>1760.370361328125</v>
+        <v>1760.370239257812</v>
       </c>
       <c r="E30" t="n">
         <v>1907.599975585938</v>
       </c>
       <c r="F30" t="n">
-        <v>704.4608764648438</v>
+        <v>704.4608154296875</v>
       </c>
       <c r="G30" t="n">
         <v>25</v>
@@ -1414,7 +1414,7 @@
         <v>44606</v>
       </c>
       <c r="B31" t="n">
-        <v>2058.96630859375</v>
+        <v>2058.966064453125</v>
       </c>
       <c r="C31" t="n">
         <v>1915.25</v>
@@ -1435,7 +1435,7 @@
         <v>341.6999206542969</v>
       </c>
       <c r="I31" t="n">
-        <v>1709.794555664062</v>
+        <v>1709.794799804688</v>
       </c>
       <c r="J31" t="n">
         <v>174.3000030517578</v>
@@ -1446,7 +1446,7 @@
         <v>44607</v>
       </c>
       <c r="B32" t="n">
-        <v>2135.822265625</v>
+        <v>2135.822509765625</v>
       </c>
       <c r="C32" t="n">
         <v>1926.949951171875</v>
@@ -1464,7 +1464,7 @@
         <v>23.59000015258789</v>
       </c>
       <c r="H32" t="n">
-        <v>349.8310241699219</v>
+        <v>349.8310546875</v>
       </c>
       <c r="I32" t="n">
         <v>1735.157348632812</v>
@@ -1496,10 +1496,10 @@
         <v>25.35000038146973</v>
       </c>
       <c r="H33" t="n">
-        <v>347.088623046875</v>
+        <v>347.0885925292969</v>
       </c>
       <c r="I33" t="n">
-        <v>1683.882690429688</v>
+        <v>1683.882568359375</v>
       </c>
       <c r="J33" t="n">
         <v>165.8500061035156</v>
@@ -1516,19 +1516,19 @@
         <v>2020.849975585938</v>
       </c>
       <c r="D34" t="n">
-        <v>1727.094482421875</v>
+        <v>1727.094604492188</v>
       </c>
       <c r="E34" t="n">
         <v>2047.599975585938</v>
       </c>
       <c r="F34" t="n">
-        <v>714.6817626953125</v>
+        <v>714.6817016601562</v>
       </c>
       <c r="G34" t="n">
         <v>26.39999961853027</v>
       </c>
       <c r="H34" t="n">
-        <v>346.2225341796875</v>
+        <v>346.2225646972656</v>
       </c>
       <c r="I34" t="n">
         <v>1724.323364257812</v>
@@ -1548,7 +1548,7 @@
         <v>1958.099975585938</v>
       </c>
       <c r="D35" t="n">
-        <v>1732.432495117188</v>
+        <v>1732.4326171875</v>
       </c>
       <c r="E35" t="n">
         <v>2041.849975585938</v>
@@ -1580,22 +1580,22 @@
         <v>1895.900024414062</v>
       </c>
       <c r="D36" t="n">
-        <v>1681.446411132812</v>
+        <v>1681.4462890625</v>
       </c>
       <c r="E36" t="n">
         <v>1955.900024414062</v>
       </c>
       <c r="F36" t="n">
-        <v>692.19580078125</v>
+        <v>692.1957397460938</v>
       </c>
       <c r="G36" t="n">
         <v>24.03000068664551</v>
       </c>
       <c r="H36" t="n">
-        <v>325.7744445800781</v>
+        <v>325.7744140625</v>
       </c>
       <c r="I36" t="n">
-        <v>1588.77197265625</v>
+        <v>1588.771850585938</v>
       </c>
       <c r="J36" t="n">
         <v>162.3999938964844</v>
@@ -1612,13 +1612,13 @@
         <v>1969.099975585938</v>
       </c>
       <c r="D37" t="n">
-        <v>1663.9853515625</v>
+        <v>1663.985229492188</v>
       </c>
       <c r="E37" t="n">
         <v>1971.949951171875</v>
       </c>
       <c r="F37" t="n">
-        <v>686.7932739257812</v>
+        <v>686.7933349609375</v>
       </c>
       <c r="G37" t="n">
         <v>24.11000061035156</v>
@@ -1644,7 +1644,7 @@
         <v>2060.14990234375</v>
       </c>
       <c r="D38" t="n">
-        <v>1684.938598632812</v>
+        <v>1684.9384765625</v>
       </c>
       <c r="E38" t="n">
         <v>1987.349975585938</v>
@@ -1656,7 +1656,7 @@
         <v>25.11000061035156</v>
       </c>
       <c r="H38" t="n">
-        <v>318.4612121582031</v>
+        <v>318.4612426757812</v>
       </c>
       <c r="I38" t="n">
         <v>1639.397827148438</v>
@@ -1670,13 +1670,13 @@
         <v>44616</v>
       </c>
       <c r="B39" t="n">
-        <v>1925.232299804688</v>
+        <v>1925.232421875</v>
       </c>
       <c r="C39" t="n">
         <v>1957.300048828125</v>
       </c>
       <c r="D39" t="n">
-        <v>1540.510864257812</v>
+        <v>1540.510986328125</v>
       </c>
       <c r="E39" t="n">
         <v>1849.75</v>
@@ -1688,10 +1688,10 @@
         <v>22.22999954223633</v>
       </c>
       <c r="H39" t="n">
-        <v>295.3669128417969</v>
+        <v>295.366943359375</v>
       </c>
       <c r="I39" t="n">
-        <v>1562.760131835938</v>
+        <v>1562.76025390625</v>
       </c>
       <c r="J39" t="n">
         <v>135.5</v>
@@ -1702,7 +1702,7 @@
         <v>44617</v>
       </c>
       <c r="B40" t="n">
-        <v>1968.774536132812</v>
+        <v>1968.774658203125</v>
       </c>
       <c r="C40" t="n">
         <v>2032.849975585938</v>
@@ -1714,7 +1714,7 @@
         <v>1923.5</v>
       </c>
       <c r="F40" t="n">
-        <v>676.6697998046875</v>
+        <v>676.6698608398438</v>
       </c>
       <c r="G40" t="n">
         <v>24.80999946594238</v>
@@ -1723,7 +1723,7 @@
         <v>297.0508728027344</v>
       </c>
       <c r="I40" t="n">
-        <v>1570.89794921875</v>
+        <v>1570.898071289062</v>
       </c>
       <c r="J40" t="n">
         <v>143.9499969482422</v>
@@ -1734,19 +1734,19 @@
         <v>44620</v>
       </c>
       <c r="B41" t="n">
-        <v>1997.069702148438</v>
+        <v>1997.06982421875</v>
       </c>
       <c r="C41" t="n">
         <v>2134.39990234375</v>
       </c>
       <c r="D41" t="n">
-        <v>1640.787109375</v>
+        <v>1640.787231445312</v>
       </c>
       <c r="E41" t="n">
         <v>1843.400024414062</v>
       </c>
       <c r="F41" t="n">
-        <v>688.6915283203125</v>
+        <v>688.6914672851562</v>
       </c>
       <c r="G41" t="n">
         <v>24.75</v>
@@ -1772,7 +1772,7 @@
         <v>2241.050048828125</v>
       </c>
       <c r="D42" t="n">
-        <v>1638.143188476562</v>
+        <v>1638.14306640625</v>
       </c>
       <c r="E42" t="n">
         <v>1882.550048828125</v>
@@ -1784,10 +1784,10 @@
         <v>24.6200008392334</v>
       </c>
       <c r="H42" t="n">
-        <v>292.6725769042969</v>
+        <v>292.6725463867188</v>
       </c>
       <c r="I42" t="n">
-        <v>1665.45947265625</v>
+        <v>1665.459594726562</v>
       </c>
       <c r="J42" t="n">
         <v>153.5</v>
@@ -1804,7 +1804,7 @@
         <v>2353.10009765625</v>
       </c>
       <c r="D43" t="n">
-        <v>1640.138671875</v>
+        <v>1640.138793945312</v>
       </c>
       <c r="E43" t="n">
         <v>1950.900024414062</v>
@@ -1848,7 +1848,7 @@
         <v>23.95000076293945</v>
       </c>
       <c r="H44" t="n">
-        <v>281.5584716796875</v>
+        <v>281.5584411621094</v>
       </c>
       <c r="I44" t="n">
         <v>1802.55859375</v>
@@ -1862,7 +1862,7 @@
         <v>44627</v>
       </c>
       <c r="B45" t="n">
-        <v>1864.196411132812</v>
+        <v>1864.1962890625</v>
       </c>
       <c r="C45" t="n">
         <v>2207.35009765625</v>
@@ -1874,16 +1874,16 @@
         <v>1803.75</v>
       </c>
       <c r="F45" t="n">
-        <v>659.7809448242188</v>
+        <v>659.781005859375</v>
       </c>
       <c r="G45" t="n">
         <v>23.29000091552734</v>
       </c>
       <c r="H45" t="n">
-        <v>270.588623046875</v>
+        <v>270.5885925292969</v>
       </c>
       <c r="I45" t="n">
-        <v>1712.440673828125</v>
+        <v>1712.440551757812</v>
       </c>
       <c r="J45" t="n">
         <v>159.0500030517578</v>
@@ -1894,25 +1894,25 @@
         <v>44628</v>
       </c>
       <c r="B46" t="n">
-        <v>1875.619750976562</v>
+        <v>1875.61962890625</v>
       </c>
       <c r="C46" t="n">
         <v>2217</v>
       </c>
       <c r="D46" t="n">
-        <v>1598.032592773438</v>
+        <v>1598.03271484375</v>
       </c>
       <c r="E46" t="n">
         <v>1783.949951171875</v>
       </c>
       <c r="F46" t="n">
-        <v>670.5372314453125</v>
+        <v>670.5372924804688</v>
       </c>
       <c r="G46" t="n">
         <v>23.73999977111816</v>
       </c>
       <c r="H46" t="n">
-        <v>272.2244567871094</v>
+        <v>272.2244873046875</v>
       </c>
       <c r="I46" t="n">
         <v>1627.265625</v>
@@ -1926,25 +1926,25 @@
         <v>44629</v>
       </c>
       <c r="B47" t="n">
-        <v>1912.661743164062</v>
+        <v>1912.66162109375</v>
       </c>
       <c r="C47" t="n">
         <v>2164.64990234375</v>
       </c>
       <c r="D47" t="n">
-        <v>1652.860229492188</v>
+        <v>1652.860473632812</v>
       </c>
       <c r="E47" t="n">
         <v>1828.75</v>
       </c>
       <c r="F47" t="n">
-        <v>695.1160888671875</v>
+        <v>695.1160278320312</v>
       </c>
       <c r="G47" t="n">
         <v>24.26000022888184</v>
       </c>
       <c r="H47" t="n">
-        <v>280.6442260742188</v>
+        <v>280.6442565917969</v>
       </c>
       <c r="I47" t="n">
         <v>1612.986450195312</v>
@@ -1964,22 +1964,22 @@
         <v>2272.75</v>
       </c>
       <c r="D48" t="n">
-        <v>1738.967895507812</v>
+        <v>1738.968017578125</v>
       </c>
       <c r="E48" t="n">
         <v>1881.849975585938</v>
       </c>
       <c r="F48" t="n">
-        <v>710.9827880859375</v>
+        <v>710.9827270507812</v>
       </c>
       <c r="G48" t="n">
         <v>24.5</v>
       </c>
       <c r="H48" t="n">
-        <v>282.1357727050781</v>
+        <v>282.1358032226562</v>
       </c>
       <c r="I48" t="n">
-        <v>1693.568481445312</v>
+        <v>1693.568359375</v>
       </c>
       <c r="J48" t="n">
         <v>171.3500061035156</v>
@@ -2008,10 +2008,10 @@
         <v>24.36000061035156</v>
       </c>
       <c r="H49" t="n">
-        <v>282.3763427734375</v>
+        <v>282.3763732910156</v>
       </c>
       <c r="I49" t="n">
-        <v>1659.418579101562</v>
+        <v>1659.41845703125</v>
       </c>
       <c r="J49" t="n">
         <v>169</v>
@@ -2040,7 +2040,7 @@
         <v>24.43000030517578</v>
       </c>
       <c r="H50" t="n">
-        <v>280.2112426757812</v>
+        <v>280.2112731933594</v>
       </c>
       <c r="I50" t="n">
         <v>1647.93505859375</v>
@@ -2075,7 +2075,7 @@
         <v>283.9640808105469</v>
       </c>
       <c r="I51" t="n">
-        <v>1622.023315429688</v>
+        <v>1622.023193359375</v>
       </c>
       <c r="J51" t="n">
         <v>179.1499938964844</v>
@@ -2086,7 +2086,7 @@
         <v>44636</v>
       </c>
       <c r="B52" t="n">
-        <v>2035.306884765625</v>
+        <v>2035.306762695312</v>
       </c>
       <c r="C52" t="n">
         <v>2305.39990234375</v>
@@ -2098,7 +2098,7 @@
         <v>1833.650024414062</v>
       </c>
       <c r="F52" t="n">
-        <v>704.5582275390625</v>
+        <v>704.5581665039062</v>
       </c>
       <c r="G52" t="n">
         <v>24.57999992370605</v>
@@ -2118,19 +2118,19 @@
         <v>44637</v>
       </c>
       <c r="B53" t="n">
-        <v>2029.093383789062</v>
+        <v>2029.093505859375</v>
       </c>
       <c r="C53" t="n">
         <v>2389.800048828125</v>
       </c>
       <c r="D53" t="n">
-        <v>1815.597045898438</v>
+        <v>1815.59716796875</v>
       </c>
       <c r="E53" t="n">
         <v>1901.199951171875</v>
       </c>
       <c r="F53" t="n">
-        <v>720.4248657226562</v>
+        <v>720.4248046875</v>
       </c>
       <c r="G53" t="n">
         <v>25.02000045776367</v>
@@ -2139,7 +2139,7 @@
         <v>294.6452331542969</v>
       </c>
       <c r="I53" t="n">
-        <v>1764.215087890625</v>
+        <v>1764.214965820312</v>
       </c>
       <c r="J53" t="n">
         <v>206.6000061035156</v>
@@ -2150,19 +2150,19 @@
         <v>44641</v>
       </c>
       <c r="B54" t="n">
-        <v>1965.14208984375</v>
+        <v>1965.142211914062</v>
       </c>
       <c r="C54" t="n">
         <v>2289.050048828125</v>
       </c>
       <c r="D54" t="n">
-        <v>1798.93408203125</v>
+        <v>1798.934204101562</v>
       </c>
       <c r="E54" t="n">
         <v>1876.050048828125</v>
       </c>
       <c r="F54" t="n">
-        <v>715.6065063476562</v>
+        <v>715.6064453125</v>
       </c>
       <c r="G54" t="n">
         <v>24.90999984741211</v>
@@ -2171,7 +2171,7 @@
         <v>289.0159606933594</v>
       </c>
       <c r="I54" t="n">
-        <v>1811.49560546875</v>
+        <v>1811.495727539062</v>
       </c>
       <c r="J54" t="n">
         <v>227.25</v>
@@ -2200,7 +2200,7 @@
         <v>24.75</v>
       </c>
       <c r="H55" t="n">
-        <v>289.5452575683594</v>
+        <v>289.5452270507812</v>
       </c>
       <c r="I55" t="n">
         <v>1881.193359375</v>
@@ -2235,7 +2235,7 @@
         <v>286.6103210449219</v>
       </c>
       <c r="I56" t="n">
-        <v>1895.223022460938</v>
+        <v>1895.222900390625</v>
       </c>
       <c r="J56" t="n">
         <v>250.5</v>
@@ -2258,7 +2258,7 @@
         <v>1911.400024414062</v>
       </c>
       <c r="F57" t="n">
-        <v>713.95166015625</v>
+        <v>713.9515991210938</v>
       </c>
       <c r="G57" t="n">
         <v>26.43000030517578</v>
@@ -2267,7 +2267,7 @@
         <v>285.8404846191406</v>
       </c>
       <c r="I57" t="n">
-        <v>1976.853271484375</v>
+        <v>1976.853149414062</v>
       </c>
       <c r="J57" t="n">
         <v>263</v>
@@ -2278,25 +2278,25 @@
         <v>44645</v>
       </c>
       <c r="B58" t="n">
-        <v>1973.219360351562</v>
+        <v>1973.219482421875</v>
       </c>
       <c r="C58" t="n">
         <v>2448.75</v>
       </c>
       <c r="D58" t="n">
-        <v>1862.841674804688</v>
+        <v>1862.841552734375</v>
       </c>
       <c r="E58" t="n">
         <v>1921.25</v>
       </c>
       <c r="F58" t="n">
-        <v>723.4911499023438</v>
+        <v>723.4910888671875</v>
       </c>
       <c r="G58" t="n">
         <v>28.63999938964844</v>
       </c>
       <c r="H58" t="n">
-        <v>286.5621643066406</v>
+        <v>286.5621948242188</v>
       </c>
       <c r="I58" t="n">
         <v>2051.59375</v>
@@ -2310,7 +2310,7 @@
         <v>44648</v>
       </c>
       <c r="B59" t="n">
-        <v>1968.869873046875</v>
+        <v>1968.869995117188</v>
       </c>
       <c r="C59" t="n">
         <v>2439</v>
@@ -2328,10 +2328,10 @@
         <v>30.45000076293945</v>
       </c>
       <c r="H59" t="n">
-        <v>280.7886047363281</v>
+        <v>280.78857421875</v>
       </c>
       <c r="I59" t="n">
-        <v>2138.06689453125</v>
+        <v>2138.067138671875</v>
       </c>
       <c r="J59" t="n">
         <v>239.5</v>
@@ -2342,7 +2342,7 @@
         <v>44649</v>
       </c>
       <c r="B60" t="n">
-        <v>2034.7333984375</v>
+        <v>2034.733276367188</v>
       </c>
       <c r="C60" t="n">
         <v>2461.550048828125</v>
@@ -2354,13 +2354,13 @@
         <v>1923.300048828125</v>
       </c>
       <c r="F60" t="n">
-        <v>741.6940307617188</v>
+        <v>741.6939697265625</v>
       </c>
       <c r="G60" t="n">
         <v>34.70999908447266</v>
       </c>
       <c r="H60" t="n">
-        <v>291.0367126464844</v>
+        <v>291.0367431640625</v>
       </c>
       <c r="I60" t="n">
         <v>2177.609130859375</v>
@@ -2380,13 +2380,13 @@
         <v>2377.39990234375</v>
       </c>
       <c r="D61" t="n">
-        <v>1990.805786132812</v>
+        <v>1990.805908203125</v>
       </c>
       <c r="E61" t="n">
         <v>1857.150024414062</v>
       </c>
       <c r="F61" t="n">
-        <v>746.9991455078125</v>
+        <v>746.9990844726562</v>
       </c>
       <c r="G61" t="n">
         <v>34.29999923706055</v>
@@ -2412,19 +2412,19 @@
         <v>2368.14990234375</v>
       </c>
       <c r="D62" t="n">
-        <v>2010.262451171875</v>
+        <v>2010.262329101562</v>
       </c>
       <c r="E62" t="n">
         <v>1914.699951171875</v>
       </c>
       <c r="F62" t="n">
-        <v>753.6182861328125</v>
+        <v>753.618408203125</v>
       </c>
       <c r="G62" t="n">
         <v>37.02000045776367</v>
       </c>
       <c r="H62" t="n">
-        <v>294.0831909179688</v>
+        <v>294.0832214355469</v>
       </c>
       <c r="I62" t="n">
         <v>2146.654296875</v>
@@ -2450,16 +2450,16 @@
         <v>1945.099975585938</v>
       </c>
       <c r="F63" t="n">
-        <v>764.8612670898438</v>
+        <v>764.861328125</v>
       </c>
       <c r="G63" t="n">
         <v>40.68999862670898</v>
       </c>
       <c r="H63" t="n">
-        <v>299.6848449707031</v>
+        <v>299.684814453125</v>
       </c>
       <c r="I63" t="n">
-        <v>2246.20849609375</v>
+        <v>2246.208251953125</v>
       </c>
       <c r="J63" t="n">
         <v>223.25</v>
@@ -2482,7 +2482,7 @@
         <v>2110.449951171875</v>
       </c>
       <c r="F64" t="n">
-        <v>796.789306640625</v>
+        <v>796.7892456054688</v>
       </c>
       <c r="G64" t="n">
         <v>42.38999938964844</v>
@@ -2491,7 +2491,7 @@
         <v>306.2691040039062</v>
       </c>
       <c r="I64" t="n">
-        <v>2366.332763671875</v>
+        <v>2366.33251953125</v>
       </c>
       <c r="J64" t="n">
         <v>224.0500030517578</v>
@@ -2514,16 +2514,16 @@
         <v>2189.800048828125</v>
       </c>
       <c r="F65" t="n">
-        <v>825.505126953125</v>
+        <v>825.5050659179688</v>
       </c>
       <c r="G65" t="n">
         <v>46.61999893188477</v>
       </c>
       <c r="H65" t="n">
-        <v>311.3301696777344</v>
+        <v>311.3302001953125</v>
       </c>
       <c r="I65" t="n">
-        <v>2464.538330078125</v>
+        <v>2464.53857421875</v>
       </c>
       <c r="J65" t="n">
         <v>224.5</v>
@@ -2540,7 +2540,7 @@
         <v>2484.050048828125</v>
       </c>
       <c r="D66" t="n">
-        <v>2155.18896484375</v>
+        <v>2155.188720703125</v>
       </c>
       <c r="E66" t="n">
         <v>2197.39990234375</v>
@@ -2552,7 +2552,7 @@
         <v>48.95000076293945</v>
       </c>
       <c r="H66" t="n">
-        <v>315.162841796875</v>
+        <v>315.1628723144531</v>
       </c>
       <c r="I66" t="n">
         <v>2533.23779296875</v>
@@ -2572,19 +2572,19 @@
         <v>2449.64990234375</v>
       </c>
       <c r="D67" t="n">
-        <v>2094.374755859375</v>
+        <v>2094.37451171875</v>
       </c>
       <c r="E67" t="n">
         <v>2166</v>
       </c>
       <c r="F67" t="n">
-        <v>795.6698608398438</v>
+        <v>795.669921875</v>
       </c>
       <c r="G67" t="n">
         <v>46.5099983215332</v>
       </c>
       <c r="H67" t="n">
-        <v>319.9782409667969</v>
+        <v>319.978271484375</v>
       </c>
       <c r="I67" t="n">
         <v>2359.242919921875</v>
@@ -2604,7 +2604,7 @@
         <v>2540.25</v>
       </c>
       <c r="D68" t="n">
-        <v>2166.114501953125</v>
+        <v>2166.11474609375</v>
       </c>
       <c r="E68" t="n">
         <v>2321.85009765625</v>
@@ -2636,7 +2636,7 @@
         <v>2756.5</v>
       </c>
       <c r="D69" t="n">
-        <v>2175.343994140625</v>
+        <v>2175.34375</v>
       </c>
       <c r="E69" t="n">
         <v>2665.14990234375</v>
@@ -2651,7 +2651,7 @@
         <v>353.9808654785156</v>
       </c>
       <c r="I69" t="n">
-        <v>2661.100830078125</v>
+        <v>2661.1005859375</v>
       </c>
       <c r="J69" t="n">
         <v>214.4499969482422</v>
@@ -2680,7 +2680,7 @@
         <v>46.15999984741211</v>
       </c>
       <c r="H70" t="n">
-        <v>353.4403686523438</v>
+        <v>353.4403381347656</v>
       </c>
       <c r="I70" t="n">
         <v>2498.388916015625</v>
@@ -2700,19 +2700,19 @@
         <v>2690.75</v>
       </c>
       <c r="D71" t="n">
-        <v>2194.55126953125</v>
+        <v>2194.551025390625</v>
       </c>
       <c r="E71" t="n">
         <v>2864.300048828125</v>
       </c>
       <c r="F71" t="n">
-        <v>818.1558227539062</v>
+        <v>818.15576171875</v>
       </c>
       <c r="G71" t="n">
         <v>44.65000152587891</v>
       </c>
       <c r="H71" t="n">
-        <v>362.8255004882812</v>
+        <v>362.8254699707031</v>
       </c>
       <c r="I71" t="n">
         <v>2497.19091796875</v>
@@ -2732,19 +2732,19 @@
         <v>2728.300048828125</v>
       </c>
       <c r="D72" t="n">
-        <v>2228.874755859375</v>
+        <v>2228.87451171875</v>
       </c>
       <c r="E72" t="n">
         <v>2970.5</v>
       </c>
       <c r="F72" t="n">
-        <v>820.29736328125</v>
+        <v>820.2973022460938</v>
       </c>
       <c r="G72" t="n">
         <v>46.88000106811523</v>
       </c>
       <c r="H72" t="n">
-        <v>357.1255798339844</v>
+        <v>357.1256103515625</v>
       </c>
       <c r="I72" t="n">
         <v>2491.349365234375</v>
@@ -2764,7 +2764,7 @@
         <v>2598.050048828125</v>
       </c>
       <c r="D73" t="n">
-        <v>2163.470703125</v>
+        <v>2163.470458984375</v>
       </c>
       <c r="E73" t="n">
         <v>2911.949951171875</v>
@@ -2776,7 +2776,7 @@
         <v>46.4900016784668</v>
       </c>
       <c r="H73" t="n">
-        <v>348.1336059570312</v>
+        <v>348.1336364746094</v>
       </c>
       <c r="I73" t="n">
         <v>2365.93310546875</v>
@@ -2796,13 +2796,13 @@
         <v>2687.550048828125</v>
       </c>
       <c r="D74" t="n">
-        <v>2179.085693359375</v>
+        <v>2179.08544921875</v>
       </c>
       <c r="E74" t="n">
         <v>2810.85009765625</v>
       </c>
       <c r="F74" t="n">
-        <v>805.6473388671875</v>
+        <v>805.6473999023438</v>
       </c>
       <c r="G74" t="n">
         <v>47.0099983215332</v>
@@ -2828,7 +2828,7 @@
         <v>2699.60009765625</v>
       </c>
       <c r="D75" t="n">
-        <v>2281.2578125</v>
+        <v>2281.257568359375</v>
       </c>
       <c r="E75" t="n">
         <v>2811.5</v>
@@ -2843,7 +2843,7 @@
         <v>370.8347778320312</v>
       </c>
       <c r="I75" t="n">
-        <v>2439.775146484375</v>
+        <v>2439.77490234375</v>
       </c>
       <c r="J75" t="n">
         <v>214.3500061035156</v>
@@ -2860,7 +2860,7 @@
         <v>2658.550048828125</v>
       </c>
       <c r="D76" t="n">
-        <v>2268.23681640625</v>
+        <v>2268.236572265625</v>
       </c>
       <c r="E76" t="n">
         <v>2882.800048828125</v>
@@ -2875,7 +2875,7 @@
         <v>367.7391357421875</v>
       </c>
       <c r="I76" t="n">
-        <v>2409.468994140625</v>
+        <v>2409.46923828125</v>
       </c>
       <c r="J76" t="n">
         <v>211.1999969482422</v>
@@ -2936,10 +2936,10 @@
         <v>57.13000106811523</v>
       </c>
       <c r="H78" t="n">
-        <v>378.5000610351562</v>
+        <v>378.5000915527344</v>
       </c>
       <c r="I78" t="n">
-        <v>2558.750732421875</v>
+        <v>2558.75048828125</v>
       </c>
       <c r="J78" t="n">
         <v>206.3500061035156</v>
@@ -2988,13 +2988,13 @@
         <v>2796.64990234375</v>
       </c>
       <c r="D80" t="n">
-        <v>2373.252197265625</v>
+        <v>2373.25244140625</v>
       </c>
       <c r="E80" t="n">
         <v>2912.199951171875</v>
       </c>
       <c r="F80" t="n">
-        <v>863.5169067382812</v>
+        <v>863.5169677734375</v>
       </c>
       <c r="G80" t="n">
         <v>56.84999847412109</v>
@@ -3003,7 +3003,7 @@
         <v>376.7311706542969</v>
       </c>
       <c r="I80" t="n">
-        <v>2558.850341796875</v>
+        <v>2558.8505859375</v>
       </c>
       <c r="J80" t="n">
         <v>199.8999938964844</v>
@@ -3052,22 +3052,22 @@
         <v>2804.449951171875</v>
       </c>
       <c r="D82" t="n">
-        <v>2334.288818359375</v>
+        <v>2334.2890625</v>
       </c>
       <c r="E82" t="n">
         <v>2830.35009765625</v>
       </c>
       <c r="F82" t="n">
-        <v>833.7791137695312</v>
+        <v>833.779052734375</v>
       </c>
       <c r="G82" t="n">
         <v>56.06999969482422</v>
       </c>
       <c r="H82" t="n">
-        <v>371.6209106445312</v>
+        <v>371.6209411621094</v>
       </c>
       <c r="I82" t="n">
-        <v>2484.5595703125</v>
+        <v>2484.559326171875</v>
       </c>
       <c r="J82" t="n">
         <v>186.3999938964844</v>
@@ -3096,7 +3096,7 @@
         <v>53.27000045776367</v>
       </c>
       <c r="H83" t="n">
-        <v>361.7444458007812</v>
+        <v>361.7444763183594</v>
       </c>
       <c r="I83" t="n">
         <v>2443.4697265625</v>
@@ -3116,19 +3116,19 @@
         <v>2801.64990234375</v>
       </c>
       <c r="D84" t="n">
-        <v>2250.376220703125</v>
+        <v>2250.37646484375</v>
       </c>
       <c r="E84" t="n">
         <v>2845.89990234375</v>
       </c>
       <c r="F84" t="n">
-        <v>789.7807006835938</v>
+        <v>789.7806396484375</v>
       </c>
       <c r="G84" t="n">
         <v>55.63000106811523</v>
       </c>
       <c r="H84" t="n">
-        <v>360.024658203125</v>
+        <v>360.0246887207031</v>
       </c>
       <c r="I84" t="n">
         <v>2446.91455078125</v>
@@ -3154,7 +3154,7 @@
         <v>2874.800048828125</v>
       </c>
       <c r="F85" t="n">
-        <v>789.829345703125</v>
+        <v>789.8294067382812</v>
       </c>
       <c r="G85" t="n">
         <v>58.40999984741211</v>
@@ -3186,7 +3186,7 @@
         <v>2706.39990234375</v>
       </c>
       <c r="F86" t="n">
-        <v>771.529052734375</v>
+        <v>771.5291748046875</v>
       </c>
       <c r="G86" t="n">
         <v>56.31999969482422</v>
@@ -3218,7 +3218,7 @@
         <v>2486.699951171875</v>
       </c>
       <c r="F87" t="n">
-        <v>748.65380859375</v>
+        <v>748.6538696289062</v>
       </c>
       <c r="G87" t="n">
         <v>53.5099983215332</v>
@@ -3227,7 +3227,7 @@
         <v>352.0154113769531</v>
       </c>
       <c r="I87" t="n">
-        <v>2357.196044921875</v>
+        <v>2357.19580078125</v>
       </c>
       <c r="J87" t="n">
         <v>166.1499938964844</v>
@@ -3244,13 +3244,13 @@
         <v>2296</v>
       </c>
       <c r="D88" t="n">
-        <v>2114.57958984375</v>
+        <v>2114.579345703125</v>
       </c>
       <c r="E88" t="n">
         <v>2648.050048828125</v>
       </c>
       <c r="F88" t="n">
-        <v>739.698486328125</v>
+        <v>739.6985473632812</v>
       </c>
       <c r="G88" t="n">
         <v>51.06000137329102</v>
@@ -3314,7 +3314,7 @@
         <v>2171.550048828125</v>
       </c>
       <c r="F90" t="n">
-        <v>687.1340942382812</v>
+        <v>687.134033203125</v>
       </c>
       <c r="G90" t="n">
         <v>50.93000030517578</v>
@@ -3323,7 +3323,7 @@
         <v>352.8998718261719</v>
       </c>
       <c r="I90" t="n">
-        <v>2365.6337890625</v>
+        <v>2365.633544921875</v>
       </c>
       <c r="J90" t="n">
         <v>157.5</v>
@@ -3340,7 +3340,7 @@
         <v>2249.89990234375</v>
       </c>
       <c r="D91" t="n">
-        <v>2101.208984375</v>
+        <v>2101.20947265625</v>
       </c>
       <c r="E91" t="n">
         <v>2281.699951171875</v>
@@ -3372,7 +3372,7 @@
         <v>2333.39990234375</v>
       </c>
       <c r="D92" t="n">
-        <v>2179.9833984375</v>
+        <v>2179.983642578125</v>
       </c>
       <c r="E92" t="n">
         <v>2285.800048828125</v>
@@ -3404,22 +3404,22 @@
         <v>2316</v>
       </c>
       <c r="D93" t="n">
-        <v>2176.241943359375</v>
+        <v>2176.2421875</v>
       </c>
       <c r="E93" t="n">
         <v>2396.10009765625</v>
       </c>
       <c r="F93" t="n">
-        <v>739.6011352539062</v>
+        <v>739.6011962890625</v>
       </c>
       <c r="G93" t="n">
         <v>58.93999862670898</v>
       </c>
       <c r="H93" t="n">
-        <v>354.8653259277344</v>
+        <v>354.8652954101562</v>
       </c>
       <c r="I93" t="n">
-        <v>2482.06298828125</v>
+        <v>2482.063232421875</v>
       </c>
       <c r="J93" t="n">
         <v>176.1999969482422</v>
@@ -3436,19 +3436,19 @@
         <v>2265</v>
       </c>
       <c r="D94" t="n">
-        <v>2110.03955078125</v>
+        <v>2110.039794921875</v>
       </c>
       <c r="E94" t="n">
         <v>2317.5</v>
       </c>
       <c r="F94" t="n">
-        <v>713.3189697265625</v>
+        <v>713.3189086914062</v>
       </c>
       <c r="G94" t="n">
         <v>59.47999954223633</v>
       </c>
       <c r="H94" t="n">
-        <v>357.7152709960938</v>
+        <v>357.7152099609375</v>
       </c>
       <c r="I94" t="n">
         <v>2375.02001953125</v>
@@ -3468,7 +3468,7 @@
         <v>2310.949951171875</v>
       </c>
       <c r="D95" t="n">
-        <v>2214.6064453125</v>
+        <v>2214.606201171875</v>
       </c>
       <c r="E95" t="n">
         <v>2273.64990234375</v>
@@ -3480,10 +3480,10 @@
         <v>62.45000076293945</v>
       </c>
       <c r="H95" t="n">
-        <v>356.7325134277344</v>
+        <v>356.7325439453125</v>
       </c>
       <c r="I95" t="n">
-        <v>2376.867431640625</v>
+        <v>2376.8671875</v>
       </c>
       <c r="J95" t="n">
         <v>168.3999938964844</v>
@@ -3506,7 +3506,7 @@
         <v>2248.35009765625</v>
       </c>
       <c r="F96" t="n">
-        <v>733.517333984375</v>
+        <v>733.5172729492188</v>
       </c>
       <c r="G96" t="n">
         <v>65.56999969482422</v>
@@ -3532,13 +3532,13 @@
         <v>2196.5</v>
       </c>
       <c r="D97" t="n">
-        <v>2155.388671875</v>
+        <v>2155.388427734375</v>
       </c>
       <c r="E97" t="n">
         <v>2136.300048828125</v>
       </c>
       <c r="F97" t="n">
-        <v>732.154541015625</v>
+        <v>732.1544799804688</v>
       </c>
       <c r="G97" t="n">
         <v>62.29999923706055</v>
@@ -3564,7 +3564,7 @@
         <v>2087.949951171875</v>
       </c>
       <c r="D98" t="n">
-        <v>2069.530029296875</v>
+        <v>2069.5302734375</v>
       </c>
       <c r="E98" t="n">
         <v>2187.35009765625</v>
@@ -3579,7 +3579,7 @@
         <v>355.4549560546875</v>
       </c>
       <c r="I98" t="n">
-        <v>2213.7060546875</v>
+        <v>2213.706298828125</v>
       </c>
       <c r="J98" t="n">
         <v>155.3500061035156</v>
@@ -3634,7 +3634,7 @@
         <v>2166.449951171875</v>
       </c>
       <c r="F100" t="n">
-        <v>684.4083862304688</v>
+        <v>684.408447265625</v>
       </c>
       <c r="G100" t="n">
         <v>65.62000274658203</v>
@@ -3643,7 +3643,7 @@
         <v>359.9755249023438</v>
       </c>
       <c r="I100" t="n">
-        <v>2452.855712890625</v>
+        <v>2452.85595703125</v>
       </c>
       <c r="J100" t="n">
         <v>154.6999969482422</v>
@@ -3660,7 +3660,7 @@
         <v>2162</v>
       </c>
       <c r="D101" t="n">
-        <v>2160.826416015625</v>
+        <v>2160.826171875</v>
       </c>
       <c r="E101" t="n">
         <v>2151.64990234375</v>
@@ -3704,7 +3704,7 @@
         <v>64.65000152587891</v>
       </c>
       <c r="H102" t="n">
-        <v>363.0220031738281</v>
+        <v>363.0220336914062</v>
       </c>
       <c r="I102" t="n">
         <v>2394.391357421875</v>
@@ -3730,13 +3730,13 @@
         <v>1848.400024414062</v>
       </c>
       <c r="F103" t="n">
-        <v>717.3099365234375</v>
+        <v>717.3098754882812</v>
       </c>
       <c r="G103" t="n">
         <v>61.41999816894531</v>
       </c>
       <c r="H103" t="n">
-        <v>365.233154296875</v>
+        <v>365.2331848144531</v>
       </c>
       <c r="I103" t="n">
         <v>2322.496826171875</v>
@@ -3756,7 +3756,7 @@
         <v>2025.699951171875</v>
       </c>
       <c r="D104" t="n">
-        <v>2204.47900390625</v>
+        <v>2204.478759765625</v>
       </c>
       <c r="E104" t="n">
         <v>1925.800048828125</v>
@@ -3768,7 +3768,7 @@
         <v>59.06999969482422</v>
       </c>
       <c r="H104" t="n">
-        <v>367.0512390136719</v>
+        <v>367.0512084960938</v>
       </c>
       <c r="I104" t="n">
         <v>2442.271484375</v>
@@ -3788,13 +3788,13 @@
         <v>1956.050048828125</v>
       </c>
       <c r="D105" t="n">
-        <v>2185.122314453125</v>
+        <v>2185.1220703125</v>
       </c>
       <c r="E105" t="n">
         <v>1855.900024414062</v>
       </c>
       <c r="F105" t="n">
-        <v>720.2301635742188</v>
+        <v>720.230224609375</v>
       </c>
       <c r="G105" t="n">
         <v>56.81999969482422</v>
@@ -3803,7 +3803,7 @@
         <v>360.5651550292969</v>
       </c>
       <c r="I105" t="n">
-        <v>2386.9521484375</v>
+        <v>2386.952392578125</v>
       </c>
       <c r="J105" t="n">
         <v>170</v>
@@ -3832,10 +3832,10 @@
         <v>59.65999984741211</v>
       </c>
       <c r="H106" t="n">
-        <v>358.5997314453125</v>
+        <v>358.5997009277344</v>
       </c>
       <c r="I106" t="n">
-        <v>2476.47119140625</v>
+        <v>2476.471435546875</v>
       </c>
       <c r="J106" t="n">
         <v>178.5</v>
@@ -3867,7 +3867,7 @@
         <v>357.0764770507812</v>
       </c>
       <c r="I107" t="n">
-        <v>2495.29345703125</v>
+        <v>2495.2939453125</v>
       </c>
       <c r="J107" t="n">
         <v>206.5</v>
@@ -3884,7 +3884,7 @@
         <v>2091.89990234375</v>
       </c>
       <c r="D108" t="n">
-        <v>2172.350341796875</v>
+        <v>2172.3505859375</v>
       </c>
       <c r="E108" t="n">
         <v>1801.900024414062</v>
@@ -3896,10 +3896,10 @@
         <v>56.90000152587891</v>
       </c>
       <c r="H108" t="n">
-        <v>356.7816162109375</v>
+        <v>356.7816467285156</v>
       </c>
       <c r="I108" t="n">
-        <v>2443.76904296875</v>
+        <v>2443.768798828125</v>
       </c>
       <c r="J108" t="n">
         <v>210.6999969482422</v>
@@ -3980,22 +3980,22 @@
         <v>2051.89990234375</v>
       </c>
       <c r="D111" t="n">
-        <v>2075.117431640625</v>
+        <v>2075.117919921875</v>
       </c>
       <c r="E111" t="n">
         <v>1798.699951171875</v>
       </c>
       <c r="F111" t="n">
-        <v>676.7671508789062</v>
+        <v>676.7672119140625</v>
       </c>
       <c r="G111" t="n">
         <v>53.2400016784668</v>
       </c>
       <c r="H111" t="n">
-        <v>356.437744140625</v>
+        <v>356.4377136230469</v>
       </c>
       <c r="I111" t="n">
-        <v>2334.129638671875</v>
+        <v>2334.12939453125</v>
       </c>
       <c r="J111" t="n">
         <v>180</v>
@@ -4012,13 +4012,13 @@
         <v>2057.5</v>
       </c>
       <c r="D112" t="n">
-        <v>2191.557861328125</v>
+        <v>2191.5576171875</v>
       </c>
       <c r="E112" t="n">
         <v>1788.75</v>
       </c>
       <c r="F112" t="n">
-        <v>685.9658813476562</v>
+        <v>685.9659423828125</v>
       </c>
       <c r="G112" t="n">
         <v>53.33000183105469</v>
@@ -4076,7 +4076,7 @@
         <v>2124.64990234375</v>
       </c>
       <c r="D114" t="n">
-        <v>2078.360595703125</v>
+        <v>2078.3603515625</v>
       </c>
       <c r="E114" t="n">
         <v>1711.099975585938</v>
@@ -4088,10 +4088,10 @@
         <v>51.86000061035156</v>
       </c>
       <c r="H114" t="n">
-        <v>353.1946716308594</v>
+        <v>353.1946411132812</v>
       </c>
       <c r="I114" t="n">
-        <v>2373.0224609375</v>
+        <v>2373.022705078125</v>
       </c>
       <c r="J114" t="n">
         <v>182.8500061035156</v>
@@ -4108,7 +4108,7 @@
         <v>2032.599975585938</v>
       </c>
       <c r="D115" t="n">
-        <v>2091.131591796875</v>
+        <v>2091.132080078125</v>
       </c>
       <c r="E115" t="n">
         <v>1711.25</v>
@@ -4140,7 +4140,7 @@
         <v>2060.25</v>
       </c>
       <c r="D116" t="n">
-        <v>2075.217529296875</v>
+        <v>2075.21728515625</v>
       </c>
       <c r="E116" t="n">
         <v>1743.650024414062</v>
@@ -4184,10 +4184,10 @@
         <v>50.81000137329102</v>
       </c>
       <c r="H117" t="n">
-        <v>352.7032775878906</v>
+        <v>352.7033081054688</v>
       </c>
       <c r="I117" t="n">
-        <v>2379.413330078125</v>
+        <v>2379.4130859375</v>
       </c>
       <c r="J117" t="n">
         <v>170.75</v>
@@ -4216,10 +4216,10 @@
         <v>49.45999908447266</v>
       </c>
       <c r="H118" t="n">
-        <v>351.7697143554688</v>
+        <v>351.7696838378906</v>
       </c>
       <c r="I118" t="n">
-        <v>2267.477294921875</v>
+        <v>2267.4775390625</v>
       </c>
       <c r="J118" t="n">
         <v>172.3500061035156</v>
@@ -4236,7 +4236,7 @@
         <v>2105</v>
       </c>
       <c r="D119" t="n">
-        <v>2105.6494140625</v>
+        <v>2105.649658203125</v>
       </c>
       <c r="E119" t="n">
         <v>1796.75</v>
@@ -4248,10 +4248,10 @@
         <v>50.52000045776367</v>
       </c>
       <c r="H119" t="n">
-        <v>352.75244140625</v>
+        <v>352.7524719238281</v>
       </c>
       <c r="I119" t="n">
-        <v>2261.33642578125</v>
+        <v>2261.336181640625</v>
       </c>
       <c r="J119" t="n">
         <v>173</v>
@@ -4280,10 +4280,10 @@
         <v>52.88999938964844</v>
       </c>
       <c r="H120" t="n">
-        <v>354.3739624023438</v>
+        <v>354.3739929199219</v>
       </c>
       <c r="I120" t="n">
-        <v>2288.247314453125</v>
+        <v>2288.2470703125</v>
       </c>
       <c r="J120" t="n">
         <v>171.8000030517578</v>
@@ -4300,7 +4300,7 @@
         <v>2140.550048828125</v>
       </c>
       <c r="D121" t="n">
-        <v>2176.74072265625</v>
+        <v>2176.7412109375</v>
       </c>
       <c r="E121" t="n">
         <v>1917.650024414062</v>
@@ -4344,7 +4344,7 @@
         <v>54.04999923706055</v>
       </c>
       <c r="H122" t="n">
-        <v>360.1229248046875</v>
+        <v>360.1229553222656</v>
       </c>
       <c r="I122" t="n">
         <v>2390.896728515625</v>
@@ -4364,19 +4364,19 @@
         <v>2347.89990234375</v>
       </c>
       <c r="D123" t="n">
-        <v>2215.1552734375</v>
+        <v>2215.155029296875</v>
       </c>
       <c r="E123" t="n">
         <v>1901.699951171875</v>
       </c>
       <c r="F123" t="n">
-        <v>659.7809448242188</v>
+        <v>659.781005859375</v>
       </c>
       <c r="G123" t="n">
         <v>54.0099983215332</v>
       </c>
       <c r="H123" t="n">
-        <v>359.1893310546875</v>
+        <v>359.1893615722656</v>
       </c>
       <c r="I123" t="n">
         <v>2344.2646484375</v>
@@ -4396,7 +4396,7 @@
         <v>2473.64990234375</v>
       </c>
       <c r="D124" t="n">
-        <v>2186.019775390625</v>
+        <v>2186.02001953125</v>
       </c>
       <c r="E124" t="n">
         <v>1929.599975585938</v>
@@ -4408,10 +4408,10 @@
         <v>52.56999969482422</v>
       </c>
       <c r="H124" t="n">
-        <v>356.7325134277344</v>
+        <v>356.7325439453125</v>
       </c>
       <c r="I124" t="n">
-        <v>2389.398681640625</v>
+        <v>2389.3984375</v>
       </c>
       <c r="J124" t="n">
         <v>176</v>
@@ -4428,7 +4428,7 @@
         <v>2400.64990234375</v>
       </c>
       <c r="D125" t="n">
-        <v>2227.22802734375</v>
+        <v>2227.228271484375</v>
       </c>
       <c r="E125" t="n">
         <v>1963.650024414062</v>
@@ -4492,7 +4492,7 @@
         <v>2476.300048828125</v>
       </c>
       <c r="D127" t="n">
-        <v>2241.446533203125</v>
+        <v>2241.4462890625</v>
       </c>
       <c r="E127" t="n">
         <v>1876.400024414062</v>
@@ -4524,19 +4524,19 @@
         <v>2511.64990234375</v>
       </c>
       <c r="D128" t="n">
-        <v>2267.787353515625</v>
+        <v>2267.787841796875</v>
       </c>
       <c r="E128" t="n">
         <v>1903.699951171875</v>
       </c>
       <c r="F128" t="n">
-        <v>675.89111328125</v>
+        <v>675.8910522460938</v>
       </c>
       <c r="G128" t="n">
         <v>52.54000091552734</v>
       </c>
       <c r="H128" t="n">
-        <v>361.891845703125</v>
+        <v>361.8918762207031</v>
       </c>
       <c r="I128" t="n">
         <v>2471.728271484375</v>
@@ -4568,10 +4568,10 @@
         <v>55.11999893188477</v>
       </c>
       <c r="H129" t="n">
-        <v>360.6143188476562</v>
+        <v>360.6143493652344</v>
       </c>
       <c r="I129" t="n">
-        <v>2482.113037109375</v>
+        <v>2482.11328125</v>
       </c>
       <c r="J129" t="n">
         <v>167.4499969482422</v>
@@ -4588,7 +4588,7 @@
         <v>2545.89990234375</v>
       </c>
       <c r="D130" t="n">
-        <v>2287.9423828125</v>
+        <v>2287.94287109375</v>
       </c>
       <c r="E130" t="n">
         <v>1921</v>
@@ -4603,7 +4603,7 @@
         <v>362.0884094238281</v>
       </c>
       <c r="I130" t="n">
-        <v>2537.08251953125</v>
+        <v>2537.082275390625</v>
       </c>
       <c r="J130" t="n">
         <v>190.5</v>
@@ -4620,7 +4620,7 @@
         <v>2690.949951171875</v>
       </c>
       <c r="D131" t="n">
-        <v>2367.96435546875</v>
+        <v>2367.9638671875</v>
       </c>
       <c r="E131" t="n">
         <v>2207.35009765625</v>
@@ -4632,10 +4632,10 @@
         <v>57.02000045776367</v>
       </c>
       <c r="H131" t="n">
-        <v>362.8255004882812</v>
+        <v>362.8254699707031</v>
       </c>
       <c r="I131" t="n">
-        <v>2712.6748046875</v>
+        <v>2712.675048828125</v>
       </c>
       <c r="J131" t="n">
         <v>191.0500030517578</v>
@@ -4652,7 +4652,7 @@
         <v>2749.800048828125</v>
       </c>
       <c r="D132" t="n">
-        <v>2360.380859375</v>
+        <v>2360.380615234375</v>
       </c>
       <c r="E132" t="n">
         <v>2294.75</v>
@@ -4664,10 +4664,10 @@
         <v>58.54999923706055</v>
       </c>
       <c r="H132" t="n">
-        <v>364.4961547851562</v>
+        <v>364.49609375</v>
       </c>
       <c r="I132" t="n">
-        <v>2793.456787109375</v>
+        <v>2793.45654296875</v>
       </c>
       <c r="J132" t="n">
         <v>196.8500061035156</v>
@@ -4684,7 +4684,7 @@
         <v>2730.800048828125</v>
       </c>
       <c r="D133" t="n">
-        <v>2348.25830078125</v>
+        <v>2348.258056640625</v>
       </c>
       <c r="E133" t="n">
         <v>2104.75</v>
@@ -4699,7 +4699,7 @@
         <v>364.7909545898438</v>
       </c>
       <c r="I133" t="n">
-        <v>2668.190185546875</v>
+        <v>2668.18994140625</v>
       </c>
       <c r="J133" t="n">
         <v>201.6000061035156</v>
@@ -4716,19 +4716,19 @@
         <v>2889.14990234375</v>
       </c>
       <c r="D134" t="n">
-        <v>2378.772216796875</v>
+        <v>2378.77197265625</v>
       </c>
       <c r="E134" t="n">
         <v>2087</v>
       </c>
       <c r="F134" t="n">
-        <v>710.0762329101562</v>
+        <v>710.076171875</v>
       </c>
       <c r="G134" t="n">
         <v>56.7400016784668</v>
       </c>
       <c r="H134" t="n">
-        <v>363.5133666992188</v>
+        <v>363.5133972167969</v>
       </c>
       <c r="I134" t="n">
         <v>2761.06298828125</v>
@@ -4760,7 +4760,7 @@
         <v>57.34999847412109</v>
       </c>
       <c r="H135" t="n">
-        <v>362.7763671875</v>
+        <v>362.7763366699219</v>
       </c>
       <c r="I135" t="n">
         <v>2803.85400390625</v>
@@ -4786,7 +4786,7 @@
         <v>2093.25</v>
       </c>
       <c r="F136" t="n">
-        <v>725.0726318359375</v>
+        <v>725.0725708007812</v>
       </c>
       <c r="G136" t="n">
         <v>57.97000122070312</v>
@@ -4824,7 +4824,7 @@
         <v>58.66999816894531</v>
       </c>
       <c r="H137" t="n">
-        <v>364.5452880859375</v>
+        <v>364.5452575683594</v>
       </c>
       <c r="I137" t="n">
         <v>2828.470703125</v>
@@ -4850,16 +4850,16 @@
         <v>2084.300048828125</v>
       </c>
       <c r="F138" t="n">
-        <v>728.7972412109375</v>
+        <v>728.7971801757812</v>
       </c>
       <c r="G138" t="n">
         <v>57.97999954223633</v>
       </c>
       <c r="H138" t="n">
-        <v>361.4988098144531</v>
+        <v>361.498779296875</v>
       </c>
       <c r="I138" t="n">
-        <v>2776.141845703125</v>
+        <v>2776.14208984375</v>
       </c>
       <c r="J138" t="n">
         <v>242.5</v>
@@ -4888,10 +4888,10 @@
         <v>58.79999923706055</v>
       </c>
       <c r="H139" t="n">
-        <v>364.3487243652344</v>
+        <v>364.3486938476562</v>
       </c>
       <c r="I139" t="n">
-        <v>2872.659912109375</v>
+        <v>2872.66015625</v>
       </c>
       <c r="J139" t="n">
         <v>230.4499969482422</v>
@@ -4908,7 +4908,7 @@
         <v>2977.449951171875</v>
       </c>
       <c r="D140" t="n">
-        <v>2494.86083984375</v>
+        <v>2494.860595703125</v>
       </c>
       <c r="E140" t="n">
         <v>2120.449951171875</v>
@@ -4946,7 +4946,7 @@
         <v>2137.60009765625</v>
       </c>
       <c r="F141" t="n">
-        <v>735.0703125</v>
+        <v>735.0702514648438</v>
       </c>
       <c r="G141" t="n">
         <v>58.34000015258789</v>
@@ -4984,7 +4984,7 @@
         <v>59.54000091552734</v>
       </c>
       <c r="H142" t="n">
-        <v>363.5625</v>
+        <v>363.5625305175781</v>
       </c>
       <c r="I142" t="n">
         <v>2894.230224609375</v>
@@ -5004,13 +5004,13 @@
         <v>2996.10009765625</v>
       </c>
       <c r="D143" t="n">
-        <v>2544.071044921875</v>
+        <v>2544.0712890625</v>
       </c>
       <c r="E143" t="n">
         <v>2099.199951171875</v>
       </c>
       <c r="F143" t="n">
-        <v>745.5579833984375</v>
+        <v>745.5579223632812</v>
       </c>
       <c r="G143" t="n">
         <v>62.4900016784668</v>
@@ -5019,7 +5019,7 @@
         <v>364.4469909667969</v>
       </c>
       <c r="I143" t="n">
-        <v>2956.04541015625</v>
+        <v>2956.045654296875</v>
       </c>
       <c r="J143" t="n">
         <v>252.5</v>
@@ -5080,10 +5080,10 @@
         <v>62.79000091552734</v>
       </c>
       <c r="H145" t="n">
-        <v>368.3287963867188</v>
+        <v>368.3287658691406</v>
       </c>
       <c r="I145" t="n">
-        <v>3122.91650390625</v>
+        <v>3122.916748046875</v>
       </c>
       <c r="J145" t="n">
         <v>256.6000061035156</v>
@@ -5100,19 +5100,19 @@
         <v>3261.75</v>
       </c>
       <c r="D146" t="n">
-        <v>2655.318603515625</v>
+        <v>2655.31884765625</v>
       </c>
       <c r="E146" t="n">
         <v>2273.699951171875</v>
       </c>
       <c r="F146" t="n">
-        <v>785.3524169921875</v>
+        <v>785.3523559570312</v>
       </c>
       <c r="G146" t="n">
         <v>64.37000274658203</v>
       </c>
       <c r="H146" t="n">
-        <v>368.9183959960938</v>
+        <v>368.9184265136719</v>
       </c>
       <c r="I146" t="n">
         <v>3213.24267578125</v>
@@ -5132,7 +5132,7 @@
         <v>3421.449951171875</v>
       </c>
       <c r="D147" t="n">
-        <v>2678.77587890625</v>
+        <v>2678.776123046875</v>
       </c>
       <c r="E147" t="n">
         <v>2296.14990234375</v>
@@ -5144,7 +5144,7 @@
         <v>65.70999908447266</v>
       </c>
       <c r="H147" t="n">
-        <v>372.1122741699219</v>
+        <v>372.1123046875</v>
       </c>
       <c r="I147" t="n">
         <v>3244.39990234375</v>
@@ -5196,7 +5196,7 @@
         <v>3530.449951171875</v>
       </c>
       <c r="D149" t="n">
-        <v>2718.653564453125</v>
+        <v>2718.65380859375</v>
       </c>
       <c r="E149" t="n">
         <v>2190.949951171875</v>
@@ -5228,7 +5228,7 @@
         <v>3313.550048828125</v>
       </c>
       <c r="D150" t="n">
-        <v>2693.4990234375</v>
+        <v>2693.499267578125</v>
       </c>
       <c r="E150" t="n">
         <v>2106.199951171875</v>
@@ -5240,10 +5240,10 @@
         <v>66.41000366210938</v>
       </c>
       <c r="H150" t="n">
-        <v>376.0432434082031</v>
+        <v>376.043212890625</v>
       </c>
       <c r="I150" t="n">
-        <v>3342.81494140625</v>
+        <v>3342.814697265625</v>
       </c>
       <c r="J150" t="n">
         <v>298.7999877929688</v>
@@ -5272,10 +5272,10 @@
         <v>65.72000122070312</v>
       </c>
       <c r="H151" t="n">
-        <v>373.6355285644531</v>
+        <v>373.6355590820312</v>
       </c>
       <c r="I151" t="n">
-        <v>3360.39111328125</v>
+        <v>3360.390869140625</v>
       </c>
       <c r="J151" t="n">
         <v>291.8500061035156</v>
@@ -5292,19 +5292,19 @@
         <v>3436.14990234375</v>
       </c>
       <c r="D152" t="n">
-        <v>2822.0654296875</v>
+        <v>2822.065185546875</v>
       </c>
       <c r="E152" t="n">
         <v>2164.949951171875</v>
       </c>
       <c r="F152" t="n">
-        <v>774.8646850585938</v>
+        <v>774.8646240234375</v>
       </c>
       <c r="G152" t="n">
         <v>67.94999694824219</v>
       </c>
       <c r="H152" t="n">
-        <v>373.4881286621094</v>
+        <v>373.4880981445312</v>
       </c>
       <c r="I152" t="n">
         <v>3346.809326171875</v>
@@ -5324,19 +5324,19 @@
         <v>3493.949951171875</v>
       </c>
       <c r="D153" t="n">
-        <v>2828.90283203125</v>
+        <v>2828.903076171875</v>
       </c>
       <c r="E153" t="n">
         <v>2164.89990234375</v>
       </c>
       <c r="F153" t="n">
-        <v>777.0210571289062</v>
+        <v>777.02099609375</v>
       </c>
       <c r="G153" t="n">
         <v>68.48000335693359</v>
       </c>
       <c r="H153" t="n">
-        <v>373.6355285644531</v>
+        <v>373.6355590820312</v>
       </c>
       <c r="I153" t="n">
         <v>3347.708251953125</v>
@@ -5368,7 +5368,7 @@
         <v>69.02999877929688</v>
       </c>
       <c r="H154" t="n">
-        <v>378.1560974121094</v>
+        <v>378.1561279296875</v>
       </c>
       <c r="I154" t="n">
         <v>3420.7080078125</v>
@@ -5388,22 +5388,22 @@
         <v>3581.60009765625</v>
       </c>
       <c r="D155" t="n">
-        <v>2970.445556640625</v>
+        <v>2970.445068359375</v>
       </c>
       <c r="E155" t="n">
         <v>2218.199951171875</v>
       </c>
       <c r="F155" t="n">
-        <v>807.7980346679688</v>
+        <v>807.798095703125</v>
       </c>
       <c r="G155" t="n">
         <v>72.47000122070312</v>
       </c>
       <c r="H155" t="n">
-        <v>389.2610473632812</v>
+        <v>389.2610168457031</v>
       </c>
       <c r="I155" t="n">
-        <v>3484.920166015625</v>
+        <v>3484.919921875</v>
       </c>
       <c r="J155" t="n">
         <v>301.25</v>
@@ -5432,10 +5432,10 @@
         <v>76.08999633789062</v>
       </c>
       <c r="H156" t="n">
-        <v>391.4230346679688</v>
+        <v>391.4230041503906</v>
       </c>
       <c r="I156" t="n">
-        <v>3467.094482421875</v>
+        <v>3467.0947265625</v>
       </c>
       <c r="J156" t="n">
         <v>331.3500061035156</v>
@@ -5464,7 +5464,7 @@
         <v>79.88999938964844</v>
       </c>
       <c r="H157" t="n">
-        <v>402.5279235839844</v>
+        <v>402.5279541015625</v>
       </c>
       <c r="I157" t="n">
         <v>3458.556396484375</v>
@@ -5496,10 +5496,10 @@
         <v>82.38999938964844</v>
       </c>
       <c r="H158" t="n">
-        <v>413.1906433105469</v>
+        <v>413.1906127929688</v>
       </c>
       <c r="I158" t="n">
-        <v>3386.25537109375</v>
+        <v>3386.255126953125</v>
       </c>
       <c r="J158" t="n">
         <v>366.3500061035156</v>
@@ -5522,7 +5522,7 @@
         <v>2519.75</v>
       </c>
       <c r="F159" t="n">
-        <v>823.5785522460938</v>
+        <v>823.57861328125</v>
       </c>
       <c r="G159" t="n">
         <v>86.5</v>
@@ -5548,7 +5548,7 @@
         <v>3601.89990234375</v>
       </c>
       <c r="D160" t="n">
-        <v>3025.1455078125</v>
+        <v>3025.145751953125</v>
       </c>
       <c r="E160" t="n">
         <v>2412.89990234375</v>
@@ -5595,7 +5595,7 @@
         <v>397.1720275878906</v>
       </c>
       <c r="I161" t="n">
-        <v>3423.10498046875</v>
+        <v>3423.104736328125</v>
       </c>
       <c r="J161" t="n">
         <v>388.2000122070312</v>
@@ -5618,7 +5618,7 @@
         <v>2368.300048828125</v>
       </c>
       <c r="F162" t="n">
-        <v>799.8096923828125</v>
+        <v>799.8097534179688</v>
       </c>
       <c r="G162" t="n">
         <v>78.69999694824219</v>
@@ -5650,13 +5650,13 @@
         <v>2392.75</v>
       </c>
       <c r="F163" t="n">
-        <v>821.0792236328125</v>
+        <v>821.0791625976562</v>
       </c>
       <c r="G163" t="n">
         <v>75.09999847412109</v>
       </c>
       <c r="H163" t="n">
-        <v>395.8944702148438</v>
+        <v>395.8945007324219</v>
       </c>
       <c r="I163" t="n">
         <v>3454.9111328125</v>
@@ -5714,16 +5714,16 @@
         <v>2436.199951171875</v>
       </c>
       <c r="F165" t="n">
-        <v>825.44091796875</v>
+        <v>825.4409790039062</v>
       </c>
       <c r="G165" t="n">
         <v>82.79000091552734</v>
       </c>
       <c r="H165" t="n">
-        <v>404.1494445800781</v>
+        <v>404.1494140625</v>
       </c>
       <c r="I165" t="n">
-        <v>3739.820556640625</v>
+        <v>3739.8203125</v>
       </c>
       <c r="J165" t="n">
         <v>471.5</v>
@@ -5752,7 +5752,7 @@
         <v>81.69999694824219</v>
       </c>
       <c r="H166" t="n">
-        <v>402.7244262695312</v>
+        <v>402.7244567871094</v>
       </c>
       <c r="I166" t="n">
         <v>3634.26513671875</v>
@@ -5787,7 +5787,7 @@
         <v>408.4243469238281</v>
       </c>
       <c r="I167" t="n">
-        <v>3617.887939453125</v>
+        <v>3617.8876953125</v>
       </c>
       <c r="J167" t="n">
         <v>519.7999877929688</v>
@@ -5804,13 +5804,13 @@
         <v>3881.25</v>
       </c>
       <c r="D168" t="n">
-        <v>3340.47216796875</v>
+        <v>3340.471923828125</v>
       </c>
       <c r="E168" t="n">
         <v>2353.800048828125</v>
       </c>
       <c r="F168" t="n">
-        <v>834.0172729492188</v>
+        <v>834.0172119140625</v>
       </c>
       <c r="G168" t="n">
         <v>77.97000122070312</v>
@@ -5819,7 +5819,7 @@
         <v>410.7337646484375</v>
       </c>
       <c r="I168" t="n">
-        <v>3525.763916015625</v>
+        <v>3525.76416015625</v>
       </c>
       <c r="J168" t="n">
         <v>545.75</v>
@@ -5851,7 +5851,7 @@
         <v>428.9634704589844</v>
       </c>
       <c r="I169" t="n">
-        <v>3677.8056640625</v>
+        <v>3677.805419921875</v>
       </c>
       <c r="J169" t="n">
         <v>518.5</v>
@@ -5868,7 +5868,7 @@
         <v>3893.10009765625</v>
       </c>
       <c r="D170" t="n">
-        <v>3467.44091796875</v>
+        <v>3467.441162109375</v>
       </c>
       <c r="E170" t="n">
         <v>2346.949951171875</v>
@@ -5880,7 +5880,7 @@
         <v>81.26000213623047</v>
       </c>
       <c r="H170" t="n">
-        <v>441.1493530273438</v>
+        <v>441.1493835449219</v>
       </c>
       <c r="I170" t="n">
         <v>3656.235107421875</v>
@@ -5915,7 +5915,7 @@
         <v>453.9249267578125</v>
       </c>
       <c r="I171" t="n">
-        <v>3624.927978515625</v>
+        <v>3624.92822265625</v>
       </c>
       <c r="J171" t="n">
         <v>468</v>
@@ -5932,7 +5932,7 @@
         <v>3931.10009765625</v>
       </c>
       <c r="D172" t="n">
-        <v>3444.931884765625</v>
+        <v>3444.93212890625</v>
       </c>
       <c r="E172" t="n">
         <v>2315.89990234375</v>
@@ -5964,13 +5964,13 @@
         <v>4006</v>
       </c>
       <c r="D173" t="n">
-        <v>3457.509033203125</v>
+        <v>3457.50927734375</v>
       </c>
       <c r="E173" t="n">
         <v>2355.949951171875</v>
       </c>
       <c r="F173" t="n">
-        <v>919.879150390625</v>
+        <v>919.8792114257812</v>
       </c>
       <c r="G173" t="n">
         <v>79.51999664306641</v>
@@ -5996,7 +5996,7 @@
         <v>4037.050048828125</v>
       </c>
       <c r="D174" t="n">
-        <v>3549.342041015625</v>
+        <v>3549.34228515625</v>
       </c>
       <c r="E174" t="n">
         <v>2335.64990234375</v>
@@ -6008,10 +6008,10 @@
         <v>78.72000122070312</v>
       </c>
       <c r="H174" t="n">
-        <v>478.1001892089844</v>
+        <v>478.1002197265625</v>
       </c>
       <c r="I174" t="n">
-        <v>3599.812255859375</v>
+        <v>3599.8125</v>
       </c>
       <c r="J174" t="n">
         <v>443.5</v>
@@ -6040,7 +6040,7 @@
         <v>76.91000366210938</v>
       </c>
       <c r="H175" t="n">
-        <v>515.5422973632812</v>
+        <v>515.5423583984375</v>
       </c>
       <c r="I175" t="n">
         <v>3559.517578125</v>
@@ -6066,7 +6066,7 @@
         <v>2343.89990234375</v>
       </c>
       <c r="F176" t="n">
-        <v>949.3330078125</v>
+        <v>949.3329467773438</v>
       </c>
       <c r="G176" t="n">
         <v>79.83999633789062</v>
@@ -6075,7 +6075,7 @@
         <v>529.447998046875</v>
       </c>
       <c r="I176" t="n">
-        <v>3596.417236328125</v>
+        <v>3596.41748046875</v>
       </c>
       <c r="J176" t="n">
         <v>488.8999938964844</v>
@@ -6098,13 +6098,13 @@
         <v>2316.60009765625</v>
       </c>
       <c r="F177" t="n">
-        <v>919.5851440429688</v>
+        <v>919.585205078125</v>
       </c>
       <c r="G177" t="n">
         <v>77.55000305175781</v>
       </c>
       <c r="H177" t="n">
-        <v>507.7787475585938</v>
+        <v>507.7787780761719</v>
       </c>
       <c r="I177" t="n">
         <v>3523.96630859375</v>
@@ -6124,7 +6124,7 @@
         <v>4029.39990234375</v>
       </c>
       <c r="D178" t="n">
-        <v>3771.787353515625</v>
+        <v>3771.787109375</v>
       </c>
       <c r="E178" t="n">
         <v>2346.35009765625</v>
@@ -6139,7 +6139,7 @@
         <v>555.1466064453125</v>
       </c>
       <c r="I178" t="n">
-        <v>3615.091796875</v>
+        <v>3615.091552734375</v>
       </c>
       <c r="J178" t="n">
         <v>442.25</v>
@@ -6162,7 +6162,7 @@
         <v>2399.949951171875</v>
       </c>
       <c r="F179" t="n">
-        <v>950.999267578125</v>
+        <v>950.9992065429688</v>
       </c>
       <c r="G179" t="n">
         <v>79.65000152587891</v>
@@ -6203,7 +6203,7 @@
         <v>532.0031127929688</v>
       </c>
       <c r="I180" t="n">
-        <v>3560.616455078125</v>
+        <v>3560.6162109375</v>
       </c>
       <c r="J180" t="n">
         <v>421.2000122070312</v>
@@ -6220,13 +6220,13 @@
         <v>3997.89990234375</v>
       </c>
       <c r="D181" t="n">
-        <v>3709.550537109375</v>
+        <v>3709.55078125</v>
       </c>
       <c r="E181" t="n">
         <v>2363.60009765625</v>
       </c>
       <c r="F181" t="n">
-        <v>927.8675537109375</v>
+        <v>927.8674926757812</v>
       </c>
       <c r="G181" t="n">
         <v>79.25</v>
@@ -6235,7 +6235,7 @@
         <v>524.8291625976562</v>
       </c>
       <c r="I181" t="n">
-        <v>3624.927978515625</v>
+        <v>3624.92822265625</v>
       </c>
       <c r="J181" t="n">
         <v>408.4500122070312</v>
@@ -6252,19 +6252,19 @@
         <v>3872.550048828125</v>
       </c>
       <c r="D182" t="n">
-        <v>3667.627197265625</v>
+        <v>3667.626953125</v>
       </c>
       <c r="E182" t="n">
         <v>2323.85009765625</v>
       </c>
       <c r="F182" t="n">
-        <v>895.6692504882812</v>
+        <v>895.669189453125</v>
       </c>
       <c r="G182" t="n">
         <v>77.12000274658203</v>
       </c>
       <c r="H182" t="n">
-        <v>530.0377197265625</v>
+        <v>530.0376586914062</v>
       </c>
       <c r="I182" t="n">
         <v>3540.393798828125</v>
@@ -6284,7 +6284,7 @@
         <v>3713</v>
       </c>
       <c r="D183" t="n">
-        <v>3579.6865234375</v>
+        <v>3579.686767578125</v>
       </c>
       <c r="E183" t="n">
         <v>2210.35009765625</v>
@@ -6299,7 +6299,7 @@
         <v>502.3737487792969</v>
       </c>
       <c r="I183" t="n">
-        <v>3366.432373046875</v>
+        <v>3366.432861328125</v>
       </c>
       <c r="J183" t="n">
         <v>368.6499938964844</v>
@@ -6322,7 +6322,7 @@
         <v>2146.300048828125</v>
       </c>
       <c r="F184" t="n">
-        <v>827.4502563476562</v>
+        <v>827.4501953125</v>
       </c>
       <c r="G184" t="n">
         <v>74.51000213623047</v>
@@ -6331,7 +6331,7 @@
         <v>495.6419982910156</v>
       </c>
       <c r="I184" t="n">
-        <v>3374.072265625</v>
+        <v>3374.072021484375</v>
       </c>
       <c r="J184" t="n">
         <v>350.25</v>
@@ -6354,13 +6354,13 @@
         <v>2051.050048828125</v>
       </c>
       <c r="F185" t="n">
-        <v>810.6895141601562</v>
+        <v>810.689453125</v>
       </c>
       <c r="G185" t="n">
         <v>73.55000305175781</v>
       </c>
       <c r="H185" t="n">
-        <v>491.4162292480469</v>
+        <v>491.4161987304688</v>
       </c>
       <c r="I185" t="n">
         <v>3443.3271484375</v>
@@ -6412,22 +6412,22 @@
         <v>3289.800048828125</v>
       </c>
       <c r="D187" t="n">
-        <v>3449.473876953125</v>
+        <v>3449.47412109375</v>
       </c>
       <c r="E187" t="n">
         <v>2260.800048828125</v>
       </c>
       <c r="F187" t="n">
-        <v>804.3674926757812</v>
+        <v>804.3675537109375</v>
       </c>
       <c r="G187" t="n">
         <v>74.69999694824219</v>
       </c>
       <c r="H187" t="n">
-        <v>506.69775390625</v>
+        <v>506.6977233886719</v>
       </c>
       <c r="I187" t="n">
-        <v>3335.275390625</v>
+        <v>3335.275146484375</v>
       </c>
       <c r="J187" t="n">
         <v>373.0499877929688</v>
@@ -6444,13 +6444,13 @@
         <v>3123.64990234375</v>
       </c>
       <c r="D188" t="n">
-        <v>3151.565673828125</v>
+        <v>3151.56591796875</v>
       </c>
       <c r="E188" t="n">
         <v>2074.050048828125</v>
       </c>
       <c r="F188" t="n">
-        <v>768.836669921875</v>
+        <v>768.8367309570312</v>
       </c>
       <c r="G188" t="n">
         <v>70.97000122070312</v>
@@ -6459,7 +6459,7 @@
         <v>480.2130737304688</v>
       </c>
       <c r="I188" t="n">
-        <v>3096.552734375</v>
+        <v>3096.552978515625</v>
       </c>
       <c r="J188" t="n">
         <v>354.3999938964844</v>
@@ -6491,7 +6491,7 @@
         <v>483.7017822265625</v>
       </c>
       <c r="I189" t="n">
-        <v>3211.744873046875</v>
+        <v>3211.74462890625</v>
       </c>
       <c r="J189" t="n">
         <v>341.6499938964844</v>
@@ -6546,16 +6546,16 @@
         <v>2204.14990234375</v>
       </c>
       <c r="F191" t="n">
-        <v>800.6919555664062</v>
+        <v>800.69189453125</v>
       </c>
       <c r="G191" t="n">
         <v>74.56999969482422</v>
       </c>
       <c r="H191" t="n">
-        <v>512.7906494140625</v>
+        <v>512.7907104492188</v>
       </c>
       <c r="I191" t="n">
-        <v>3183.23388671875</v>
+        <v>3183.234130859375</v>
       </c>
       <c r="J191" t="n">
         <v>349.8500061035156</v>
@@ -6610,7 +6610,7 @@
         <v>2128.800048828125</v>
       </c>
       <c r="F193" t="n">
-        <v>781.52978515625</v>
+        <v>781.5297241210938</v>
       </c>
       <c r="G193" t="n">
         <v>71.37000274658203</v>
@@ -6619,7 +6619,7 @@
         <v>491.5636596679688</v>
       </c>
       <c r="I193" t="n">
-        <v>3169.25341796875</v>
+        <v>3169.253173828125</v>
       </c>
       <c r="J193" t="n">
         <v>337.3500061035156</v>
@@ -6648,7 +6648,7 @@
         <v>71.36000061035156</v>
       </c>
       <c r="H194" t="n">
-        <v>496.7230529785156</v>
+        <v>496.7230224609375</v>
       </c>
       <c r="I194" t="n">
         <v>3198.463134765625</v>
@@ -6706,13 +6706,13 @@
         <v>2033.150024414062</v>
       </c>
       <c r="F196" t="n">
-        <v>764.6219482421875</v>
+        <v>764.6220092773438</v>
       </c>
       <c r="G196" t="n">
         <v>66.25</v>
       </c>
       <c r="H196" t="n">
-        <v>493.1851501464844</v>
+        <v>493.1851806640625</v>
       </c>
       <c r="I196" t="n">
         <v>3042.975830078125</v>
@@ -6779,7 +6779,7 @@
         <v>499.0815734863281</v>
       </c>
       <c r="I198" t="n">
-        <v>3148.531494140625</v>
+        <v>3148.53173828125</v>
       </c>
       <c r="J198" t="n">
         <v>326.2999877929688</v>
@@ -6796,19 +6796,19 @@
         <v>3141.699951171875</v>
       </c>
       <c r="D199" t="n">
-        <v>3271.298095703125</v>
+        <v>3271.2978515625</v>
       </c>
       <c r="E199" t="n">
         <v>2119.800048828125</v>
       </c>
       <c r="F199" t="n">
-        <v>789.0770263671875</v>
+        <v>789.0769653320312</v>
       </c>
       <c r="G199" t="n">
         <v>66.72000122070312</v>
       </c>
       <c r="H199" t="n">
-        <v>501.8823547363281</v>
+        <v>501.8823852539062</v>
       </c>
       <c r="I199" t="n">
         <v>3162.512451171875</v>
@@ -6828,7 +6828,7 @@
         <v>3270.050048828125</v>
       </c>
       <c r="D200" t="n">
-        <v>3351.003173828125</v>
+        <v>3351.0029296875</v>
       </c>
       <c r="E200" t="n">
         <v>2138.89990234375</v>
@@ -6840,10 +6840,10 @@
         <v>67.69000244140625</v>
       </c>
       <c r="H200" t="n">
-        <v>508.7615051269531</v>
+        <v>508.761474609375</v>
       </c>
       <c r="I200" t="n">
-        <v>3272.611572265625</v>
+        <v>3272.611328125</v>
       </c>
       <c r="J200" t="n">
         <v>325.7999877929688</v>
@@ -6860,7 +6860,7 @@
         <v>3273.699951171875</v>
       </c>
       <c r="D201" t="n">
-        <v>3305.884765625</v>
+        <v>3305.885009765625</v>
       </c>
       <c r="E201" t="n">
         <v>2105.300048828125</v>
@@ -6892,7 +6892,7 @@
         <v>3283.949951171875</v>
       </c>
       <c r="D202" t="n">
-        <v>3303.7890625</v>
+        <v>3303.788818359375</v>
       </c>
       <c r="E202" t="n">
         <v>2121.25</v>
@@ -6924,22 +6924,22 @@
         <v>3188.449951171875</v>
       </c>
       <c r="D203" t="n">
-        <v>3294.505615234375</v>
+        <v>3294.505859375</v>
       </c>
       <c r="E203" t="n">
         <v>2079.89990234375</v>
       </c>
       <c r="F203" t="n">
-        <v>784.47021484375</v>
+        <v>784.4701538085938</v>
       </c>
       <c r="G203" t="n">
         <v>66.47000122070312</v>
       </c>
       <c r="H203" t="n">
-        <v>504.2408752441406</v>
+        <v>504.2409057617188</v>
       </c>
       <c r="I203" t="n">
-        <v>3378.31591796875</v>
+        <v>3378.316162109375</v>
       </c>
       <c r="J203" t="n">
         <v>323.8500061035156</v>
@@ -6956,22 +6956,22 @@
         <v>3282.449951171875</v>
       </c>
       <c r="D204" t="n">
-        <v>3318.961181640625</v>
+        <v>3318.96142578125</v>
       </c>
       <c r="E204" t="n">
         <v>2117.60009765625</v>
       </c>
       <c r="F204" t="n">
-        <v>804.95556640625</v>
+        <v>804.9556274414062</v>
       </c>
       <c r="G204" t="n">
         <v>67.48000335693359</v>
       </c>
       <c r="H204" t="n">
-        <v>518.4905395507812</v>
+        <v>518.4906005859375</v>
       </c>
       <c r="I204" t="n">
-        <v>3502.945068359375</v>
+        <v>3502.9453125</v>
       </c>
       <c r="J204" t="n">
         <v>321.3500061035156</v>
@@ -6988,7 +6988,7 @@
         <v>3277.949951171875</v>
       </c>
       <c r="D205" t="n">
-        <v>3317.26416015625</v>
+        <v>3317.264404296875</v>
       </c>
       <c r="E205" t="n">
         <v>2098.550048828125</v>
@@ -7000,7 +7000,7 @@
         <v>66.66000366210938</v>
       </c>
       <c r="H205" t="n">
-        <v>511.1200561523438</v>
+        <v>511.1200256347656</v>
       </c>
       <c r="I205" t="n">
         <v>3439.33251953125</v>
@@ -7020,19 +7020,19 @@
         <v>3348.699951171875</v>
       </c>
       <c r="D206" t="n">
-        <v>3341.3701171875</v>
+        <v>3341.370361328125</v>
       </c>
       <c r="E206" t="n">
         <v>2102.89990234375</v>
       </c>
       <c r="F206" t="n">
-        <v>807.2098999023438</v>
+        <v>807.2099609375</v>
       </c>
       <c r="G206" t="n">
         <v>66.98000335693359</v>
       </c>
       <c r="H206" t="n">
-        <v>523.7481689453125</v>
+        <v>523.7482299804688</v>
       </c>
       <c r="I206" t="n">
         <v>3597.9150390625</v>
@@ -7052,7 +7052,7 @@
         <v>3342.449951171875</v>
       </c>
       <c r="D207" t="n">
-        <v>3569.205810546875</v>
+        <v>3569.2060546875</v>
       </c>
       <c r="E207" t="n">
         <v>2121.25</v>
@@ -7064,7 +7064,7 @@
         <v>69.77999877929688</v>
       </c>
       <c r="H207" t="n">
-        <v>534.6565551757812</v>
+        <v>534.656494140625</v>
       </c>
       <c r="I207" t="n">
         <v>3676.157958984375</v>
@@ -7084,7 +7084,7 @@
         <v>3308.60009765625</v>
       </c>
       <c r="D208" t="n">
-        <v>3574.196533203125</v>
+        <v>3574.19677734375</v>
       </c>
       <c r="E208" t="n">
         <v>2137.050048828125</v>
@@ -7116,22 +7116,22 @@
         <v>3292.14990234375</v>
       </c>
       <c r="D209" t="n">
-        <v>3583.87939453125</v>
+        <v>3583.879150390625</v>
       </c>
       <c r="E209" t="n">
         <v>2106.699951171875</v>
       </c>
       <c r="F209" t="n">
-        <v>817.3054809570312</v>
+        <v>817.3055419921875</v>
       </c>
       <c r="G209" t="n">
         <v>67.34999847412109</v>
       </c>
       <c r="H209" t="n">
-        <v>530.1851806640625</v>
+        <v>530.1851196289062</v>
       </c>
       <c r="I209" t="n">
-        <v>3655.88525390625</v>
+        <v>3655.885498046875</v>
       </c>
       <c r="J209" t="n">
         <v>318.6000061035156</v>
@@ -7148,19 +7148,19 @@
         <v>3319.449951171875</v>
       </c>
       <c r="D210" t="n">
-        <v>3826.2880859375</v>
+        <v>3826.288330078125</v>
       </c>
       <c r="E210" t="n">
         <v>2121.25</v>
       </c>
       <c r="F210" t="n">
-        <v>845.7792358398438</v>
+        <v>845.7791748046875</v>
       </c>
       <c r="G210" t="n">
         <v>69.37000274658203</v>
       </c>
       <c r="H210" t="n">
-        <v>548.9552612304688</v>
+        <v>548.955322265625</v>
       </c>
       <c r="I210" t="n">
         <v>3754.10107421875</v>
@@ -7195,7 +7195,7 @@
         <v>558.291259765625</v>
       </c>
       <c r="I211" t="n">
-        <v>3795.194580078125</v>
+        <v>3795.1943359375</v>
       </c>
       <c r="J211" t="n">
         <v>351.2000122070312</v>
@@ -7224,10 +7224,10 @@
         <v>73.16000366210938</v>
       </c>
       <c r="H212" t="n">
-        <v>554.75341796875</v>
+        <v>554.7534790039062</v>
       </c>
       <c r="I212" t="n">
-        <v>3790.00146484375</v>
+        <v>3790.001708984375</v>
       </c>
       <c r="J212" t="n">
         <v>368.75</v>
@@ -7250,13 +7250,13 @@
         <v>2176</v>
       </c>
       <c r="F213" t="n">
-        <v>875.7230224609375</v>
+        <v>875.7230834960938</v>
       </c>
       <c r="G213" t="n">
         <v>74.27999877929688</v>
       </c>
       <c r="H213" t="n">
-        <v>548.5130615234375</v>
+        <v>548.5131225585938</v>
       </c>
       <c r="I213" t="n">
         <v>3702.0224609375</v>
@@ -7276,22 +7276,22 @@
         <v>3292.050048828125</v>
       </c>
       <c r="D214" t="n">
-        <v>4001.5693359375</v>
+        <v>4001.569580078125</v>
       </c>
       <c r="E214" t="n">
         <v>2196.699951171875</v>
       </c>
       <c r="F214" t="n">
-        <v>876.752197265625</v>
+        <v>876.7522583007812</v>
       </c>
       <c r="G214" t="n">
         <v>72.04000091552734</v>
       </c>
       <c r="H214" t="n">
-        <v>547.9234619140625</v>
+        <v>547.9234008789062</v>
       </c>
       <c r="I214" t="n">
-        <v>3795.39404296875</v>
+        <v>3795.394287109375</v>
       </c>
       <c r="J214" t="n">
         <v>357.8500061035156</v>
@@ -7308,19 +7308,19 @@
         <v>3287.64990234375</v>
       </c>
       <c r="D215" t="n">
-        <v>4015.244384765625</v>
+        <v>4015.24462890625</v>
       </c>
       <c r="E215" t="n">
         <v>2178.550048828125</v>
       </c>
       <c r="F215" t="n">
-        <v>877.2911987304688</v>
+        <v>877.291259765625</v>
       </c>
       <c r="G215" t="n">
         <v>71.95999908447266</v>
       </c>
       <c r="H215" t="n">
-        <v>570.2807006835938</v>
+        <v>570.2806396484375</v>
       </c>
       <c r="I215" t="n">
         <v>3864.998779296875</v>
@@ -7384,10 +7384,10 @@
         <v>69.02999877929688</v>
       </c>
       <c r="H217" t="n">
-        <v>567.2341918945312</v>
+        <v>567.2342529296875</v>
       </c>
       <c r="I217" t="n">
-        <v>3804.431884765625</v>
+        <v>3804.431640625</v>
       </c>
       <c r="J217" t="n">
         <v>402.1499938964844</v>
@@ -7404,7 +7404,7 @@
         <v>3117.550048828125</v>
       </c>
       <c r="D218" t="n">
-        <v>4010.8525390625</v>
+        <v>4010.852294921875</v>
       </c>
       <c r="E218" t="n">
         <v>2102.60009765625</v>
@@ -7448,10 +7448,10 @@
         <v>67.30000305175781</v>
       </c>
       <c r="H219" t="n">
-        <v>564.1876220703125</v>
+        <v>564.1876831054688</v>
       </c>
       <c r="I219" t="n">
-        <v>3639.657470703125</v>
+        <v>3639.65771484375</v>
       </c>
       <c r="J219" t="n">
         <v>401.1499938964844</v>
@@ -7468,13 +7468,13 @@
         <v>3018.699951171875</v>
       </c>
       <c r="D220" t="n">
-        <v>3994.58203125</v>
+        <v>3994.582275390625</v>
       </c>
       <c r="E220" t="n">
         <v>2003.300048828125</v>
       </c>
       <c r="F220" t="n">
-        <v>854.3065795898438</v>
+        <v>854.3065185546875</v>
       </c>
       <c r="G220" t="n">
         <v>66.23999786376953</v>
@@ -7515,7 +7515,7 @@
         <v>556.0801391601562</v>
       </c>
       <c r="I221" t="n">
-        <v>3666.370849609375</v>
+        <v>3666.37109375</v>
       </c>
       <c r="J221" t="n">
         <v>372.6000061035156</v>
@@ -7538,16 +7538,16 @@
         <v>2036.5</v>
       </c>
       <c r="F222" t="n">
-        <v>856.266845703125</v>
+        <v>856.2667846679688</v>
       </c>
       <c r="G222" t="n">
         <v>65.19000244140625</v>
       </c>
       <c r="H222" t="n">
-        <v>553.1810913085938</v>
+        <v>553.1810302734375</v>
       </c>
       <c r="I222" t="n">
-        <v>3747.309814453125</v>
+        <v>3747.31005859375</v>
       </c>
       <c r="J222" t="n">
         <v>358.5499877929688</v>
@@ -7579,7 +7579,7 @@
         <v>548.2182006835938</v>
       </c>
       <c r="I223" t="n">
-        <v>3725.8896484375</v>
+        <v>3725.889404296875</v>
       </c>
       <c r="J223" t="n">
         <v>367.25</v>
@@ -7628,7 +7628,7 @@
         <v>2716.14990234375</v>
       </c>
       <c r="D225" t="n">
-        <v>3879.092041015625</v>
+        <v>3879.091796875</v>
       </c>
       <c r="E225" t="n">
         <v>1990.699951171875</v>
@@ -7640,10 +7640,10 @@
         <v>65.65000152587891</v>
       </c>
       <c r="H225" t="n">
-        <v>558.63525390625</v>
+        <v>558.6353149414062</v>
       </c>
       <c r="I225" t="n">
-        <v>3600.2119140625</v>
+        <v>3600.211669921875</v>
       </c>
       <c r="J225" t="n">
         <v>404.8500061035156</v>
@@ -7660,22 +7660,22 @@
         <v>2782.699951171875</v>
       </c>
       <c r="D226" t="n">
-        <v>3871.35595703125</v>
+        <v>3871.356201171875</v>
       </c>
       <c r="E226" t="n">
         <v>2012.050048828125</v>
       </c>
       <c r="F226" t="n">
-        <v>860.775634765625</v>
+        <v>860.7755737304688</v>
       </c>
       <c r="G226" t="n">
         <v>64.94000244140625</v>
       </c>
       <c r="H226" t="n">
-        <v>555.1956787109375</v>
+        <v>555.1957397460938</v>
       </c>
       <c r="I226" t="n">
-        <v>3595.06884765625</v>
+        <v>3595.069091796875</v>
       </c>
       <c r="J226" t="n">
         <v>425.0499877929688</v>
@@ -7692,22 +7692,22 @@
         <v>2908.5</v>
       </c>
       <c r="D227" t="n">
-        <v>3910.784423828125</v>
+        <v>3910.7841796875</v>
       </c>
       <c r="E227" t="n">
         <v>2116.5</v>
       </c>
       <c r="F227" t="n">
-        <v>863.5200805664062</v>
+        <v>863.52001953125</v>
       </c>
       <c r="G227" t="n">
         <v>66.55000305175781</v>
       </c>
       <c r="H227" t="n">
-        <v>560.8955078125</v>
+        <v>560.8955688476562</v>
       </c>
       <c r="I227" t="n">
-        <v>3627.77392578125</v>
+        <v>3627.774169921875</v>
       </c>
       <c r="J227" t="n">
         <v>446.2999877929688</v>
@@ -7724,7 +7724,7 @@
         <v>2834.25</v>
       </c>
       <c r="D228" t="n">
-        <v>3907.989501953125</v>
+        <v>3907.98974609375</v>
       </c>
       <c r="E228" t="n">
         <v>2113.550048828125</v>
@@ -7736,7 +7736,7 @@
         <v>66.08000183105469</v>
       </c>
       <c r="H228" t="n">
-        <v>570.9194946289062</v>
+        <v>570.91943359375</v>
       </c>
       <c r="I228" t="n">
         <v>3607.451904296875</v>
@@ -7756,7 +7756,7 @@
         <v>2745.699951171875</v>
       </c>
       <c r="D229" t="n">
-        <v>3915.37646484375</v>
+        <v>3915.376220703125</v>
       </c>
       <c r="E229" t="n">
         <v>2062.300048828125</v>
@@ -7768,10 +7768,10 @@
         <v>65.05999755859375</v>
       </c>
       <c r="H229" t="n">
-        <v>567.97119140625</v>
+        <v>567.9712524414062</v>
       </c>
       <c r="I229" t="n">
-        <v>3574.74658203125</v>
+        <v>3574.746826171875</v>
       </c>
       <c r="J229" t="n">
         <v>410.9500122070312</v>
@@ -7788,22 +7788,22 @@
         <v>2716.14990234375</v>
       </c>
       <c r="D230" t="n">
-        <v>3923.26171875</v>
+        <v>3923.261474609375</v>
       </c>
       <c r="E230" t="n">
         <v>2042.099975585938</v>
       </c>
       <c r="F230" t="n">
-        <v>875.428955078125</v>
+        <v>875.4290161132812</v>
       </c>
       <c r="G230" t="n">
         <v>64.61000061035156</v>
       </c>
       <c r="H230" t="n">
-        <v>563.4506225585938</v>
+        <v>563.45068359375</v>
       </c>
       <c r="I230" t="n">
-        <v>3585.182373046875</v>
+        <v>3585.1826171875</v>
       </c>
       <c r="J230" t="n">
         <v>392.9500122070312</v>
@@ -7820,7 +7820,7 @@
         <v>2773</v>
       </c>
       <c r="D231" t="n">
-        <v>4024.477783203125</v>
+        <v>4024.4775390625</v>
       </c>
       <c r="E231" t="n">
         <v>2063.300048828125</v>
@@ -7835,7 +7835,7 @@
         <v>570.9685668945312</v>
       </c>
       <c r="I231" t="n">
-        <v>3691.78662109375</v>
+        <v>3691.786376953125</v>
       </c>
       <c r="J231" t="n">
         <v>373.3500061035156</v>
@@ -7858,7 +7858,7 @@
         <v>2032.699951171875</v>
       </c>
       <c r="F232" t="n">
-        <v>869.1559448242188</v>
+        <v>869.156005859375</v>
       </c>
       <c r="G232" t="n">
         <v>64.88999938964844</v>
@@ -7890,7 +7890,7 @@
         <v>2052.699951171875</v>
       </c>
       <c r="F233" t="n">
-        <v>875.1840209960938</v>
+        <v>875.1839599609375</v>
       </c>
       <c r="G233" t="n">
         <v>64.75</v>
@@ -7899,7 +7899,7 @@
         <v>577.6019897460938</v>
       </c>
       <c r="I233" t="n">
-        <v>3689.839111328125</v>
+        <v>3689.8388671875</v>
       </c>
       <c r="J233" t="n">
         <v>339.3999938964844</v>
@@ -7960,7 +7960,7 @@
         <v>62.04000091552734</v>
       </c>
       <c r="H235" t="n">
-        <v>574.9486083984375</v>
+        <v>574.9486694335938</v>
       </c>
       <c r="I235" t="n">
         <v>3636.012939453125</v>
@@ -7980,19 +7980,19 @@
         <v>2652.800048828125</v>
       </c>
       <c r="D236" t="n">
-        <v>4052.826171875</v>
+        <v>4052.825927734375</v>
       </c>
       <c r="E236" t="n">
         <v>2021.400024414062</v>
       </c>
       <c r="F236" t="n">
-        <v>877.0462646484375</v>
+        <v>877.0462036132812</v>
       </c>
       <c r="G236" t="n">
         <v>64.59999847412109</v>
       </c>
       <c r="H236" t="n">
-        <v>574.457275390625</v>
+        <v>574.4573364257812</v>
       </c>
       <c r="I236" t="n">
         <v>3581.3876953125</v>
@@ -8018,13 +8018,13 @@
         <v>2018.150024414062</v>
       </c>
       <c r="F237" t="n">
-        <v>882.6821899414062</v>
+        <v>882.68212890625</v>
       </c>
       <c r="G237" t="n">
         <v>63.86999893188477</v>
       </c>
       <c r="H237" t="n">
-        <v>572.1478881835938</v>
+        <v>572.1478271484375</v>
       </c>
       <c r="I237" t="n">
         <v>3513.03173828125</v>
@@ -8056,10 +8056,10 @@
         <v>63.09000015258789</v>
       </c>
       <c r="H238" t="n">
-        <v>551.5104370117188</v>
+        <v>551.510498046875</v>
       </c>
       <c r="I238" t="n">
-        <v>3545.88671875</v>
+        <v>3545.886474609375</v>
       </c>
       <c r="J238" t="n">
         <v>366.3999938964844</v>
@@ -8088,10 +8088,10 @@
         <v>61.58000183105469</v>
       </c>
       <c r="H239" t="n">
-        <v>546.4494018554688</v>
+        <v>546.4493408203125</v>
       </c>
       <c r="I239" t="n">
-        <v>3579.889892578125</v>
+        <v>3579.8896484375</v>
       </c>
       <c r="J239" t="n">
         <v>363.4500122070312</v>
@@ -8108,7 +8108,7 @@
         <v>2679.300048828125</v>
       </c>
       <c r="D240" t="n">
-        <v>4067.898681640625</v>
+        <v>4067.8984375</v>
       </c>
       <c r="E240" t="n">
         <v>2062.050048828125</v>
@@ -8155,7 +8155,7 @@
         <v>550.429443359375</v>
       </c>
       <c r="I241" t="n">
-        <v>3609.249267578125</v>
+        <v>3609.24951171875</v>
       </c>
       <c r="J241" t="n">
         <v>359.1000061035156</v>
@@ -8172,7 +8172,7 @@
         <v>2615.75</v>
       </c>
       <c r="D242" t="n">
-        <v>3894.863037109375</v>
+        <v>3894.86328125</v>
       </c>
       <c r="E242" t="n">
         <v>1968.25</v>
@@ -8204,7 +8204,7 @@
         <v>2518</v>
       </c>
       <c r="D243" t="n">
-        <v>3861.52392578125</v>
+        <v>3861.524169921875</v>
       </c>
       <c r="E243" t="n">
         <v>1980.75</v>
@@ -8274,7 +8274,7 @@
         <v>1876.849975585938</v>
       </c>
       <c r="F245" t="n">
-        <v>790.05712890625</v>
+        <v>790.0570678710938</v>
       </c>
       <c r="G245" t="n">
         <v>55.06000137329102</v>
@@ -8300,7 +8300,7 @@
         <v>2501.800048828125</v>
       </c>
       <c r="D246" t="n">
-        <v>3762.803466796875</v>
+        <v>3762.80322265625</v>
       </c>
       <c r="E246" t="n">
         <v>1908.699951171875</v>
@@ -8315,7 +8315,7 @@
         <v>514.2648315429688</v>
       </c>
       <c r="I246" t="n">
-        <v>3348.307373046875</v>
+        <v>3348.30712890625</v>
       </c>
       <c r="J246" t="n">
         <v>338.4500122070312</v>
@@ -8344,7 +8344,7 @@
         <v>60.70000076293945</v>
       </c>
       <c r="H247" t="n">
-        <v>509.4494323730469</v>
+        <v>509.4495239257812</v>
       </c>
       <c r="I247" t="n">
         <v>3600.861083984375</v>
@@ -8364,7 +8364,7 @@
         <v>2669.5</v>
       </c>
       <c r="D248" t="n">
-        <v>3803.67919921875</v>
+        <v>3803.679443359375</v>
       </c>
       <c r="E248" t="n">
         <v>1910.25</v>
@@ -8396,19 +8396,19 @@
         <v>2589.25</v>
       </c>
       <c r="D249" t="n">
-        <v>3851.3427734375</v>
+        <v>3851.342529296875</v>
       </c>
       <c r="E249" t="n">
         <v>1931.800048828125</v>
       </c>
       <c r="F249" t="n">
-        <v>801.8679809570312</v>
+        <v>801.8680419921875</v>
       </c>
       <c r="G249" t="n">
         <v>59.90999984741211</v>
       </c>
       <c r="H249" t="n">
-        <v>515.0509643554688</v>
+        <v>515.051025390625</v>
       </c>
       <c r="I249" t="n">
         <v>3687.7919921875</v>
@@ -8443,7 +8443,7 @@
         <v>517.4096069335938</v>
       </c>
       <c r="I250" t="n">
-        <v>3545.73681640625</v>
+        <v>3545.736572265625</v>
       </c>
       <c r="J250" t="n">
         <v>339.75</v>
@@ -8466,16 +8466,16 @@
         <v>1892.949951171875</v>
       </c>
       <c r="F251" t="n">
-        <v>804.17138671875</v>
+        <v>804.1714477539062</v>
       </c>
       <c r="G251" t="n">
         <v>58.95000076293945</v>
       </c>
       <c r="H251" t="n">
-        <v>521.78271484375</v>
+        <v>521.7827758789062</v>
       </c>
       <c r="I251" t="n">
-        <v>3593.720703125</v>
+        <v>3593.720458984375</v>
       </c>
       <c r="J251" t="n">
         <v>344.75</v>
@@ -8498,7 +8498,7 @@
         <v>1860.5</v>
       </c>
       <c r="F252" t="n">
-        <v>793.9288330078125</v>
+        <v>793.9287719726562</v>
       </c>
       <c r="G252" t="n">
         <v>57.31999969482422</v>
@@ -8536,7 +8536,7 @@
         <v>57.75</v>
       </c>
       <c r="H253" t="n">
-        <v>515.6897583007812</v>
+        <v>515.6898193359375</v>
       </c>
       <c r="I253" t="n">
         <v>3628.722900390625</v>
@@ -8556,7 +8556,7 @@
         <v>2523.35009765625</v>
       </c>
       <c r="D254" t="n">
-        <v>3817.304443359375</v>
+        <v>3817.3046875</v>
       </c>
       <c r="E254" t="n">
         <v>1838.25</v>
@@ -8568,10 +8568,10 @@
         <v>56.68000030517578</v>
       </c>
       <c r="H254" t="n">
-        <v>510.8252563476562</v>
+        <v>510.8252258300781</v>
       </c>
       <c r="I254" t="n">
-        <v>3550.530029296875</v>
+        <v>3550.52978515625</v>
       </c>
       <c r="J254" t="n">
         <v>318.5</v>
@@ -8588,7 +8588,7 @@
         <v>2614.5</v>
       </c>
       <c r="D255" t="n">
-        <v>3848.29833984375</v>
+        <v>3848.298095703125</v>
       </c>
       <c r="E255" t="n">
         <v>1891.449951171875</v>
@@ -8600,7 +8600,7 @@
         <v>57.54000091552734</v>
       </c>
       <c r="H255" t="n">
-        <v>515.6897583007812</v>
+        <v>515.6898193359375</v>
       </c>
       <c r="I255" t="n">
         <v>3624.029296875</v>
@@ -8620,7 +8620,7 @@
         <v>2652</v>
       </c>
       <c r="D256" t="n">
-        <v>3640.2763671875</v>
+        <v>3640.276611328125</v>
       </c>
       <c r="E256" t="n">
         <v>1895.199951171875</v>
@@ -8652,22 +8652,22 @@
         <v>2585.35009765625</v>
       </c>
       <c r="D257" t="n">
-        <v>3629.19677734375</v>
+        <v>3629.197021484375</v>
       </c>
       <c r="E257" t="n">
         <v>1877.150024414062</v>
       </c>
       <c r="F257" t="n">
-        <v>780.6476440429688</v>
+        <v>780.6475830078125</v>
       </c>
       <c r="G257" t="n">
         <v>55.2400016784668</v>
       </c>
       <c r="H257" t="n">
-        <v>499.3272399902344</v>
+        <v>499.3272094726562</v>
       </c>
       <c r="I257" t="n">
-        <v>3611.546630859375</v>
+        <v>3611.54638671875</v>
       </c>
       <c r="J257" t="n">
         <v>297.6499938964844</v>
@@ -8684,7 +8684,7 @@
         <v>2624</v>
       </c>
       <c r="D258" t="n">
-        <v>3640.576171875</v>
+        <v>3640.575927734375</v>
       </c>
       <c r="E258" t="n">
         <v>1889.849975585938</v>
@@ -8716,13 +8716,13 @@
         <v>2689.050048828125</v>
       </c>
       <c r="D259" t="n">
-        <v>3714.391845703125</v>
+        <v>3714.3916015625</v>
       </c>
       <c r="E259" t="n">
         <v>1915.650024414062</v>
       </c>
       <c r="F259" t="n">
-        <v>778.8833618164062</v>
+        <v>778.88330078125</v>
       </c>
       <c r="G259" t="n">
         <v>55.7400016784668</v>
@@ -8731,7 +8731,7 @@
         <v>509.6951599121094</v>
       </c>
       <c r="I259" t="n">
-        <v>3710.011474609375</v>
+        <v>3710.01123046875</v>
       </c>
       <c r="J259" t="n">
         <v>304.5499877929688</v>
@@ -8748,22 +8748,22 @@
         <v>2703.10009765625</v>
       </c>
       <c r="D260" t="n">
-        <v>3613.22607421875</v>
+        <v>3613.225830078125</v>
       </c>
       <c r="E260" t="n">
         <v>2089.800048828125</v>
       </c>
       <c r="F260" t="n">
-        <v>771.4341430664062</v>
+        <v>771.43408203125</v>
       </c>
       <c r="G260" t="n">
         <v>54.59000015258789</v>
       </c>
       <c r="H260" t="n">
-        <v>508.0735778808594</v>
+        <v>508.0735473632812</v>
       </c>
       <c r="I260" t="n">
-        <v>3725.58984375</v>
+        <v>3725.590087890625</v>
       </c>
       <c r="J260" t="n">
         <v>296.9500122070312</v>
@@ -8780,7 +8780,7 @@
         <v>2725.050048828125</v>
       </c>
       <c r="D261" t="n">
-        <v>3632.740478515625</v>
+        <v>3632.74072265625</v>
       </c>
       <c r="E261" t="n">
         <v>2166.14990234375</v>
@@ -8792,7 +8792,7 @@
         <v>56.38999938964844</v>
       </c>
       <c r="H261" t="n">
-        <v>508.56494140625</v>
+        <v>508.5649108886719</v>
       </c>
       <c r="I261" t="n">
         <v>3844.7265625</v>
@@ -8824,7 +8824,7 @@
         <v>55.7400016784668</v>
       </c>
       <c r="H262" t="n">
-        <v>511.4640502929688</v>
+        <v>511.4640197753906</v>
       </c>
       <c r="I262" t="n">
         <v>3800.23779296875</v>
@@ -8844,7 +8844,7 @@
         <v>2734.10009765625</v>
       </c>
       <c r="D263" t="n">
-        <v>3457.259765625</v>
+        <v>3457.259521484375</v>
       </c>
       <c r="E263" t="n">
         <v>1954.300048828125</v>
@@ -8856,10 +8856,10 @@
         <v>55.5099983215332</v>
       </c>
       <c r="H263" t="n">
-        <v>510.2847595214844</v>
+        <v>510.2847290039062</v>
       </c>
       <c r="I263" t="n">
-        <v>3830.296630859375</v>
+        <v>3830.29638671875</v>
       </c>
       <c r="J263" t="n">
         <v>288.2999877929688</v>
@@ -8876,7 +8876,7 @@
         <v>2737.949951171875</v>
       </c>
       <c r="D264" t="n">
-        <v>3449.872802734375</v>
+        <v>3449.873046875</v>
       </c>
       <c r="E264" t="n">
         <v>1975.599975585938</v>
@@ -8888,10 +8888,10 @@
         <v>55.0099983215332</v>
       </c>
       <c r="H264" t="n">
-        <v>508.8106079101562</v>
+        <v>508.8106384277344</v>
       </c>
       <c r="I264" t="n">
-        <v>3913.531982421875</v>
+        <v>3913.5322265625</v>
       </c>
       <c r="J264" t="n">
         <v>280.75</v>
@@ -8914,7 +8914,7 @@
         <v>1931.849975585938</v>
       </c>
       <c r="F265" t="n">
-        <v>753.791259765625</v>
+        <v>753.7911987304688</v>
       </c>
       <c r="G265" t="n">
         <v>54.63999938964844</v>
@@ -8923,7 +8923,7 @@
         <v>492.4481201171875</v>
       </c>
       <c r="I265" t="n">
-        <v>3895.7568359375</v>
+        <v>3895.756591796875</v>
       </c>
       <c r="J265" t="n">
         <v>284.0499877929688</v>
@@ -8940,7 +8940,7 @@
         <v>2762.14990234375</v>
       </c>
       <c r="D266" t="n">
-        <v>3435.748779296875</v>
+        <v>3435.7490234375</v>
       </c>
       <c r="E266" t="n">
         <v>1916.800048828125</v>
@@ -8984,10 +8984,10 @@
         <v>52.20000076293945</v>
       </c>
       <c r="H267" t="n">
-        <v>452.2543029785156</v>
+        <v>452.2542724609375</v>
       </c>
       <c r="I267" t="n">
-        <v>3654.986572265625</v>
+        <v>3654.98681640625</v>
       </c>
       <c r="J267" t="n">
         <v>269.7999877929688</v>
@@ -9048,7 +9048,7 @@
         <v>47.11000061035156</v>
       </c>
       <c r="H269" t="n">
-        <v>380.8095397949219</v>
+        <v>380.8095092773438</v>
       </c>
       <c r="I269" t="n">
         <v>2339.191650390625</v>
@@ -9083,7 +9083,7 @@
         <v>394.27294921875</v>
       </c>
       <c r="I270" t="n">
-        <v>2105.312255859375</v>
+        <v>2105.31201171875</v>
       </c>
       <c r="J270" t="n">
         <v>248.1000061035156</v>
@@ -9115,7 +9115,7 @@
         <v>328.3315124511719</v>
       </c>
       <c r="I271" t="n">
-        <v>1894.801147460938</v>
+        <v>1894.801025390625</v>
       </c>
       <c r="J271" t="n">
         <v>235.6999969482422</v>
@@ -9138,7 +9138,7 @@
         <v>1039.849975585938</v>
       </c>
       <c r="F272" t="n">
-        <v>453.2745056152344</v>
+        <v>453.2745361328125</v>
       </c>
       <c r="G272" t="n">
         <v>40.40999984741211</v>
@@ -9170,7 +9170,7 @@
         <v>935.9000244140625</v>
       </c>
       <c r="F273" t="n">
-        <v>488.9523010253906</v>
+        <v>488.9523315429688</v>
       </c>
       <c r="G273" t="n">
         <v>38.38999938964844</v>
@@ -9211,7 +9211,7 @@
         <v>373.1933288574219</v>
       </c>
       <c r="I274" t="n">
-        <v>1539.138916015625</v>
+        <v>1539.139038085938</v>
       </c>
       <c r="J274" t="n">
         <v>216.0500030517578</v>
@@ -9266,7 +9266,7 @@
         <v>802.4500122070312</v>
       </c>
       <c r="F276" t="n">
-        <v>587.3603515625</v>
+        <v>587.3602905273438</v>
       </c>
       <c r="G276" t="n">
         <v>36.38000106811523</v>
@@ -9275,7 +9275,7 @@
         <v>378.0086975097656</v>
       </c>
       <c r="I276" t="n">
-        <v>1389.094604492188</v>
+        <v>1389.0947265625</v>
       </c>
       <c r="J276" t="n">
         <v>227.6999969482422</v>
@@ -9292,7 +9292,7 @@
         <v>1249.099975585938</v>
       </c>
       <c r="D277" t="n">
-        <v>1922.202514648438</v>
+        <v>1922.20263671875</v>
       </c>
       <c r="E277" t="n">
         <v>762.3499755859375</v>
@@ -9330,7 +9330,7 @@
         <v>724.25</v>
       </c>
       <c r="F278" t="n">
-        <v>572.3638916015625</v>
+        <v>572.3638305664062</v>
       </c>
       <c r="G278" t="n">
         <v>32.84000015258789</v>
@@ -9339,7 +9339,7 @@
         <v>354.5704956054688</v>
       </c>
       <c r="I278" t="n">
-        <v>1253.680419921875</v>
+        <v>1253.680297851562</v>
       </c>
       <c r="J278" t="n">
         <v>208.5</v>
@@ -9368,7 +9368,7 @@
         <v>31.20000076293945</v>
       </c>
       <c r="H279" t="n">
-        <v>336.537353515625</v>
+        <v>336.5373229980469</v>
       </c>
       <c r="I279" t="n">
         <v>1191.016357421875</v>
@@ -9388,7 +9388,7 @@
         <v>1071</v>
       </c>
       <c r="D280" t="n">
-        <v>1746.522094726562</v>
+        <v>1746.522216796875</v>
       </c>
       <c r="E280" t="n">
         <v>653.6500244140625</v>
@@ -9420,7 +9420,7 @@
         <v>1017.450012207031</v>
       </c>
       <c r="D281" t="n">
-        <v>1775.868774414062</v>
+        <v>1775.868896484375</v>
       </c>
       <c r="E281" t="n">
         <v>621</v>
@@ -9452,7 +9452,7 @@
         <v>968.5499877929688</v>
       </c>
       <c r="D282" t="n">
-        <v>1793.3369140625</v>
+        <v>1793.337036132812</v>
       </c>
       <c r="E282" t="n">
         <v>616.2999877929688</v>
@@ -9484,7 +9484,7 @@
         <v>920.4000244140625</v>
       </c>
       <c r="D283" t="n">
-        <v>1719.5712890625</v>
+        <v>1719.571166992188</v>
       </c>
       <c r="E283" t="n">
         <v>628.6500244140625</v>
@@ -9499,7 +9499,7 @@
         <v>347.1999816894531</v>
       </c>
       <c r="I283" t="n">
-        <v>970.1692504882812</v>
+        <v>970.1693115234375</v>
       </c>
       <c r="J283" t="n">
         <v>217.1999969482422</v>
@@ -9516,7 +9516,7 @@
         <v>874.4000244140625</v>
       </c>
       <c r="D284" t="n">
-        <v>1618.505249023438</v>
+        <v>1618.505126953125</v>
       </c>
       <c r="E284" t="n">
         <v>597.25</v>
@@ -9528,7 +9528,7 @@
         <v>32.58000183105469</v>
       </c>
       <c r="H284" t="n">
-        <v>346.3647155761719</v>
+        <v>346.3646850585938</v>
       </c>
       <c r="I284" t="n">
         <v>921.685791015625</v>
@@ -9563,7 +9563,7 @@
         <v>346.7577819824219</v>
       </c>
       <c r="I285" t="n">
-        <v>875.5989990234375</v>
+        <v>875.5989379882812</v>
       </c>
       <c r="J285" t="n">
         <v>211.1999969482422</v>
@@ -9586,7 +9586,7 @@
         <v>539.0499877929688</v>
       </c>
       <c r="F286" t="n">
-        <v>536.2449340820312</v>
+        <v>536.2449951171875</v>
       </c>
       <c r="G286" t="n">
         <v>32.4900016784668</v>
@@ -9618,7 +9618,7 @@
         <v>512.0999755859375</v>
       </c>
       <c r="F287" t="n">
-        <v>540.9006958007812</v>
+        <v>540.900634765625</v>
       </c>
       <c r="G287" t="n">
         <v>30.8700008392334</v>
@@ -9656,10 +9656,10 @@
         <v>29.32999992370605</v>
       </c>
       <c r="H288" t="n">
-        <v>339.2889404296875</v>
+        <v>339.2890014648438</v>
       </c>
       <c r="I288" t="n">
-        <v>750.7703247070312</v>
+        <v>750.7702026367188</v>
       </c>
       <c r="J288" t="n">
         <v>190.6000061035156</v>
@@ -9676,13 +9676,13 @@
         <v>676.7000122070312</v>
       </c>
       <c r="D289" t="n">
-        <v>1191.332275390625</v>
+        <v>1191.332397460938</v>
       </c>
       <c r="E289" t="n">
         <v>462.2000122070312</v>
       </c>
       <c r="F289" t="n">
-        <v>550.8493041992188</v>
+        <v>550.849365234375</v>
       </c>
       <c r="G289" t="n">
         <v>27.8700008392334</v>
@@ -9691,7 +9691,7 @@
         <v>324.2040100097656</v>
       </c>
       <c r="I289" t="n">
-        <v>713.2716674804688</v>
+        <v>713.271728515625</v>
       </c>
       <c r="J289" t="n">
         <v>181.1000061035156</v>
@@ -9708,22 +9708,22 @@
         <v>642.9000244140625</v>
       </c>
       <c r="D290" t="n">
-        <v>1361.372924804688</v>
+        <v>1361.373046875</v>
       </c>
       <c r="E290" t="n">
         <v>485.2999877929688</v>
       </c>
       <c r="F290" t="n">
-        <v>580.6951904296875</v>
+        <v>580.6951293945312</v>
       </c>
       <c r="G290" t="n">
         <v>29.26000022888184</v>
       </c>
       <c r="H290" t="n">
-        <v>336.193359375</v>
+        <v>336.1933898925781</v>
       </c>
       <c r="I290" t="n">
-        <v>677.6204833984375</v>
+        <v>677.6205444335938</v>
       </c>
       <c r="J290" t="n">
         <v>190.1499938964844</v>
@@ -9740,7 +9740,7 @@
         <v>675</v>
       </c>
       <c r="D291" t="n">
-        <v>1561.458984375</v>
+        <v>1561.459106445312</v>
       </c>
       <c r="E291" t="n">
         <v>509.5499877929688</v>
@@ -9755,7 +9755,7 @@
         <v>347.4948120117188</v>
       </c>
       <c r="I291" t="n">
-        <v>710.6752319335938</v>
+        <v>710.67529296875</v>
       </c>
       <c r="J291" t="n">
         <v>199.6499938964844</v>
@@ -9787,7 +9787,7 @@
         <v>364.2995910644531</v>
       </c>
       <c r="I292" t="n">
-        <v>743.080810546875</v>
+        <v>743.0807495117188</v>
       </c>
       <c r="J292" t="n">
         <v>209.5500030517578</v>
@@ -9804,7 +9804,7 @@
         <v>744.1500244140625</v>
       </c>
       <c r="D293" t="n">
-        <v>1876.086547851562</v>
+        <v>1876.08642578125</v>
       </c>
       <c r="E293" t="n">
         <v>561.75</v>
@@ -9819,7 +9819,7 @@
         <v>385.0844116210938</v>
       </c>
       <c r="I293" t="n">
-        <v>780.2297973632812</v>
+        <v>780.2298583984375</v>
       </c>
       <c r="J293" t="n">
         <v>220</v>
@@ -9836,19 +9836,19 @@
         <v>781.3499755859375</v>
       </c>
       <c r="D294" t="n">
-        <v>1979.298706054688</v>
+        <v>1979.298828125</v>
       </c>
       <c r="E294" t="n">
         <v>589.7999877929688</v>
       </c>
       <c r="F294" t="n">
-        <v>677.0448608398438</v>
+        <v>677.0447998046875</v>
       </c>
       <c r="G294" t="n">
         <v>35.54999923706055</v>
       </c>
       <c r="H294" t="n">
-        <v>378.8440551757812</v>
+        <v>378.8440246582031</v>
       </c>
       <c r="I294" t="n">
         <v>819.2263793945312</v>
@@ -9868,7 +9868,7 @@
         <v>820.4000244140625</v>
       </c>
       <c r="D295" t="n">
-        <v>2035.94580078125</v>
+        <v>2035.945678710938</v>
       </c>
       <c r="E295" t="n">
         <v>619.25</v>
@@ -9880,10 +9880,10 @@
         <v>37.31999969482422</v>
       </c>
       <c r="H295" t="n">
-        <v>385.3300476074219</v>
+        <v>385.330078125</v>
       </c>
       <c r="I295" t="n">
-        <v>860.170166015625</v>
+        <v>860.1701049804688</v>
       </c>
       <c r="J295" t="n">
         <v>242.1999969482422</v>
@@ -9900,7 +9900,7 @@
         <v>861.4000244140625</v>
       </c>
       <c r="D296" t="n">
-        <v>1949.602661132812</v>
+        <v>1949.602783203125</v>
       </c>
       <c r="E296" t="n">
         <v>650.2000122070312</v>
@@ -9912,7 +9912,7 @@
         <v>39.18000030517578</v>
       </c>
       <c r="H296" t="n">
-        <v>378.0578308105469</v>
+        <v>378.057861328125</v>
       </c>
       <c r="I296" t="n">
         <v>903.1611938476562</v>
@@ -9938,7 +9938,7 @@
         <v>682.7000122070312</v>
       </c>
       <c r="F297" t="n">
-        <v>683.9548950195312</v>
+        <v>683.954833984375</v>
       </c>
       <c r="G297" t="n">
         <v>40.97999954223633</v>
@@ -9947,7 +9947,7 @@
         <v>371.8174743652344</v>
       </c>
       <c r="I297" t="n">
-        <v>948.29931640625</v>
+        <v>948.2992553710938</v>
       </c>
       <c r="J297" t="n">
         <v>233.8999938964844</v>
@@ -9964,7 +9964,7 @@
         <v>949.6500244140625</v>
       </c>
       <c r="D298" t="n">
-        <v>1870.995849609375</v>
+        <v>1870.995971679688</v>
       </c>
       <c r="E298" t="n">
         <v>716.7999877929688</v>
@@ -9996,7 +9996,7 @@
         <v>902.2000122070312</v>
       </c>
       <c r="D299" t="n">
-        <v>1735.043090820312</v>
+        <v>1735.043212890625</v>
       </c>
       <c r="E299" t="n">
         <v>706.0999755859375</v>
@@ -10011,7 +10011,7 @@
         <v>347.2982482910156</v>
       </c>
       <c r="I299" t="n">
-        <v>945.902587890625</v>
+        <v>945.9026489257812</v>
       </c>
       <c r="J299" t="n">
         <v>211.1000061035156</v>
@@ -10060,22 +10060,22 @@
         <v>973.7000122070312</v>
       </c>
       <c r="D301" t="n">
-        <v>1840.451416015625</v>
+        <v>1840.451538085938</v>
       </c>
       <c r="E301" t="n">
         <v>777.4000244140625</v>
       </c>
       <c r="F301" t="n">
-        <v>666.1160278320312</v>
+        <v>666.115966796875</v>
       </c>
       <c r="G301" t="n">
         <v>39.7400016784668</v>
       </c>
       <c r="H301" t="n">
-        <v>372.2596740722656</v>
+        <v>372.2597045898438</v>
       </c>
       <c r="I301" t="n">
-        <v>887.1832275390625</v>
+        <v>887.1831665039062</v>
       </c>
       <c r="J301" t="n">
         <v>209.1000061035156</v>
@@ -10104,7 +10104,7 @@
         <v>39.9900016784668</v>
       </c>
       <c r="H302" t="n">
-        <v>371.9157409667969</v>
+        <v>371.915771484375</v>
       </c>
       <c r="I302" t="n">
         <v>896.5203247070312</v>
@@ -10130,7 +10130,7 @@
         <v>848.6500244140625</v>
       </c>
       <c r="F303" t="n">
-        <v>653.52099609375</v>
+        <v>653.5210571289062</v>
       </c>
       <c r="G303" t="n">
         <v>38.04000091552734</v>
@@ -10156,7 +10156,7 @@
         <v>1006.099975585938</v>
       </c>
       <c r="D304" t="n">
-        <v>1820.936889648438</v>
+        <v>1820.936767578125</v>
       </c>
       <c r="E304" t="n">
         <v>891.0499877929688</v>
@@ -10168,7 +10168,7 @@
         <v>39.93999862670898</v>
       </c>
       <c r="H304" t="n">
-        <v>364.4961547851562</v>
+        <v>364.49609375</v>
       </c>
       <c r="I304" t="n">
         <v>889.579833984375</v>
@@ -10220,22 +10220,22 @@
         <v>1084.400024414062</v>
       </c>
       <c r="D306" t="n">
-        <v>1790.741943359375</v>
+        <v>1790.741821289062</v>
       </c>
       <c r="E306" t="n">
         <v>982.3499755859375</v>
       </c>
       <c r="F306" t="n">
-        <v>641.955078125</v>
+        <v>641.9551391601562</v>
       </c>
       <c r="G306" t="n">
         <v>40.27999877929688</v>
       </c>
       <c r="H306" t="n">
-        <v>365.7244873046875</v>
+        <v>365.7245483398438</v>
       </c>
       <c r="I306" t="n">
-        <v>980.704833984375</v>
+        <v>980.7048950195312</v>
       </c>
       <c r="J306" t="n">
         <v>202.1000061035156</v>
@@ -10252,7 +10252,7 @@
         <v>1124.550048828125</v>
       </c>
       <c r="D307" t="n">
-        <v>1737.488647460938</v>
+        <v>1737.48876953125</v>
       </c>
       <c r="E307" t="n">
         <v>1029.349975585938</v>
@@ -10284,7 +10284,7 @@
         <v>1068.400024414062</v>
       </c>
       <c r="D308" t="n">
-        <v>1719.920776367188</v>
+        <v>1719.920654296875</v>
       </c>
       <c r="E308" t="n">
         <v>984.9000244140625</v>
@@ -10299,7 +10299,7 @@
         <v>363.6116333007812</v>
       </c>
       <c r="I308" t="n">
-        <v>956.5379638671875</v>
+        <v>956.5380249023438</v>
       </c>
       <c r="J308" t="n">
         <v>182.9499969482422</v>
@@ -10316,7 +10316,7 @@
         <v>1015</v>
       </c>
       <c r="D309" t="n">
-        <v>1597.942504882812</v>
+        <v>1597.942626953125</v>
       </c>
       <c r="E309" t="n">
         <v>935.6500244140625</v>
@@ -10328,10 +10328,10 @@
         <v>34.77000045776367</v>
       </c>
       <c r="H309" t="n">
-        <v>352.75244140625</v>
+        <v>352.7524719238281</v>
       </c>
       <c r="I309" t="n">
-        <v>908.70361328125</v>
+        <v>908.7036743164062</v>
       </c>
       <c r="J309" t="n">
         <v>173.9499969482422</v>
@@ -10348,7 +10348,7 @@
         <v>1003.450012207031</v>
       </c>
       <c r="D310" t="n">
-        <v>1737.239135742188</v>
+        <v>1737.2392578125</v>
       </c>
       <c r="E310" t="n">
         <v>894.3499755859375</v>
@@ -10363,7 +10363,7 @@
         <v>357.616943359375</v>
       </c>
       <c r="I310" t="n">
-        <v>870.5060424804688</v>
+        <v>870.5059814453125</v>
       </c>
       <c r="J310" t="n">
         <v>182.6000061035156</v>
@@ -10386,7 +10386,7 @@
         <v>881.1500244140625</v>
       </c>
       <c r="F311" t="n">
-        <v>619.3624267578125</v>
+        <v>619.3624877929688</v>
       </c>
       <c r="G311" t="n">
         <v>38.31999969482422</v>
@@ -10412,19 +10412,19 @@
         <v>943.4000244140625</v>
       </c>
       <c r="D312" t="n">
-        <v>1714.330688476562</v>
+        <v>1714.330810546875</v>
       </c>
       <c r="E312" t="n">
         <v>837.4500122070312</v>
       </c>
       <c r="F312" t="n">
-        <v>615.3438720703125</v>
+        <v>615.3438110351562</v>
       </c>
       <c r="G312" t="n">
         <v>38.11000061035156</v>
       </c>
       <c r="H312" t="n">
-        <v>368.3287963867188</v>
+        <v>368.3287658691406</v>
       </c>
       <c r="I312" t="n">
         <v>844.192138671875</v>
@@ -10476,7 +10476,7 @@
         <v>953.2000122070312</v>
       </c>
       <c r="D314" t="n">
-        <v>1750.864379882812</v>
+        <v>1750.864501953125</v>
       </c>
       <c r="E314" t="n">
         <v>856.3499755859375</v>
@@ -10508,7 +10508,7 @@
         <v>1000.849975585938</v>
       </c>
       <c r="D315" t="n">
-        <v>1793.98583984375</v>
+        <v>1793.985961914062</v>
       </c>
       <c r="E315" t="n">
         <v>899.1500244140625</v>
@@ -10523,7 +10523,7 @@
         <v>377.7138977050781</v>
       </c>
       <c r="I315" t="n">
-        <v>904.9088745117188</v>
+        <v>904.9088134765625</v>
       </c>
       <c r="J315" t="n">
         <v>195.25</v>
@@ -10540,13 +10540,13 @@
         <v>1050.849975585938</v>
       </c>
       <c r="D316" t="n">
-        <v>1799.875122070312</v>
+        <v>1799.875244140625</v>
       </c>
       <c r="E316" t="n">
         <v>944.0999755859375</v>
       </c>
       <c r="F316" t="n">
-        <v>640.9749755859375</v>
+        <v>640.9750366210938</v>
       </c>
       <c r="G316" t="n">
         <v>38.79999923706055</v>
@@ -10578,7 +10578,7 @@
         <v>941.8499755859375</v>
       </c>
       <c r="F317" t="n">
-        <v>644.6995849609375</v>
+        <v>644.6996459960938</v>
       </c>
       <c r="G317" t="n">
         <v>38.4900016784668</v>
@@ -10587,7 +10587,7 @@
         <v>389.2118835449219</v>
       </c>
       <c r="I317" t="n">
-        <v>937.5640258789062</v>
+        <v>937.5640869140625</v>
       </c>
       <c r="J317" t="n">
         <v>187</v>
@@ -10610,7 +10610,7 @@
         <v>941.1500244140625</v>
       </c>
       <c r="F318" t="n">
-        <v>648.522216796875</v>
+        <v>648.5222778320312</v>
       </c>
       <c r="G318" t="n">
         <v>37.83000183105469</v>
@@ -10619,7 +10619,7 @@
         <v>385.8705749511719</v>
       </c>
       <c r="I318" t="n">
-        <v>912.8978881835938</v>
+        <v>912.89794921875</v>
       </c>
       <c r="J318" t="n">
         <v>191.6000061035156</v>
@@ -10642,16 +10642,16 @@
         <v>962.5499877929688</v>
       </c>
       <c r="F319" t="n">
-        <v>651.5116577148438</v>
+        <v>651.5115966796875</v>
       </c>
       <c r="G319" t="n">
         <v>37.88999938964844</v>
       </c>
       <c r="H319" t="n">
-        <v>384.7895812988281</v>
+        <v>384.78955078125</v>
       </c>
       <c r="I319" t="n">
-        <v>945.5031127929688</v>
+        <v>945.5030517578125</v>
       </c>
       <c r="J319" t="n">
         <v>188.1999969482422</v>
@@ -10668,19 +10668,19 @@
         <v>1032.050048828125</v>
       </c>
       <c r="D320" t="n">
-        <v>1847.588256835938</v>
+        <v>1847.58837890625</v>
       </c>
       <c r="E320" t="n">
         <v>952.25</v>
       </c>
       <c r="F320" t="n">
-        <v>645.4837646484375</v>
+        <v>645.4837036132812</v>
       </c>
       <c r="G320" t="n">
         <v>37.66999816894531</v>
       </c>
       <c r="H320" t="n">
-        <v>376.4363403320312</v>
+        <v>376.4363098144531</v>
       </c>
       <c r="I320" t="n">
         <v>946.75146484375</v>
@@ -10712,7 +10712,7 @@
         <v>37.45999908447266</v>
       </c>
       <c r="H321" t="n">
-        <v>373.4881286621094</v>
+        <v>373.4880981445312</v>
       </c>
       <c r="I321" t="n">
         <v>929.0756225585938</v>
@@ -10738,13 +10738,13 @@
         <v>933.0499877929688</v>
       </c>
       <c r="F322" t="n">
-        <v>652.8839721679688</v>
+        <v>652.8839111328125</v>
       </c>
       <c r="G322" t="n">
         <v>39.15999984741211</v>
       </c>
       <c r="H322" t="n">
-        <v>374.1269226074219</v>
+        <v>374.1268920898438</v>
       </c>
       <c r="I322" t="n">
         <v>926.9285888671875</v>
@@ -10776,10 +10776,10 @@
         <v>39.84999847412109</v>
       </c>
       <c r="H323" t="n">
-        <v>368.6235961914062</v>
+        <v>368.6236267089844</v>
       </c>
       <c r="I323" t="n">
-        <v>916.5427856445312</v>
+        <v>916.5428466796875</v>
       </c>
       <c r="J323" t="n">
         <v>183.6999969482422</v>
@@ -10796,13 +10796,13 @@
         <v>965.0999755859375</v>
       </c>
       <c r="D324" t="n">
-        <v>1798.67724609375</v>
+        <v>1798.677368164062</v>
       </c>
       <c r="E324" t="n">
         <v>887.0999755859375</v>
       </c>
       <c r="F324" t="n">
-        <v>657.9807739257812</v>
+        <v>657.980712890625</v>
       </c>
       <c r="G324" t="n">
         <v>40.27999877929688</v>
@@ -10811,7 +10811,7 @@
         <v>373.7337951660156</v>
       </c>
       <c r="I324" t="n">
-        <v>889.929443359375</v>
+        <v>889.9293823242188</v>
       </c>
       <c r="J324" t="n">
         <v>179.25</v>
@@ -10843,7 +10843,7 @@
         <v>375.8958129882812</v>
       </c>
       <c r="I325" t="n">
-        <v>933.968994140625</v>
+        <v>933.9689331054688</v>
       </c>
       <c r="J325" t="n">
         <v>182.8000030517578</v>
@@ -10860,13 +10860,13 @@
         <v>987.7999877929688</v>
       </c>
       <c r="D326" t="n">
-        <v>1844.5439453125</v>
+        <v>1844.544067382812</v>
       </c>
       <c r="E326" t="n">
         <v>924.5999755859375</v>
       </c>
       <c r="F326" t="n">
-        <v>651.5116577148438</v>
+        <v>651.5115966796875</v>
       </c>
       <c r="G326" t="n">
         <v>42.27000045776367</v>
@@ -10875,7 +10875,7 @@
         <v>379.7776184082031</v>
       </c>
       <c r="I326" t="n">
-        <v>918.789794921875</v>
+        <v>918.7897338867188</v>
       </c>
       <c r="J326" t="n">
         <v>181.8500061035156</v>
@@ -10892,22 +10892,22 @@
         <v>982.2999877929688</v>
       </c>
       <c r="D327" t="n">
-        <v>1849.684692382812</v>
+        <v>1849.6845703125</v>
       </c>
       <c r="E327" t="n">
         <v>917.0499877929688</v>
       </c>
       <c r="F327" t="n">
-        <v>646.6598510742188</v>
+        <v>646.659912109375</v>
       </c>
       <c r="G327" t="n">
         <v>42.83000183105469</v>
       </c>
       <c r="H327" t="n">
-        <v>382.0870361328125</v>
+        <v>382.0870056152344</v>
       </c>
       <c r="I327" t="n">
-        <v>915.84375</v>
+        <v>915.8438110351562</v>
       </c>
       <c r="J327" t="n">
         <v>181.5</v>
@@ -10930,7 +10930,7 @@
         <v>951</v>
       </c>
       <c r="F328" t="n">
-        <v>667.7823486328125</v>
+        <v>667.7822875976562</v>
       </c>
       <c r="G328" t="n">
         <v>44.97000122070312</v>
@@ -10939,7 +10939,7 @@
         <v>389.6541137695312</v>
       </c>
       <c r="I328" t="n">
-        <v>943.7056274414062</v>
+        <v>943.70556640625</v>
       </c>
       <c r="J328" t="n">
         <v>189.5500030517578</v>
@@ -10956,13 +10956,13 @@
         <v>1021.950012207031</v>
       </c>
       <c r="D329" t="n">
-        <v>1916.363159179688</v>
+        <v>1916.363037109375</v>
       </c>
       <c r="E329" t="n">
         <v>974.6500244140625</v>
       </c>
       <c r="F329" t="n">
-        <v>667.9783325195312</v>
+        <v>667.978271484375</v>
       </c>
       <c r="G329" t="n">
         <v>47.18999862670898</v>
@@ -10971,7 +10971,7 @@
         <v>387.5903625488281</v>
       </c>
       <c r="I329" t="n">
-        <v>957.7363891601562</v>
+        <v>957.736328125</v>
       </c>
       <c r="J329" t="n">
         <v>185.6999969482422</v>
@@ -11000,7 +11000,7 @@
         <v>46.33000183105469</v>
       </c>
       <c r="H330" t="n">
-        <v>377.0259704589844</v>
+        <v>377.0260009765625</v>
       </c>
       <c r="I330" t="n">
         <v>921.685791015625</v>
@@ -11020,7 +11020,7 @@
         <v>1011.549987792969</v>
       </c>
       <c r="D331" t="n">
-        <v>1907.778930664062</v>
+        <v>1907.77880859375</v>
       </c>
       <c r="E331" t="n">
         <v>945.5499877929688</v>
@@ -11032,10 +11032,10 @@
         <v>47.63000106811523</v>
       </c>
       <c r="H331" t="n">
-        <v>381.5956726074219</v>
+        <v>381.595703125</v>
       </c>
       <c r="I331" t="n">
-        <v>928.9259033203125</v>
+        <v>928.9258422851562</v>
       </c>
       <c r="J331" t="n">
         <v>183.3500061035156</v>
@@ -11052,7 +11052,7 @@
         <v>999</v>
       </c>
       <c r="D332" t="n">
-        <v>1916.812622070312</v>
+        <v>1916.8125</v>
       </c>
       <c r="E332" t="n">
         <v>940.5499877929688</v>
@@ -11084,22 +11084,22 @@
         <v>949.0499877929688</v>
       </c>
       <c r="D333" t="n">
-        <v>1884.072021484375</v>
+        <v>1884.072143554688</v>
       </c>
       <c r="E333" t="n">
         <v>917.2999877929688</v>
       </c>
       <c r="F333" t="n">
-        <v>671.5069580078125</v>
+        <v>671.5068969726562</v>
       </c>
       <c r="G333" t="n">
         <v>47.7400016784668</v>
       </c>
       <c r="H333" t="n">
-        <v>398.4987182617188</v>
+        <v>398.4986877441406</v>
       </c>
       <c r="I333" t="n">
-        <v>871.7044067382812</v>
+        <v>871.704345703125</v>
       </c>
       <c r="J333" t="n">
         <v>180.9499969482422</v>
@@ -11116,7 +11116,7 @@
         <v>901.5999755859375</v>
       </c>
       <c r="D334" t="n">
-        <v>1892.656372070312</v>
+        <v>1892.65625</v>
       </c>
       <c r="E334" t="n">
         <v>903.1500244140625</v>
@@ -11148,7 +11148,7 @@
         <v>890.6500244140625</v>
       </c>
       <c r="D335" t="n">
-        <v>1888.713745117188</v>
+        <v>1888.713623046875</v>
       </c>
       <c r="E335" t="n">
         <v>902.3499755859375</v>
@@ -11180,13 +11180,13 @@
         <v>917.25</v>
       </c>
       <c r="D336" t="n">
-        <v>1981.045654296875</v>
+        <v>1981.045532226562</v>
       </c>
       <c r="E336" t="n">
         <v>913.5499877929688</v>
       </c>
       <c r="F336" t="n">
-        <v>694.7366943359375</v>
+        <v>694.7366333007812</v>
       </c>
       <c r="G336" t="n">
         <v>48.52999877929688</v>
@@ -11212,22 +11212,22 @@
         <v>884.7999877929688</v>
       </c>
       <c r="D337" t="n">
-        <v>1961.1318359375</v>
+        <v>1961.131713867188</v>
       </c>
       <c r="E337" t="n">
         <v>895.5999755859375</v>
       </c>
       <c r="F337" t="n">
-        <v>686.111328125</v>
+        <v>686.1112670898438</v>
       </c>
       <c r="G337" t="n">
         <v>48.16999816894531</v>
       </c>
       <c r="H337" t="n">
-        <v>402.9210510253906</v>
+        <v>402.9210205078125</v>
       </c>
       <c r="I337" t="n">
-        <v>817.2290649414062</v>
+        <v>817.22900390625</v>
       </c>
       <c r="J337" t="n">
         <v>180.75</v>
@@ -11244,7 +11244,7 @@
         <v>840.5999755859375</v>
       </c>
       <c r="D338" t="n">
-        <v>1912.570190429688</v>
+        <v>1912.570068359375</v>
       </c>
       <c r="E338" t="n">
         <v>868.7000122070312</v>
@@ -11259,7 +11259,7 @@
         <v>399.5797424316406</v>
       </c>
       <c r="I338" t="n">
-        <v>776.3851928710938</v>
+        <v>776.3851318359375</v>
       </c>
       <c r="J338" t="n">
         <v>178.6000061035156</v>
@@ -11276,7 +11276,7 @@
         <v>812.0999755859375</v>
       </c>
       <c r="D339" t="n">
-        <v>1885.718994140625</v>
+        <v>1885.719116210938</v>
       </c>
       <c r="E339" t="n">
         <v>874.1500244140625</v>
@@ -11288,7 +11288,7 @@
         <v>47.2400016784668</v>
       </c>
       <c r="H339" t="n">
-        <v>393.9781494140625</v>
+        <v>393.9781188964844</v>
       </c>
       <c r="I339" t="n">
         <v>737.5883178710938</v>
@@ -11320,7 +11320,7 @@
         <v>46.86999893188477</v>
       </c>
       <c r="H340" t="n">
-        <v>399.2848815917969</v>
+        <v>399.284912109375</v>
       </c>
       <c r="I340" t="n">
         <v>700.7388916015625</v>
@@ -11340,7 +11340,7 @@
         <v>751.5999755859375</v>
       </c>
       <c r="D341" t="n">
-        <v>1886.567260742188</v>
+        <v>1886.567504882812</v>
       </c>
       <c r="E341" t="n">
         <v>860.5499877929688</v>
@@ -11378,7 +11378,7 @@
         <v>896.9500122070312</v>
       </c>
       <c r="F342" t="n">
-        <v>674.4473876953125</v>
+        <v>674.4473266601562</v>
       </c>
       <c r="G342" t="n">
         <v>47.22000122070312</v>
@@ -11416,7 +11416,7 @@
         <v>49.58000183105469</v>
       </c>
       <c r="H343" t="n">
-        <v>416.5810241699219</v>
+        <v>416.5809936523438</v>
       </c>
       <c r="I343" t="n">
         <v>721.5103759765625</v>
@@ -11448,7 +11448,7 @@
         <v>52.04999923706055</v>
       </c>
       <c r="H344" t="n">
-        <v>419.9223327636719</v>
+        <v>419.9223022460938</v>
       </c>
       <c r="I344" t="n">
         <v>757.5609130859375</v>
@@ -11506,16 +11506,16 @@
         <v>970.6500244140625</v>
       </c>
       <c r="F346" t="n">
-        <v>710.1251831054688</v>
+        <v>710.125244140625</v>
       </c>
       <c r="G346" t="n">
         <v>51.83000183105469</v>
       </c>
       <c r="H346" t="n">
-        <v>411.9621887207031</v>
+        <v>411.962158203125</v>
       </c>
       <c r="I346" t="n">
-        <v>795.3092041015625</v>
+        <v>795.3091430664062</v>
       </c>
       <c r="J346" t="n">
         <v>216.3500061035156</v>
@@ -11547,7 +11547,7 @@
         <v>417.2197875976562</v>
       </c>
       <c r="I347" t="n">
-        <v>759.6580810546875</v>
+        <v>759.6580200195312</v>
       </c>
       <c r="J347" t="n">
         <v>227.1499938964844</v>
@@ -11596,7 +11596,7 @@
         <v>804.2999877929688</v>
       </c>
       <c r="D349" t="n">
-        <v>2491.915771484375</v>
+        <v>2491.916015625</v>
       </c>
       <c r="E349" t="n">
         <v>966.8499755859375</v>
@@ -11611,7 +11611,7 @@
         <v>423.4601745605469</v>
       </c>
       <c r="I349" t="n">
-        <v>697.0938720703125</v>
+        <v>697.0938110351562</v>
       </c>
       <c r="J349" t="n">
         <v>250.3999938964844</v>
@@ -11640,7 +11640,7 @@
         <v>49.93000030517578</v>
       </c>
       <c r="H350" t="n">
-        <v>416.2861938476562</v>
+        <v>416.2862243652344</v>
       </c>
       <c r="I350" t="n">
         <v>663.2403564453125</v>
@@ -11675,7 +11675,7 @@
         <v>421.8386535644531</v>
       </c>
       <c r="I351" t="n">
-        <v>693.3988647460938</v>
+        <v>693.39892578125</v>
       </c>
       <c r="J351" t="n">
         <v>241</v>
@@ -11724,19 +11724,19 @@
         <v>828</v>
       </c>
       <c r="D353" t="n">
-        <v>2429.529296875</v>
+        <v>2429.529541015625</v>
       </c>
       <c r="E353" t="n">
         <v>987.8499755859375</v>
       </c>
       <c r="F353" t="n">
-        <v>724.1414184570312</v>
+        <v>724.1414794921875</v>
       </c>
       <c r="G353" t="n">
         <v>51.88999938964844</v>
       </c>
       <c r="H353" t="n">
-        <v>431.469482421875</v>
+        <v>431.4694519042969</v>
       </c>
       <c r="I353" t="n">
         <v>680.5665283203125</v>
@@ -11762,16 +11762,16 @@
         <v>991.8499755859375</v>
       </c>
       <c r="F354" t="n">
-        <v>730.6105346679688</v>
+        <v>730.610595703125</v>
       </c>
       <c r="G354" t="n">
         <v>52.59999847412109</v>
       </c>
       <c r="H354" t="n">
-        <v>451.2223815917969</v>
+        <v>451.2223510742188</v>
       </c>
       <c r="I354" t="n">
-        <v>677.4707641601562</v>
+        <v>677.4708251953125</v>
       </c>
       <c r="J354" t="n">
         <v>236.3000030517578</v>
@@ -11788,7 +11788,7 @@
         <v>837.25</v>
       </c>
       <c r="D355" t="n">
-        <v>2435.119140625</v>
+        <v>2435.119384765625</v>
       </c>
       <c r="E355" t="n">
         <v>985.5499877929688</v>
@@ -11858,16 +11858,16 @@
         <v>963.6500244140625</v>
       </c>
       <c r="F357" t="n">
-        <v>720.367919921875</v>
+        <v>720.3678588867188</v>
       </c>
       <c r="G357" t="n">
         <v>55.2400016784668</v>
       </c>
       <c r="H357" t="n">
-        <v>447.8320007324219</v>
+        <v>447.83203125</v>
       </c>
       <c r="I357" t="n">
-        <v>668.1834716796875</v>
+        <v>668.1835327148438</v>
       </c>
       <c r="J357" t="n">
         <v>230</v>
@@ -11890,7 +11890,7 @@
         <v>961.0999755859375</v>
       </c>
       <c r="F358" t="n">
-        <v>727.3759155273438</v>
+        <v>727.3759765625</v>
       </c>
       <c r="G358" t="n">
         <v>54.31000137329102</v>
@@ -11899,7 +11899,7 @@
         <v>448.4216003417969</v>
       </c>
       <c r="I358" t="n">
-        <v>669.2820434570312</v>
+        <v>669.2821044921875</v>
       </c>
       <c r="J358" t="n">
         <v>228.5500030517578</v>
@@ -11916,7 +11916,7 @@
         <v>823</v>
       </c>
       <c r="D359" t="n">
-        <v>2458.077880859375</v>
+        <v>2458.07763671875</v>
       </c>
       <c r="E359" t="n">
         <v>955.2999877929688</v>
@@ -11931,7 +11931,7 @@
         <v>451.0258483886719</v>
       </c>
       <c r="I359" t="n">
-        <v>662.2416381835938</v>
+        <v>662.24169921875</v>
       </c>
       <c r="J359" t="n">
         <v>239.9499969482422</v>
@@ -11960,10 +11960,10 @@
         <v>53.04999923706055</v>
       </c>
       <c r="H360" t="n">
-        <v>456.5783081054688</v>
+        <v>456.5783386230469</v>
       </c>
       <c r="I360" t="n">
-        <v>653.4537353515625</v>
+        <v>653.4536743164062</v>
       </c>
       <c r="J360" t="n">
         <v>245.25</v>
@@ -11986,16 +11986,16 @@
         <v>962.5999755859375</v>
       </c>
       <c r="F361" t="n">
-        <v>724.8275756835938</v>
+        <v>724.82763671875</v>
       </c>
       <c r="G361" t="n">
         <v>53.84999847412109</v>
       </c>
       <c r="H361" t="n">
-        <v>450.4362182617188</v>
+        <v>450.4362487792969</v>
       </c>
       <c r="I361" t="n">
-        <v>668.1834716796875</v>
+        <v>668.1835327148438</v>
       </c>
       <c r="J361" t="n">
         <v>242.5500030517578</v>
@@ -12012,7 +12012,7 @@
         <v>810.9000244140625</v>
       </c>
       <c r="D362" t="n">
-        <v>2505.0419921875</v>
+        <v>2505.042236328125</v>
       </c>
       <c r="E362" t="n">
         <v>975.0499877929688</v>
@@ -12024,7 +12024,7 @@
         <v>53.22000122070312</v>
       </c>
       <c r="H362" t="n">
-        <v>452.9421691894531</v>
+        <v>452.9421997070312</v>
       </c>
       <c r="I362" t="n">
         <v>670.33056640625</v>
@@ -12044,7 +12044,7 @@
         <v>806.5999755859375</v>
       </c>
       <c r="D363" t="n">
-        <v>2397.03857421875</v>
+        <v>2397.038818359375</v>
       </c>
       <c r="E363" t="n">
         <v>960.3499755859375</v>
@@ -12056,10 +12056,10 @@
         <v>52.72999954223633</v>
       </c>
       <c r="H363" t="n">
-        <v>445.0311584472656</v>
+        <v>445.0311889648438</v>
       </c>
       <c r="I363" t="n">
-        <v>656.6492919921875</v>
+        <v>656.6493530273438</v>
       </c>
       <c r="J363" t="n">
         <v>232.3999938964844</v>
@@ -12076,19 +12076,19 @@
         <v>811.9500122070312</v>
       </c>
       <c r="D364" t="n">
-        <v>2410.41455078125</v>
+        <v>2410.414306640625</v>
       </c>
       <c r="E364" t="n">
         <v>961.7000122070312</v>
       </c>
       <c r="F364" t="n">
-        <v>723.1612548828125</v>
+        <v>723.1613159179688</v>
       </c>
       <c r="G364" t="n">
         <v>52.34000015258789</v>
       </c>
       <c r="H364" t="n">
-        <v>441.1985168457031</v>
+        <v>441.1985473632812</v>
       </c>
       <c r="I364" t="n">
         <v>657.6978759765625</v>
@@ -12114,7 +12114,7 @@
         <v>977</v>
       </c>
       <c r="F365" t="n">
-        <v>734.5801391601562</v>
+        <v>734.5802001953125</v>
       </c>
       <c r="G365" t="n">
         <v>52.13000106811523</v>
@@ -12152,7 +12152,7 @@
         <v>51.31999969482422</v>
       </c>
       <c r="H366" t="n">
-        <v>437.1692810058594</v>
+        <v>437.1693115234375</v>
       </c>
       <c r="I366" t="n">
         <v>654.252685546875</v>
@@ -12204,22 +12204,22 @@
         <v>770.75</v>
       </c>
       <c r="D368" t="n">
-        <v>2291.43115234375</v>
+        <v>2291.4306640625</v>
       </c>
       <c r="E368" t="n">
         <v>968.4500122070312</v>
       </c>
       <c r="F368" t="n">
-        <v>710.0271606445312</v>
+        <v>710.0272216796875</v>
       </c>
       <c r="G368" t="n">
         <v>50.11999893188477</v>
       </c>
       <c r="H368" t="n">
-        <v>424.5903015136719</v>
+        <v>424.5902709960938</v>
       </c>
       <c r="I368" t="n">
-        <v>643.117919921875</v>
+        <v>643.1178588867188</v>
       </c>
       <c r="J368" t="n">
         <v>224.8999938964844</v>
@@ -12236,7 +12236,7 @@
         <v>773.2000122070312</v>
       </c>
       <c r="D369" t="n">
-        <v>2280.301025390625</v>
+        <v>2280.30126953125</v>
       </c>
       <c r="E369" t="n">
         <v>959.5499877929688</v>
@@ -12274,16 +12274,16 @@
         <v>956.6500244140625</v>
       </c>
       <c r="F370" t="n">
-        <v>741.490234375</v>
+        <v>741.4902954101562</v>
       </c>
       <c r="G370" t="n">
         <v>50.93000030517578</v>
       </c>
       <c r="H370" t="n">
-        <v>426.7523498535156</v>
+        <v>426.7523193359375</v>
       </c>
       <c r="I370" t="n">
-        <v>653.603515625</v>
+        <v>653.6034545898438</v>
       </c>
       <c r="J370" t="n">
         <v>230.8500061035156</v>
@@ -12300,7 +12300,7 @@
         <v>767.25</v>
       </c>
       <c r="D371" t="n">
-        <v>2383.713134765625</v>
+        <v>2383.712890625</v>
       </c>
       <c r="E371" t="n">
         <v>945.9000244140625</v>
@@ -12315,7 +12315,7 @@
         <v>418.5464782714844</v>
       </c>
       <c r="I371" t="n">
-        <v>653.7033081054688</v>
+        <v>653.703369140625</v>
       </c>
       <c r="J371" t="n">
         <v>227.3999938964844</v>
@@ -12364,13 +12364,13 @@
         <v>770.5999755859375</v>
       </c>
       <c r="D373" t="n">
-        <v>2383.36328125</v>
+        <v>2383.363525390625</v>
       </c>
       <c r="E373" t="n">
         <v>946</v>
       </c>
       <c r="F373" t="n">
-        <v>726.98388671875</v>
+        <v>726.9839477539062</v>
       </c>
       <c r="G373" t="n">
         <v>49.41999816894531</v>
@@ -12402,7 +12402,7 @@
         <v>948.2000122070312</v>
       </c>
       <c r="F374" t="n">
-        <v>728.0130615234375</v>
+        <v>728.0131225585938</v>
       </c>
       <c r="G374" t="n">
         <v>49.13000106811523</v>
@@ -12443,7 +12443,7 @@
         <v>424.0498046875</v>
       </c>
       <c r="I375" t="n">
-        <v>647.8613891601562</v>
+        <v>647.861328125</v>
       </c>
       <c r="J375" t="n">
         <v>227</v>
@@ -12460,13 +12460,13 @@
         <v>759.8499755859375</v>
       </c>
       <c r="D376" t="n">
-        <v>2376.428955078125</v>
+        <v>2376.42919921875</v>
       </c>
       <c r="E376" t="n">
         <v>951</v>
       </c>
       <c r="F376" t="n">
-        <v>704.4403076171875</v>
+        <v>704.4403686523438</v>
       </c>
       <c r="G376" t="n">
         <v>48.75</v>
@@ -12475,7 +12475,7 @@
         <v>413.077880859375</v>
       </c>
       <c r="I376" t="n">
-        <v>642.6165771484375</v>
+        <v>642.6165161132812</v>
       </c>
       <c r="J376" t="n">
         <v>224.6499938964844</v>
@@ -12492,13 +12492,13 @@
         <v>749.8499755859375</v>
       </c>
       <c r="D377" t="n">
-        <v>2407.037841796875</v>
+        <v>2407.0380859375</v>
       </c>
       <c r="E377" t="n">
         <v>959.4500122070312</v>
       </c>
       <c r="F377" t="n">
-        <v>705.8124389648438</v>
+        <v>705.8125</v>
       </c>
       <c r="G377" t="n">
         <v>48.40999984741211</v>
@@ -12524,7 +12524,7 @@
         <v>754.0499877929688</v>
       </c>
       <c r="D378" t="n">
-        <v>2419.671142578125</v>
+        <v>2419.6708984375</v>
       </c>
       <c r="E378" t="n">
         <v>965.1500244140625</v>
@@ -12539,7 +12539,7 @@
         <v>414.9065246582031</v>
       </c>
       <c r="I378" t="n">
-        <v>640.2688598632812</v>
+        <v>640.2689208984375</v>
       </c>
       <c r="J378" t="n">
         <v>223.6999969482422</v>
@@ -12556,7 +12556,7 @@
         <v>752.6500244140625</v>
       </c>
       <c r="D379" t="n">
-        <v>2384.7177734375</v>
+        <v>2384.717529296875</v>
       </c>
       <c r="E379" t="n">
         <v>954.5499877929688</v>
@@ -12571,7 +12571,7 @@
         <v>416.6857604980469</v>
       </c>
       <c r="I379" t="n">
-        <v>635.0740356445312</v>
+        <v>635.073974609375</v>
       </c>
       <c r="J379" t="n">
         <v>225.0500030517578</v>
@@ -12588,7 +12588,7 @@
         <v>745.2000122070312</v>
       </c>
       <c r="D380" t="n">
-        <v>2358.902099609375</v>
+        <v>2358.90234375</v>
       </c>
       <c r="E380" t="n">
         <v>947.0499877929688</v>
@@ -12603,7 +12603,7 @@
         <v>412.0894165039062</v>
       </c>
       <c r="I380" t="n">
-        <v>629.6293334960938</v>
+        <v>629.6292724609375</v>
       </c>
       <c r="J380" t="n">
         <v>220.3500061035156</v>
@@ -12667,7 +12667,7 @@
         <v>411.7929077148438</v>
       </c>
       <c r="I382" t="n">
-        <v>646.3628540039062</v>
+        <v>646.3629150390625</v>
       </c>
       <c r="J382" t="n">
         <v>228.5</v>
@@ -12684,7 +12684,7 @@
         <v>783</v>
       </c>
       <c r="D383" t="n">
-        <v>2413.67919921875</v>
+        <v>2413.678955078125</v>
       </c>
       <c r="E383" t="n">
         <v>973.75</v>
@@ -12699,7 +12699,7 @@
         <v>411.3975219726562</v>
       </c>
       <c r="I383" t="n">
-        <v>645.114013671875</v>
+        <v>645.1140747070312</v>
       </c>
       <c r="J383" t="n">
         <v>229.8500061035156</v>
@@ -12722,7 +12722,7 @@
         <v>979.6500244140625</v>
       </c>
       <c r="F384" t="n">
-        <v>716.8882446289062</v>
+        <v>716.8883056640625</v>
       </c>
       <c r="G384" t="n">
         <v>49.13999938964844</v>
@@ -12754,7 +12754,7 @@
         <v>985</v>
       </c>
       <c r="F385" t="n">
-        <v>717.9174194335938</v>
+        <v>717.91748046875</v>
       </c>
       <c r="G385" t="n">
         <v>48.83000183105469</v>
@@ -12786,7 +12786,7 @@
         <v>995.5499877929688</v>
       </c>
       <c r="F386" t="n">
-        <v>713.9968872070312</v>
+        <v>713.996826171875</v>
       </c>
       <c r="G386" t="n">
         <v>48.34999847412109</v>
@@ -12795,7 +12795,7 @@
         <v>411.2986755371094</v>
       </c>
       <c r="I386" t="n">
-        <v>635.5735473632812</v>
+        <v>635.573486328125</v>
       </c>
       <c r="J386" t="n">
         <v>230.3999938964844</v>
@@ -12818,7 +12818,7 @@
         <v>989.1500244140625</v>
       </c>
       <c r="F387" t="n">
-        <v>720.7108154296875</v>
+        <v>720.7108764648438</v>
       </c>
       <c r="G387" t="n">
         <v>47.59999847412109</v>
@@ -12844,7 +12844,7 @@
         <v>834.8499755859375</v>
       </c>
       <c r="D388" t="n">
-        <v>2463.36279296875</v>
+        <v>2463.362548828125</v>
       </c>
       <c r="E388" t="n">
         <v>1088.050048828125</v>
@@ -12859,7 +12859,7 @@
         <v>435.021728515625</v>
       </c>
       <c r="I388" t="n">
-        <v>661.9974975585938</v>
+        <v>661.9974365234375</v>
       </c>
       <c r="J388" t="n">
         <v>238.5500030517578</v>
@@ -12923,7 +12923,7 @@
         <v>444.5603637695312</v>
       </c>
       <c r="I390" t="n">
-        <v>653.8056030273438</v>
+        <v>653.8055419921875</v>
       </c>
       <c r="J390" t="n">
         <v>231.4499969482422</v>
@@ -13019,7 +13019,7 @@
         <v>456.2242431640625</v>
       </c>
       <c r="I393" t="n">
-        <v>660.9984741210938</v>
+        <v>660.9984130859375</v>
       </c>
       <c r="J393" t="n">
         <v>228.9499969482422</v>
@@ -13147,7 +13147,7 @@
         <v>468.6294250488281</v>
       </c>
       <c r="I397" t="n">
-        <v>650.0592041015625</v>
+        <v>650.0592651367188</v>
       </c>
       <c r="J397" t="n">
         <v>223.9499969482422</v>
@@ -13164,7 +13164,7 @@
         <v>823.5999755859375</v>
       </c>
       <c r="D398" t="n">
-        <v>2471.252197265625</v>
+        <v>2471.25244140625</v>
       </c>
       <c r="E398" t="n">
         <v>984.2999877929688</v>
@@ -13228,7 +13228,7 @@
         <v>820.7999877929688</v>
       </c>
       <c r="D400" t="n">
-        <v>2548.99853515625</v>
+        <v>2548.998291015625</v>
       </c>
       <c r="E400" t="n">
         <v>973.9000244140625</v>
@@ -13339,7 +13339,7 @@
         <v>432.1552124023438</v>
       </c>
       <c r="I403" t="n">
-        <v>634.9241333007812</v>
+        <v>634.924072265625</v>
       </c>
       <c r="J403" t="n">
         <v>218.0500030517578</v>
@@ -13403,7 +13403,7 @@
         <v>447.822265625</v>
       </c>
       <c r="I405" t="n">
-        <v>653.8554077148438</v>
+        <v>653.85546875</v>
       </c>
       <c r="J405" t="n">
         <v>224.3999938964844</v>
@@ -13435,7 +13435,7 @@
         <v>459.8815002441406</v>
       </c>
       <c r="I406" t="n">
-        <v>663.8455810546875</v>
+        <v>663.8456420898438</v>
       </c>
       <c r="J406" t="n">
         <v>227.8000030517578</v>
@@ -13467,7 +13467,7 @@
         <v>458.4482727050781</v>
       </c>
       <c r="I407" t="n">
-        <v>671.8876342773438</v>
+        <v>671.8876953125</v>
       </c>
       <c r="J407" t="n">
         <v>227.0500030517578</v>
@@ -13499,7 +13499,7 @@
         <v>448.0693969726562</v>
       </c>
       <c r="I408" t="n">
-        <v>653.5557861328125</v>
+        <v>653.5558471679688</v>
       </c>
       <c r="J408" t="n">
         <v>223.4499969482422</v>
@@ -13516,7 +13516,7 @@
         <v>895.1500244140625</v>
       </c>
       <c r="D409" t="n">
-        <v>2536.16552734375</v>
+        <v>2536.165771484375</v>
       </c>
       <c r="E409" t="n">
         <v>983.6500244140625</v>
@@ -13531,7 +13531,7 @@
         <v>443.7696228027344</v>
       </c>
       <c r="I409" t="n">
-        <v>661.2481689453125</v>
+        <v>661.2482299804688</v>
       </c>
       <c r="J409" t="n">
         <v>223.75</v>
@@ -13563,7 +13563,7 @@
         <v>429.585205078125</v>
       </c>
       <c r="I410" t="n">
-        <v>653.1062622070312</v>
+        <v>653.106201171875</v>
       </c>
       <c r="J410" t="n">
         <v>220.6499938964844</v>
@@ -13612,7 +13612,7 @@
         <v>857.1500244140625</v>
       </c>
       <c r="D412" t="n">
-        <v>2503.109619140625</v>
+        <v>2503.10986328125</v>
       </c>
       <c r="E412" t="n">
         <v>974.5</v>
@@ -13627,7 +13627,7 @@
         <v>436.1090393066406</v>
       </c>
       <c r="I412" t="n">
-        <v>656.1531372070312</v>
+        <v>656.1531982421875</v>
       </c>
       <c r="J412" t="n">
         <v>220.1499938964844</v>
@@ -13644,7 +13644,7 @@
         <v>841.7000122070312</v>
       </c>
       <c r="D413" t="n">
-        <v>2509.751220703125</v>
+        <v>2509.7509765625</v>
       </c>
       <c r="E413" t="n">
         <v>970.5</v>
@@ -13691,7 +13691,7 @@
         <v>423.4567260742188</v>
       </c>
       <c r="I414" t="n">
-        <v>635.173828125</v>
+        <v>635.1738891601562</v>
       </c>
       <c r="J414" t="n">
         <v>214.3000030517578</v>
@@ -13787,7 +13787,7 @@
         <v>435.12060546875</v>
       </c>
       <c r="I417" t="n">
-        <v>632.7763061523438</v>
+        <v>632.7762451171875</v>
       </c>
       <c r="J417" t="n">
         <v>214.4499969482422</v>
@@ -13804,7 +13804,7 @@
         <v>855.9500122070312</v>
       </c>
       <c r="D418" t="n">
-        <v>2493.1728515625</v>
+        <v>2493.173095703125</v>
       </c>
       <c r="E418" t="n">
         <v>1006.099975585938</v>
@@ -13819,7 +13819,7 @@
         <v>432.6988220214844</v>
       </c>
       <c r="I418" t="n">
-        <v>644.0651245117188</v>
+        <v>644.065185546875</v>
       </c>
       <c r="J418" t="n">
         <v>214.4499969482422</v>
@@ -13915,7 +13915,7 @@
         <v>445.6970825195312</v>
       </c>
       <c r="I421" t="n">
-        <v>658.2510986328125</v>
+        <v>658.2511596679688</v>
       </c>
       <c r="J421" t="n">
         <v>224.4499969482422</v>
@@ -13947,7 +13947,7 @@
         <v>439.8652038574219</v>
       </c>
       <c r="I422" t="n">
-        <v>642.1170654296875</v>
+        <v>642.1170043945312</v>
       </c>
       <c r="J422" t="n">
         <v>217.1499938964844</v>
@@ -13964,7 +13964,7 @@
         <v>836.9000244140625</v>
       </c>
       <c r="D423" t="n">
-        <v>2515.54296875</v>
+        <v>2515.543212890625</v>
       </c>
       <c r="E423" t="n">
         <v>985.7999877929688</v>
@@ -14124,7 +14124,7 @@
         <v>847.3499755859375</v>
       </c>
       <c r="D428" t="n">
-        <v>2475.946044921875</v>
+        <v>2475.94580078125</v>
       </c>
       <c r="E428" t="n">
         <v>1023.450012207031</v>
@@ -14188,7 +14188,7 @@
         <v>830.4000244140625</v>
       </c>
       <c r="D430" t="n">
-        <v>2478.792236328125</v>
+        <v>2478.79248046875</v>
       </c>
       <c r="E430" t="n">
         <v>1013.799987792969</v>
@@ -14220,7 +14220,7 @@
         <v>817.8499755859375</v>
       </c>
       <c r="D431" t="n">
-        <v>2454.674560546875</v>
+        <v>2454.67431640625</v>
       </c>
       <c r="E431" t="n">
         <v>1012.299987792969</v>
@@ -14252,7 +14252,7 @@
         <v>816.2000122070312</v>
       </c>
       <c r="D432" t="n">
-        <v>2479.990478515625</v>
+        <v>2479.99072265625</v>
       </c>
       <c r="E432" t="n">
         <v>1018.75</v>
@@ -14267,7 +14267,7 @@
         <v>425.4830932617188</v>
       </c>
       <c r="I432" t="n">
-        <v>627.031982421875</v>
+        <v>627.0319213867188</v>
       </c>
       <c r="J432" t="n">
         <v>211</v>
@@ -14284,7 +14284,7 @@
         <v>830.5</v>
       </c>
       <c r="D433" t="n">
-        <v>2471.951416015625</v>
+        <v>2471.95166015625</v>
       </c>
       <c r="E433" t="n">
         <v>1012.450012207031</v>
@@ -14299,7 +14299,7 @@
         <v>415.0547790527344</v>
       </c>
       <c r="I433" t="n">
-        <v>621.5372924804688</v>
+        <v>621.537353515625</v>
       </c>
       <c r="J433" t="n">
         <v>207.9499969482422</v>
@@ -14316,7 +14316,7 @@
         <v>810.25</v>
       </c>
       <c r="D434" t="n">
-        <v>2410.682861328125</v>
+        <v>2410.68310546875</v>
       </c>
       <c r="E434" t="n">
         <v>987.1500244140625</v>
@@ -14331,7 +14331,7 @@
         <v>419.8982849121094</v>
       </c>
       <c r="I434" t="n">
-        <v>612.6460571289062</v>
+        <v>612.6461181640625</v>
       </c>
       <c r="J434" t="n">
         <v>208.4499969482422</v>
@@ -14363,7 +14363,7 @@
         <v>427.212890625</v>
       </c>
       <c r="I435" t="n">
-        <v>610.1486206054688</v>
+        <v>610.1485595703125</v>
       </c>
       <c r="J435" t="n">
         <v>209.8500061035156</v>
@@ -14444,7 +14444,7 @@
         <v>806</v>
       </c>
       <c r="D438" t="n">
-        <v>2474.7978515625</v>
+        <v>2474.797607421875</v>
       </c>
       <c r="E438" t="n">
         <v>961.25</v>
@@ -14476,7 +14476,7 @@
         <v>778.9000244140625</v>
       </c>
       <c r="D439" t="n">
-        <v>2439.34521484375</v>
+        <v>2439.344970703125</v>
       </c>
       <c r="E439" t="n">
         <v>938.9500122070312</v>
@@ -14523,7 +14523,7 @@
         <v>432.1552124023438</v>
       </c>
       <c r="I440" t="n">
-        <v>607.201416015625</v>
+        <v>607.2014770507812</v>
       </c>
       <c r="J440" t="n">
         <v>209.6000061035156</v>
@@ -14604,7 +14604,7 @@
         <v>785.2000122070312</v>
       </c>
       <c r="D443" t="n">
-        <v>2451.279052734375</v>
+        <v>2451.279296875</v>
       </c>
       <c r="E443" t="n">
         <v>948.9000244140625</v>
@@ -14683,7 +14683,7 @@
         <v>437.5422973632812</v>
       </c>
       <c r="I445" t="n">
-        <v>594.9635009765625</v>
+        <v>594.9635620117188</v>
       </c>
       <c r="J445" t="n">
         <v>211.8999938964844</v>
@@ -14732,7 +14732,7 @@
         <v>759.4000244140625</v>
       </c>
       <c r="D447" t="n">
-        <v>2398.998779296875</v>
+        <v>2398.99853515625</v>
       </c>
       <c r="E447" t="n">
         <v>933</v>
@@ -14811,7 +14811,7 @@
         <v>411.150390625</v>
       </c>
       <c r="I449" t="n">
-        <v>572.5855712890625</v>
+        <v>572.5856323242188</v>
       </c>
       <c r="J449" t="n">
         <v>199.5500030517578</v>
@@ -14843,7 +14843,7 @@
         <v>413.1273193359375</v>
       </c>
       <c r="I450" t="n">
-        <v>549.9080200195312</v>
+        <v>549.907958984375</v>
       </c>
       <c r="J450" t="n">
         <v>195.75</v>
@@ -14860,7 +14860,7 @@
         <v>739.0999755859375</v>
       </c>
       <c r="D451" t="n">
-        <v>2200.263916015625</v>
+        <v>2200.263671875</v>
       </c>
       <c r="E451" t="n">
         <v>848.1500244140625</v>
@@ -14892,7 +14892,7 @@
         <v>764.5</v>
       </c>
       <c r="D452" t="n">
-        <v>2258.68603515625</v>
+        <v>2258.685791015625</v>
       </c>
       <c r="E452" t="n">
         <v>870.9000244140625</v>
@@ -14924,7 +14924,7 @@
         <v>759.25</v>
       </c>
       <c r="D453" t="n">
-        <v>2296.0361328125</v>
+        <v>2296.036376953125</v>
       </c>
       <c r="E453" t="n">
         <v>915.25</v>
@@ -14956,7 +14956,7 @@
         <v>769.7999877929688</v>
       </c>
       <c r="D454" t="n">
-        <v>2291.591796875</v>
+        <v>2291.592041015625</v>
       </c>
       <c r="E454" t="n">
         <v>911.6500244140625</v>
@@ -15099,7 +15099,7 @@
         <v>416.3892517089844</v>
       </c>
       <c r="I458" t="n">
-        <v>550.4075317382812</v>
+        <v>550.407470703125</v>
       </c>
       <c r="J458" t="n">
         <v>194.1499938964844</v>
@@ -15180,7 +15180,7 @@
         <v>750.2000122070312</v>
       </c>
       <c r="D461" t="n">
-        <v>2211.698486328125</v>
+        <v>2211.69873046875</v>
       </c>
       <c r="E461" t="n">
         <v>938.0999755859375</v>
@@ -15195,7 +15195,7 @@
         <v>413.4732971191406</v>
       </c>
       <c r="I461" t="n">
-        <v>534.4732055664062</v>
+        <v>534.47314453125</v>
       </c>
       <c r="J461" t="n">
         <v>192.5</v>
@@ -15244,7 +15244,7 @@
         <v>759</v>
       </c>
       <c r="D463" t="n">
-        <v>2210.699951171875</v>
+        <v>2210.69970703125</v>
       </c>
       <c r="E463" t="n">
         <v>940.1500244140625</v>
@@ -15276,7 +15276,7 @@
         <v>754.3499755859375</v>
       </c>
       <c r="D464" t="n">
-        <v>2222.43408203125</v>
+        <v>2222.434326171875</v>
       </c>
       <c r="E464" t="n">
         <v>950.1500244140625</v>
@@ -15308,7 +15308,7 @@
         <v>747.2000122070312</v>
       </c>
       <c r="D465" t="n">
-        <v>2202.960205078125</v>
+        <v>2202.96044921875</v>
       </c>
       <c r="E465" t="n">
         <v>941.3499755859375</v>
@@ -15340,7 +15340,7 @@
         <v>741.2000122070312</v>
       </c>
       <c r="D466" t="n">
-        <v>2205.856689453125</v>
+        <v>2205.8564453125</v>
       </c>
       <c r="E466" t="n">
         <v>936.0999755859375</v>
@@ -15372,7 +15372,7 @@
         <v>727.5</v>
       </c>
       <c r="D467" t="n">
-        <v>2146.985107421875</v>
+        <v>2146.98486328125</v>
       </c>
       <c r="E467" t="n">
         <v>926.2000122070312</v>
@@ -15387,7 +15387,7 @@
         <v>416.6363525390625</v>
       </c>
       <c r="I467" t="n">
-        <v>530.527099609375</v>
+        <v>530.5270385742188</v>
       </c>
       <c r="J467" t="n">
         <v>191.5</v>
@@ -15436,7 +15436,7 @@
         <v>726.9500122070312</v>
       </c>
       <c r="D469" t="n">
-        <v>2169.754638671875</v>
+        <v>2169.75439453125</v>
       </c>
       <c r="E469" t="n">
         <v>914.4500122070312</v>
@@ -15468,7 +15468,7 @@
         <v>723.0499877929688</v>
       </c>
       <c r="D470" t="n">
-        <v>2172.35107421875</v>
+        <v>2172.351318359375</v>
       </c>
       <c r="E470" t="n">
         <v>930.7000122070312</v>
@@ -15532,7 +15532,7 @@
         <v>865.0999755859375</v>
       </c>
       <c r="D472" t="n">
-        <v>2420.2705078125</v>
+        <v>2420.270263671875</v>
       </c>
       <c r="E472" t="n">
         <v>1052.800048828125</v>
@@ -15547,7 +15547,7 @@
         <v>426.2244567871094</v>
       </c>
       <c r="I472" t="n">
-        <v>643.5656127929688</v>
+        <v>643.565673828125</v>
       </c>
       <c r="J472" t="n">
         <v>229.8999938964844</v>
@@ -15596,7 +15596,7 @@
         <v>872.6500244140625</v>
       </c>
       <c r="D474" t="n">
-        <v>2355.406982421875</v>
+        <v>2355.40673828125</v>
       </c>
       <c r="E474" t="n">
         <v>1028.800048828125</v>
@@ -15611,7 +15611,7 @@
         <v>434.1815490722656</v>
       </c>
       <c r="I474" t="n">
-        <v>708.1019897460938</v>
+        <v>708.1019287109375</v>
       </c>
       <c r="J474" t="n">
         <v>218.8999938964844</v>
@@ -15628,7 +15628,7 @@
         <v>854.7000122070312</v>
       </c>
       <c r="D475" t="n">
-        <v>2359.55126953125</v>
+        <v>2359.551513671875</v>
       </c>
       <c r="E475" t="n">
         <v>1026.5</v>
@@ -15675,7 +15675,7 @@
         <v>469.0741882324219</v>
       </c>
       <c r="I476" t="n">
-        <v>731.5289306640625</v>
+        <v>731.5288696289062</v>
       </c>
       <c r="J476" t="n">
         <v>225.0500030517578</v>
@@ -15707,7 +15707,7 @@
         <v>503.1761169433594</v>
       </c>
       <c r="I477" t="n">
-        <v>876.9855346679688</v>
+        <v>876.9854736328125</v>
       </c>
       <c r="J477" t="n">
         <v>266.6499938964844</v>
@@ -15835,7 +15835,7 @@
         <v>498.1843872070312</v>
       </c>
       <c r="I481" t="n">
-        <v>1170.995849609375</v>
+        <v>1170.995727539062</v>
       </c>
       <c r="J481" t="n">
         <v>281.25</v>
@@ -15931,7 +15931,7 @@
         <v>514.2468872070312</v>
       </c>
       <c r="I484" t="n">
-        <v>1050.514526367188</v>
+        <v>1050.5146484375</v>
       </c>
       <c r="J484" t="n">
         <v>269.4500122070312</v>
@@ -15963,7 +15963,7 @@
         <v>516.3721313476562</v>
       </c>
       <c r="I485" t="n">
-        <v>1045.9189453125</v>
+        <v>1045.919067382812</v>
       </c>
       <c r="J485" t="n">
         <v>266.2000122070312</v>
@@ -16059,7 +16059,7 @@
         <v>484.790771484375</v>
       </c>
       <c r="I488" t="n">
-        <v>959.75390625</v>
+        <v>959.7539672851562</v>
       </c>
       <c r="J488" t="n">
         <v>264.0499877929688</v>
@@ -16091,7 +16091,7 @@
         <v>498.0855407714844</v>
       </c>
       <c r="I489" t="n">
-        <v>984.030029296875</v>
+        <v>984.0299682617188</v>
       </c>
       <c r="J489" t="n">
         <v>264.8500061035156</v>
@@ -16123,7 +16123,7 @@
         <v>497.9866943359375</v>
       </c>
       <c r="I490" t="n">
-        <v>995.31884765625</v>
+        <v>995.3189086914062</v>
       </c>
       <c r="J490" t="n">
         <v>267.1499938964844</v>
@@ -16251,7 +16251,7 @@
         <v>514.889404296875</v>
       </c>
       <c r="I494" t="n">
-        <v>986.9771118164062</v>
+        <v>986.9771728515625</v>
       </c>
       <c r="J494" t="n">
         <v>262.3999938964844</v>
@@ -16283,7 +16283,7 @@
         <v>528.1347045898438</v>
       </c>
       <c r="I495" t="n">
-        <v>999.9642944335938</v>
+        <v>999.9642333984375</v>
       </c>
       <c r="J495" t="n">
         <v>275.7999877929688</v>
@@ -16315,7 +16315,7 @@
         <v>524.7740478515625</v>
       </c>
       <c r="I496" t="n">
-        <v>999.9143676757812</v>
+        <v>999.9144287109375</v>
       </c>
       <c r="J496" t="n">
         <v>272.2000122070312</v>
@@ -16364,7 +16364,7 @@
         <v>1179.800048828125</v>
       </c>
       <c r="D498" t="n">
-        <v>2994.30419921875</v>
+        <v>2994.304443359375</v>
       </c>
       <c r="E498" t="n">
         <v>1692.5</v>
@@ -16443,7 +16443,7 @@
         <v>524.0820922851562</v>
       </c>
       <c r="I500" t="n">
-        <v>1067.197998046875</v>
+        <v>1067.198120117188</v>
       </c>
       <c r="J500" t="n">
         <v>278.7000122070312</v>
@@ -16475,7 +16475,7 @@
         <v>519.1397705078125</v>
       </c>
       <c r="I501" t="n">
-        <v>1066.298950195312</v>
+        <v>1066.298828125</v>
       </c>
       <c r="J501" t="n">
         <v>279.7999877929688</v>
@@ -16492,7 +16492,7 @@
         <v>1170.300048828125</v>
       </c>
       <c r="D502" t="n">
-        <v>3094.0712890625</v>
+        <v>3094.071044921875</v>
       </c>
       <c r="E502" t="n">
         <v>1723.25</v>
@@ -16539,7 +16539,7 @@
         <v>532.0391235351562</v>
       </c>
       <c r="I503" t="n">
-        <v>1061.203857421875</v>
+        <v>1061.203979492188</v>
       </c>
       <c r="J503" t="n">
         <v>288.2000122070312</v>
@@ -16588,7 +16588,7 @@
         <v>1152.199951171875</v>
       </c>
       <c r="D505" t="n">
-        <v>3085.382568359375</v>
+        <v>3085.3828125</v>
       </c>
       <c r="E505" t="n">
         <v>1694.800048828125</v>
@@ -16699,7 +16699,7 @@
         <v>518.1019287109375</v>
       </c>
       <c r="I508" t="n">
-        <v>982.1318359375</v>
+        <v>982.1318969726562</v>
       </c>
       <c r="J508" t="n">
         <v>268.8999938964844</v>
@@ -16795,7 +16795,7 @@
         <v>521.3638305664062</v>
       </c>
       <c r="I511" t="n">
-        <v>1001.213134765625</v>
+        <v>1001.213073730469</v>
       </c>
       <c r="J511" t="n">
         <v>264.25</v>
@@ -16827,7 +16827,7 @@
         <v>553.6865234375</v>
       </c>
       <c r="I512" t="n">
-        <v>1001.962280273438</v>
+        <v>1001.962341308594</v>
       </c>
       <c r="J512" t="n">
         <v>277.7999877929688</v>
@@ -16908,7 +16908,7 @@
         <v>1067.849975585938</v>
       </c>
       <c r="D515" t="n">
-        <v>3137.812744140625</v>
+        <v>3137.81298828125</v>
       </c>
       <c r="E515" t="n">
         <v>1669.449951171875</v>
@@ -16923,7 +16923,7 @@
         <v>553.8347778320312</v>
       </c>
       <c r="I515" t="n">
-        <v>1011.353088378906</v>
+        <v>1011.35302734375</v>
       </c>
       <c r="J515" t="n">
         <v>270.7000122070312</v>
@@ -16940,7 +16940,7 @@
         <v>1067.699951171875</v>
       </c>
       <c r="D516" t="n">
-        <v>3149.29736328125</v>
+        <v>3149.297607421875</v>
       </c>
       <c r="E516" t="n">
         <v>1665.949951171875</v>
@@ -16972,7 +16972,7 @@
         <v>1052.050048828125</v>
       </c>
       <c r="D517" t="n">
-        <v>3153.2421875</v>
+        <v>3153.241943359375</v>
       </c>
       <c r="E517" t="n">
         <v>1674.25</v>
@@ -17019,7 +17019,7 @@
         <v>548.5958862304688</v>
       </c>
       <c r="I518" t="n">
-        <v>988.0759887695312</v>
+        <v>988.0760498046875</v>
       </c>
       <c r="J518" t="n">
         <v>260.8500061035156</v>
@@ -17132,7 +17132,7 @@
         <v>1054.699951171875</v>
       </c>
       <c r="D522" t="n">
-        <v>3210.9150390625</v>
+        <v>3210.915283203125</v>
       </c>
       <c r="E522" t="n">
         <v>1880.699951171875</v>
@@ -17147,7 +17147,7 @@
         <v>569.5513305664062</v>
       </c>
       <c r="I522" t="n">
-        <v>1022.741821289062</v>
+        <v>1022.741882324219</v>
       </c>
       <c r="J522" t="n">
         <v>266.75</v>
@@ -17179,7 +17179,7 @@
         <v>556.997802734375</v>
       </c>
       <c r="I523" t="n">
-        <v>1024.240356445312</v>
+        <v>1024.240478515625</v>
       </c>
       <c r="J523" t="n">
         <v>245.5500030517578</v>
@@ -17260,7 +17260,7 @@
         <v>1052</v>
       </c>
       <c r="D526" t="n">
-        <v>3189.5439453125</v>
+        <v>3189.543701171875</v>
       </c>
       <c r="E526" t="n">
         <v>1900.75</v>
@@ -17275,7 +17275,7 @@
         <v>565.6469116210938</v>
       </c>
       <c r="I526" t="n">
-        <v>1006.457946777344</v>
+        <v>1006.457885742188</v>
       </c>
       <c r="J526" t="n">
         <v>262.0499877929688</v>
@@ -17307,7 +17307,7 @@
         <v>578.3485717773438</v>
       </c>
       <c r="I527" t="n">
-        <v>1005.209167480469</v>
+        <v>1005.209106445312</v>
       </c>
       <c r="J527" t="n">
         <v>264.2999877929688</v>
@@ -17324,7 +17324,7 @@
         <v>1074.449951171875</v>
       </c>
       <c r="D528" t="n">
-        <v>3254.45751953125</v>
+        <v>3254.457275390625</v>
       </c>
       <c r="E528" t="n">
         <v>1955.050048828125</v>
@@ -17339,7 +17339,7 @@
         <v>578.1015014648438</v>
       </c>
       <c r="I528" t="n">
-        <v>1010.703674316406</v>
+        <v>1010.703735351562</v>
       </c>
       <c r="J528" t="n">
         <v>267.4500122070312</v>
@@ -17388,7 +17388,7 @@
         <v>1064.800048828125</v>
       </c>
       <c r="D530" t="n">
-        <v>3218.90478515625</v>
+        <v>3218.904541015625</v>
       </c>
       <c r="E530" t="n">
         <v>1904.949951171875</v>
@@ -17420,7 +17420,7 @@
         <v>1058.900024414062</v>
       </c>
       <c r="D531" t="n">
-        <v>3258.70166015625</v>
+        <v>3258.701416015625</v>
       </c>
       <c r="E531" t="n">
         <v>1922.650024414062</v>
@@ -17467,7 +17467,7 @@
         <v>595.9926147460938</v>
       </c>
       <c r="I532" t="n">
-        <v>1028.38623046875</v>
+        <v>1028.386352539062</v>
       </c>
       <c r="J532" t="n">
         <v>269.8999938964844</v>
@@ -17484,7 +17484,7 @@
         <v>1176.150024414062</v>
       </c>
       <c r="D533" t="n">
-        <v>3323.315185546875</v>
+        <v>3323.3154296875</v>
       </c>
       <c r="E533" t="n">
         <v>1970.449951171875</v>
@@ -17548,7 +17548,7 @@
         <v>1076.449951171875</v>
       </c>
       <c r="D535" t="n">
-        <v>3214.7099609375</v>
+        <v>3214.710205078125</v>
       </c>
       <c r="E535" t="n">
         <v>1918.150024414062</v>
@@ -17563,7 +17563,7 @@
         <v>582.4507446289062</v>
       </c>
       <c r="I535" t="n">
-        <v>1017.896606445312</v>
+        <v>1017.896667480469</v>
       </c>
       <c r="J535" t="n">
         <v>256.75</v>
@@ -17595,7 +17595,7 @@
         <v>598.9086303710938</v>
       </c>
       <c r="I536" t="n">
-        <v>1024.64013671875</v>
+        <v>1024.640014648438</v>
       </c>
       <c r="J536" t="n">
         <v>255.3500061035156</v>
@@ -17612,7 +17612,7 @@
         <v>1072.400024414062</v>
       </c>
       <c r="D537" t="n">
-        <v>3314.327392578125</v>
+        <v>3314.3271484375</v>
       </c>
       <c r="E537" t="n">
         <v>1969.550048828125</v>
@@ -17627,7 +17627,7 @@
         <v>610.4735717773438</v>
       </c>
       <c r="I537" t="n">
-        <v>1038.126586914062</v>
+        <v>1038.126708984375</v>
       </c>
       <c r="J537" t="n">
         <v>257.1499938964844</v>
@@ -17676,7 +17676,7 @@
         <v>1070.300048828125</v>
       </c>
       <c r="D539" t="n">
-        <v>3305.788330078125</v>
+        <v>3305.78857421875</v>
       </c>
       <c r="E539" t="n">
         <v>1947.400024414062</v>
@@ -17691,7 +17691,7 @@
         <v>606.0254516601562</v>
       </c>
       <c r="I539" t="n">
-        <v>1019.145446777344</v>
+        <v>1019.145385742188</v>
       </c>
       <c r="J539" t="n">
         <v>251.4499969482422</v>
@@ -17723,7 +17723,7 @@
         <v>591.3963012695312</v>
       </c>
       <c r="I540" t="n">
-        <v>1004.859497070312</v>
+        <v>1004.859436035156</v>
       </c>
       <c r="J540" t="n">
         <v>246.75</v>
@@ -17787,7 +17787,7 @@
         <v>595.10302734375</v>
       </c>
       <c r="I542" t="n">
-        <v>999.1650390625</v>
+        <v>999.1651000976562</v>
       </c>
       <c r="J542" t="n">
         <v>242.3999938964844</v>
@@ -17804,7 +17804,7 @@
         <v>1037.25</v>
       </c>
       <c r="D543" t="n">
-        <v>3118.3388671875</v>
+        <v>3118.338623046875</v>
       </c>
       <c r="E543" t="n">
         <v>1897.099975585938</v>
@@ -17851,7 +17851,7 @@
         <v>552.796875</v>
       </c>
       <c r="I544" t="n">
-        <v>872.1403198242188</v>
+        <v>872.1402587890625</v>
       </c>
       <c r="J544" t="n">
         <v>211.75</v>
@@ -17900,7 +17900,7 @@
         <v>1045.849975585938</v>
       </c>
       <c r="D546" t="n">
-        <v>3128.025634765625</v>
+        <v>3128.02587890625</v>
       </c>
       <c r="E546" t="n">
         <v>1902.599975585938</v>
@@ -17979,7 +17979,7 @@
         <v>573.6039428710938</v>
       </c>
       <c r="I548" t="n">
-        <v>943.7197875976562</v>
+        <v>943.7197265625</v>
       </c>
       <c r="J548" t="n">
         <v>211.5</v>
@@ -18011,7 +18011,7 @@
         <v>569.6995239257812</v>
       </c>
       <c r="I549" t="n">
-        <v>935.1781616210938</v>
+        <v>935.1781005859375</v>
       </c>
       <c r="J549" t="n">
         <v>208.1000061035156</v>
@@ -18043,7 +18043,7 @@
         <v>580.42431640625</v>
       </c>
       <c r="I550" t="n">
-        <v>935.1282348632812</v>
+        <v>935.128173828125</v>
       </c>
       <c r="J550" t="n">
         <v>214.1499938964844</v>
@@ -18075,7 +18075,7 @@
         <v>582.549560546875</v>
       </c>
       <c r="I551" t="n">
-        <v>937.9254150390625</v>
+        <v>937.9253540039062</v>
       </c>
       <c r="J551" t="n">
         <v>217.3999938964844</v>
@@ -18092,7 +18092,7 @@
         <v>1045.900024414062</v>
       </c>
       <c r="D552" t="n">
-        <v>3105.8056640625</v>
+        <v>3105.805419921875</v>
       </c>
       <c r="E552" t="n">
         <v>1859</v>
@@ -18107,7 +18107,7 @@
         <v>588.1837768554688</v>
       </c>
       <c r="I552" t="n">
-        <v>948.165283203125</v>
+        <v>948.1653442382812</v>
       </c>
       <c r="J552" t="n">
         <v>212.3500061035156</v>
@@ -18156,7 +18156,7 @@
         <v>1026.699951171875</v>
       </c>
       <c r="D554" t="n">
-        <v>3192.83935546875</v>
+        <v>3192.839599609375</v>
       </c>
       <c r="E554" t="n">
         <v>1835.150024414062</v>
@@ -18171,7 +18171,7 @@
         <v>605.2841186523438</v>
       </c>
       <c r="I554" t="n">
-        <v>925.6375122070312</v>
+        <v>925.6375732421875</v>
       </c>
       <c r="J554" t="n">
         <v>210.5500030517578</v>
@@ -18267,7 +18267,7 @@
         <v>627.6234130859375</v>
       </c>
       <c r="I557" t="n">
-        <v>974.93896484375</v>
+        <v>974.9390258789062</v>
       </c>
       <c r="J557" t="n">
         <v>229.3999938964844</v>
@@ -18284,7 +18284,7 @@
         <v>1102</v>
       </c>
       <c r="D558" t="n">
-        <v>3206.52099609375</v>
+        <v>3206.521240234375</v>
       </c>
       <c r="E558" t="n">
         <v>1890.849975585938</v>
@@ -18348,7 +18348,7 @@
         <v>1075.849975585938</v>
       </c>
       <c r="D560" t="n">
-        <v>3220.252685546875</v>
+        <v>3220.2529296875</v>
       </c>
       <c r="E560" t="n">
         <v>1919.099975585938</v>
@@ -18395,7 +18395,7 @@
         <v>615.9100952148438</v>
       </c>
       <c r="I561" t="n">
-        <v>961.2025756835938</v>
+        <v>961.2025146484375</v>
       </c>
       <c r="J561" t="n">
         <v>223.6000061035156</v>
@@ -18412,7 +18412,7 @@
         <v>1064.25</v>
       </c>
       <c r="D562" t="n">
-        <v>3237.679443359375</v>
+        <v>3237.6796875</v>
       </c>
       <c r="E562" t="n">
         <v>1907.5</v>
@@ -18427,7 +18427,7 @@
         <v>618.4307250976562</v>
       </c>
       <c r="I562" t="n">
-        <v>960.3533935546875</v>
+        <v>960.3533325195312</v>
       </c>
       <c r="J562" t="n">
         <v>231.3999938964844</v>
@@ -18444,7 +18444,7 @@
         <v>1068.900024414062</v>
       </c>
       <c r="D563" t="n">
-        <v>3205.622314453125</v>
+        <v>3205.6220703125</v>
       </c>
       <c r="E563" t="n">
         <v>1884.050048828125</v>
@@ -18523,7 +18523,7 @@
         <v>610.4241333007812</v>
       </c>
       <c r="I565" t="n">
-        <v>926.83642578125</v>
+        <v>926.8363647460938</v>
       </c>
       <c r="J565" t="n">
         <v>218.9499969482422</v>
@@ -18555,7 +18555,7 @@
         <v>608.1506958007812</v>
       </c>
       <c r="I566" t="n">
-        <v>919.243896484375</v>
+        <v>919.2438354492188</v>
       </c>
       <c r="J566" t="n">
         <v>217.1499938964844</v>
@@ -18572,7 +18572,7 @@
         <v>1040.599975585938</v>
       </c>
       <c r="D567" t="n">
-        <v>3022.916259765625</v>
+        <v>3022.916015625</v>
       </c>
       <c r="E567" t="n">
         <v>1770.050048828125</v>
@@ -18587,7 +18587,7 @@
         <v>602.6153564453125</v>
       </c>
       <c r="I567" t="n">
-        <v>911.50146484375</v>
+        <v>911.5015869140625</v>
       </c>
       <c r="J567" t="n">
         <v>217.5500030517578</v>
@@ -18604,7 +18604,7 @@
         <v>1042.949951171875</v>
       </c>
       <c r="D568" t="n">
-        <v>3059.267578125</v>
+        <v>3059.267822265625</v>
       </c>
       <c r="E568" t="n">
         <v>1793.75</v>
@@ -18619,7 +18619,7 @@
         <v>609.1885986328125</v>
       </c>
       <c r="I568" t="n">
-        <v>917.6454467773438</v>
+        <v>917.6453857421875</v>
       </c>
       <c r="J568" t="n">
         <v>218.8000030517578</v>
@@ -18651,7 +18651,7 @@
         <v>629.2048950195312</v>
       </c>
       <c r="I569" t="n">
-        <v>922.240966796875</v>
+        <v>922.2409057617188</v>
       </c>
       <c r="J569" t="n">
         <v>220.75</v>
@@ -18700,7 +18700,7 @@
         <v>1050.150024414062</v>
       </c>
       <c r="D571" t="n">
-        <v>3111.098388671875</v>
+        <v>3111.0986328125</v>
       </c>
       <c r="E571" t="n">
         <v>1812.650024414062</v>
@@ -18715,7 +18715,7 @@
         <v>630.984130859375</v>
       </c>
       <c r="I571" t="n">
-        <v>917.2457885742188</v>
+        <v>917.2459106445312</v>
       </c>
       <c r="J571" t="n">
         <v>234.6499938964844</v>
@@ -18779,7 +18779,7 @@
         <v>622.384521484375</v>
       </c>
       <c r="I573" t="n">
-        <v>918.1448974609375</v>
+        <v>918.1449584960938</v>
       </c>
       <c r="J573" t="n">
         <v>229.8000030517578</v>
@@ -18875,7 +18875,7 @@
         <v>615.2676391601562</v>
       </c>
       <c r="I576" t="n">
-        <v>929.4837646484375</v>
+        <v>929.4838256835938</v>
       </c>
       <c r="J576" t="n">
         <v>223.1499938964844</v>
@@ -18907,7 +18907,7 @@
         <v>600.440673828125</v>
       </c>
       <c r="I577" t="n">
-        <v>916.2468872070312</v>
+        <v>916.246826171875</v>
       </c>
       <c r="J577" t="n">
         <v>217.9499969482422</v>
@@ -18971,7 +18971,7 @@
         <v>587.6895141601562</v>
       </c>
       <c r="I579" t="n">
-        <v>894.718017578125</v>
+        <v>894.7180786132812</v>
       </c>
       <c r="J579" t="n">
         <v>216.1499938964844</v>
@@ -19035,7 +19035,7 @@
         <v>575.086669921875</v>
       </c>
       <c r="I581" t="n">
-        <v>866.1961059570312</v>
+        <v>866.1961669921875</v>
       </c>
       <c r="J581" t="n">
         <v>214</v>
@@ -19067,7 +19067,7 @@
         <v>581.4127807617188</v>
       </c>
       <c r="I582" t="n">
-        <v>861.001220703125</v>
+        <v>861.0012817382812</v>
       </c>
       <c r="J582" t="n">
         <v>216.1999969482422</v>
@@ -19084,7 +19084,7 @@
         <v>1022.049987792969</v>
       </c>
       <c r="D583" t="n">
-        <v>3033.502197265625</v>
+        <v>3033.501953125</v>
       </c>
       <c r="E583" t="n">
         <v>1788.800048828125</v>
@@ -19099,7 +19099,7 @@
         <v>603.1589965820312</v>
       </c>
       <c r="I583" t="n">
-        <v>908.0548706054688</v>
+        <v>908.054931640625</v>
       </c>
       <c r="J583" t="n">
         <v>219.8999938964844</v>
@@ -19131,7 +19131,7 @@
         <v>606.1737670898438</v>
       </c>
       <c r="I584" t="n">
-        <v>915.6973266601562</v>
+        <v>915.6973876953125</v>
       </c>
       <c r="J584" t="n">
         <v>216.6000061035156</v>
@@ -19163,7 +19163,7 @@
         <v>608.2990112304688</v>
       </c>
       <c r="I585" t="n">
-        <v>905.906982421875</v>
+        <v>905.9070434570312</v>
       </c>
       <c r="J585" t="n">
         <v>215.1499938964844</v>
@@ -19195,7 +19195,7 @@
         <v>613.5377807617188</v>
       </c>
       <c r="I586" t="n">
-        <v>912.7503051757812</v>
+        <v>912.750244140625</v>
       </c>
       <c r="J586" t="n">
         <v>216.3000030517578</v>
@@ -19212,7 +19212,7 @@
         <v>1061.400024414062</v>
       </c>
       <c r="D587" t="n">
-        <v>3113.345458984375</v>
+        <v>3113.34521484375</v>
       </c>
       <c r="E587" t="n">
         <v>1859.349975585938</v>
@@ -19244,7 +19244,7 @@
         <v>1086.949951171875</v>
       </c>
       <c r="D588" t="n">
-        <v>3136.76416015625</v>
+        <v>3136.764404296875</v>
       </c>
       <c r="E588" t="n">
         <v>1866.449951171875</v>
@@ -19276,7 +19276,7 @@
         <v>1099.599975585938</v>
       </c>
       <c r="D589" t="n">
-        <v>3382.785888671875</v>
+        <v>3382.7861328125</v>
       </c>
       <c r="E589" t="n">
         <v>1888.800048828125</v>
@@ -19308,7 +19308,7 @@
         <v>1106.699951171875</v>
       </c>
       <c r="D590" t="n">
-        <v>3380.439208984375</v>
+        <v>3380.43896484375</v>
       </c>
       <c r="E590" t="n">
         <v>1926.650024414062</v>
@@ -19323,7 +19323,7 @@
         <v>627.9693603515625</v>
       </c>
       <c r="I590" t="n">
-        <v>978.7852172851562</v>
+        <v>978.78515625</v>
       </c>
       <c r="J590" t="n">
         <v>242.3000030517578</v>
@@ -19340,7 +19340,7 @@
         <v>1104.349975585938</v>
       </c>
       <c r="D591" t="n">
-        <v>3284.666748046875</v>
+        <v>3284.6669921875</v>
       </c>
       <c r="E591" t="n">
         <v>1929.5</v>
@@ -19404,7 +19404,7 @@
         <v>1085.699951171875</v>
       </c>
       <c r="D593" t="n">
-        <v>3254.45751953125</v>
+        <v>3254.457275390625</v>
       </c>
       <c r="E593" t="n">
         <v>1879.599975585938</v>
@@ -19468,7 +19468,7 @@
         <v>1122.800048828125</v>
       </c>
       <c r="D595" t="n">
-        <v>3406.8037109375</v>
+        <v>3406.803955078125</v>
       </c>
       <c r="E595" t="n">
         <v>1908.349975585938</v>
@@ -19500,7 +19500,7 @@
         <v>1221.949951171875</v>
       </c>
       <c r="D596" t="n">
-        <v>3640.39208984375</v>
+        <v>3640.392333984375</v>
       </c>
       <c r="E596" t="n">
         <v>2038</v>
@@ -19547,7 +19547,7 @@
         <v>550.1774291992188</v>
       </c>
       <c r="I597" t="n">
-        <v>907.8051147460938</v>
+        <v>907.80517578125</v>
       </c>
       <c r="J597" t="n">
         <v>213.5500030517578</v>
@@ -19628,7 +19628,7 @@
         <v>1020.049987792969</v>
       </c>
       <c r="D600" t="n">
-        <v>3215.25927734375</v>
+        <v>3215.259521484375</v>
       </c>
       <c r="E600" t="n">
         <v>1864.25</v>
@@ -19643,7 +19643,7 @@
         <v>614.130859375</v>
       </c>
       <c r="I600" t="n">
-        <v>977.1368408203125</v>
+        <v>977.13671875</v>
       </c>
       <c r="J600" t="n">
         <v>239.75</v>
@@ -19660,7 +19660,7 @@
         <v>1026.800048828125</v>
       </c>
       <c r="D601" t="n">
-        <v>3215.80859375</v>
+        <v>3215.808837890625</v>
       </c>
       <c r="E601" t="n">
         <v>1880.349975585938</v>
@@ -19675,7 +19675,7 @@
         <v>632.9610595703125</v>
       </c>
       <c r="I601" t="n">
-        <v>969.8439331054688</v>
+        <v>969.843994140625</v>
       </c>
       <c r="J601" t="n">
         <v>242.9499969482422</v>
@@ -19724,7 +19724,7 @@
         <v>1020.5</v>
       </c>
       <c r="D603" t="n">
-        <v>3214.760009765625</v>
+        <v>3214.76025390625</v>
       </c>
       <c r="E603" t="n">
         <v>1827.349975585938</v>
@@ -19867,7 +19867,7 @@
         <v>661.0955810546875</v>
       </c>
       <c r="I607" t="n">
-        <v>926.7317504882812</v>
+        <v>926.731689453125</v>
       </c>
       <c r="J607" t="n">
         <v>227.5399932861328</v>
@@ -20027,7 +20027,7 @@
         <v>651.4290161132812</v>
       </c>
       <c r="I612" t="n">
-        <v>893.006103515625</v>
+        <v>893.0060424804688</v>
       </c>
       <c r="J612" t="n">
         <v>222.3899993896484</v>
@@ -20123,7 +20123,7 @@
         <v>689.0543823242188</v>
       </c>
       <c r="I615" t="n">
-        <v>887.4100952148438</v>
+        <v>887.4100341796875</v>
       </c>
       <c r="J615" t="n">
         <v>220.5800018310547</v>
@@ -20219,7 +20219,7 @@
         <v>676.2647094726562</v>
       </c>
       <c r="I618" t="n">
-        <v>895.8040771484375</v>
+        <v>895.8040161132812</v>
       </c>
       <c r="J618" t="n">
         <v>222.1699981689453</v>
@@ -20251,7 +20251,7 @@
         <v>680.13134765625</v>
       </c>
       <c r="I619" t="n">
-        <v>890.4078369140625</v>
+        <v>890.4078979492188</v>
       </c>
       <c r="J619" t="n">
         <v>221.6600036621094</v>
@@ -20283,7 +20283,7 @@
         <v>677.7023315429688</v>
       </c>
       <c r="I620" t="n">
-        <v>883.0132446289062</v>
+        <v>883.0133056640625</v>
       </c>
       <c r="J620" t="n">
         <v>220.7599945068359</v>
@@ -20603,7 +20603,7 @@
         <v>685.435546875</v>
       </c>
       <c r="I630" t="n">
-        <v>878.5165405273438</v>
+        <v>878.5164794921875</v>
       </c>
       <c r="J630" t="n">
         <v>212.1100006103516</v>
@@ -20731,7 +20731,7 @@
         <v>674.0339965820312</v>
       </c>
       <c r="I634" t="n">
-        <v>892.3065795898438</v>
+        <v>892.3065185546875</v>
       </c>
       <c r="J634" t="n">
         <v>220.7599945068359</v>
@@ -20891,7 +20891,7 @@
         <v>630.7078247070312</v>
       </c>
       <c r="I639" t="n">
-        <v>856.432373046875</v>
+        <v>856.4324340820312</v>
       </c>
       <c r="J639" t="n">
         <v>207.5200042724609</v>
@@ -21019,7 +21019,7 @@
         <v>626.5933227539062</v>
       </c>
       <c r="I643" t="n">
-        <v>869.22314453125</v>
+        <v>869.2232055664062</v>
       </c>
       <c r="J643" t="n">
         <v>208.3300018310547</v>
@@ -21083,7 +21083,7 @@
         <v>619.058349609375</v>
       </c>
       <c r="I645" t="n">
-        <v>850.7365112304688</v>
+        <v>850.7364501953125</v>
       </c>
       <c r="J645" t="n">
         <v>202.3999938964844</v>
@@ -21115,7 +21115,7 @@
         <v>617.86865234375</v>
       </c>
       <c r="I646" t="n">
-        <v>842.642333984375</v>
+        <v>842.6423950195312</v>
       </c>
       <c r="J646" t="n">
         <v>201.7200012207031</v>
@@ -21435,7 +21435,7 @@
         <v>607.2601318359375</v>
       </c>
       <c r="I656" t="n">
-        <v>836.896484375</v>
+        <v>836.8965454101562</v>
       </c>
       <c r="J656" t="n">
         <v>202.7899932861328</v>
@@ -21467,7 +21467,7 @@
         <v>611.7711791992188</v>
       </c>
       <c r="I657" t="n">
-        <v>829.7516479492188</v>
+        <v>829.7515869140625</v>
       </c>
       <c r="J657" t="n">
         <v>201.6900024414062</v>
@@ -21595,7 +21595,7 @@
         <v>626.444580078125</v>
       </c>
       <c r="I661" t="n">
-        <v>843.391845703125</v>
+        <v>843.3917846679688</v>
       </c>
       <c r="J661" t="n">
         <v>199.1399993896484</v>
@@ -21691,7 +21691,7 @@
         <v>621.6856689453125</v>
       </c>
       <c r="I664" t="n">
-        <v>812.9637451171875</v>
+        <v>812.9636840820312</v>
       </c>
       <c r="J664" t="n">
         <v>196.3899993896484</v>
@@ -21755,7 +21755,7 @@
         <v>622.7763061523438</v>
       </c>
       <c r="I666" t="n">
-        <v>805.2192993164062</v>
+        <v>805.2193603515625</v>
       </c>
       <c r="J666" t="n">
         <v>192.3300018310547</v>
@@ -21819,7 +21819,7 @@
         <v>621.9335327148438</v>
       </c>
       <c r="I668" t="n">
-        <v>806.168701171875</v>
+        <v>806.1686401367188</v>
       </c>
       <c r="J668" t="n">
         <v>196.6999969482422</v>
@@ -21915,7 +21915,7 @@
         <v>603.1952514648438</v>
       </c>
       <c r="I671" t="n">
-        <v>775.640625</v>
+        <v>775.6406860351562</v>
       </c>
       <c r="J671" t="n">
         <v>190.9100036621094</v>
@@ -21947,7 +21947,7 @@
         <v>611.2754516601562</v>
       </c>
       <c r="I672" t="n">
-        <v>788.1316528320312</v>
+        <v>788.1317138671875</v>
       </c>
       <c r="J672" t="n">
         <v>190.6699981689453</v>
@@ -21979,7 +21979,7 @@
         <v>616.7284545898438</v>
       </c>
       <c r="I673" t="n">
-        <v>834.7479858398438</v>
+        <v>834.748046875</v>
       </c>
       <c r="J673" t="n">
         <v>192.5899963378906</v>
@@ -22171,7 +22171,7 @@
         <v>627.0394897460938</v>
       </c>
       <c r="I679" t="n">
-        <v>785.88330078125</v>
+        <v>785.8832397460938</v>
       </c>
       <c r="J679" t="n">
         <v>184.7899932861328</v>
@@ -22299,7 +22299,7 @@
         <v>601.2123413085938</v>
       </c>
       <c r="I683" t="n">
-        <v>759.40234375</v>
+        <v>759.4024047851562</v>
       </c>
       <c r="J683" t="n">
         <v>176.6900024414062</v>
@@ -22331,7 +22331,7 @@
         <v>602.7490844726562</v>
       </c>
       <c r="I684" t="n">
-        <v>756.6043701171875</v>
+        <v>756.6044311523438</v>
       </c>
       <c r="J684" t="n">
         <v>180.2400054931641</v>
@@ -22363,7 +22363,7 @@
         <v>580.2432861328125</v>
       </c>
       <c r="I685" t="n">
-        <v>757.0540771484375</v>
+        <v>757.0540161132812</v>
       </c>
       <c r="J685" t="n">
         <v>182.3500061035156</v>
@@ -22395,7 +22395,7 @@
         <v>580.1937255859375</v>
       </c>
       <c r="I686" t="n">
-        <v>756.80419921875</v>
+        <v>756.8042602539062</v>
       </c>
       <c r="J686" t="n">
         <v>181.2599945068359</v>
@@ -22427,7 +22427,7 @@
         <v>583.8621215820312</v>
       </c>
       <c r="I687" t="n">
-        <v>753.8063354492188</v>
+        <v>753.806396484375</v>
       </c>
       <c r="J687" t="n">
         <v>177.8399963378906</v>
@@ -22459,7 +22459,7 @@
         <v>585.2996215820312</v>
       </c>
       <c r="I688" t="n">
-        <v>745.362548828125</v>
+        <v>745.3624877929688</v>
       </c>
       <c r="J688" t="n">
         <v>178.5</v>
@@ -22555,7 +22555,7 @@
         <v>569.0399780273438</v>
       </c>
       <c r="I691" t="n">
-        <v>732.0720825195312</v>
+        <v>732.072021484375</v>
       </c>
       <c r="J691" t="n">
         <v>175.4100036621094</v>
@@ -22619,7 +22619,7 @@
         <v>553.7221069335938</v>
       </c>
       <c r="I693" t="n">
-        <v>691.3514404296875</v>
+        <v>691.3513793945312</v>
       </c>
       <c r="J693" t="n">
         <v>169.0700073242188</v>
@@ -22651,7 +22651,7 @@
         <v>551.0947875976562</v>
       </c>
       <c r="I694" t="n">
-        <v>699.9453125</v>
+        <v>699.9452514648438</v>
       </c>
       <c r="J694" t="n">
         <v>167.7899932861328</v>
@@ -22683,7 +22683,7 @@
         <v>554.1187133789062</v>
       </c>
       <c r="I695" t="n">
-        <v>754.406005859375</v>
+        <v>754.4059448242188</v>
       </c>
       <c r="J695" t="n">
         <v>165.3300018310547</v>
@@ -22715,7 +22715,7 @@
         <v>547.9717407226562</v>
       </c>
       <c r="I696" t="n">
-        <v>723.628173828125</v>
+        <v>723.6282348632812</v>
       </c>
       <c r="J696" t="n">
         <v>158.4199981689453</v>
@@ -22747,7 +22747,7 @@
         <v>564.5288696289062</v>
       </c>
       <c r="I697" t="n">
-        <v>711.5868530273438</v>
+        <v>711.5867919921875</v>
       </c>
       <c r="J697" t="n">
         <v>157.7799987792969</v>
@@ -22779,7 +22779,7 @@
         <v>570.0809326171875</v>
       </c>
       <c r="I698" t="n">
-        <v>710.3877563476562</v>
+        <v>710.3876953125</v>
       </c>
       <c r="J698" t="n">
         <v>164.0299987792969</v>
@@ -22811,7 +22811,7 @@
         <v>574.74072265625</v>
       </c>
       <c r="I699" t="n">
-        <v>713.0358276367188</v>
+        <v>713.0357666015625</v>
       </c>
       <c r="J699" t="n">
         <v>165.4900054931641</v>
@@ -22875,7 +22875,7 @@
         <v>577.4672241210938</v>
       </c>
       <c r="I701" t="n">
-        <v>722.4290771484375</v>
+        <v>722.4290161132812</v>
       </c>
       <c r="J701" t="n">
         <v>169.7599945068359</v>
@@ -22907,7 +22907,7 @@
         <v>566.5117797851562</v>
       </c>
       <c r="I702" t="n">
-        <v>710.8373413085938</v>
+        <v>710.83740234375</v>
       </c>
       <c r="J702" t="n">
         <v>162.3800048828125</v>
@@ -22939,7 +22939,7 @@
         <v>567.1066284179688</v>
       </c>
       <c r="I703" t="n">
-        <v>721.5296630859375</v>
+        <v>721.5297241210938</v>
       </c>
       <c r="J703" t="n">
         <v>164.9700012207031</v>
@@ -23131,7 +23131,7 @@
         <v>540.6845703125</v>
       </c>
       <c r="I709" t="n">
-        <v>678.4108276367188</v>
+        <v>678.4107666015625</v>
       </c>
       <c r="J709" t="n">
         <v>167.8500061035156</v>
@@ -23163,7 +23163,7 @@
         <v>539.8419189453125</v>
       </c>
       <c r="I710" t="n">
-        <v>683.4071655273438</v>
+        <v>683.4072265625</v>
       </c>
       <c r="J710" t="n">
         <v>167.4199981689453</v>
@@ -23195,7 +23195,7 @@
         <v>545.840087890625</v>
       </c>
       <c r="I711" t="n">
-        <v>669.417236328125</v>
+        <v>669.4172973632812</v>
       </c>
       <c r="J711" t="n">
         <v>167.7799987792969</v>
@@ -23259,7 +23259,7 @@
         <v>480.0081787109375</v>
       </c>
       <c r="I713" t="n">
-        <v>601.4662475585938</v>
+        <v>601.46630859375</v>
       </c>
       <c r="J713" t="n">
         <v>167.6699981689453</v>
@@ -23291,7 +23291,7 @@
         <v>495.5738525390625</v>
       </c>
       <c r="I714" t="n">
-        <v>608.6610717773438</v>
+        <v>608.6610107421875</v>
       </c>
       <c r="J714" t="n">
         <v>169.3899993896484</v>
@@ -23323,7 +23323,7 @@
         <v>500.6302490234375</v>
       </c>
       <c r="I715" t="n">
-        <v>599.9674072265625</v>
+        <v>599.9673461914062</v>
       </c>
       <c r="J715" t="n">
         <v>166.6499938964844</v>
@@ -23387,7 +23387,7 @@
         <v>510.5942687988281</v>
       </c>
       <c r="I717" t="n">
-        <v>693.5498046875</v>
+        <v>693.5498657226562</v>
       </c>
       <c r="J717" t="n">
         <v>180.1600036621094</v>
@@ -23547,7 +23547,7 @@
         <v>559.8690795898438</v>
       </c>
       <c r="I722" t="n">
-        <v>746.1119384765625</v>
+        <v>746.1119995117188</v>
       </c>
       <c r="J722" t="n">
         <v>175.2100067138672</v>
@@ -23579,7 +23579,7 @@
         <v>566.2142944335938</v>
       </c>
       <c r="I723" t="n">
-        <v>743.4139404296875</v>
+        <v>743.4138793945312</v>
       </c>
       <c r="J723" t="n">
         <v>174.6399993896484</v>
@@ -23739,7 +23739,7 @@
         <v>566.8587646484375</v>
       </c>
       <c r="I728" t="n">
-        <v>729.8736572265625</v>
+        <v>729.8737182617188</v>
       </c>
       <c r="J728" t="n">
         <v>173.1699981689453</v>
@@ -23803,7 +23803,7 @@
         <v>572.0142822265625</v>
       </c>
       <c r="I730" t="n">
-        <v>712.1864624023438</v>
+        <v>712.1864013671875</v>
       </c>
       <c r="J730" t="n">
         <v>171.3399963378906</v>
@@ -23835,7 +23835,7 @@
         <v>566.2142944335938</v>
       </c>
       <c r="I731" t="n">
-        <v>714.135009765625</v>
+        <v>714.1350708007812</v>
       </c>
       <c r="J731" t="n">
         <v>169.5899963378906</v>
@@ -23995,7 +23995,7 @@
         <v>538.453857421875</v>
       </c>
       <c r="I736" t="n">
-        <v>670.4664916992188</v>
+        <v>670.466552734375</v>
       </c>
       <c r="J736" t="n">
         <v>163.8000030517578</v>
@@ -24091,7 +24091,7 @@
         <v>539.9410400390625</v>
       </c>
       <c r="I739" t="n">
-        <v>750.6087646484375</v>
+        <v>750.6087036132812</v>
       </c>
       <c r="J739" t="n">
         <v>164.1399993896484</v>
@@ -24251,7 +24251,7 @@
         <v>525.3667602539062</v>
       </c>
       <c r="I744" t="n">
-        <v>703.2927856445312</v>
+        <v>703.2928466796875</v>
       </c>
       <c r="J744" t="n">
         <v>157.1999969482422</v>
@@ -24283,7 +24283,7 @@
         <v>531.166748046875</v>
       </c>
       <c r="I745" t="n">
-        <v>702.7931518554688</v>
+        <v>702.793212890625</v>
       </c>
       <c r="J745" t="n">
         <v>158.2200012207031</v>
@@ -24379,7 +24379,7 @@
         <v>506.8763427734375</v>
       </c>
       <c r="I748" t="n">
-        <v>680.759033203125</v>
+        <v>680.7590942382812</v>
       </c>
       <c r="J748" t="n">
         <v>150.3300018310547</v>
@@ -24475,7 +24475,7 @@
         <v>514.8574829101562</v>
       </c>
       <c r="I751" t="n">
-        <v>661.7727661132812</v>
+        <v>661.7728271484375</v>
       </c>
       <c r="J751" t="n">
         <v>147.2899932861328</v>
@@ -24539,7 +24539,7 @@
         <v>531.6624755859375</v>
       </c>
       <c r="I753" t="n">
-        <v>672.6649780273438</v>
+        <v>672.6649169921875</v>
       </c>
       <c r="J753" t="n">
         <v>159.4799957275391</v>
@@ -24571,7 +24571,7 @@
         <v>530.7701416015625</v>
       </c>
       <c r="I754" t="n">
-        <v>675.2630615234375</v>
+        <v>675.2630004882812</v>
       </c>
       <c r="J754" t="n">
         <v>159.9700012207031</v>
@@ -24731,7 +24731,7 @@
         <v>530.3240356445312</v>
       </c>
       <c r="I759" t="n">
-        <v>618.9536743164062</v>
+        <v>618.9537353515625</v>
       </c>
       <c r="J759" t="n">
         <v>140.1100006103516</v>
@@ -24763,7 +24763,7 @@
         <v>538.5034790039062</v>
       </c>
       <c r="I760" t="n">
-        <v>615.6060180664062</v>
+        <v>615.6060791015625</v>
       </c>
       <c r="J760" t="n">
         <v>137.9900054931641</v>
@@ -24795,7 +24795,7 @@
         <v>517.6334838867188</v>
       </c>
       <c r="I761" t="n">
-        <v>623.4004516601562</v>
+        <v>623.400390625</v>
       </c>
       <c r="J761" t="n">
         <v>140.6699981689453</v>
@@ -24859,7 +24859,7 @@
         <v>508.4130554199219</v>
       </c>
       <c r="I763" t="n">
-        <v>642.6365966796875</v>
+        <v>642.6365356445312</v>
       </c>
       <c r="J763" t="n">
         <v>141.9600067138672</v>
@@ -24891,7 +24891,7 @@
         <v>497.2097473144531</v>
       </c>
       <c r="I764" t="n">
-        <v>634.2925415039062</v>
+        <v>634.2926025390625</v>
       </c>
       <c r="J764" t="n">
         <v>141.7700042724609</v>
@@ -24955,7 +24955,7 @@
         <v>509.3053894042969</v>
       </c>
       <c r="I766" t="n">
-        <v>628.496826171875</v>
+        <v>628.4967651367188</v>
       </c>
       <c r="J766" t="n">
         <v>141.1199951171875</v>
@@ -24987,7 +24987,7 @@
         <v>517.3360595703125</v>
       </c>
       <c r="I767" t="n">
-        <v>640.3382568359375</v>
+        <v>640.3381958007812</v>
       </c>
       <c r="J767" t="n">
         <v>143.8500061035156</v>
@@ -25019,7 +25019,7 @@
         <v>509.7515869140625</v>
       </c>
       <c r="I768" t="n">
-        <v>634.24267578125</v>
+        <v>634.2426147460938</v>
       </c>
       <c r="J768" t="n">
         <v>142.9499969482422</v>
@@ -25051,7 +25051,7 @@
         <v>508.3634948730469</v>
       </c>
       <c r="I769" t="n">
-        <v>628.9964599609375</v>
+        <v>628.9963989257812</v>
       </c>
       <c r="J769" t="n">
         <v>142.1600036621094</v>
@@ -25083,7 +25083,7 @@
         <v>502.4148254394531</v>
       </c>
       <c r="I770" t="n">
-        <v>608.1114501953125</v>
+        <v>608.1115112304688</v>
       </c>
       <c r="J770" t="n">
         <v>139.6399993896484</v>
@@ -25147,7 +25147,7 @@
         <v>496.8131713867188</v>
       </c>
       <c r="I772" t="n">
-        <v>595.3206787109375</v>
+        <v>595.3207397460938</v>
       </c>
       <c r="J772" t="n">
         <v>136.0899963378906</v>
@@ -25211,7 +25211,7 @@
         <v>485.3124084472656</v>
       </c>
       <c r="I774" t="n">
-        <v>573.3365478515625</v>
+        <v>573.3366088867188</v>
       </c>
       <c r="J774" t="n">
         <v>128.5399932861328</v>
@@ -25243,7 +25243,7 @@
         <v>484.1226806640625</v>
       </c>
       <c r="I775" t="n">
-        <v>574.0360107421875</v>
+        <v>574.0360717773438</v>
       </c>
       <c r="J775" t="n">
         <v>124.370002746582</v>
@@ -25403,7 +25403,7 @@
         <v>466.3757934570312</v>
       </c>
       <c r="I780" t="n">
-        <v>574.9854125976562</v>
+        <v>574.9853515625</v>
       </c>
       <c r="J780" t="n">
         <v>129.6300048828125</v>
@@ -25467,7 +25467,7 @@
         <v>465.7809448242188</v>
       </c>
       <c r="I782" t="n">
-        <v>580.3314819335938</v>
+        <v>580.33154296875</v>
       </c>
       <c r="J782" t="n">
         <v>123.0400009155273</v>
@@ -25691,7 +25691,7 @@
         <v>485.4115600585938</v>
       </c>
       <c r="I789" t="n">
-        <v>605.3134765625</v>
+        <v>605.3135375976562</v>
       </c>
       <c r="J789" t="n">
         <v>120.5400009155273</v>
@@ -25755,7 +25755,7 @@
         <v>485.0149841308594</v>
       </c>
       <c r="I791" t="n">
-        <v>600.0672607421875</v>
+        <v>600.0673217773438</v>
       </c>
       <c r="J791" t="n">
         <v>116.7699966430664</v>
@@ -25787,7 +25787,7 @@
         <v>481.64404296875</v>
       </c>
       <c r="I792" t="n">
-        <v>603.9144287109375</v>
+        <v>603.9144897460938</v>
       </c>
       <c r="J792" t="n">
         <v>116.3499984741211</v>
@@ -25819,7 +25819,7 @@
         <v>486.3534240722656</v>
       </c>
       <c r="I793" t="n">
-        <v>602.9152221679688</v>
+        <v>602.9151611328125</v>
       </c>
       <c r="J793" t="n">
         <v>113.8300018310547</v>
@@ -25851,7 +25851,7 @@
         <v>486.3534240722656</v>
       </c>
       <c r="I794" t="n">
-        <v>602.9152221679688</v>
+        <v>602.9151611328125</v>
       </c>
       <c r="J794" t="n">
         <v>113.8300018310547</v>
@@ -26011,7 +26011,7 @@
         <v>516.0967407226562</v>
       </c>
       <c r="I799" t="n">
-        <v>607.3120727539062</v>
+        <v>607.31201171875</v>
       </c>
       <c r="J799" t="n">
         <v>118.1699981689453</v>
@@ -26043,7 +26043,7 @@
         <v>527.8949584960938</v>
       </c>
       <c r="I800" t="n">
-        <v>597.6190185546875</v>
+        <v>597.6190795898438</v>
       </c>
       <c r="J800" t="n">
         <v>114.1900024414062</v>
@@ -26075,7 +26075,7 @@
         <v>538.1563720703125</v>
       </c>
       <c r="I801" t="n">
-        <v>611.4591064453125</v>
+        <v>611.4590454101562</v>
       </c>
       <c r="J801" t="n">
         <v>113.5400009155273</v>
@@ -26107,7 +26107,7 @@
         <v>533.7444458007812</v>
       </c>
       <c r="I802" t="n">
-        <v>602.1657104492188</v>
+        <v>602.165771484375</v>
       </c>
       <c r="J802" t="n">
         <v>111.7600021362305</v>
@@ -26139,7 +26139,7 @@
         <v>525.3667602539062</v>
       </c>
       <c r="I803" t="n">
-        <v>591.7233276367188</v>
+        <v>591.7232666015625</v>
       </c>
       <c r="J803" t="n">
         <v>114.8099975585938</v>
@@ -26203,7 +26203,7 @@
         <v>536.0744018554688</v>
       </c>
       <c r="I805" t="n">
-        <v>604.6139526367188</v>
+        <v>604.614013671875</v>
       </c>
       <c r="J805" t="n">
         <v>121.0599975585938</v>
@@ -26267,7 +26267,7 @@
         <v>520.7069702148438</v>
       </c>
       <c r="I807" t="n">
-        <v>569.2894287109375</v>
+        <v>569.2894897460938</v>
       </c>
       <c r="J807" t="n">
         <v>113.5199966430664</v>
@@ -26299,7 +26299,7 @@
         <v>532.207763671875</v>
       </c>
       <c r="I808" t="n">
-        <v>584.5285034179688</v>
+        <v>584.5284423828125</v>
       </c>
       <c r="J808" t="n">
         <v>114.7799987792969</v>
@@ -26395,7 +26395,7 @@
         <v>553.2759399414062</v>
       </c>
       <c r="I811" t="n">
-        <v>610.2099609375</v>
+        <v>610.2100219726562</v>
       </c>
       <c r="J811" t="n">
         <v>121.1800003051758</v>
@@ -26427,7 +26427,7 @@
         <v>560.9100952148438</v>
       </c>
       <c r="I812" t="n">
-        <v>607.5618286132812</v>
+        <v>607.5618896484375</v>
       </c>
       <c r="J812" t="n">
         <v>122.5699996948242</v>
@@ -26459,7 +26459,7 @@
         <v>564.9254150390625</v>
       </c>
       <c r="I813" t="n">
-        <v>607.8117065429688</v>
+        <v>607.8116455078125</v>
       </c>
       <c r="J813" t="n">
         <v>122.6900024414062</v>
@@ -26491,7 +26491,7 @@
         <v>573.9476318359375</v>
       </c>
       <c r="I814" t="n">
-        <v>623.8001098632812</v>
+        <v>623.8001708984375</v>
       </c>
       <c r="J814" t="n">
         <v>128.6799926757812</v>
@@ -26555,7 +26555,7 @@
         <v>569.4364624023438</v>
       </c>
       <c r="I816" t="n">
-        <v>626.048583984375</v>
+        <v>626.0485229492188</v>
       </c>
       <c r="J816" t="n">
         <v>128.0200042724609</v>
@@ -26587,7 +26587,7 @@
         <v>567.1066284179688</v>
       </c>
       <c r="I817" t="n">
-        <v>624.4996337890625</v>
+        <v>624.4996948242188</v>
       </c>
       <c r="J817" t="n">
         <v>128.1199951171875</v>
@@ -26715,7 +26715,7 @@
         <v>535.0829467773438</v>
       </c>
       <c r="I821" t="n">
-        <v>599.7675170898438</v>
+        <v>599.7674560546875</v>
       </c>
       <c r="J821" t="n">
         <v>117.8499984741211</v>
@@ -26747,7 +26747,7 @@
         <v>523.92919921875</v>
       </c>
       <c r="I822" t="n">
-        <v>599.3677368164062</v>
+        <v>599.3677978515625</v>
       </c>
       <c r="J822" t="n">
         <v>118.1900024414062</v>
@@ -26779,7 +26779,7 @@
         <v>536.7684326171875</v>
       </c>
       <c r="I823" t="n">
-        <v>665.0703735351562</v>
+        <v>665.0704345703125</v>
       </c>
       <c r="J823" t="n">
         <v>122.5400009155273</v>
@@ -26971,7 +26971,7 @@
         <v>532.3069458007812</v>
       </c>
       <c r="I829" t="n">
-        <v>647.8828125</v>
+        <v>647.8827514648438</v>
       </c>
       <c r="J829" t="n">
         <v>121.9499969482422</v>
@@ -27003,7 +27003,7 @@
         <v>538.9495849609375</v>
       </c>
       <c r="I830" t="n">
-        <v>655.5772705078125</v>
+        <v>655.5772094726562</v>
       </c>
       <c r="J830" t="n">
         <v>124.7799987792969</v>
@@ -27067,7 +27067,7 @@
         <v>558.6793212890625</v>
       </c>
       <c r="I832" t="n">
-        <v>681.1087646484375</v>
+        <v>681.1088256835938</v>
       </c>
       <c r="J832" t="n">
         <v>129.9799957275391</v>
@@ -27099,7 +27099,7 @@
         <v>560.7117919921875</v>
       </c>
       <c r="I833" t="n">
-        <v>675.5128173828125</v>
+        <v>675.5128784179688</v>
       </c>
       <c r="J833" t="n">
         <v>147.4799957275391</v>
@@ -27131,7 +27131,7 @@
         <v>557.24169921875</v>
       </c>
       <c r="I834" t="n">
-        <v>659.4744262695312</v>
+        <v>659.4744873046875</v>
       </c>
       <c r="J834" t="n">
         <v>163.8099975585938</v>
@@ -27227,7 +27227,7 @@
         <v>566.0160522460938</v>
       </c>
       <c r="I837" t="n">
-        <v>658.0255126953125</v>
+        <v>658.0254516601562</v>
       </c>
       <c r="J837" t="n">
         <v>162.4600067138672</v>
@@ -27323,7 +27323,7 @@
         <v>556.84521484375</v>
       </c>
       <c r="I840" t="n">
-        <v>672.5150756835938</v>
+        <v>672.5150146484375</v>
       </c>
       <c r="J840" t="n">
         <v>163.3200073242188</v>
@@ -27355,7 +27355,7 @@
         <v>556.6469116210938</v>
       </c>
       <c r="I841" t="n">
-        <v>680.2593994140625</v>
+        <v>680.2594604492188</v>
       </c>
       <c r="J841" t="n">
         <v>162.75</v>
@@ -27387,7 +27387,7 @@
         <v>548.764892578125</v>
       </c>
       <c r="I842" t="n">
-        <v>683.2572631835938</v>
+        <v>683.25732421875</v>
       </c>
       <c r="J842" t="n">
         <v>163.8999938964844</v>
@@ -27419,7 +27419,7 @@
         <v>550.79736328125</v>
       </c>
       <c r="I843" t="n">
-        <v>689.8524780273438</v>
+        <v>689.8525390625</v>
       </c>
       <c r="J843" t="n">
         <v>166.6000061035156</v>
@@ -27451,7 +27451,7 @@
         <v>547.67431640625</v>
       </c>
       <c r="I844" t="n">
-        <v>678.3607788085938</v>
+        <v>678.36083984375</v>
       </c>
       <c r="J844" t="n">
         <v>162.6799926757812</v>
@@ -27643,7 +27643,7 @@
         <v>556.4486083984375</v>
       </c>
       <c r="I850" t="n">
-        <v>697.0972900390625</v>
+        <v>697.0972290039062</v>
       </c>
       <c r="J850" t="n">
         <v>165.4499969482422</v>
@@ -38666,7 +38666,7 @@
         <v>4.708916641196659</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.133272118677697</v>
+        <v>-1.133280950410598</v>
       </c>
       <c r="J17" t="n">
         <v>-3.703473027133464</v>
@@ -38698,7 +38698,7 @@
         <v>2.556976611417694</v>
       </c>
       <c r="I18" t="n">
-        <v>13.9203514219733</v>
+        <v>13.92037319151405</v>
       </c>
       <c r="J18" t="n">
         <v>39.0750920819702</v>
@@ -38730,7 +38730,7 @@
         <v>0.250775626255817</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3982613619074926</v>
+        <v>-0.3982815934182926</v>
       </c>
       <c r="J19" t="n">
         <v>5.449173426524445</v>
@@ -38762,7 +38762,7 @@
         <v>15.78663533429408</v>
       </c>
       <c r="I20" t="n">
-        <v>8.15757427726731</v>
+        <v>8.157585240054344</v>
       </c>
       <c r="J20" t="n">
         <v>-4.885104564910236</v>
@@ -38794,7 +38794,7 @@
         <v>-9.331122166279437</v>
       </c>
       <c r="I21" t="n">
-        <v>-13.36495026383427</v>
+        <v>-13.36494203556915</v>
       </c>
       <c r="J21" t="n">
         <v>-17.230209606265</v>
@@ -38826,7 +38826,7 @@
         <v>-4.292649304045937</v>
       </c>
       <c r="I22" t="n">
-        <v>-15.49832272048813</v>
+        <v>-15.49833074613296</v>
       </c>
       <c r="J22" t="n">
         <v>-11.93001764146588</v>
@@ -38954,7 +38954,7 @@
         <v>2.511957438194501</v>
       </c>
       <c r="I26" t="n">
-        <v>-5.280907910030197</v>
+        <v>-5.280900942650235</v>
       </c>
       <c r="J26" t="n">
         <v>-7.114882210229778</v>
@@ -38986,7 +38986,7 @@
         <v>-9.250694296187289</v>
       </c>
       <c r="I27" t="n">
-        <v>-7.280442020723066</v>
+        <v>-7.280448841020104</v>
       </c>
       <c r="J27" t="n">
         <v>-8.00072692056778</v>
@@ -39035,7 +39035,7 @@
         <v>-11.17296649328798</v>
       </c>
       <c r="D29" t="n">
-        <v>-6.828899946596989</v>
+        <v>-6.82890662348562</v>
       </c>
       <c r="E29" t="n">
         <v>-6.264570350682453</v>
@@ -39067,7 +39067,7 @@
         <v>5.407444639185499</v>
       </c>
       <c r="D30" t="n">
-        <v>11.67544604696602</v>
+        <v>11.67545404992583</v>
       </c>
       <c r="E30" t="n">
         <v>6.158036863040528</v>
@@ -39099,7 +39099,7 @@
         <v>3.749878429044062</v>
       </c>
       <c r="D31" t="n">
-        <v>-4.454035710708237</v>
+        <v>-4.454043016634746</v>
       </c>
       <c r="E31" t="n">
         <v>-2.043429665210794</v>
@@ -39114,7 +39114,7 @@
         <v>1.232966706077199</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2752207373969195</v>
+        <v>0.2752141253989482</v>
       </c>
       <c r="J31" t="n">
         <v>9.047733448417429</v>
@@ -39131,7 +39131,7 @@
         <v>-3.582666599871998</v>
       </c>
       <c r="D32" t="n">
-        <v>-2.687649773254319</v>
+        <v>-2.687642332260465</v>
       </c>
       <c r="E32" t="n">
         <v>-3.160867674766898</v>
@@ -39146,7 +39146,7 @@
         <v>1.064517683991228</v>
       </c>
       <c r="I32" t="n">
-        <v>-9.662184894372693</v>
+        <v>-9.662168175251139</v>
       </c>
       <c r="J32" t="n">
         <v>-17.54454747637502</v>
@@ -39163,7 +39163,7 @@
         <v>-0.2809383404587251</v>
       </c>
       <c r="D33" t="n">
-        <v>4.563974846568541</v>
+        <v>4.563966710865652</v>
       </c>
       <c r="E33" t="n">
         <v>13.51343881245972</v>
@@ -39178,7 +39178,7 @@
         <v>8.138501651251051</v>
       </c>
       <c r="I33" t="n">
-        <v>1.313789268309984</v>
+        <v>1.313783312597083</v>
       </c>
       <c r="J33" t="n">
         <v>-5.670485929559521</v>
@@ -39195,7 +39195,7 @@
         <v>2.113313467457556</v>
       </c>
       <c r="D34" t="n">
-        <v>10.28624439107486</v>
+        <v>10.28625297200523</v>
       </c>
       <c r="E34" t="n">
         <v>4.536628125978392</v>
@@ -39210,7 +39210,7 @@
         <v>7.563832778485602</v>
       </c>
       <c r="I34" t="n">
-        <v>2.469761078617028</v>
+        <v>2.469748557786922</v>
       </c>
       <c r="J34" t="n">
         <v>3.163116807777522</v>
@@ -39227,7 +39227,7 @@
         <v>19.83612797148144</v>
       </c>
       <c r="D35" t="n">
-        <v>20.79242956930774</v>
+        <v>20.79244208958237</v>
       </c>
       <c r="E35" t="n">
         <v>55.22938610073884</v>
@@ -39242,7 +39242,7 @@
         <v>18.58850414004494</v>
       </c>
       <c r="I35" t="n">
-        <v>39.38346821625365</v>
+        <v>39.38348885001665</v>
       </c>
       <c r="J35" t="n">
         <v>19.8720882653705</v>
@@ -39259,7 +39259,7 @@
         <v>13.36061811535836</v>
       </c>
       <c r="D36" t="n">
-        <v>2.784753621212066</v>
+        <v>2.784732017019165</v>
       </c>
       <c r="E36" t="n">
         <v>12.8503286652526</v>
@@ -39274,7 +39274,7 @@
         <v>3.486862093974996</v>
       </c>
       <c r="I36" t="n">
-        <v>25.60695276269311</v>
+        <v>25.60694193594768</v>
       </c>
       <c r="J36" t="n">
         <v>12.19886573470481</v>
@@ -39291,7 +39291,7 @@
         <v>-4.992287837955112</v>
       </c>
       <c r="D37" t="n">
-        <v>-4.940138180910026</v>
+        <v>-4.940137680600209</v>
       </c>
       <c r="E37" t="n">
         <v>-7.648280214024627</v>
@@ -39306,7 +39306,7 @@
         <v>-0.0823883492873545</v>
       </c>
       <c r="I37" t="n">
-        <v>-7.982063030449627</v>
+        <v>-7.982072197779666</v>
       </c>
       <c r="J37" t="n">
         <v>-6.404409230114472</v>
@@ -39323,7 +39323,7 @@
         <v>-0.20937399858032</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2211490209924283</v>
+        <v>-0.2211389159423538</v>
       </c>
       <c r="E38" t="n">
         <v>6.299466802567633</v>
@@ -39338,7 +39338,7 @@
         <v>-0.8403317134902943</v>
       </c>
       <c r="I38" t="n">
-        <v>-3.546709577533214</v>
+        <v>-3.546709236722645</v>
       </c>
       <c r="J38" t="n">
         <v>-2.729820821375695</v>
@@ -39370,7 +39370,7 @@
         <v>-7.47300040276011</v>
       </c>
       <c r="I39" t="n">
-        <v>-4.203720527170574</v>
+        <v>-4.203711321909543</v>
       </c>
       <c r="J39" t="n">
         <v>-6.357877502164633</v>
@@ -39387,7 +39387,7 @@
         <v>6.966440170352728</v>
       </c>
       <c r="D40" t="n">
-        <v>4.411836550713577</v>
+        <v>4.411847244606748</v>
       </c>
       <c r="E40" t="n">
         <v>15.58304478376236</v>
@@ -39402,7 +39402,7 @@
         <v>9.344480114409626</v>
       </c>
       <c r="I40" t="n">
-        <v>1.429263020790783</v>
+        <v>1.429253550515419</v>
       </c>
       <c r="J40" t="n">
         <v>0.6376483051671933</v>
@@ -39419,7 +39419,7 @@
         <v>-1.216687531673721</v>
       </c>
       <c r="D41" t="n">
-        <v>-4.223228980674721</v>
+        <v>-4.223238790160777</v>
       </c>
       <c r="E41" t="n">
         <v>-3.252530162210432</v>
@@ -39431,10 +39431,10 @@
         <v>0.08011399015193099</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5429640610794095</v>
+        <v>0.5429566903628613</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.437947532468964</v>
+        <v>-1.437938329899247</v>
       </c>
       <c r="J41" t="n">
         <v>-4.413619280952474</v>
@@ -39457,16 +39457,16 @@
         <v>2.807572261517488</v>
       </c>
       <c r="F42" t="n">
-        <v>8.447075783026436</v>
+        <v>8.447085695065649</v>
       </c>
       <c r="G42" t="n">
         <v>11.02957293714546</v>
       </c>
       <c r="H42" t="n">
-        <v>6.834800182265521</v>
+        <v>6.834808014231619</v>
       </c>
       <c r="I42" t="n">
-        <v>-29.71957174362697</v>
+        <v>-29.71956719816589</v>
       </c>
       <c r="J42" t="n">
         <v>25.50777634729149</v>
@@ -39489,7 +39489,7 @@
         <v>7.927137678102603</v>
       </c>
       <c r="F43" t="n">
-        <v>7.817704107184009</v>
+        <v>7.81768362776154</v>
       </c>
       <c r="G43" t="n">
         <v>17.35386633308638</v>
@@ -39498,7 +39498,7 @@
         <v>8.466701768317897</v>
       </c>
       <c r="I43" t="n">
-        <v>8.902338132359366</v>
+        <v>8.902331088985838</v>
       </c>
       <c r="J43" t="n">
         <v>-1.121540913255659</v>
@@ -39515,22 +39515,22 @@
         <v>54.46413907015047</v>
       </c>
       <c r="D44" t="n">
-        <v>28.34622461760807</v>
+        <v>28.34621310918004</v>
       </c>
       <c r="E44" t="n">
         <v>81.56811180262491</v>
       </c>
       <c r="F44" t="n">
-        <v>6.658783638196319</v>
+        <v>6.658805359492947</v>
       </c>
       <c r="G44" t="n">
         <v>30.96377100161289</v>
       </c>
       <c r="H44" t="n">
-        <v>6.854717482614991</v>
+        <v>6.854707782997771</v>
       </c>
       <c r="I44" t="n">
-        <v>27.88299979085103</v>
+        <v>27.8829882720756</v>
       </c>
       <c r="J44" t="n">
         <v>0.815147568504071</v>
@@ -39547,22 +39547,22 @@
         <v>-63.75986333629861</v>
       </c>
       <c r="D45" t="n">
-        <v>-54.139346989149</v>
+        <v>-54.13934287695892</v>
       </c>
       <c r="E45" t="n">
         <v>-60.34806944094112</v>
       </c>
       <c r="F45" t="n">
-        <v>-3.297148955633478</v>
+        <v>-3.297159119784521</v>
       </c>
       <c r="G45" t="n">
         <v>-34.62913019188968</v>
       </c>
       <c r="H45" t="n">
-        <v>-14.73080766987297</v>
+        <v>-14.73079992965691</v>
       </c>
       <c r="I45" t="n">
-        <v>-67.81377767062695</v>
+        <v>-67.81377103907782</v>
       </c>
       <c r="J45" t="n">
         <v>-23.35752147577641</v>
@@ -39579,22 +39579,22 @@
         <v>-31.48595153036594</v>
       </c>
       <c r="D46" t="n">
-        <v>-22.92301792064709</v>
+        <v>-22.9230130346567</v>
       </c>
       <c r="E46" t="n">
         <v>-36.64458052185531</v>
       </c>
       <c r="F46" t="n">
-        <v>-25.11306112398533</v>
+        <v>-25.11306682409529</v>
       </c>
       <c r="G46" t="n">
         <v>-25.28793450920587</v>
       </c>
       <c r="H46" t="n">
-        <v>-23.44972119173867</v>
+        <v>-23.44973026318596</v>
       </c>
       <c r="I46" t="n">
-        <v>-42.91130681124561</v>
+        <v>-42.91131343148411</v>
       </c>
       <c r="J46" t="n">
         <v>-28.25332132398638</v>
@@ -39611,22 +39611,22 @@
         <v>-10.97644834106928</v>
       </c>
       <c r="D47" t="n">
-        <v>-1.51994188246356</v>
+        <v>-1.519941977349792</v>
       </c>
       <c r="E47" t="n">
         <v>-8.726669084425943</v>
       </c>
       <c r="F47" t="n">
-        <v>-7.139625469848454</v>
+        <v>-7.139611838128479</v>
       </c>
       <c r="G47" t="n">
         <v>-9.977464913384882</v>
       </c>
       <c r="H47" t="n">
-        <v>-8.17345527259179</v>
+        <v>-8.173454383178235</v>
       </c>
       <c r="I47" t="n">
-        <v>1.654404812265819</v>
+        <v>1.654397971164712</v>
       </c>
       <c r="J47" t="n">
         <v>-22.51848593969048</v>
@@ -39643,22 +39643,22 @@
         <v>-13.14539844090323</v>
       </c>
       <c r="D48" t="n">
-        <v>17.04134192472855</v>
+        <v>17.04132606638209</v>
       </c>
       <c r="E48" t="n">
         <v>0.6467306237967874</v>
       </c>
       <c r="F48" t="n">
-        <v>6.975903128898064</v>
+        <v>6.975887478934362</v>
       </c>
       <c r="G48" t="n">
         <v>-0.6419831048444791</v>
       </c>
       <c r="H48" t="n">
-        <v>7.092595462814155</v>
+        <v>7.092594636276428</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8298941579935271</v>
+        <v>0.8299009436074867</v>
       </c>
       <c r="J48" t="n">
         <v>38.71017491622961</v>
@@ -39675,22 +39675,22 @@
         <v>1.790379399037678</v>
       </c>
       <c r="D49" t="n">
-        <v>-3.133920233108467</v>
+        <v>-3.133920011301539</v>
       </c>
       <c r="E49" t="n">
         <v>-6.984259690113759</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3533717178334728</v>
+        <v>0.3533716910197437</v>
       </c>
       <c r="G49" t="n">
         <v>-10.33466386438756</v>
       </c>
       <c r="H49" t="n">
-        <v>3.365007029854961</v>
+        <v>3.365025301034952</v>
       </c>
       <c r="I49" t="n">
-        <v>7.87460157490274</v>
+        <v>7.874609471274563</v>
       </c>
       <c r="J49" t="n">
         <v>-13.75150501852815</v>
@@ -39707,22 +39707,22 @@
         <v>-16.93892268070564</v>
       </c>
       <c r="D50" t="n">
-        <v>8.183191253858269</v>
+        <v>8.183198910652557</v>
       </c>
       <c r="E50" t="n">
         <v>-7.199733431542765</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.55299014553656</v>
+        <v>-2.552989956762131</v>
       </c>
       <c r="G50" t="n">
         <v>-9.771716243293183</v>
       </c>
       <c r="H50" t="n">
-        <v>25.37385877957157</v>
+        <v>25.37386069556771</v>
       </c>
       <c r="I50" t="n">
-        <v>-10.81723467446301</v>
+        <v>-10.81723538062699</v>
       </c>
       <c r="J50" t="n">
         <v>-20.88017226023993</v>
@@ -39745,16 +39745,16 @@
         <v>12.02464734774498</v>
       </c>
       <c r="F51" t="n">
-        <v>10.27236099604043</v>
+        <v>10.2723691498533</v>
       </c>
       <c r="G51" t="n">
         <v>31.85220530081916</v>
       </c>
       <c r="H51" t="n">
-        <v>9.725182647883512</v>
+        <v>9.725183453655561</v>
       </c>
       <c r="I51" t="n">
-        <v>19.75410011643701</v>
+        <v>19.75408293669523</v>
       </c>
       <c r="J51" t="n">
         <v>83.74902135029218</v>
@@ -39771,7 +39771,7 @@
         <v>25.70898148157286</v>
       </c>
       <c r="D52" t="n">
-        <v>17.3152212261489</v>
+        <v>17.31520812406786</v>
       </c>
       <c r="E52" t="n">
         <v>12.70211332333331</v>
@@ -39783,10 +39783,10 @@
         <v>19.44074810734559</v>
       </c>
       <c r="H52" t="n">
-        <v>3.250694153879952</v>
+        <v>3.250676766290717</v>
       </c>
       <c r="I52" t="n">
-        <v>30.69884602773665</v>
+        <v>30.69886959976198</v>
       </c>
       <c r="J52" t="n">
         <v>45.79545801336116</v>
@@ -39803,7 +39803,7 @@
         <v>20.37225802159368</v>
       </c>
       <c r="D53" t="n">
-        <v>1.077246746602611</v>
+        <v>1.077258035184014</v>
       </c>
       <c r="E53" t="n">
         <v>2.151990548444327</v>
@@ -39815,10 +39815,10 @@
         <v>-18.6852305428317</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.73253678595402</v>
+        <v>-1.732536640307691</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2085154444687709</v>
+        <v>-0.2085256408230207</v>
       </c>
       <c r="J53" t="n">
         <v>3.2258064516129</v>
@@ -39847,7 +39847,7 @@
         <v>15.30230404450439</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.752289900808234</v>
+        <v>-0.7522815575130015</v>
       </c>
       <c r="I54" t="n">
         <v>-2.164458504802436</v>
@@ -39867,19 +39867,19 @@
         <v>17.7923744286306</v>
       </c>
       <c r="D55" t="n">
-        <v>15.7463625063532</v>
+        <v>15.74636953488597</v>
       </c>
       <c r="E55" t="n">
         <v>50.56145204702873</v>
       </c>
       <c r="F55" t="n">
-        <v>10.61742171272997</v>
+        <v>10.61740379503704</v>
       </c>
       <c r="G55" t="n">
         <v>51.45866829146802</v>
       </c>
       <c r="H55" t="n">
-        <v>24.37762270562873</v>
+        <v>24.37760979872503</v>
       </c>
       <c r="I55" t="n">
         <v>14.00827459518674</v>
@@ -39893,25 +39893,25 @@
         <v>44651</v>
       </c>
       <c r="B56" t="n">
-        <v>2.977305310912381</v>
+        <v>2.977299016454538</v>
       </c>
       <c r="C56" t="n">
         <v>10.95155597333577</v>
       </c>
       <c r="D56" t="n">
-        <v>22.51817677539005</v>
+        <v>22.51816022061508</v>
       </c>
       <c r="E56" t="n">
         <v>3.867848856109002</v>
       </c>
       <c r="F56" t="n">
-        <v>9.427552850962662</v>
+        <v>9.427580273923365</v>
       </c>
       <c r="G56" t="n">
         <v>49.57575942530777</v>
       </c>
       <c r="H56" t="n">
-        <v>-2.747517525648757</v>
+        <v>-2.747507433571683</v>
       </c>
       <c r="I56" t="n">
         <v>35.33520825688752</v>
@@ -39925,19 +39925,19 @@
         <v>44620</v>
       </c>
       <c r="B57" t="n">
-        <v>-8.601112787378639</v>
+        <v>-8.60111741306685</v>
       </c>
       <c r="C57" t="n">
         <v>8.295696174558387</v>
       </c>
       <c r="D57" t="n">
-        <v>-4.110909887571157</v>
+        <v>-4.110902753671142</v>
       </c>
       <c r="E57" t="n">
         <v>-1.834542248835702</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.228533102798457</v>
+        <v>-1.228541856401</v>
       </c>
       <c r="G57" t="n">
         <v>16.47058823529413</v>
@@ -39946,7 +39946,7 @@
         <v>-13.93947252815208</v>
       </c>
       <c r="I57" t="n">
-        <v>-12.77968297438892</v>
+        <v>-12.77967711983119</v>
       </c>
       <c r="J57" t="n">
         <v>34.45945945945945</v>
@@ -40229,7 +40229,7 @@
         <v>7.655597813986703</v>
       </c>
       <c r="I7" t="n">
-        <v>12.18076476276884</v>
+        <v>12.18075339219475</v>
       </c>
       <c r="J7" t="n">
         <v>41.22226092897434</v>
@@ -40261,7 +40261,7 @@
         <v>0.4759148328340679</v>
       </c>
       <c r="I8" t="n">
-        <v>-20.81992716245783</v>
+        <v>-20.819919136813</v>
       </c>
       <c r="J8" t="n">
         <v>-30.66567377411881</v>
@@ -40342,7 +40342,7 @@
         <v>-2.858671177731864</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5851488048130182</v>
+        <v>-0.5851564065741277</v>
       </c>
       <c r="E11" t="n">
         <v>-2.52567773584268</v>
@@ -40357,7 +40357,7 @@
         <v>9.785816743513021</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.271604999325783</v>
+        <v>-3.271611377451378</v>
       </c>
       <c r="J11" t="n">
         <v>4.88719693041435</v>
@@ -40374,7 +40374,7 @@
         <v>-1.821663765539083</v>
       </c>
       <c r="D12" t="n">
-        <v>12.22029170357897</v>
+        <v>12.22030028450933</v>
       </c>
       <c r="E12" t="n">
         <v>14.91233715805025</v>
@@ -40389,7 +40389,7 @@
         <v>17.55614188233498</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.214895854726277</v>
+        <v>-6.214895470394044</v>
       </c>
       <c r="J12" t="n">
         <v>-19.7599055071553</v>
@@ -40406,7 +40406,7 @@
         <v>29.06510336315953</v>
       </c>
       <c r="D13" t="n">
-        <v>18.02271323010156</v>
+        <v>18.02270127741525</v>
       </c>
       <c r="E13" t="n">
         <v>61.77885432844141</v>
@@ -40421,7 +40421,7 @@
         <v>22.62241185496832</v>
       </c>
       <c r="I13" t="n">
-        <v>61.10070412299044</v>
+        <v>61.1006980358042</v>
       </c>
       <c r="J13" t="n">
         <v>25.88150527132791</v>
@@ -40438,7 +40438,7 @@
         <v>5.604431410883026</v>
       </c>
       <c r="D14" t="n">
-        <v>1.131416619271675</v>
+        <v>1.131437219214715</v>
       </c>
       <c r="E14" t="n">
         <v>4.360925989567699</v>
@@ -40453,7 +40453,7 @@
         <v>0.3229764699508975</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.280716414844623</v>
+        <v>-6.280715828424965</v>
       </c>
       <c r="J14" t="n">
         <v>-8.333332214981715</v>
@@ -40470,13 +40470,13 @@
         <v>-22.73802835392045</v>
       </c>
       <c r="D15" t="n">
-        <v>36.42494342110834</v>
+        <v>36.4249294484241</v>
       </c>
       <c r="E15" t="n">
         <v>7.348351382394469</v>
       </c>
       <c r="F15" t="n">
-        <v>16.9884526777375</v>
+        <v>16.98844114909532</v>
       </c>
       <c r="G15" t="n">
         <v>30.40188313846057</v>
@@ -40485,7 +40485,7 @@
         <v>16.50937185204364</v>
       </c>
       <c r="I15" t="n">
-        <v>-24.56353270822924</v>
+        <v>-24.56352566485572</v>
       </c>
       <c r="J15" t="n">
         <v>18.62284690483378</v>
@@ -40502,19 +40502,19 @@
         <v>-61.64719560517645</v>
       </c>
       <c r="D16" t="n">
-        <v>-54.63216714949509</v>
+        <v>-54.63216427358078</v>
       </c>
       <c r="E16" t="n">
         <v>-54.3871000029952</v>
       </c>
       <c r="F16" t="n">
-        <v>-22.76005009969322</v>
+        <v>-22.76004836728446</v>
       </c>
       <c r="G16" t="n">
         <v>-36.03738976394022</v>
       </c>
       <c r="H16" t="n">
-        <v>-30.25186064741821</v>
+        <v>-30.2518689127907</v>
       </c>
       <c r="I16" t="n">
         <v>-76.50189047530399</v>
@@ -40534,22 +40534,22 @@
         <v>-21.29460874309583</v>
       </c>
       <c r="D17" t="n">
-        <v>11.65015045248989</v>
+        <v>11.65013547269929</v>
       </c>
       <c r="E17" t="n">
         <v>-14.55237052788174</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3107425078101023</v>
+        <v>-0.3107424842310635</v>
       </c>
       <c r="G17" t="n">
         <v>-19.79919371493109</v>
       </c>
       <c r="H17" t="n">
-        <v>1.648558807459066</v>
+        <v>1.648576975260174</v>
       </c>
       <c r="I17" t="n">
-        <v>10.5693401676328</v>
+        <v>10.56934826125826</v>
       </c>
       <c r="J17" t="n">
         <v>-7.304651090116887</v>
@@ -40566,22 +40566,22 @@
         <v>32.99376139327897</v>
       </c>
       <c r="D18" t="n">
-        <v>57.79701152688477</v>
+        <v>57.79700507195828</v>
       </c>
       <c r="E18" t="n">
         <v>17.16418311736432</v>
       </c>
       <c r="F18" t="n">
-        <v>22.95739684156284</v>
+        <v>22.95740617153204</v>
       </c>
       <c r="G18" t="n">
         <v>42.09624763531581</v>
       </c>
       <c r="H18" t="n">
-        <v>42.03856806814304</v>
+        <v>42.03854736234809</v>
       </c>
       <c r="I18" t="n">
-        <v>39.58639118085186</v>
+        <v>39.58639522565499</v>
       </c>
       <c r="J18" t="n">
         <v>111.9602203369141</v>
@@ -40598,22 +40598,22 @@
         <v>4.454954472923656</v>
       </c>
       <c r="D19" t="n">
-        <v>8.743003885701238</v>
+        <v>8.743022633679765</v>
       </c>
       <c r="E19" t="n">
         <v>0.7781910896766497</v>
       </c>
       <c r="F19" t="n">
-        <v>-13.19426413035678</v>
+        <v>-13.19427819105805</v>
       </c>
       <c r="G19" t="n">
         <v>42.00431940783369</v>
       </c>
       <c r="H19" t="n">
-        <v>21.30326534957958</v>
+        <v>21.30326313889901</v>
       </c>
       <c r="I19" t="n">
-        <v>11.30803339499058</v>
+        <v>11.30802202191454</v>
       </c>
       <c r="J19" t="n">
         <v>-22.46696035242291</v>
